--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD3F50B-C932-44AF-8ADD-8BCE51087F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1599CD73-2FF5-40ED-AC39-A6EA4C6F54A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -942,19 +942,19 @@
                   <c:v>275.11199999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>279.69720000000001</c:v>
+                  <c:v>355.35300000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>304.91579999999999</c:v>
+                  <c:v>412.66800000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>373.69379999999995</c:v>
+                  <c:v>550.22399999999993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>458.52</c:v>
+                  <c:v>660.26879999999994</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>532.34172000000001</c:v>
+                  <c:v>862.47611999999992</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1230,19 +1230,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.01</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34.725000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>58.930769230769229</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>80.2</c:v>
+                  <c:v>0.33333333333333337</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>93.775000000000006</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5867,17 +5867,17 @@
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="str">
         <f>VLOOKUP(B3,$C$9:$F$999,2,FALSE)</f>
-        <v>C4</v>
+        <v>C3</v>
       </c>
       <c r="E5" s="1" t="str">
         <f>VLOOKUP($B$3,$C$9:$F$999,3,FALSE)</f>
-        <v>C4</v>
+        <v>C7</v>
       </c>
       <c r="F5" s="1" t="str">
         <f>VLOOKUP($B$3,$C$9:$F$999,4,FALSE)</f>
@@ -6193,23 +6193,23 @@
       </c>
       <c r="W14" s="8">
         <f t="shared" si="4"/>
-        <v>279.69720000000001</v>
+        <v>355.35300000000001</v>
       </c>
       <c r="X14" s="8">
         <f t="shared" si="4"/>
-        <v>304.91579999999999</v>
+        <v>412.66800000000001</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="4"/>
-        <v>373.69379999999995</v>
+        <v>550.22399999999993</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="4"/>
-        <v>458.52</v>
+        <v>660.26879999999994</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="4"/>
-        <v>532.34172000000001</v>
+        <v>862.47611999999992</v>
       </c>
       <c r="AH14">
         <v>6</v>
@@ -6262,23 +6262,23 @@
       </c>
       <c r="L15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="M15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="N15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="O15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="P15" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H15)*0.9</f>
-        <v>2.3220000000000001</v>
+        <v>3.762</v>
       </c>
       <c r="AH15">
         <v>7</v>
@@ -6469,15 +6469,15 @@
       </c>
       <c r="N18" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O18" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="P18" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="T18" s="10" t="s">
         <v>16</v>
@@ -6500,15 +6500,15 @@
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>5.5022399999999996</v>
       </c>
       <c r="Z18" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>6.6026879999999997</v>
       </c>
       <c r="AA18" s="6">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8.6247612</v>
       </c>
       <c r="AB18" t="s">
         <v>17</v>
@@ -6556,27 +6556,27 @@
       </c>
       <c r="J19" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="K19" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="L19" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="M19" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="N19" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="O19" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="P19" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
@@ -6587,31 +6587,31 @@
       </c>
       <c r="U19" s="6">
         <f t="shared" si="11"/>
-        <v>91.704000000000008</v>
+        <v>98.581800000000001</v>
       </c>
       <c r="V19" s="6">
         <f t="shared" si="11"/>
-        <v>96.28919999999998</v>
+        <v>118.29815999999998</v>
       </c>
       <c r="W19" s="6">
         <f t="shared" si="11"/>
-        <v>92.300076000000004</v>
+        <v>120.82002000000001</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" si="11"/>
-        <v>97.573055999999994</v>
+        <v>152.68716000000001</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="11"/>
-        <v>115.84507799999999</v>
+        <v>176.07167999999999</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="11"/>
-        <v>142.1412</v>
+        <v>217.88870399999999</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="11"/>
-        <v>165.0259332</v>
+        <v>267.36759719999998</v>
       </c>
       <c r="AB19" t="s">
         <v>17</v>
@@ -6658,62 +6658,62 @@
       </c>
       <c r="J20" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="K20" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="L20" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.54</v>
+        <v>0.42</v>
       </c>
       <c r="M20" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="N20" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="O20" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="P20" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="T20" s="10" t="s">
         <v>22</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="11"/>
-        <v>107.75219999999999</v>
+        <v>110.0448</v>
       </c>
       <c r="V20" s="6">
         <f t="shared" si="11"/>
-        <v>143.05823999999998</v>
+        <v>123.80039999999998</v>
       </c>
       <c r="W20" s="6">
         <f t="shared" si="11"/>
-        <v>151.03648800000002</v>
+        <v>149.24825999999999</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" si="11"/>
-        <v>161.60537400000001</v>
+        <v>181.57392000000002</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="11"/>
-        <v>194.320776</v>
+        <v>242.09855999999996</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="11"/>
-        <v>229.26</v>
+        <v>277.31289599999997</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="11"/>
-        <v>255.52402559999999</v>
+        <v>344.99044800000001</v>
       </c>
       <c r="AB20" t="s">
         <v>17</v>
@@ -6753,19 +6753,19 @@
       </c>
       <c r="M21" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="N21" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O21" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="P21" s="11">
         <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="T21" s="10" t="s">
         <v>24</v>
@@ -6818,31 +6818,31 @@
       </c>
       <c r="U22" s="6">
         <f t="shared" ref="U22:AA22" si="15">U14-SUM(U19:U21)</f>
-        <v>27.511200000000002</v>
+        <v>18.340800000000002</v>
       </c>
       <c r="V22" s="6">
         <f t="shared" si="15"/>
-        <v>33.471960000000024</v>
+        <v>30.72084000000001</v>
       </c>
       <c r="W22" s="6">
         <f t="shared" si="15"/>
-        <v>34.068036000000006</v>
+        <v>82.99212</v>
       </c>
       <c r="X22" s="6">
         <f t="shared" si="15"/>
-        <v>43.444770000000005</v>
+        <v>76.114320000000021</v>
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="15"/>
-        <v>61.235345999999993</v>
+        <v>129.76116000000002</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="15"/>
-        <v>84.826199999999972</v>
+        <v>162.77459999999996</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="15"/>
-        <v>109.4991612</v>
+        <v>247.82547479999994</v>
       </c>
       <c r="AB22" t="s">
         <v>17</v>
@@ -6879,23 +6879,23 @@
       </c>
       <c r="L24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H24)/4</f>
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H24)/1.6</f>
-        <v>34.725000000000001</v>
+        <v>0</v>
       </c>
       <c r="N24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H24)/1.3</f>
-        <v>58.930769230769229</v>
+        <v>0</v>
       </c>
       <c r="O24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H24)/1.2</f>
-        <v>80.2</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="P24" s="8">
         <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H24)/1.2</f>
-        <v>93.775000000000006</v>
+        <v>0</v>
       </c>
       <c r="T24" t="s">
         <v>28</v>
@@ -6905,23 +6905,23 @@
       </c>
       <c r="W24" s="11">
         <f>L24/1000</f>
-        <v>3.0099999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="X24" s="11">
         <f>M24/1000</f>
-        <v>3.4724999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="11">
         <f>N24/1000</f>
-        <v>5.8930769230769231E-2</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="11">
         <f>O24/1000</f>
-        <v>8.0200000000000007E-2</v>
+        <v>3.3333333333333338E-4</v>
       </c>
       <c r="AA24" s="11">
         <f>P24/1000</f>
-        <v>9.3775000000000011E-2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="s">
         <v>29</v>
@@ -7142,24 +7142,27 @@
         <v>1</v>
       </c>
       <c r="L37" s="11">
-        <f t="shared" ref="L37:P37" si="17">K37</f>
-        <v>1</v>
+        <f>K37*(1+$R37)^5</f>
+        <v>1.0510100500999999</v>
       </c>
       <c r="M37" s="11">
-        <f t="shared" si="17"/>
-        <v>1</v>
+        <f t="shared" ref="M37:P37" si="17">L37*(1+$R37)^5</f>
+        <v>1.1046221254112043</v>
       </c>
       <c r="N37" s="11">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>1.1609689553699982</v>
       </c>
       <c r="O37" s="11">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>1.2201900399479664</v>
       </c>
       <c r="P37" s="11">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>1.2824319950172332</v>
+      </c>
+      <c r="R37">
+        <v>0.01</v>
       </c>
       <c r="AK37" s="10">
         <f t="shared" si="6"/>
@@ -7377,39 +7380,39 @@
       </c>
       <c r="J45">
         <f t="shared" ref="J45:P48" si="22">AVERAGE($S45:$T45)*J37</f>
-        <v>43.2</v>
+        <v>45</v>
       </c>
       <c r="K45">
         <f t="shared" si="22"/>
-        <v>43.2</v>
+        <v>45</v>
       </c>
       <c r="L45">
         <f t="shared" si="22"/>
-        <v>43.2</v>
+        <v>47.295452254499999</v>
       </c>
       <c r="M45">
         <f t="shared" si="22"/>
-        <v>43.2</v>
+        <v>49.707995643504191</v>
       </c>
       <c r="N45">
         <f t="shared" si="22"/>
-        <v>43.2</v>
+        <v>52.243602991649922</v>
       </c>
       <c r="O45">
         <f t="shared" si="22"/>
-        <v>43.2</v>
+        <v>54.90855179765849</v>
       </c>
       <c r="P45">
         <f t="shared" si="22"/>
-        <v>43.2</v>
+        <v>57.709439775775493</v>
       </c>
       <c r="S45">
         <f>HLOOKUP($H45&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
-        <v>43.2</v>
+        <v>45</v>
       </c>
       <c r="T45">
         <f>HLOOKUP($H45&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
-        <v>43.2</v>
+        <v>45</v>
       </c>
       <c r="AK45" s="10">
         <f t="shared" si="6"/>
@@ -8059,12 +8062,12 @@
         <v>110</v>
       </c>
       <c r="B11">
-        <f>12*3.6</f>
-        <v>43.2</v>
+        <f>12.5*3.6</f>
+        <v>45</v>
       </c>
       <c r="C11">
         <f>B11</f>
-        <v>43.2</v>
+        <v>45</v>
       </c>
       <c r="D11">
         <f>1.2*3.6</f>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1599CD73-2FF5-40ED-AC39-A6EA4C6F54A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCF08ED-511A-4090-9FB6-08B82F056AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,33 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AO8" authorId="0" shapeId="0" xr:uid="{B8774821-523C-49C0-8481-0CFAD2313CD6}">
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{3E464726-1383-487A-BC9B-27E3D5D65A9D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+27-05-2026
+1.22 overridden
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AQ8" authorId="0" shapeId="0" xr:uid="{B8774821-523C-49C0-8481-0CFAD2313CD6}">
       <text>
         <r>
           <rPr>
@@ -76,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="169">
   <si>
     <t>C1</t>
   </si>
@@ -516,9 +542,6 @@
     <t>coalflex</t>
   </si>
   <si>
-    <t>CF3</t>
-  </si>
-  <si>
     <t>CF1</t>
   </si>
   <si>
@@ -528,13 +551,64 @@
     <t>c216</t>
   </si>
   <si>
-    <t>1-12</t>
-  </si>
-  <si>
     <t>ts_108c</t>
   </si>
   <si>
     <t>c108</t>
+  </si>
+  <si>
+    <t>Hi</t>
+  </si>
+  <si>
+    <t>This is the q25 demand growth for C4 - the lowest demand cohort</t>
+  </si>
+  <si>
+    <t>Lo</t>
+  </si>
+  <si>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>timeslice</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>UC_N</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchablePrd</t>
+  </si>
+  <si>
+    <t>UC_RHSRT</t>
+  </si>
+  <si>
+    <t>UCE_Min-DispatchableCAP</t>
+  </si>
+  <si>
+    <t>GAS</t>
+  </si>
+  <si>
+    <t>1-32</t>
+  </si>
+  <si>
+    <t>START</t>
+  </si>
+  <si>
+    <t>pset_ci</t>
   </si>
 </sst>
 </file>
@@ -901,7 +975,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$U$17:$AA$17</c:f>
+              <c:f>Veda!$W$17:$AC$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -931,7 +1005,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$U$14:$AA$14</c:f>
+              <c:f>Veda!$W$14:$AC$14</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -942,19 +1016,19 @@
                   <c:v>275.11199999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>355.35300000000001</c:v>
+                  <c:v>290.01390000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>412.66800000000001</c:v>
+                  <c:v>304.91579999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>550.22399999999993</c:v>
+                  <c:v>373.69379999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>660.26879999999994</c:v>
+                  <c:v>458.52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>862.47611999999992</c:v>
+                  <c:v>532.34172000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1189,7 +1263,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$J$17:$P$17</c:f>
+              <c:f>Veda!$L$17:$R$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1219,9 +1293,9 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$J$24:$P$24</c:f>
+              <c:f>Veda!$L$24:$R$24</c:f>
               <c:numCache>
-                <c:formatCode>0</c:formatCode>
+                <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -1239,7 +1313,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.33333333333333337</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -1337,7 +1411,7 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1376,13 +1450,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>454817</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>309562</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>95248</xdr:rowOff>
@@ -1412,13 +1486,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>481012</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>250032</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
@@ -5831,65 +5905,185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AQ78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.46484375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.06640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.53125" customWidth="1"/>
-    <col min="7" max="7" width="1.73046875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.53125" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="9.265625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="2.9296875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.73046875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.86328125" customWidth="1"/>
+    <col min="9" max="9" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.53125" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="5.265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="5.265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="2.9296875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="H1" s="16" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="J1" s="16" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
-        <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,H1:EF1)</f>
-        <v>~Inputcell: 1-12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.45">
+        <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,J1:EH1)</f>
+        <v>~Inputcell: 1-32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1.2</v>
+      </c>
+      <c r="N2">
+        <f>AVERAGE(M2,O2)</f>
+        <v>1.2650000000000001</v>
+      </c>
+      <c r="O2">
+        <v>1.33</v>
+      </c>
+      <c r="P2">
+        <v>1.63</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <v>2.3220000000000001</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+      <c r="K3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <f>1+(M2-1)/2</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:R3" si="0">1+(N2-1)/2</f>
+        <v>1.1325000000000001</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>1.165</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>1.3149999999999999</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="R3">
+        <f t="shared" si="0"/>
+        <v>1.661</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="str">
         <f>VLOOKUP(B3,$C$9:$F$999,2,FALSE)</f>
-        <v>C3</v>
-      </c>
-      <c r="E5" s="1" t="str">
+        <v>Hi</v>
+      </c>
+      <c r="E5" s="1">
         <f>VLOOKUP($B$3,$C$9:$F$999,3,FALSE)</f>
-        <v>C7</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="str">
         <f>VLOOKUP($B$3,$C$9:$F$999,4,FALSE)</f>
-        <v>CF3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.45">
+        <v>CF1</v>
+      </c>
+      <c r="G5" s="1" t="str">
+        <f>VLOOKUP($B$3,$C$9:$G$999,5,FALSE)</f>
+        <v>N</v>
+      </c>
+      <c r="H5" s="1" t="str">
+        <f>VLOOKUP($B$3,$C$9:$H$999,6,FALSE)</f>
+        <v>N</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.45">
+      <c r="K6">
+        <v>95</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>35</v>
+      </c>
+      <c r="P6">
+        <v>60</v>
+      </c>
+      <c r="Q6">
+        <v>80</v>
+      </c>
+      <c r="R6">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:43" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
         <v>98</v>
       </c>
@@ -5908,1007 +6102,1192 @@
       <c r="F8" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="AO8" s="2" t="s">
+      <c r="G8" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="AQ8" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>5</v>
       </c>
       <c r="B9" t="str">
-        <f>VLOOKUP(D9,$AL$9:$AM$15,2,FALSE)&amp;"."&amp;F9</f>
-        <v>b 2 deg (50%).CF3</v>
+        <f>_xlfn.TEXTJOIN(".",TRUE,D9:H9)</f>
+        <v>Lo.0.CF1.Y.Y</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
-      <c r="D9" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>9</v>
+      <c r="D9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" s="15">
+        <v>0</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="H9" t="s">
-        <v>1</v>
-      </c>
-      <c r="AH9">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="s">
+      <c r="G9" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="s">
         <v>86</v>
       </c>
-      <c r="AJ9" t="s">
+      <c r="AL9" t="s">
         <v>109</v>
       </c>
-      <c r="AK9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="s">
+      <c r="AM9" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="s">
         <v>88</v>
       </c>
-      <c r="AN9" s="12">
+      <c r="AP9" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>5</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" ref="B10:B20" si="0">VLOOKUP(D10,$AL$9:$AM$15,2,FALSE)&amp;"."&amp;F10</f>
-        <v>c 2 deg (67%).CF3</v>
+        <f t="shared" ref="B10:B40" si="1">_xlfn.TEXTJOIN(".",TRUE,D10:H10)</f>
+        <v>Hi.0.CF1.Y.Y</v>
       </c>
       <c r="C10">
         <f>C9+1</f>
         <v>2</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>9</v>
+      <c r="D10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0</v>
       </c>
       <c r="F10" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="H10" t="s">
+      <c r="G10" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J10" t="s">
         <v>3</v>
       </c>
-      <c r="T10" t="s">
+      <c r="V10" t="s">
         <v>4</v>
       </c>
-      <c r="AH10">
+      <c r="AJ10">
         <v>2</v>
       </c>
-      <c r="AI10" t="s">
+      <c r="AK10" t="s">
         <v>113</v>
       </c>
-      <c r="AJ10" t="s">
+      <c r="AL10" t="s">
         <v>116</v>
       </c>
-      <c r="AK10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="s">
+      <c r="AM10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="s">
         <v>2</v>
       </c>
-      <c r="AM10" t="s">
+      <c r="AO10" t="s">
         <v>90</v>
       </c>
-      <c r="AN10" s="12">
+      <c r="AP10" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>5</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="0"/>
-        <v>b 2 deg (50%).CF3</v>
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF1.Y.Y</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C20" si="1">C10+1</f>
+        <f t="shared" ref="C11:C41" si="2">C10+1</f>
         <v>3</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>7</v>
+      <c r="D11" t="str">
+        <f>D9</f>
+        <v>Lo</v>
+      </c>
+      <c r="E11">
+        <v>95</v>
       </c>
       <c r="F11" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="H11" t="s">
+      <c r="G11" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" t="s">
         <v>6</v>
       </c>
-      <c r="T11" s="1">
+      <c r="V11" s="1">
         <v>2022</v>
       </c>
-      <c r="AH11">
+      <c r="AJ11">
         <v>3</v>
       </c>
-      <c r="AI11" t="s">
+      <c r="AK11" t="s">
         <v>99</v>
       </c>
-      <c r="AJ11" t="str">
-        <f>AI11</f>
+      <c r="AL11" t="str">
+        <f>AK11</f>
         <v>ts_012</v>
       </c>
-      <c r="AK11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="s">
+      <c r="AM11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="s">
         <v>5</v>
       </c>
-      <c r="AM11" t="s">
+      <c r="AO11" t="s">
         <v>91</v>
       </c>
-      <c r="AN11" s="12">
+      <c r="AP11" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:43" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="0"/>
-        <v>c 2 deg (67%).CF3</v>
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF1.Y.Y</v>
       </c>
       <c r="C12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>7</v>
+      <c r="D12" t="str">
+        <f t="shared" ref="D12:D41" si="3">D10</f>
+        <v>Hi</v>
+      </c>
+      <c r="E12">
+        <v>95</v>
       </c>
       <c r="F12" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="H12" t="s">
+      <c r="G12" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" t="s">
         <v>8</v>
       </c>
-      <c r="T12" s="3">
-        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,Veda!$T$11)+U28-U29</f>
+      <c r="V12" s="3">
+        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,Veda!$V$11)+W28-W29</f>
         <v>229.26</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="W12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AH12">
+      <c r="AJ12">
         <v>4</v>
       </c>
-      <c r="AI12" t="s">
+      <c r="AK12" t="s">
         <v>104</v>
       </c>
-      <c r="AJ12" t="str">
-        <f t="shared" ref="AJ12:AJ14" si="2">AI12</f>
+      <c r="AL12" t="str">
+        <f t="shared" ref="AL12:AL14" si="4">AK12</f>
         <v>ts_030</v>
       </c>
-      <c r="AK12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="s">
+      <c r="AM12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="s">
         <v>7</v>
       </c>
-      <c r="AM12" t="s">
+      <c r="AO12" t="s">
         <v>92</v>
       </c>
-      <c r="AN12" s="12">
+      <c r="AP12" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:43" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="0"/>
-        <v>b 2 deg (50%).CF1</v>
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF1.N.Y</v>
       </c>
       <c r="C13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="D13" t="str">
-        <f>D9</f>
-        <v>C4</v>
-      </c>
-      <c r="E13" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E13">
         <f>E9</f>
-        <v>C7</v>
+        <v>0</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="H13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J13" t="s">
         <v>10</v>
       </c>
-      <c r="AH13">
+      <c r="AJ13">
         <v>5</v>
       </c>
-      <c r="AI13" t="s">
+      <c r="AK13" t="s">
         <v>100</v>
       </c>
-      <c r="AJ13" t="str">
-        <f t="shared" si="2"/>
+      <c r="AL13" t="str">
+        <f t="shared" si="4"/>
         <v>ts_048</v>
       </c>
-      <c r="AK13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="s">
+      <c r="AM13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="s">
         <v>9</v>
       </c>
-      <c r="AM13" t="s">
+      <c r="AO13" t="s">
         <v>93</v>
       </c>
-      <c r="AN13" s="12">
+      <c r="AP13" s="12">
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="0"/>
-        <v>c 2 deg (67%).CF1</v>
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF1.N.Y</v>
       </c>
       <c r="C14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="D14" t="str">
-        <f t="shared" ref="D14:E14" si="3">D10</f>
-        <v>C3</v>
-      </c>
-      <c r="E14" t="str">
         <f t="shared" si="3"/>
-        <v>C7</v>
+        <v>Hi</v>
+      </c>
+      <c r="E14">
+        <f t="shared" ref="E14" si="5">E10</f>
+        <v>0</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="U14" s="8">
-        <f>T12</f>
+        <v>146</v>
+      </c>
+      <c r="G14" t="s">
+        <v>156</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W14" s="8">
+        <f>V12</f>
         <v>229.26</v>
       </c>
-      <c r="V14" s="8">
-        <f t="shared" ref="V14:AA14" si="4">$T$12*K15</f>
+      <c r="X14" s="8">
+        <f t="shared" ref="X14:AC14" si="6">$V$12*M15</f>
         <v>275.11199999999997</v>
       </c>
-      <c r="W14" s="8">
+      <c r="Y14" s="8">
+        <f t="shared" si="6"/>
+        <v>290.01390000000004</v>
+      </c>
+      <c r="Z14" s="8">
+        <f t="shared" si="6"/>
+        <v>304.91579999999999</v>
+      </c>
+      <c r="AA14" s="8">
+        <f t="shared" si="6"/>
+        <v>373.69379999999995</v>
+      </c>
+      <c r="AB14" s="8">
+        <f t="shared" si="6"/>
+        <v>458.52</v>
+      </c>
+      <c r="AC14" s="8">
+        <f t="shared" si="6"/>
+        <v>532.34172000000001</v>
+      </c>
+      <c r="AJ14">
+        <v>6</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL14" t="str">
         <f t="shared" si="4"/>
-        <v>355.35300000000001</v>
-      </c>
-      <c r="X14" s="8">
-        <f t="shared" si="4"/>
-        <v>412.66800000000001</v>
-      </c>
-      <c r="Y14" s="8">
-        <f t="shared" si="4"/>
-        <v>550.22399999999993</v>
-      </c>
-      <c r="Z14" s="8">
-        <f t="shared" si="4"/>
-        <v>660.26879999999994</v>
-      </c>
-      <c r="AA14" s="8">
-        <f t="shared" si="4"/>
-        <v>862.47611999999992</v>
-      </c>
-      <c r="AH14">
-        <v>6</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AJ14" t="str">
-        <f t="shared" si="2"/>
         <v>ts_072</v>
       </c>
-      <c r="AK14" s="10">
-        <f>AK9+1</f>
+      <c r="AM14" s="10">
+        <f>AM9+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>5</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="0"/>
-        <v>b 2 deg (50%).CF1</v>
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF1.N.Y</v>
       </c>
       <c r="C15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="D15" t="str">
-        <f t="shared" ref="D15:E15" si="5">D11</f>
-        <v>C4</v>
-      </c>
-      <c r="E15" t="str">
-        <f t="shared" si="5"/>
-        <v>C4</v>
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E15">
+        <f t="shared" ref="E15" si="7">E11</f>
+        <v>95</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="H15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J15" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>1</v>
-      </c>
-      <c r="K15" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
+      <c r="L15" s="11">
+        <f>SUMIF($K$2:$K$6,$D$5,L$2:L$6)</f>
+        <v>1</v>
+      </c>
+      <c r="M15" s="11">
+        <f>SUMIF($K$2:$K$6,$D$5,M$2:M$6)</f>
         <v>1.2</v>
       </c>
-      <c r="L15" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>1.55</v>
-      </c>
-      <c r="M15" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>1.8</v>
-      </c>
       <c r="N15" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>2.4</v>
+        <f>SUMIF($K$2:$K$6,$D$5,N$2:N$6)</f>
+        <v>1.2650000000000001</v>
       </c>
       <c r="O15" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H15)</f>
-        <v>2.88</v>
+        <f>SUMIF($K$2:$K$6,$D$5,O$2:O$6)</f>
+        <v>1.33</v>
       </c>
       <c r="P15" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H15)*0.9</f>
-        <v>3.762</v>
-      </c>
-      <c r="AH15">
+        <f>SUMIF($K$2:$K$6,$D$5,P$2:P$6)</f>
+        <v>1.63</v>
+      </c>
+      <c r="Q15" s="11">
+        <f>SUMIF($K$2:$K$6,$D$5,Q$2:Q$6)</f>
+        <v>2</v>
+      </c>
+      <c r="R15" s="11">
+        <f>SUMIF($K$2:$K$6,$D$5,R$2:R$6)</f>
+        <v>2.3220000000000001</v>
+      </c>
+      <c r="AJ15">
         <v>7</v>
       </c>
-      <c r="AI15" t="s">
-        <v>151</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>152</v>
-      </c>
-      <c r="AK15" s="10">
-        <f t="shared" ref="AK15:AK78" si="6">AK10+1</f>
+      <c r="AK15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>150</v>
+      </c>
+      <c r="AM15" s="10">
+        <f t="shared" ref="AM15:AM78" si="8">AM10+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:41" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:43" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>5</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="0"/>
-        <v>c 2 deg (67%).CF1</v>
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF1.N.Y</v>
       </c>
       <c r="C16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="D16" t="str">
-        <f t="shared" ref="D16:E16" si="7">D12</f>
-        <v>C3</v>
-      </c>
-      <c r="E16" t="str">
-        <f t="shared" si="7"/>
-        <v>C4</v>
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ref="E16" si="9">E12</f>
+        <v>95</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="T16" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" t="s">
+        <v>156</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="V16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AH16">
+      <c r="AJ16">
         <v>8</v>
       </c>
-      <c r="AI16" t="s">
+      <c r="AK16" t="s">
         <v>114</v>
       </c>
-      <c r="AJ16" t="s">
-        <v>149</v>
-      </c>
-      <c r="AK16" s="10">
-        <f t="shared" si="6"/>
+      <c r="AL16" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM16" s="10">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:39" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17">
         <v>5</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="0"/>
-        <v>b 2 deg (50%).CF6</v>
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF6.Y.Y</v>
       </c>
       <c r="C17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="D17" t="str">
-        <f t="shared" ref="D17:E17" si="8">D13</f>
-        <v>C4</v>
-      </c>
-      <c r="E17" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ref="E17" si="10">E13</f>
+        <v>0</v>
+      </c>
+      <c r="F17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" t="str">
+        <f>G9</f>
+        <v>Y</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="7">
+        <v>2020</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" ref="M17:R17" si="11">X17</f>
+        <v>2025</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="11"/>
+        <v>2030</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="11"/>
+        <v>2035</v>
+      </c>
+      <c r="P17" s="7">
+        <f t="shared" si="11"/>
+        <v>2040</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="11"/>
+        <v>2045</v>
+      </c>
+      <c r="R17" s="7">
+        <f t="shared" si="11"/>
+        <v>2050</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="W17" s="4">
+        <v>2022</v>
+      </c>
+      <c r="X17" s="4">
+        <v>2025</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>2030</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>2035</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>2040</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>2045</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>2050</v>
+      </c>
+      <c r="AD17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ17">
+        <v>9</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM17" s="10">
         <f t="shared" si="8"/>
-        <v>C7</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="J17" s="7">
-        <v>2020</v>
-      </c>
-      <c r="K17" s="7">
-        <f t="shared" ref="K17:P17" si="9">V17</f>
-        <v>2025</v>
-      </c>
-      <c r="L17" s="7">
-        <f t="shared" si="9"/>
-        <v>2030</v>
-      </c>
-      <c r="M17" s="7">
-        <f t="shared" si="9"/>
-        <v>2035</v>
-      </c>
-      <c r="N17" s="7">
-        <f t="shared" si="9"/>
-        <v>2040</v>
-      </c>
-      <c r="O17" s="7">
-        <f t="shared" si="9"/>
-        <v>2045</v>
-      </c>
-      <c r="P17" s="7">
-        <f t="shared" si="9"/>
-        <v>2050</v>
-      </c>
-      <c r="T17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="U17" s="4">
-        <v>2022</v>
-      </c>
-      <c r="V17" s="4">
-        <v>2025</v>
-      </c>
-      <c r="W17" s="4">
-        <v>2030</v>
-      </c>
-      <c r="X17" s="4">
-        <v>2035</v>
-      </c>
-      <c r="Y17" s="4">
-        <v>2040</v>
-      </c>
-      <c r="Z17" s="4">
-        <v>2045</v>
-      </c>
-      <c r="AA17" s="4">
-        <v>2050</v>
-      </c>
-      <c r="AB17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH17">
-        <v>9</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>105</v>
-      </c>
-      <c r="AK17" s="10">
-        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>5</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="0"/>
-        <v>c 2 deg (67%).CF6</v>
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF6.Y.Y</v>
       </c>
       <c r="C18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="D18" t="str">
-        <f t="shared" ref="D18:E18" si="10">D14</f>
-        <v>C3</v>
-      </c>
-      <c r="E18" t="str">
-        <f t="shared" si="10"/>
-        <v>C7</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="H18" t="s">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ref="E18" si="12">E14</f>
+        <v>0</v>
+      </c>
+      <c r="F18" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" t="str">
+        <f t="shared" ref="G18:G41" si="13">G10</f>
+        <v>Y</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J18" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
-        <v>0</v>
-      </c>
       <c r="L18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
         <v>0</v>
       </c>
       <c r="M18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
         <v>0</v>
       </c>
       <c r="N18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
-        <v>0.01</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <v>0</v>
       </c>
       <c r="O18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
-        <v>0.01</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <v>0</v>
       </c>
       <c r="P18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H18)</f>
-        <v>0.01</v>
-      </c>
-      <c r="T18" s="10" t="s">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U18" s="6">
-        <f t="shared" ref="U18:AA20" si="11">J18*U$14</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
       <c r="W18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="W18:AC20" si="14">L18*W$14</f>
         <v>0</v>
       </c>
       <c r="X18" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Y18" s="6">
-        <f t="shared" si="11"/>
-        <v>5.5022399999999996</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" si="11"/>
-        <v>6.6026879999999997</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="11"/>
-        <v>8.6247612</v>
-      </c>
-      <c r="AB18" t="s">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="6">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="6">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" t="s">
         <v>17</v>
       </c>
-      <c r="AD18" s="2"/>
-      <c r="AH18">
+      <c r="AF18" s="2"/>
+      <c r="AJ18">
         <v>10</v>
       </c>
-      <c r="AI18" t="s">
+      <c r="AK18" t="s">
         <v>106</v>
       </c>
-      <c r="AJ18" t="s">
+      <c r="AL18" t="s">
         <v>107</v>
       </c>
-      <c r="AK18" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM18" s="10">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>5</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="0"/>
-        <v>b 2 deg (50%).CF6</v>
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF6.Y.Y</v>
       </c>
       <c r="C19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" ref="D19:E19" si="12">D15</f>
-        <v>C4</v>
-      </c>
-      <c r="E19" t="str">
-        <f t="shared" si="12"/>
-        <v>C4</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="H19" t="s">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E19">
+        <f t="shared" ref="E19" si="15">E15</f>
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>147</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J19" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.43</v>
-      </c>
-      <c r="K19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.43</v>
-      </c>
       <c r="L19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.34</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+        <v>0.4</v>
       </c>
       <c r="M19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.37</v>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+        <v>0.35</v>
       </c>
       <c r="N19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+        <v>0.33</v>
+      </c>
+      <c r="O19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
         <v>0.32</v>
       </c>
-      <c r="O19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
-        <v>0.33</v>
-      </c>
       <c r="P19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H19)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
         <v>0.31</v>
       </c>
-      <c r="T19" s="10" t="s">
+      <c r="Q19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+        <v>0.31</v>
+      </c>
+      <c r="R19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+        <v>0.31</v>
+      </c>
+      <c r="V19" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="U19" s="6">
-        <f t="shared" si="11"/>
-        <v>98.581800000000001</v>
-      </c>
-      <c r="V19" s="6">
-        <f t="shared" si="11"/>
-        <v>118.29815999999998</v>
-      </c>
       <c r="W19" s="6">
-        <f t="shared" si="11"/>
-        <v>120.82002000000001</v>
+        <f t="shared" si="14"/>
+        <v>91.704000000000008</v>
       </c>
       <c r="X19" s="6">
-        <f t="shared" si="11"/>
-        <v>152.68716000000001</v>
+        <f t="shared" si="14"/>
+        <v>96.28919999999998</v>
       </c>
       <c r="Y19" s="6">
-        <f t="shared" si="11"/>
-        <v>176.07167999999999</v>
+        <f t="shared" si="14"/>
+        <v>95.704587000000018</v>
       </c>
       <c r="Z19" s="6">
-        <f t="shared" si="11"/>
-        <v>217.88870399999999</v>
+        <f t="shared" si="14"/>
+        <v>97.573055999999994</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="11"/>
-        <v>267.36759719999998</v>
-      </c>
-      <c r="AB19" t="s">
+        <f t="shared" si="14"/>
+        <v>115.84507799999999</v>
+      </c>
+      <c r="AB19" s="6">
+        <f t="shared" si="14"/>
+        <v>142.1412</v>
+      </c>
+      <c r="AC19" s="6">
+        <f t="shared" si="14"/>
+        <v>165.0259332</v>
+      </c>
+      <c r="AD19" t="s">
         <v>17</v>
       </c>
-      <c r="AH19">
+      <c r="AJ19">
         <v>11</v>
       </c>
-      <c r="AI19" t="s">
+      <c r="AK19" t="s">
         <v>84</v>
       </c>
-      <c r="AJ19" t="s">
+      <c r="AL19" t="s">
         <v>89</v>
       </c>
-      <c r="AK19" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM19" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>5</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="0"/>
-        <v>c 2 deg (67%).CF6</v>
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF6.Y.Y</v>
       </c>
       <c r="C20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="D20" t="str">
-        <f t="shared" ref="D20:E20" si="13">D16</f>
-        <v>C3</v>
-      </c>
-      <c r="E20" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ref="E20:E41" si="16">E16</f>
+        <v>95</v>
+      </c>
+      <c r="F20" t="s">
+        <v>147</v>
+      </c>
+      <c r="G20" t="str">
         <f t="shared" si="13"/>
-        <v>C4</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="H20" t="s">
+        <v>Y</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J20" t="s">
         <v>21</v>
       </c>
-      <c r="J20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
+      <c r="L20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+        <v>0.47</v>
+      </c>
+      <c r="M20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+        <v>0.52</v>
+      </c>
+      <c r="N20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+        <v>0.54</v>
+      </c>
+      <c r="O20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+        <v>0.53</v>
+      </c>
+      <c r="P20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+        <v>0.52</v>
+      </c>
+      <c r="Q20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+        <v>0.5</v>
+      </c>
+      <c r="R20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
         <v>0.48</v>
       </c>
-      <c r="K20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.45</v>
-      </c>
-      <c r="L20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.42</v>
-      </c>
-      <c r="M20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.44</v>
-      </c>
-      <c r="N20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.44</v>
-      </c>
-      <c r="O20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.42</v>
-      </c>
-      <c r="P20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H20)</f>
-        <v>0.4</v>
-      </c>
-      <c r="T20" s="10" t="s">
+      <c r="V20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="U20" s="6">
-        <f t="shared" si="11"/>
-        <v>110.0448</v>
-      </c>
-      <c r="V20" s="6">
-        <f t="shared" si="11"/>
-        <v>123.80039999999998</v>
-      </c>
       <c r="W20" s="6">
-        <f t="shared" si="11"/>
-        <v>149.24825999999999</v>
+        <f t="shared" si="14"/>
+        <v>107.75219999999999</v>
       </c>
       <c r="X20" s="6">
-        <f t="shared" si="11"/>
-        <v>181.57392000000002</v>
+        <f t="shared" si="14"/>
+        <v>143.05823999999998</v>
       </c>
       <c r="Y20" s="6">
-        <f t="shared" si="11"/>
-        <v>242.09855999999996</v>
+        <f t="shared" si="14"/>
+        <v>156.60750600000003</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" si="11"/>
-        <v>277.31289599999997</v>
+        <f t="shared" si="14"/>
+        <v>161.60537400000001</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="11"/>
-        <v>344.99044800000001</v>
-      </c>
-      <c r="AB20" t="s">
+        <f t="shared" si="14"/>
+        <v>194.320776</v>
+      </c>
+      <c r="AB20" s="6">
+        <f t="shared" si="14"/>
+        <v>229.26</v>
+      </c>
+      <c r="AC20" s="6">
+        <f t="shared" si="14"/>
+        <v>255.52402559999999</v>
+      </c>
+      <c r="AD20" t="s">
         <v>17</v>
       </c>
-      <c r="AH20">
+      <c r="AJ20">
         <v>12</v>
       </c>
-      <c r="AI20" t="s">
+      <c r="AK20" t="s">
         <v>85</v>
       </c>
-      <c r="AJ20" t="s">
+      <c r="AL20" t="s">
         <v>94</v>
       </c>
-      <c r="AK20" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM20" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>5</v>
       </c>
-      <c r="H21" t="s">
+      <c r="B21" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF6.N.Y</v>
+      </c>
+      <c r="C21">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="D21" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>147</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J21" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
+      <c r="L21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
         <v>0.01</v>
       </c>
-      <c r="K21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!K$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
+      <c r="M21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
         <v>0.01</v>
       </c>
-      <c r="L21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
+      <c r="N21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
         <v>0.01</v>
       </c>
-      <c r="M21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
+      <c r="O21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+        <v>0.01</v>
+      </c>
+      <c r="P21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+        <v>0.01</v>
+      </c>
+      <c r="Q21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
         <v>0.02</v>
       </c>
-      <c r="N21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
+      <c r="R21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
         <v>0.02</v>
       </c>
-      <c r="O21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
-        <v>0.03</v>
-      </c>
-      <c r="P21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$D$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H21)</f>
-        <v>0.03</v>
-      </c>
-      <c r="T21" s="10" t="s">
+      <c r="V21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="U21" s="6">
-        <f>J21*U$14</f>
+      <c r="W21" s="6">
+        <f>L21*W$14</f>
         <v>2.2925999999999997</v>
       </c>
-      <c r="V21" s="6">
-        <f t="shared" ref="V21:AA21" si="14">U21</f>
+      <c r="X21" s="6">
+        <f t="shared" ref="X21:AC21" si="17">W21</f>
         <v>2.2925999999999997</v>
       </c>
-      <c r="W21" s="6">
-        <f t="shared" si="14"/>
+      <c r="Y21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="X21" s="6">
-        <f t="shared" si="14"/>
+      <c r="Z21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="Y21" s="6">
-        <f t="shared" si="14"/>
+      <c r="AA21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="Z21" s="6">
-        <f t="shared" si="14"/>
+      <c r="AB21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="AA21" s="6">
-        <f t="shared" si="14"/>
+      <c r="AC21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AD21" t="s">
         <v>17</v>
       </c>
-      <c r="AD21" s="2" t="s">
+      <c r="AF21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AK21" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM21" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>5</v>
       </c>
-      <c r="T22" s="10" t="s">
+      <c r="B22" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF6.N.Y</v>
+      </c>
+      <c r="C22">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="D22" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="V22" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="U22" s="6">
-        <f t="shared" ref="U22:AA22" si="15">U14-SUM(U19:U21)</f>
-        <v>18.340800000000002</v>
-      </c>
-      <c r="V22" s="6">
-        <f t="shared" si="15"/>
-        <v>30.72084000000001</v>
-      </c>
       <c r="W22" s="6">
-        <f t="shared" si="15"/>
-        <v>82.99212</v>
+        <f t="shared" ref="W22:AC22" si="18">W14-SUM(W19:W21)</f>
+        <v>27.511200000000002</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" si="15"/>
-        <v>76.114320000000021</v>
+        <f t="shared" si="18"/>
+        <v>33.471960000000024</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="15"/>
-        <v>129.76116000000002</v>
+        <f t="shared" si="18"/>
+        <v>35.409206999999981</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="15"/>
-        <v>162.77459999999996</v>
+        <f t="shared" si="18"/>
+        <v>43.444770000000005</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="15"/>
-        <v>247.82547479999994</v>
-      </c>
-      <c r="AB22" t="s">
+        <f t="shared" si="18"/>
+        <v>61.235345999999993</v>
+      </c>
+      <c r="AB22" s="6">
+        <f t="shared" si="18"/>
+        <v>84.826199999999972</v>
+      </c>
+      <c r="AC22" s="6">
+        <f t="shared" si="18"/>
+        <v>109.4991612</v>
+      </c>
+      <c r="AD22" t="s">
         <v>17</v>
       </c>
-      <c r="AK22" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM22" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>5</v>
       </c>
-      <c r="T23" t="s">
+      <c r="B23" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF6.N.Y</v>
+      </c>
+      <c r="C23">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F23" t="s">
+        <v>147</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="V23" t="s">
         <v>26</v>
       </c>
-      <c r="AK23" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM23" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:39" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>5</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="B24" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF6.N.Y</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F24" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J24" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="8">
-        <v>0</v>
-      </c>
-      <c r="K24" s="8">
-        <v>0</v>
-      </c>
-      <c r="L24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$H24)/4</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$H24)/1.6</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$H24)/1.3</f>
-        <v>0</v>
-      </c>
-      <c r="O24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$H24)/1.2</f>
-        <v>0.33333333333333337</v>
-      </c>
-      <c r="P24" s="8">
-        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$E$5,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$H24)/1.2</f>
-        <v>0</v>
-      </c>
-      <c r="T24" t="s">
+      <c r="L24" s="11">
+        <f>SUMIF($K$2:$K$6,$E$5,L$2:L$6)</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="11">
+        <f>SUMIF($K$2:$K$6,$E$5,M$2:M$6)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="11">
+        <f>SUMIF($K$2:$K$6,$E$5,N$2:N$6)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="11">
+        <f>SUMIF($K$2:$K$6,$E$5,O$2:O$6)</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="11">
+        <f>SUMIF($K$2:$K$6,$E$5,P$2:P$6)</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="11">
+        <f>SUMIF($K$2:$K$6,$E$5,Q$2:Q$6)</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="11">
+        <f>SUMIF($K$2:$K$6,$E$5,R$2:R$6)</f>
+        <v>0</v>
+      </c>
+      <c r="V24" t="s">
         <v>28</v>
       </c>
-      <c r="V24">
-        <v>0</v>
-      </c>
-      <c r="W24" s="11">
-        <f>L24/1000</f>
-        <v>0</v>
-      </c>
-      <c r="X24" s="11">
-        <f>M24/1000</f>
+      <c r="X24">
         <v>0</v>
       </c>
       <c r="Y24" s="11">
@@ -6917,821 +7296,1335 @@
       </c>
       <c r="Z24" s="11">
         <f>O24/1000</f>
-        <v>3.3333333333333338E-4</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="11">
         <f>P24/1000</f>
         <v>0</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AB24" s="11">
+        <f>Q24/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="11">
+        <f>R24/1000</f>
+        <v>0</v>
+      </c>
+      <c r="AD24" t="s">
         <v>29</v>
       </c>
-      <c r="AK24" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM24" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:39" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>5</v>
       </c>
-      <c r="AK25" s="10">
-        <f t="shared" si="6"/>
+      <c r="B25" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF1.Y.N</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F25" t="str">
+        <f>F9</f>
+        <v>CF1</v>
+      </c>
+      <c r="G25" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM25" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:39" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A26">
         <v>5</v>
       </c>
-      <c r="T26" s="5" t="s">
+      <c r="B26" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF1.Y.N</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" ref="F26:F41" si="19">F10</f>
+        <v>CF1</v>
+      </c>
+      <c r="G26" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="V26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AK26" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM26" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:39" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27">
         <v>5</v>
       </c>
-      <c r="T27" s="4" t="s">
+      <c r="B27" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF1.Y.N</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G27" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="V27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="U27" s="4">
-        <f t="shared" ref="U27:AA27" si="16">U17</f>
+      <c r="W27" s="4">
+        <f t="shared" ref="W27:AC27" si="20">W17</f>
         <v>2022</v>
       </c>
-      <c r="V27" s="4">
-        <f t="shared" si="16"/>
+      <c r="X27" s="4">
+        <f t="shared" si="20"/>
         <v>2025</v>
       </c>
-      <c r="W27" s="4">
-        <f t="shared" si="16"/>
+      <c r="Y27" s="4">
+        <f t="shared" si="20"/>
         <v>2030</v>
       </c>
-      <c r="X27" s="4">
-        <f t="shared" si="16"/>
+      <c r="Z27" s="4">
+        <f t="shared" si="20"/>
         <v>2035</v>
       </c>
-      <c r="Y27" s="4">
-        <f t="shared" si="16"/>
+      <c r="AA27" s="4">
+        <f t="shared" si="20"/>
         <v>2040</v>
       </c>
-      <c r="Z27" s="4">
-        <f t="shared" si="16"/>
+      <c r="AB27" s="4">
+        <f t="shared" si="20"/>
         <v>2045</v>
       </c>
-      <c r="AA27" s="4">
-        <f t="shared" si="16"/>
+      <c r="AC27" s="4">
+        <f t="shared" si="20"/>
         <v>2050</v>
       </c>
-      <c r="AB27" s="4" t="s">
+      <c r="AD27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AC27" s="4" t="s">
+      <c r="AE27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AK27" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM27" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:39" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A28">
         <v>5</v>
       </c>
-      <c r="R28" s="3">
-        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,Veda!$T$11)</f>
+      <c r="B28" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF1.Y.N</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G28" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="T28" s="3">
+        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,Veda!$V$11)</f>
         <v>10.76</v>
       </c>
-      <c r="T28" t="s">
+      <c r="V28" t="s">
         <v>32</v>
       </c>
-      <c r="U28" s="3">
-        <f>R28</f>
+      <c r="W28" s="3">
+        <f>T28</f>
         <v>10.76</v>
       </c>
-      <c r="W28" s="6"/>
-      <c r="X28" s="6"/>
       <c r="Y28" s="6"/>
       <c r="Z28" s="6"/>
       <c r="AA28" s="6"/>
-      <c r="AB28" t="s">
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" t="s">
         <v>33</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AE28" t="s">
         <v>34</v>
       </c>
-      <c r="AK28" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM28" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:39" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,Veda!$T$11)</f>
+      <c r="B29" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF1.N.N</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G29" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="T29" s="3">
+        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,Veda!$V$11)</f>
         <v>-12.27</v>
       </c>
-      <c r="T29" t="s">
+      <c r="V29" t="s">
         <v>35</v>
       </c>
-      <c r="U29" s="3">
-        <f>-1*R29</f>
+      <c r="W29" s="3">
+        <f>-1*T29</f>
         <v>12.27</v>
       </c>
-      <c r="W29" s="6"/>
-      <c r="X29" s="6"/>
       <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
       <c r="AA29" s="6"/>
-      <c r="AB29" t="s">
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" t="s">
         <v>33</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AE29" t="s">
         <v>34</v>
       </c>
-      <c r="AK29" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM29" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:39" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>5</v>
       </c>
-      <c r="AK30" s="10">
-        <f t="shared" si="6"/>
+      <c r="B30" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF1.N.N</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM30" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>5</v>
       </c>
-      <c r="AK31" s="10">
-        <f t="shared" si="6"/>
+      <c r="B31" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF1.N.N</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM31" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>5</v>
       </c>
-      <c r="AK32" s="10">
-        <f t="shared" si="6"/>
+      <c r="B32" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF1.N.N</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="D32" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM32" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>5</v>
       </c>
-      <c r="AK33" s="10">
-        <f t="shared" si="6"/>
+      <c r="B33" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF6.Y.N</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="D33" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM33" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>5</v>
       </c>
-      <c r="AK34" s="10">
-        <f t="shared" si="6"/>
+      <c r="B34" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF6.Y.N</v>
+      </c>
+      <c r="C34">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="D34" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM34" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>5</v>
       </c>
-      <c r="AK35" s="10">
-        <f t="shared" si="6"/>
+      <c r="B35" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF6.Y.N</v>
+      </c>
+      <c r="C35">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="D35" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM35" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A36">
         <v>5</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="B36" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF6.Y.N</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="D36" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G36" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AK36" s="10">
-        <f t="shared" si="6"/>
+      <c r="V36" s="5" t="str">
+        <f>IF($G$5="N","~TFM_INS: limtype=LO","DEF correction active")</f>
+        <v>~TFM_INS: limtype=LO</v>
+      </c>
+      <c r="AM36" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:39" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37">
         <v>5</v>
       </c>
-      <c r="H37" t="s">
+      <c r="B37" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF6.N.N</v>
+      </c>
+      <c r="C37">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="D37" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J37" t="s">
         <v>74</v>
       </c>
-      <c r="J37" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$H$36,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H37)</f>
-        <v>1</v>
-      </c>
-      <c r="K37" s="11">
-        <f>J37</f>
-        <v>1</v>
-      </c>
       <c r="L37" s="11">
-        <f>K37*(1+$R37)^5</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$J$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J37)</f>
+        <v>1</v>
+      </c>
+      <c r="M37" s="11">
+        <f>L37</f>
+        <v>1</v>
+      </c>
+      <c r="N37" s="11">
+        <f>M37*(1+$T37)^5</f>
         <v>1.0510100500999999</v>
       </c>
-      <c r="M37" s="11">
-        <f t="shared" ref="M37:P37" si="17">L37*(1+$R37)^5</f>
+      <c r="O37" s="11">
+        <f t="shared" ref="O37:R37" si="21">N37*(1+$T37)^5</f>
         <v>1.1046221254112043</v>
       </c>
-      <c r="N37" s="11">
-        <f t="shared" si="17"/>
+      <c r="P37" s="11">
+        <f t="shared" si="21"/>
         <v>1.1609689553699982</v>
       </c>
-      <c r="O37" s="11">
-        <f t="shared" si="17"/>
+      <c r="Q37" s="11">
+        <f t="shared" si="21"/>
         <v>1.2201900399479664</v>
       </c>
-      <c r="P37" s="11">
-        <f t="shared" si="17"/>
+      <c r="R37" s="11">
+        <f t="shared" si="21"/>
         <v>1.2824319950172332</v>
       </c>
-      <c r="R37">
+      <c r="T37">
         <v>0.01</v>
       </c>
-      <c r="AK37" s="10">
-        <f t="shared" si="6"/>
+      <c r="V37" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="W37" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="X37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y37" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z37" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="AM37" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>5</v>
       </c>
-      <c r="H38" t="s">
+      <c r="B38" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF6.N.N</v>
+      </c>
+      <c r="C38">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="D38" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J38" t="s">
         <v>75</v>
       </c>
-      <c r="J38" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$H$36,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H38)</f>
-        <v>1</v>
-      </c>
-      <c r="K38" s="11">
-        <f t="shared" ref="K38:P38" si="18">J38</f>
-        <v>1</v>
-      </c>
       <c r="L38" s="11">
-        <f t="shared" si="18"/>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$J$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J38)</f>
         <v>1</v>
       </c>
       <c r="M38" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="M38:R38" si="22">L38</f>
         <v>1</v>
       </c>
       <c r="N38" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O38" s="11">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="P38" s="11">
-        <f t="shared" si="18"/>
-        <v>1</v>
-      </c>
-      <c r="AK38" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="Q38" s="11">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="R38" s="11">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="V38" t="s">
+        <v>160</v>
+      </c>
+      <c r="W38" t="s">
+        <v>161</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>-13</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>162</v>
+      </c>
+      <c r="AM38" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>5</v>
       </c>
-      <c r="H39" t="s">
+      <c r="B39" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF6.N.N</v>
+      </c>
+      <c r="C39">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H39" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J39" t="s">
         <v>76</v>
       </c>
-      <c r="J39" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$H$36,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H39)</f>
-        <v>1</v>
-      </c>
-      <c r="K39" s="11">
-        <f t="shared" ref="K39:P39" si="19">J39</f>
-        <v>1</v>
-      </c>
       <c r="L39" s="11">
-        <f t="shared" si="19"/>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$J$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J39)</f>
         <v>1</v>
       </c>
       <c r="M39" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="M39:R39" si="23">L39</f>
         <v>1</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="O39" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P39" s="11">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="AK39" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="Q39" s="11">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="R39" s="11">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="V39" t="s">
+        <v>163</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>-13</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>164</v>
+      </c>
+      <c r="AM39" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>5</v>
       </c>
-      <c r="H40" t="s">
+      <c r="B40" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF6.N.N</v>
+      </c>
+      <c r="C40">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G40" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H40" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J40" t="s">
         <v>77</v>
       </c>
-      <c r="J40" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$H$36,ar6_r10!$C$2:$C$999,Veda!J$17,ar6_r10!$M$2:$M$999,Veda!$H40)</f>
-        <v>1</v>
-      </c>
-      <c r="K40" s="11">
-        <f t="shared" ref="K40:P40" si="20">J40</f>
-        <v>1</v>
-      </c>
       <c r="L40" s="11">
-        <f t="shared" si="20"/>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$J$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J40)</f>
         <v>1</v>
       </c>
       <c r="M40" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="M40:R40" si="24">L40</f>
         <v>1</v>
       </c>
       <c r="N40" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="O40" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="P40" s="11">
-        <f t="shared" si="20"/>
-        <v>1</v>
-      </c>
-      <c r="AK40" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="Q40" s="11">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="R40" s="11">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="AM40" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>5</v>
       </c>
-      <c r="AK41" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM41" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>5</v>
       </c>
-      <c r="AK42" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM42" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>5</v>
       </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
         <v>101</v>
       </c>
-      <c r="AK43" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM43" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>5</v>
       </c>
-      <c r="H44" t="s">
+      <c r="J44" t="s">
         <v>13</v>
       </c>
-      <c r="I44" t="s">
+      <c r="K44" t="s">
         <v>87</v>
       </c>
-      <c r="J44">
+      <c r="L44">
         <v>2022</v>
       </c>
-      <c r="K44">
-        <f>K17</f>
+      <c r="M44">
+        <f>M17</f>
         <v>2025</v>
       </c>
-      <c r="L44">
-        <f t="shared" ref="L44:P44" si="21">L17</f>
+      <c r="N44">
+        <f t="shared" ref="N44:R44" si="25">N17</f>
         <v>2030</v>
       </c>
-      <c r="M44">
-        <f t="shared" si="21"/>
+      <c r="O44">
+        <f t="shared" si="25"/>
         <v>2035</v>
       </c>
-      <c r="N44">
-        <f t="shared" si="21"/>
+      <c r="P44">
+        <f t="shared" si="25"/>
         <v>2040</v>
       </c>
-      <c r="O44">
-        <f t="shared" si="21"/>
+      <c r="Q44">
+        <f t="shared" si="25"/>
         <v>2045</v>
       </c>
-      <c r="P44">
-        <f t="shared" si="21"/>
+      <c r="R44">
+        <f t="shared" si="25"/>
         <v>2050</v>
       </c>
-      <c r="S44" t="s">
+      <c r="U44" t="s">
         <v>82</v>
       </c>
-      <c r="T44" t="s">
+      <c r="V44" t="s">
         <v>83</v>
       </c>
-      <c r="AK44" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM44" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>5</v>
       </c>
-      <c r="H45" t="s">
+      <c r="J45" t="s">
         <v>78</v>
       </c>
-      <c r="I45" t="str">
-        <f>H45</f>
+      <c r="K45" t="str">
+        <f>J45</f>
         <v>Gas</v>
       </c>
-      <c r="J45">
-        <f t="shared" ref="J45:P48" si="22">AVERAGE($S45:$T45)*J37</f>
+      <c r="L45">
+        <f t="shared" ref="L45:R48" si="26">AVERAGE($U45:$V45)*L37</f>
         <v>45</v>
       </c>
-      <c r="K45">
-        <f t="shared" si="22"/>
+      <c r="M45">
+        <f t="shared" si="26"/>
         <v>45</v>
       </c>
-      <c r="L45">
-        <f t="shared" si="22"/>
+      <c r="N45">
+        <f t="shared" si="26"/>
         <v>47.295452254499999</v>
       </c>
-      <c r="M45">
-        <f t="shared" si="22"/>
+      <c r="O45">
+        <f t="shared" si="26"/>
         <v>49.707995643504191</v>
       </c>
-      <c r="N45">
-        <f t="shared" si="22"/>
+      <c r="P45">
+        <f t="shared" si="26"/>
         <v>52.243602991649922</v>
       </c>
-      <c r="O45">
-        <f t="shared" si="22"/>
+      <c r="Q45">
+        <f t="shared" si="26"/>
         <v>54.90855179765849</v>
       </c>
-      <c r="P45">
-        <f t="shared" si="22"/>
+      <c r="R45">
+        <f t="shared" si="26"/>
         <v>57.709439775775493</v>
       </c>
-      <c r="S45">
-        <f>HLOOKUP($H45&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="U45">
+        <f>HLOOKUP($J45&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>45</v>
       </c>
-      <c r="T45">
-        <f>HLOOKUP($H45&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="V45">
+        <f>HLOOKUP($J45&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AK45" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM45" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>5</v>
       </c>
-      <c r="H46" t="s">
+      <c r="J46" t="s">
         <v>79</v>
       </c>
-      <c r="I46" t="str">
-        <f t="shared" ref="I46:I48" si="23">H46</f>
+      <c r="K46" t="str">
+        <f t="shared" ref="K46:K48" si="27">J46</f>
         <v>Coal</v>
       </c>
-      <c r="J46">
-        <f t="shared" si="22"/>
+      <c r="L46">
+        <f t="shared" si="26"/>
         <v>4.68</v>
       </c>
-      <c r="K46">
-        <f t="shared" si="22"/>
+      <c r="M46">
+        <f t="shared" si="26"/>
         <v>4.68</v>
       </c>
-      <c r="L46">
-        <f t="shared" si="22"/>
+      <c r="N46">
+        <f t="shared" si="26"/>
         <v>4.68</v>
       </c>
-      <c r="M46">
-        <f t="shared" si="22"/>
+      <c r="O46">
+        <f t="shared" si="26"/>
         <v>4.68</v>
       </c>
-      <c r="N46">
-        <f t="shared" si="22"/>
+      <c r="P46">
+        <f t="shared" si="26"/>
         <v>4.68</v>
       </c>
-      <c r="O46">
-        <f t="shared" si="22"/>
+      <c r="Q46">
+        <f t="shared" si="26"/>
         <v>4.68</v>
       </c>
-      <c r="P46">
-        <f t="shared" si="22"/>
+      <c r="R46">
+        <f t="shared" si="26"/>
         <v>4.68</v>
       </c>
-      <c r="S46">
-        <f>HLOOKUP($H46&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="U46">
+        <f>HLOOKUP($J46&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>4.32</v>
       </c>
-      <c r="T46">
-        <f>HLOOKUP($H46&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="V46">
+        <f>HLOOKUP($J46&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>5.04</v>
       </c>
-      <c r="AK46" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM46" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>5</v>
       </c>
-      <c r="H47" t="s">
+      <c r="J47" t="s">
         <v>80</v>
       </c>
-      <c r="I47" t="str">
-        <f t="shared" si="23"/>
+      <c r="K47" t="str">
+        <f t="shared" si="27"/>
         <v>Oil</v>
       </c>
-      <c r="J47">
-        <f t="shared" si="22"/>
+      <c r="L47">
+        <f t="shared" si="26"/>
         <v>79.2</v>
       </c>
-      <c r="K47">
-        <f t="shared" si="22"/>
+      <c r="M47">
+        <f t="shared" si="26"/>
         <v>79.2</v>
       </c>
-      <c r="L47">
-        <f t="shared" si="22"/>
+      <c r="N47">
+        <f t="shared" si="26"/>
         <v>79.2</v>
       </c>
-      <c r="M47">
-        <f t="shared" si="22"/>
+      <c r="O47">
+        <f t="shared" si="26"/>
         <v>79.2</v>
       </c>
-      <c r="N47">
-        <f t="shared" si="22"/>
+      <c r="P47">
+        <f t="shared" si="26"/>
         <v>79.2</v>
       </c>
-      <c r="O47">
-        <f t="shared" si="22"/>
+      <c r="Q47">
+        <f t="shared" si="26"/>
         <v>79.2</v>
       </c>
-      <c r="P47">
-        <f t="shared" si="22"/>
+      <c r="R47">
+        <f t="shared" si="26"/>
         <v>79.2</v>
       </c>
-      <c r="S47">
-        <f>HLOOKUP($H47&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="U47">
+        <f>HLOOKUP($J47&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>79.2</v>
       </c>
-      <c r="T47">
-        <f>HLOOKUP($H47&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="V47">
+        <f>HLOOKUP($J47&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>79.2</v>
       </c>
-      <c r="AK47" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM47" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>5</v>
       </c>
-      <c r="H48" t="s">
+      <c r="J48" t="s">
         <v>81</v>
       </c>
-      <c r="I48" t="str">
-        <f t="shared" si="23"/>
+      <c r="K48" t="str">
+        <f t="shared" si="27"/>
         <v>Bioenergy</v>
       </c>
-      <c r="J48">
-        <f t="shared" si="22"/>
+      <c r="L48">
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
-      <c r="P48">
-        <f>VLOOKUP($D$5,$AL$9:$AN$15,3,FALSE)*J48</f>
-        <v>66</v>
-      </c>
-      <c r="S48">
-        <f>HLOOKUP($H48&amp;"_"&amp;S$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="R48" t="e">
+        <f>VLOOKUP($D$5,$AN$9:$AP$15,3,FALSE)*L48</f>
+        <v>#N/A</v>
+      </c>
+      <c r="U48">
+        <f>HLOOKUP($J48&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>18</v>
       </c>
-      <c r="T48">
-        <f>HLOOKUP($H48&amp;"_"&amp;T$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="V48">
+        <f>HLOOKUP($J48&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AK48" s="10">
-        <f t="shared" si="6"/>
+      <c r="AM48" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK49" s="10">
-        <f t="shared" si="6"/>
+    <row r="49" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM49" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK50" s="10">
-        <f t="shared" si="6"/>
+    <row r="50" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM50" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK51" s="10">
-        <f t="shared" si="6"/>
+    <row r="51" spans="22:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="V51" s="5" t="str">
+        <f>IF($H$5="N","~TFM_INS: limtype=LO","GAS available")</f>
+        <v>~TFM_INS: limtype=LO</v>
+      </c>
+      <c r="AM51" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK52" s="10">
-        <f t="shared" si="6"/>
+    <row r="52" spans="22:39" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="V52" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="W52" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="X52" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y52" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z52" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="AM52" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK53" s="10">
-        <f t="shared" si="6"/>
+    <row r="53" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="V53" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y53">
+        <v>2100</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>165</v>
+      </c>
+      <c r="AM53" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK54" s="10">
-        <f t="shared" si="6"/>
+    <row r="54" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM54" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK55" s="10">
-        <f t="shared" si="6"/>
+    <row r="55" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM55" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK56" s="10">
-        <f t="shared" si="6"/>
+    <row r="56" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM56" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK57" s="10">
-        <f t="shared" si="6"/>
+    <row r="57" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM57" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK58" s="10">
-        <f t="shared" si="6"/>
+    <row r="58" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM58" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK59" s="10">
-        <f t="shared" si="6"/>
+    <row r="59" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM59" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK60" s="10">
-        <f t="shared" si="6"/>
+    <row r="60" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM60" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK61" s="10">
-        <f t="shared" si="6"/>
+    <row r="61" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM61" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK62" s="10">
-        <f t="shared" si="6"/>
+    <row r="62" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM62" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK63" s="10">
-        <f t="shared" si="6"/>
+    <row r="63" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM63" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK64" s="10">
-        <f t="shared" si="6"/>
+    <row r="64" spans="22:39" x14ac:dyDescent="0.45">
+      <c r="AM64" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK65" s="10">
-        <f t="shared" si="6"/>
+    <row r="65" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM65" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK66" s="10">
-        <f t="shared" si="6"/>
+    <row r="66" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM66" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK67" s="10">
-        <f t="shared" si="6"/>
+    <row r="67" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM67" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK68" s="10">
-        <f t="shared" si="6"/>
+    <row r="68" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM68" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK69" s="10">
-        <f t="shared" si="6"/>
+    <row r="69" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM69" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK70" s="10">
-        <f t="shared" si="6"/>
+    <row r="70" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM70" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK71" s="10">
-        <f t="shared" si="6"/>
+    <row r="71" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM71" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK72" s="10">
-        <f t="shared" si="6"/>
+    <row r="72" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM72" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK73" s="10">
-        <f t="shared" si="6"/>
+    <row r="73" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM73" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK74" s="10">
-        <f t="shared" si="6"/>
+    <row r="74" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM74" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK75" s="10">
-        <f t="shared" si="6"/>
+    <row r="75" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM75" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK76" s="10">
-        <f t="shared" si="6"/>
+    <row r="76" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM76" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK77" s="10">
-        <f t="shared" si="6"/>
+    <row r="77" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM77" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="37:37" x14ac:dyDescent="0.45">
-      <c r="AK78" s="10">
-        <f t="shared" si="6"/>
+    <row r="78" spans="39:39" x14ac:dyDescent="0.45">
+      <c r="AM78" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
@@ -7760,7 +8653,7 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="str">
         <f>Veda!F5</f>
-        <v>CF3</v>
+        <v>CF1</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.45">
@@ -7971,7 +8864,7 @@
       </c>
       <c r="H14" s="11">
         <f>SUMIF($A$7:$A$12,$A$1,H7:H12)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
@@ -7997,7 +8890,7 @@
       </c>
       <c r="H18" t="str">
         <f>"*"&amp;H14</f>
-        <v>*1</v>
+        <v>*0.5</v>
       </c>
       <c r="I18" t="s">
         <v>140</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCF08ED-511A-4090-9FB6-08B82F056AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2106EB90-2440-4CEE-AD25-6A7EE470FA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="172">
   <si>
     <t>C1</t>
   </si>
@@ -610,6 +610,15 @@
   <si>
     <t>pset_ci</t>
   </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>ELC?H</t>
+  </si>
+  <si>
+    <t>distr*</t>
+  </si>
 </sst>
 </file>
 
@@ -1013,22 +1022,22 @@
                   <c:v>229.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>275.11199999999997</c:v>
+                  <c:v>252.18600000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>290.01390000000004</c:v>
+                  <c:v>259.63695000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>304.91579999999999</c:v>
+                  <c:v>267.08789999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>373.69379999999995</c:v>
+                  <c:v>301.4769</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>458.52</c:v>
+                  <c:v>343.89</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>532.34172000000001</c:v>
+                  <c:v>380.80086</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5973,7 +5982,7 @@
     </row>
     <row r="3" spans="1:43" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
         <v>153</v>
@@ -6009,7 +6018,7 @@
     <row r="5" spans="1:43" x14ac:dyDescent="0.45">
       <c r="D5" s="1" t="str">
         <f>VLOOKUP(B3,$C$9:$F$999,2,FALSE)</f>
-        <v>Hi</v>
+        <v>Lo</v>
       </c>
       <c r="E5" s="1">
         <f>VLOOKUP($B$3,$C$9:$F$999,3,FALSE)</f>
@@ -6021,11 +6030,11 @@
       </c>
       <c r="G5" s="1" t="str">
         <f>VLOOKUP($B$3,$C$9:$G$999,5,FALSE)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="H5" s="1" t="str">
         <f>VLOOKUP($B$3,$C$9:$H$999,6,FALSE)</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -6228,7 +6237,7 @@
         <v>Lo.95.CF1.Y.Y</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C41" si="2">C10+1</f>
+        <f t="shared" ref="C11:C40" si="2">C10+1</f>
         <v>3</v>
       </c>
       <c r="D11" t="str">
@@ -6289,7 +6298,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="str">
-        <f t="shared" ref="D12:D41" si="3">D10</f>
+        <f t="shared" ref="D12:D40" si="3">D10</f>
         <v>Hi</v>
       </c>
       <c r="E12">
@@ -6427,27 +6436,27 @@
       </c>
       <c r="X14" s="8">
         <f t="shared" ref="X14:AC14" si="6">$V$12*M15</f>
-        <v>275.11199999999997</v>
+        <v>252.18600000000001</v>
       </c>
       <c r="Y14" s="8">
         <f t="shared" si="6"/>
-        <v>290.01390000000004</v>
+        <v>259.63695000000001</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="6"/>
-        <v>304.91579999999999</v>
+        <v>267.08789999999999</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="6"/>
-        <v>373.69379999999995</v>
+        <v>301.4769</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="6"/>
-        <v>458.52</v>
+        <v>343.89</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="6"/>
-        <v>532.34172000000001</v>
+        <v>380.80086</v>
       </c>
       <c r="AJ14">
         <v>6</v>
@@ -6497,32 +6506,32 @@
         <v>11</v>
       </c>
       <c r="L15" s="11">
-        <f>SUMIF($K$2:$K$6,$D$5,L$2:L$6)</f>
+        <f t="shared" ref="L15:R15" si="8">SUMIF($K$2:$K$6,$D$5,L$2:L$6)</f>
         <v>1</v>
       </c>
       <c r="M15" s="11">
-        <f>SUMIF($K$2:$K$6,$D$5,M$2:M$6)</f>
-        <v>1.2</v>
+        <f t="shared" si="8"/>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N15" s="11">
-        <f>SUMIF($K$2:$K$6,$D$5,N$2:N$6)</f>
-        <v>1.2650000000000001</v>
+        <f t="shared" si="8"/>
+        <v>1.1325000000000001</v>
       </c>
       <c r="O15" s="11">
-        <f>SUMIF($K$2:$K$6,$D$5,O$2:O$6)</f>
-        <v>1.33</v>
+        <f t="shared" si="8"/>
+        <v>1.165</v>
       </c>
       <c r="P15" s="11">
-        <f>SUMIF($K$2:$K$6,$D$5,P$2:P$6)</f>
-        <v>1.63</v>
+        <f t="shared" si="8"/>
+        <v>1.3149999999999999</v>
       </c>
       <c r="Q15" s="11">
-        <f>SUMIF($K$2:$K$6,$D$5,Q$2:Q$6)</f>
-        <v>2</v>
+        <f t="shared" si="8"/>
+        <v>1.5</v>
       </c>
       <c r="R15" s="11">
-        <f>SUMIF($K$2:$K$6,$D$5,R$2:R$6)</f>
-        <v>2.3220000000000001</v>
+        <f t="shared" si="8"/>
+        <v>1.661</v>
       </c>
       <c r="AJ15">
         <v>7</v>
@@ -6534,7 +6543,7 @@
         <v>150</v>
       </c>
       <c r="AM15" s="10">
-        <f t="shared" ref="AM15:AM78" si="8">AM10+1</f>
+        <f t="shared" ref="AM15:AM78" si="9">AM10+1</f>
         <v>2</v>
       </c>
     </row>
@@ -6555,7 +6564,7 @@
         <v>Hi</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16" si="9">E12</f>
+        <f t="shared" ref="E16" si="10">E12</f>
         <v>95</v>
       </c>
       <c r="F16" s="15" t="s">
@@ -6580,7 +6589,7 @@
         <v>148</v>
       </c>
       <c r="AM16" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -6601,7 +6610,7 @@
         <v>Lo</v>
       </c>
       <c r="E17">
-        <f t="shared" ref="E17" si="10">E13</f>
+        <f t="shared" ref="E17" si="11">E13</f>
         <v>0</v>
       </c>
       <c r="F17" t="s">
@@ -6621,27 +6630,27 @@
         <v>2020</v>
       </c>
       <c r="M17" s="7">
-        <f t="shared" ref="M17:R17" si="11">X17</f>
+        <f t="shared" ref="M17:R17" si="12">X17</f>
         <v>2025</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2030</v>
       </c>
       <c r="O17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2035</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2040</v>
       </c>
       <c r="Q17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2045</v>
       </c>
       <c r="R17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2050</v>
       </c>
       <c r="V17" s="4" t="s">
@@ -6681,7 +6690,7 @@
         <v>105</v>
       </c>
       <c r="AM17" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -6702,14 +6711,14 @@
         <v>Hi</v>
       </c>
       <c r="E18">
-        <f t="shared" ref="E18" si="12">E14</f>
+        <f t="shared" ref="E18" si="13">E14</f>
         <v>0</v>
       </c>
       <c r="F18" t="s">
         <v>147</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" ref="G18:G41" si="13">G10</f>
+        <f t="shared" ref="G18:G40" si="14">G10</f>
         <v>Y</v>
       </c>
       <c r="H18" s="15" t="s">
@@ -6750,31 +6759,31 @@
         <v>16</v>
       </c>
       <c r="W18" s="6">
-        <f t="shared" ref="W18:AC20" si="14">L18*W$14</f>
+        <f t="shared" ref="W18:AC20" si="15">L18*W$14</f>
         <v>0</v>
       </c>
       <c r="X18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Y18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AD18" t="s">
@@ -6791,7 +6800,7 @@
         <v>107</v>
       </c>
       <c r="AM18" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -6812,14 +6821,14 @@
         <v>Lo</v>
       </c>
       <c r="E19">
-        <f t="shared" ref="E19" si="15">E15</f>
+        <f t="shared" ref="E19" si="16">E15</f>
         <v>95</v>
       </c>
       <c r="F19" t="s">
         <v>147</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H19" s="15" t="s">
@@ -6860,32 +6869,32 @@
         <v>19</v>
       </c>
       <c r="W19" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>91.704000000000008</v>
       </c>
       <c r="X19" s="6">
-        <f t="shared" si="14"/>
-        <v>96.28919999999998</v>
+        <f t="shared" si="15"/>
+        <v>88.265100000000004</v>
       </c>
       <c r="Y19" s="6">
-        <f t="shared" si="14"/>
-        <v>95.704587000000018</v>
+        <f t="shared" si="15"/>
+        <v>85.680193500000001</v>
       </c>
       <c r="Z19" s="6">
-        <f t="shared" si="14"/>
-        <v>97.573055999999994</v>
+        <f t="shared" si="15"/>
+        <v>85.468127999999993</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="14"/>
-        <v>115.84507799999999</v>
+        <f t="shared" si="15"/>
+        <v>93.457838999999993</v>
       </c>
       <c r="AB19" s="6">
-        <f t="shared" si="14"/>
-        <v>142.1412</v>
+        <f t="shared" si="15"/>
+        <v>106.60589999999999</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="14"/>
-        <v>165.0259332</v>
+        <f t="shared" si="15"/>
+        <v>118.04826660000001</v>
       </c>
       <c r="AD19" t="s">
         <v>17</v>
@@ -6900,7 +6909,7 @@
         <v>89</v>
       </c>
       <c r="AM19" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -6921,14 +6930,14 @@
         <v>Hi</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E41" si="16">E16</f>
+        <f t="shared" ref="E20:E40" si="17">E16</f>
         <v>95</v>
       </c>
       <c r="F20" t="s">
         <v>147</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H20" s="15" t="s">
@@ -6969,32 +6978,32 @@
         <v>22</v>
       </c>
       <c r="W20" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>107.75219999999999</v>
       </c>
       <c r="X20" s="6">
-        <f t="shared" si="14"/>
-        <v>143.05823999999998</v>
+        <f t="shared" si="15"/>
+        <v>131.13672</v>
       </c>
       <c r="Y20" s="6">
-        <f t="shared" si="14"/>
-        <v>156.60750600000003</v>
+        <f t="shared" si="15"/>
+        <v>140.20395300000001</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" si="14"/>
-        <v>161.60537400000001</v>
+        <f t="shared" si="15"/>
+        <v>141.55658700000001</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="14"/>
-        <v>194.320776</v>
+        <f t="shared" si="15"/>
+        <v>156.767988</v>
       </c>
       <c r="AB20" s="6">
-        <f t="shared" si="14"/>
-        <v>229.26</v>
+        <f t="shared" si="15"/>
+        <v>171.94499999999999</v>
       </c>
       <c r="AC20" s="6">
-        <f t="shared" si="14"/>
-        <v>255.52402559999999</v>
+        <f t="shared" si="15"/>
+        <v>182.78441279999998</v>
       </c>
       <c r="AD20" t="s">
         <v>17</v>
@@ -7009,7 +7018,7 @@
         <v>94</v>
       </c>
       <c r="AM20" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -7030,14 +7039,14 @@
         <v>Lo</v>
       </c>
       <c r="E21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F21" t="s">
         <v>147</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H21" s="15" t="s">
@@ -7082,27 +7091,27 @@
         <v>2.2925999999999997</v>
       </c>
       <c r="X21" s="6">
-        <f t="shared" ref="X21:AC21" si="17">W21</f>
+        <f t="shared" ref="X21:AC21" si="18">W21</f>
         <v>2.2925999999999997</v>
       </c>
       <c r="Y21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="Z21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AA21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AB21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AC21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AD21" t="s">
@@ -7112,7 +7121,7 @@
         <v>20</v>
       </c>
       <c r="AM21" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -7133,14 +7142,14 @@
         <v>Hi</v>
       </c>
       <c r="E22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F22" t="s">
         <v>147</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H22" s="15" t="s">
@@ -7150,38 +7159,38 @@
         <v>25</v>
       </c>
       <c r="W22" s="6">
-        <f t="shared" ref="W22:AC22" si="18">W14-SUM(W19:W21)</f>
+        <f t="shared" ref="W22:AC22" si="19">W14-SUM(W19:W21)</f>
         <v>27.511200000000002</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" si="18"/>
-        <v>33.471960000000024</v>
+        <f t="shared" si="19"/>
+        <v>30.491580000000027</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="18"/>
-        <v>35.409206999999981</v>
+        <f t="shared" si="19"/>
+        <v>31.460203500000006</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="18"/>
-        <v>43.444770000000005</v>
+        <f t="shared" si="19"/>
+        <v>37.770584999999983</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="18"/>
-        <v>61.235345999999993</v>
+        <f t="shared" si="19"/>
+        <v>48.958473000000026</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="18"/>
-        <v>84.826199999999972</v>
+        <f t="shared" si="19"/>
+        <v>63.046500000000037</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="18"/>
-        <v>109.4991612</v>
+        <f t="shared" si="19"/>
+        <v>77.675580600000046</v>
       </c>
       <c r="AD22" t="s">
         <v>17</v>
       </c>
       <c r="AM22" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -7202,14 +7211,14 @@
         <v>Lo</v>
       </c>
       <c r="E23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F23" t="s">
         <v>147</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H23" s="15" t="s">
@@ -7219,7 +7228,7 @@
         <v>26</v>
       </c>
       <c r="AM23" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -7240,14 +7249,14 @@
         <v>Hi</v>
       </c>
       <c r="E24">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F24" t="s">
         <v>147</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H24" s="15" t="s">
@@ -7257,31 +7266,31 @@
         <v>27</v>
       </c>
       <c r="L24" s="11">
-        <f>SUMIF($K$2:$K$6,$E$5,L$2:L$6)</f>
+        <f t="shared" ref="L24:R24" si="20">SUMIF($K$2:$K$6,$E$5,L$2:L$6)</f>
         <v>0</v>
       </c>
       <c r="M24" s="11">
-        <f>SUMIF($K$2:$K$6,$E$5,M$2:M$6)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N24" s="11">
-        <f>SUMIF($K$2:$K$6,$E$5,N$2:N$6)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O24" s="11">
-        <f>SUMIF($K$2:$K$6,$E$5,O$2:O$6)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="P24" s="11">
-        <f>SUMIF($K$2:$K$6,$E$5,P$2:P$6)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q24" s="11">
-        <f>SUMIF($K$2:$K$6,$E$5,Q$2:Q$6)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R24" s="11">
-        <f>SUMIF($K$2:$K$6,$E$5,R$2:R$6)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="V24" t="s">
@@ -7314,7 +7323,7 @@
         <v>29</v>
       </c>
       <c r="AM24" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7335,7 +7344,7 @@
         <v>Lo</v>
       </c>
       <c r="E25">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F25" t="str">
@@ -7343,14 +7352,14 @@
         <v>CF1</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AM25" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7371,15 +7380,15 @@
         <v>Hi</v>
       </c>
       <c r="E26">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" ref="F26:F41" si="19">F10</f>
+        <f t="shared" ref="F26:F40" si="21">F10</f>
         <v>CF1</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H26" s="15" t="s">
@@ -7389,7 +7398,7 @@
         <v>12</v>
       </c>
       <c r="AM26" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7410,15 +7419,15 @@
         <v>Lo</v>
       </c>
       <c r="E27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H27" s="15" t="s">
@@ -7428,31 +7437,31 @@
         <v>30</v>
       </c>
       <c r="W27" s="4">
-        <f t="shared" ref="W27:AC27" si="20">W17</f>
+        <f t="shared" ref="W27:AC27" si="22">W17</f>
         <v>2022</v>
       </c>
       <c r="X27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2025</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2030</v>
       </c>
       <c r="Z27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2035</v>
       </c>
       <c r="AA27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2040</v>
       </c>
       <c r="AB27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2045</v>
       </c>
       <c r="AC27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2050</v>
       </c>
       <c r="AD27" s="4" t="s">
@@ -7462,7 +7471,7 @@
         <v>31</v>
       </c>
       <c r="AM27" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7483,15 +7492,15 @@
         <v>Hi</v>
       </c>
       <c r="E28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G28" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H28" s="15" t="s">
@@ -7520,7 +7529,7 @@
         <v>34</v>
       </c>
       <c r="AM28" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7541,15 +7550,15 @@
         <v>Lo</v>
       </c>
       <c r="E29">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H29" s="15" t="s">
@@ -7578,7 +7587,7 @@
         <v>34</v>
       </c>
       <c r="AM29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -7599,22 +7608,22 @@
         <v>Hi</v>
       </c>
       <c r="E30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AM30" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -7635,26 +7644,26 @@
         <v>Lo</v>
       </c>
       <c r="E31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AM31" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A32">
         <v>5</v>
       </c>
@@ -7671,26 +7680,30 @@
         <v>Hi</v>
       </c>
       <c r="E32">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>156</v>
       </c>
+      <c r="V32" s="5" t="str">
+        <f>IF($G$5="N","~TFM_UPD","DEF correction active")</f>
+        <v>DEF correction active</v>
+      </c>
       <c r="AM32" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:39" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33">
         <v>5</v>
       </c>
@@ -7707,22 +7720,34 @@
         <v>Lo</v>
       </c>
       <c r="E33">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H33" s="15" t="s">
         <v>156</v>
       </c>
+      <c r="V33" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="W33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y33" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="AM33" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -7743,22 +7768,34 @@
         <v>Hi</v>
       </c>
       <c r="E34">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>156</v>
       </c>
+      <c r="V34" t="s">
+        <v>169</v>
+      </c>
+      <c r="W34" t="s">
+        <v>170</v>
+      </c>
+      <c r="X34" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
       <c r="AM34" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
@@ -7779,26 +7816,26 @@
         <v>Lo</v>
       </c>
       <c r="E35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AM35" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>5</v>
       </c>
@@ -7815,15 +7852,15 @@
         <v>Hi</v>
       </c>
       <c r="E36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H36" s="15" t="s">
@@ -7832,16 +7869,12 @@
       <c r="J36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="V36" s="5" t="str">
-        <f>IF($G$5="N","~TFM_INS: limtype=LO","DEF correction active")</f>
-        <v>~TFM_INS: limtype=LO</v>
-      </c>
       <c r="AM36" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:39" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A37">
         <v>5</v>
       </c>
@@ -7858,15 +7891,15 @@
         <v>Lo</v>
       </c>
       <c r="E37">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H37" s="15" t="s">
@@ -7888,45 +7921,34 @@
         <v>1.0510100500999999</v>
       </c>
       <c r="O37" s="11">
-        <f t="shared" ref="O37:R37" si="21">N37*(1+$T37)^5</f>
+        <f t="shared" ref="O37:R37" si="23">N37*(1+$T37)^5</f>
         <v>1.1046221254112043</v>
       </c>
       <c r="P37" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1.1609689553699982</v>
       </c>
       <c r="Q37" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1.2201900399479664</v>
       </c>
       <c r="R37" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1.2824319950172332</v>
       </c>
       <c r="T37">
         <v>0.01</v>
       </c>
-      <c r="V37" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="W37" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="X37" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y37" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="Z37" s="4" t="s">
-        <v>159</v>
+      <c r="V37" s="5" t="str">
+        <f>IF($G$5="N","~TFM_INS: limtype=LO","DEF correction active")</f>
+        <v>DEF correction active</v>
       </c>
       <c r="AM37" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:39" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38">
         <v>5</v>
       </c>
@@ -7943,15 +7965,15 @@
         <v>Hi</v>
       </c>
       <c r="E38">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H38" s="15" t="s">
@@ -7965,46 +7987,46 @@
         <v>1</v>
       </c>
       <c r="M38" s="11">
-        <f t="shared" ref="M38:R38" si="22">L38</f>
+        <f t="shared" ref="M38:R38" si="24">L38</f>
         <v>1</v>
       </c>
       <c r="N38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="O38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="P38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R38" s="11">
-        <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="V38" t="s">
-        <v>160</v>
-      </c>
-      <c r="W38" t="s">
-        <v>161</v>
-      </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-      <c r="Y38">
-        <v>-13</v>
-      </c>
-      <c r="Z38" t="s">
-        <v>162</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="V38" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="W38" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="X38" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y38" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z38" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="AM38" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
@@ -8025,15 +8047,15 @@
         <v>Lo</v>
       </c>
       <c r="E39">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H39" s="15" t="s">
@@ -8047,31 +8069,34 @@
         <v>1</v>
       </c>
       <c r="M39" s="11">
-        <f t="shared" ref="M39:R39" si="23">L39</f>
+        <f t="shared" ref="M39:R39" si="25">L39</f>
         <v>1</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="O39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="P39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="Q39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="V39" t="s">
-        <v>163</v>
+        <v>160</v>
+      </c>
+      <c r="W39" t="s">
+        <v>161</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -8080,10 +8105,10 @@
         <v>-13</v>
       </c>
       <c r="Z39" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AM39" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8104,15 +8129,15 @@
         <v>Hi</v>
       </c>
       <c r="E40">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G40" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H40" s="15" t="s">
@@ -8126,31 +8151,43 @@
         <v>1</v>
       </c>
       <c r="M40" s="11">
-        <f t="shared" ref="M40:R40" si="24">L40</f>
+        <f t="shared" ref="M40:R40" si="26">L40</f>
         <v>1</v>
       </c>
       <c r="N40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="O40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="P40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="Q40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="R40" s="11">
-        <f t="shared" si="24"/>
-        <v>1</v>
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>163</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>-13</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>164</v>
       </c>
       <c r="AM40" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8159,7 +8196,7 @@
         <v>5</v>
       </c>
       <c r="AM41" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8168,7 +8205,7 @@
         <v>5</v>
       </c>
       <c r="AM42" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8180,7 +8217,7 @@
         <v>101</v>
       </c>
       <c r="AM43" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8202,23 +8239,23 @@
         <v>2025</v>
       </c>
       <c r="N44">
-        <f t="shared" ref="N44:R44" si="25">N17</f>
+        <f t="shared" ref="N44:R44" si="27">N17</f>
         <v>2030</v>
       </c>
       <c r="O44">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2035</v>
       </c>
       <c r="P44">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2040</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2045</v>
       </c>
       <c r="R44">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2050</v>
       </c>
       <c r="U44" t="s">
@@ -8228,7 +8265,7 @@
         <v>83</v>
       </c>
       <c r="AM44" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8244,31 +8281,31 @@
         <v>Gas</v>
       </c>
       <c r="L45">
-        <f t="shared" ref="L45:R48" si="26">AVERAGE($U45:$V45)*L37</f>
+        <f t="shared" ref="L45:R48" si="28">AVERAGE($U45:$V45)*L37</f>
         <v>45</v>
       </c>
       <c r="M45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>45</v>
       </c>
       <c r="N45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>47.295452254499999</v>
       </c>
       <c r="O45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>49.707995643504191</v>
       </c>
       <c r="P45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>52.243602991649922</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>54.90855179765849</v>
       </c>
       <c r="R45">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>57.709439775775493</v>
       </c>
       <c r="U45">
@@ -8280,7 +8317,7 @@
         <v>45</v>
       </c>
       <c r="AM45" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8292,35 +8329,35 @@
         <v>79</v>
       </c>
       <c r="K46" t="str">
-        <f t="shared" ref="K46:K48" si="27">J46</f>
+        <f t="shared" ref="K46:K48" si="29">J46</f>
         <v>Coal</v>
       </c>
       <c r="L46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="M46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="N46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="O46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="P46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="R46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="U46">
@@ -8332,7 +8369,7 @@
         <v>5.04</v>
       </c>
       <c r="AM46" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8344,35 +8381,35 @@
         <v>80</v>
       </c>
       <c r="K47" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>Oil</v>
       </c>
       <c r="L47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="M47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="N47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="O47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="P47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="R47">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="U47">
@@ -8384,7 +8421,7 @@
         <v>79.2</v>
       </c>
       <c r="AM47" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8396,11 +8433,11 @@
         <v>81</v>
       </c>
       <c r="K48" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>Bioenergy</v>
       </c>
       <c r="L48">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>22</v>
       </c>
       <c r="R48" t="e">
@@ -8416,29 +8453,29 @@
         <v>26</v>
       </c>
       <c r="AM48" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
     <row r="49" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM49" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
     <row r="50" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM50" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
     <row r="51" spans="22:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="V51" s="5" t="str">
         <f>IF($H$5="N","~TFM_INS: limtype=LO","GAS available")</f>
-        <v>~TFM_INS: limtype=LO</v>
+        <v>GAS available</v>
       </c>
       <c r="AM51" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -8459,7 +8496,7 @@
         <v>168</v>
       </c>
       <c r="AM52" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -8474,157 +8511,157 @@
         <v>165</v>
       </c>
       <c r="AM53" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
     <row r="54" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM54" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
     <row r="55" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM55" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
     <row r="56" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM56" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
     <row r="57" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM57" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
     <row r="58" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM58" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
     <row r="59" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM59" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="60" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM60" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="61" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM61" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="62" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM62" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="63" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM63" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="64" spans="22:39" x14ac:dyDescent="0.45">
       <c r="AM64" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="65" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM65" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="66" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM66" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="67" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM67" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="68" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM68" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM69" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
     <row r="70" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM70" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
     <row r="71" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM71" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
     <row r="72" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM72" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
     <row r="73" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM73" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
     <row r="74" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM74" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
     <row r="75" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM75" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
     <row r="76" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM76" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
     <row r="77" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM77" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
     <row r="78" spans="39:39" x14ac:dyDescent="0.45">
       <c r="AM78" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2106EB90-2440-4CEE-AD25-6A7EE470FA07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245922E2-256A-42DA-BDA5-7C932A3CBF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="174">
   <si>
     <t>C1</t>
   </si>
@@ -619,6 +619,12 @@
   <si>
     <t>distr*</t>
   </si>
+  <si>
+    <t>pset_pd</t>
+  </si>
+  <si>
+    <t>-Gas turbine*</t>
+  </si>
 </sst>
 </file>
 
@@ -825,7 +831,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -852,6 +858,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -8484,7 +8491,7 @@
         <v>14</v>
       </c>
       <c r="W52" s="4" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="X52" s="4" t="s">
         <v>37</v>
@@ -8503,6 +8510,9 @@
     <row r="53" spans="22:39" x14ac:dyDescent="0.45">
       <c r="V53" t="s">
         <v>167</v>
+      </c>
+      <c r="W53" s="20" t="s">
+        <v>173</v>
       </c>
       <c r="Y53">
         <v>2100</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245922E2-256A-42DA-BDA5-7C932A3CBF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD85998-77EF-4275-ABA1-3DBBC94FE875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{3E464726-1383-487A-BC9B-27E3D5D65A9D}">
+    <comment ref="O2" authorId="0" shapeId="0" xr:uid="{3E464726-1383-487A-BC9B-27E3D5D65A9D}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ8" authorId="0" shapeId="0" xr:uid="{B8774821-523C-49C0-8481-0CFAD2313CD6}">
+    <comment ref="AR8" authorId="0" shapeId="0" xr:uid="{B8774821-523C-49C0-8481-0CFAD2313CD6}">
       <text>
         <r>
           <rPr>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1674" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="177">
   <si>
     <t>C1</t>
   </si>
@@ -602,9 +602,6 @@
     <t>GAS</t>
   </si>
   <si>
-    <t>1-32</t>
-  </si>
-  <si>
     <t>START</t>
   </si>
   <si>
@@ -617,13 +614,25 @@
     <t>ELC?H</t>
   </si>
   <si>
-    <t>distr*</t>
-  </si>
-  <si>
     <t>pset_pd</t>
   </si>
   <si>
     <t>-Gas turbine*</t>
+  </si>
+  <si>
+    <t>trancost</t>
+  </si>
+  <si>
+    <t>Aggregators</t>
+  </si>
+  <si>
+    <t>NCAP_COST</t>
+  </si>
+  <si>
+    <t>grid, aggregators</t>
+  </si>
+  <si>
+    <t>33-64</t>
   </si>
 </sst>
 </file>
@@ -831,7 +840,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -859,6 +868,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -991,7 +1003,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$W$17:$AC$17</c:f>
+              <c:f>Veda!$X$17:$AD$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1021,7 +1033,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$W$14:$AC$14</c:f>
+              <c:f>Veda!$X$14:$AD$14</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1029,22 +1041,22 @@
                   <c:v>229.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>252.18600000000001</c:v>
+                  <c:v>275.11199999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>259.63695000000001</c:v>
+                  <c:v>290.01390000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>267.08789999999999</c:v>
+                  <c:v>304.91579999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>301.4769</c:v>
+                  <c:v>373.69379999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>343.89</c:v>
+                  <c:v>458.52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>380.80086</c:v>
+                  <c:v>532.34172000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1279,7 +1291,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda!$L$17:$R$17</c:f>
+              <c:f>Veda!$M$17:$S$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1309,7 +1321,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda!$L$24:$R$24</c:f>
+              <c:f>Veda!$M$24:$S$24</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1320,19 +1332,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1466,13 +1478,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>454817</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>309562</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>95248</xdr:rowOff>
@@ -1502,13 +1514,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>481012</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>250032</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>76199</xdr:rowOff>
@@ -5921,7 +5933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AQ78"/>
+  <dimension ref="A1:AR78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.46484375" bestFit="1" customWidth="1"/>
@@ -5931,120 +5943,121 @@
     <col min="5" max="5" width="7.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.1328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.86328125" customWidth="1"/>
-    <col min="9" max="9" width="1.73046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.53125" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="5.265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9.265625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="2.73046875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="2.9296875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.59765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="3.86328125" customWidth="1"/>
+    <col min="10" max="10" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.53125" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.265625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="2.73046875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="2.9296875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.45">
-      <c r="J1" s="16" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="K1" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
-        <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,J1:EH1)</f>
-        <v>~Inputcell: 1-32</v>
-      </c>
-      <c r="K2" t="s">
+        <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
+        <v>~Inputcell: 33-64</v>
+      </c>
+      <c r="L2" t="s">
         <v>151</v>
       </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
       <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
         <v>1.2</v>
       </c>
-      <c r="N2">
-        <f>AVERAGE(M2,O2)</f>
+      <c r="O2">
+        <f>AVERAGE(N2,P2)</f>
         <v>1.2650000000000001</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>1.33</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>1.63</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>2</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>2.3220000000000001</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" t="s">
         <v>153</v>
       </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
       <c r="M3">
-        <f>1+(M2-1)/2</f>
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <f>1+(N2-1)/2</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="N3">
-        <f t="shared" ref="N3:R3" si="0">1+(N2-1)/2</f>
+      <c r="O3">
+        <f t="shared" ref="O3:S3" si="0">1+(O2-1)/2</f>
         <v>1.1325000000000001</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <f t="shared" si="0"/>
         <v>1.165</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <f t="shared" si="0"/>
         <v>1.3149999999999999</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <f t="shared" si="0"/>
         <v>1.661</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.45">
-      <c r="D5" s="1" t="str">
-        <f>VLOOKUP(B3,$C$9:$F$999,2,FALSE)</f>
-        <v>Lo</v>
-      </c>
-      <c r="E5" s="1">
-        <f>VLOOKUP($B$3,$C$9:$F$999,3,FALSE)</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="str">
-        <f>VLOOKUP($B$3,$C$9:$F$999,4,FALSE)</f>
-        <v>CF1</v>
-      </c>
-      <c r="G5" s="1" t="str">
-        <f>VLOOKUP($B$3,$C$9:$G$999,5,FALSE)</f>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="D5" s="21" t="str">
+        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <v>Hi</v>
+      </c>
+      <c r="E5" s="21">
+        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <v>95</v>
+      </c>
+      <c r="F5" s="21" t="str">
+        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <v>CF6</v>
+      </c>
+      <c r="G5" s="21" t="str">
+        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
         <v>Y</v>
       </c>
-      <c r="H5" s="1" t="str">
-        <f>VLOOKUP($B$3,$C$9:$H$999,6,FALSE)</f>
+      <c r="H5" s="21" t="str">
+        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
         <v>Y</v>
       </c>
-      <c r="K5">
-        <v>0</v>
+      <c r="I5" s="21" t="str">
+        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <v>N</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -6067,39 +6080,42 @@
       <c r="R5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.45">
-      <c r="K6">
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="L6">
         <v>95</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
         <v>3</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>35</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>60</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>80</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:44" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
         <v>98</v>
       </c>
@@ -6124,18 +6140,21 @@
       <c r="H8" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="I8" s="4"/>
-      <c r="AQ8" s="2" t="s">
+      <c r="I8" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="AR8" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>5</v>
       </c>
       <c r="B9" t="str">
-        <f>_xlfn.TEXTJOIN(".",TRUE,D9:H9)</f>
-        <v>Lo.0.CF1.Y.Y</v>
+        <f>_xlfn.TEXTJOIN(".",TRUE,D9:I9)</f>
+        <v>Lo.0.CF1.Y.Y.Y</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6155,38 +6174,41 @@
       <c r="H9" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J9" t="s">
-        <v>1</v>
-      </c>
-      <c r="AJ9">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="s">
+      <c r="I9" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="s">
         <v>86</v>
       </c>
-      <c r="AL9" t="s">
+      <c r="AM9" t="s">
         <v>109</v>
       </c>
-      <c r="AM9" s="10">
-        <v>1</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>0</v>
+      <c r="AN9" s="10">
+        <v>1</v>
       </c>
       <c r="AO9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="s">
         <v>88</v>
       </c>
-      <c r="AP9" s="12">
+      <c r="AQ9" s="12">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>5</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" ref="B10:B40" si="1">_xlfn.TEXTJOIN(".",TRUE,D10:H10)</f>
-        <v>Hi.0.CF1.Y.Y</v>
+        <f t="shared" ref="B10:B72" si="1">_xlfn.TEXTJOIN(".",TRUE,D10:I10)</f>
+        <v>Hi.0.CF1.Y.Y.Y</v>
       </c>
       <c r="C10">
         <f>C9+1</f>
@@ -6207,44 +6229,47 @@
       <c r="H10" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J10" t="s">
+      <c r="I10" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K10" t="s">
         <v>3</v>
       </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
         <v>4</v>
       </c>
-      <c r="AJ10">
+      <c r="AK10">
         <v>2</v>
       </c>
-      <c r="AK10" t="s">
+      <c r="AL10" t="s">
         <v>113</v>
       </c>
-      <c r="AL10" t="s">
+      <c r="AM10" t="s">
         <v>116</v>
       </c>
-      <c r="AM10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AN10" t="s">
+      <c r="AN10" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="s">
         <v>2</v>
       </c>
-      <c r="AO10" t="s">
+      <c r="AP10" t="s">
         <v>90</v>
       </c>
-      <c r="AP10" s="12">
+      <c r="AQ10" s="12">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>5</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.95.CF1.Y.Y</v>
+        <v>Lo.95.CF1.Y.Y.Y</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C40" si="2">C10+1</f>
+        <f t="shared" ref="C11:C74" si="2">C10+1</f>
         <v>3</v>
       </c>
       <c r="D11" t="str">
@@ -6263,49 +6288,52 @@
       <c r="H11" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J11" t="s">
+      <c r="I11" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K11" t="s">
         <v>6</v>
       </c>
-      <c r="V11" s="1">
+      <c r="W11" s="1">
         <v>2022</v>
       </c>
-      <c r="AJ11">
+      <c r="AK11">
         <v>3</v>
       </c>
-      <c r="AK11" t="s">
+      <c r="AL11" t="s">
         <v>99</v>
       </c>
-      <c r="AL11" t="str">
-        <f>AK11</f>
+      <c r="AM11" t="str">
+        <f>AL11</f>
         <v>ts_012</v>
       </c>
-      <c r="AM11" s="10">
-        <v>1</v>
-      </c>
-      <c r="AN11" t="s">
+      <c r="AN11" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="s">
         <v>5</v>
       </c>
-      <c r="AO11" t="s">
+      <c r="AP11" t="s">
         <v>91</v>
       </c>
-      <c r="AP11" s="12">
+      <c r="AQ11" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:44" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.95.CF1.Y.Y</v>
+        <v>Hi.95.CF1.Y.Y.Y</v>
       </c>
       <c r="C12">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="D12" t="str">
-        <f t="shared" ref="D12:D40" si="3">D10</f>
+        <f t="shared" ref="D12:D75" si="3">D10</f>
         <v>Hi</v>
       </c>
       <c r="E12">
@@ -6320,46 +6348,49 @@
       <c r="H12" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J12" t="s">
+      <c r="I12" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K12" t="s">
         <v>8</v>
       </c>
-      <c r="V12" s="3">
-        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,Veda!$V$11)+W28-W29</f>
+      <c r="W12" s="3">
+        <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,Veda!$W$11)+X28-X29</f>
         <v>229.26</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="X12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AJ12">
+      <c r="AK12">
         <v>4</v>
       </c>
-      <c r="AK12" t="s">
+      <c r="AL12" t="s">
         <v>104</v>
       </c>
-      <c r="AL12" t="str">
-        <f t="shared" ref="AL12:AL14" si="4">AK12</f>
+      <c r="AM12" t="str">
+        <f t="shared" ref="AM12:AM14" si="4">AL12</f>
         <v>ts_030</v>
       </c>
-      <c r="AM12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AN12" t="s">
+      <c r="AN12" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="s">
         <v>7</v>
       </c>
-      <c r="AO12" t="s">
+      <c r="AP12" t="s">
         <v>92</v>
       </c>
-      <c r="AP12" s="12">
+      <c r="AQ12" s="12">
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:44" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.0.CF1.N.Y</v>
+        <v>Lo.0.CF1.N.Y.Y</v>
       </c>
       <c r="C13">
         <f t="shared" si="2"/>
@@ -6382,39 +6413,42 @@
       <c r="H13" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J13" t="s">
+      <c r="I13" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K13" t="s">
         <v>10</v>
       </c>
-      <c r="AJ13">
+      <c r="AK13">
         <v>5</v>
       </c>
-      <c r="AK13" t="s">
+      <c r="AL13" t="s">
         <v>100</v>
       </c>
-      <c r="AL13" t="str">
+      <c r="AM13" t="str">
         <f t="shared" si="4"/>
         <v>ts_048</v>
       </c>
-      <c r="AM13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AN13" t="s">
+      <c r="AN13" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="s">
         <v>9</v>
       </c>
-      <c r="AO13" t="s">
+      <c r="AP13" t="s">
         <v>93</v>
       </c>
-      <c r="AP13" s="12">
+      <c r="AQ13" s="12">
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>5</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.0.CF1.N.Y</v>
+        <v>Hi.0.CF1.N.Y.Y</v>
       </c>
       <c r="C14">
         <f t="shared" si="2"/>
@@ -6437,56 +6471,59 @@
       <c r="H14" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="W14" s="8">
-        <f>V12</f>
+      <c r="I14" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="X14" s="8">
+        <f>W12</f>
         <v>229.26</v>
       </c>
-      <c r="X14" s="8">
-        <f t="shared" ref="X14:AC14" si="6">$V$12*M15</f>
-        <v>252.18600000000001</v>
-      </c>
       <c r="Y14" s="8">
-        <f t="shared" si="6"/>
-        <v>259.63695000000001</v>
+        <f t="shared" ref="Y14:AD14" si="6">$W$12*N15</f>
+        <v>275.11199999999997</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="6"/>
-        <v>267.08789999999999</v>
+        <v>290.01390000000004</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="6"/>
-        <v>301.4769</v>
+        <v>304.91579999999999</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="6"/>
-        <v>343.89</v>
+        <v>373.69379999999995</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="6"/>
-        <v>380.80086</v>
-      </c>
-      <c r="AJ14">
+        <v>458.52</v>
+      </c>
+      <c r="AD14" s="8">
+        <f t="shared" si="6"/>
+        <v>532.34172000000001</v>
+      </c>
+      <c r="AK14">
         <v>6</v>
       </c>
-      <c r="AK14" t="s">
+      <c r="AL14" t="s">
         <v>108</v>
       </c>
-      <c r="AL14" t="str">
+      <c r="AM14" t="str">
         <f t="shared" si="4"/>
         <v>ts_072</v>
       </c>
-      <c r="AM14" s="10">
-        <f>AM9+1</f>
+      <c r="AN14" s="10">
+        <f>AN9+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>5</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.95.CF1.N.Y</v>
+        <v>Lo.95.CF1.N.Y.Y</v>
       </c>
       <c r="C15">
         <f t="shared" si="2"/>
@@ -6509,58 +6546,61 @@
       <c r="H15" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J15" t="s">
+      <c r="I15" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K15" t="s">
         <v>11</v>
       </c>
-      <c r="L15" s="11">
-        <f t="shared" ref="L15:R15" si="8">SUMIF($K$2:$K$6,$D$5,L$2:L$6)</f>
-        <v>1</v>
-      </c>
       <c r="M15" s="11">
-        <f t="shared" si="8"/>
-        <v>1.1000000000000001</v>
+        <f>SUMIF($L$2:$L$6,$D$5,M$2:M$6)</f>
+        <v>1</v>
       </c>
       <c r="N15" s="11">
-        <f t="shared" si="8"/>
-        <v>1.1325000000000001</v>
+        <f>SUMIF($L$2:$L$6,$D$5,N$2:N$6)</f>
+        <v>1.2</v>
       </c>
       <c r="O15" s="11">
-        <f t="shared" si="8"/>
-        <v>1.165</v>
+        <f>SUMIF($L$2:$L$6,$D$5,O$2:O$6)</f>
+        <v>1.2650000000000001</v>
       </c>
       <c r="P15" s="11">
-        <f t="shared" si="8"/>
-        <v>1.3149999999999999</v>
+        <f>SUMIF($L$2:$L$6,$D$5,P$2:P$6)</f>
+        <v>1.33</v>
       </c>
       <c r="Q15" s="11">
-        <f t="shared" si="8"/>
-        <v>1.5</v>
+        <f>SUMIF($L$2:$L$6,$D$5,Q$2:Q$6)</f>
+        <v>1.63</v>
       </c>
       <c r="R15" s="11">
-        <f t="shared" si="8"/>
-        <v>1.661</v>
-      </c>
-      <c r="AJ15">
+        <f>SUMIF($L$2:$L$6,$D$5,R$2:R$6)</f>
+        <v>2</v>
+      </c>
+      <c r="S15" s="11">
+        <f>SUMIF($L$2:$L$6,$D$5,S$2:S$6)</f>
+        <v>2.3220000000000001</v>
+      </c>
+      <c r="AK15">
         <v>7</v>
       </c>
-      <c r="AK15" t="s">
+      <c r="AL15" t="s">
         <v>149</v>
       </c>
-      <c r="AL15" t="s">
+      <c r="AM15" t="s">
         <v>150</v>
       </c>
-      <c r="AM15" s="10">
-        <f t="shared" ref="AM15:AM78" si="9">AM10+1</f>
+      <c r="AN15" s="10">
+        <f t="shared" ref="AN15:AN78" si="8">AN10+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:44" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>5</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.95.CF1.N.Y</v>
+        <v>Hi.95.CF1.N.Y.Y</v>
       </c>
       <c r="C16">
         <f t="shared" si="2"/>
@@ -6571,7 +6611,7 @@
         <v>Hi</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16" si="10">E12</f>
+        <f t="shared" ref="E16" si="9">E12</f>
         <v>95</v>
       </c>
       <c r="F16" s="15" t="s">
@@ -6583,30 +6623,33 @@
       <c r="H16" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="V16" s="5" t="s">
+      <c r="I16" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AJ16">
+      <c r="AK16">
         <v>8</v>
       </c>
-      <c r="AK16" t="s">
+      <c r="AL16" t="s">
         <v>114</v>
       </c>
-      <c r="AL16" t="s">
+      <c r="AM16" t="s">
         <v>148</v>
       </c>
-      <c r="AM16" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN16" s="10">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:40" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17">
         <v>5</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.0.CF6.Y.Y</v>
+        <v>Lo.0.CF6.Y.Y.Y</v>
       </c>
       <c r="C17">
         <f t="shared" si="2"/>
@@ -6617,7 +6660,7 @@
         <v>Lo</v>
       </c>
       <c r="E17">
-        <f t="shared" ref="E17" si="11">E13</f>
+        <f t="shared" ref="E17" si="10">E13</f>
         <v>0</v>
       </c>
       <c r="F17" t="s">
@@ -6630,84 +6673,87 @@
       <c r="H17" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="I17" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K17" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="L17" s="7">
+      <c r="M17" s="7">
         <v>2020</v>
       </c>
-      <c r="M17" s="7">
-        <f t="shared" ref="M17:R17" si="12">X17</f>
+      <c r="N17" s="7">
+        <f t="shared" ref="N17:S17" si="11">Y17</f>
         <v>2025</v>
       </c>
-      <c r="N17" s="7">
-        <f t="shared" si="12"/>
+      <c r="O17" s="7">
+        <f t="shared" si="11"/>
         <v>2030</v>
       </c>
-      <c r="O17" s="7">
-        <f t="shared" si="12"/>
+      <c r="P17" s="7">
+        <f t="shared" si="11"/>
         <v>2035</v>
       </c>
-      <c r="P17" s="7">
-        <f t="shared" si="12"/>
+      <c r="Q17" s="7">
+        <f t="shared" si="11"/>
         <v>2040</v>
       </c>
-      <c r="Q17" s="7">
-        <f t="shared" si="12"/>
+      <c r="R17" s="7">
+        <f t="shared" si="11"/>
         <v>2045</v>
       </c>
-      <c r="R17" s="7">
-        <f t="shared" si="12"/>
+      <c r="S17" s="7">
+        <f t="shared" si="11"/>
         <v>2050</v>
       </c>
-      <c r="V17" s="4" t="s">
+      <c r="W17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="W17" s="4">
+      <c r="X17" s="4">
         <v>2022</v>
       </c>
-      <c r="X17" s="4">
+      <c r="Y17" s="4">
         <v>2025</v>
       </c>
-      <c r="Y17" s="4">
+      <c r="Z17" s="4">
         <v>2030</v>
       </c>
-      <c r="Z17" s="4">
+      <c r="AA17" s="4">
         <v>2035</v>
       </c>
-      <c r="AA17" s="4">
+      <c r="AB17" s="4">
         <v>2040</v>
       </c>
-      <c r="AB17" s="4">
+      <c r="AC17" s="4">
         <v>2045</v>
       </c>
-      <c r="AC17" s="4">
+      <c r="AD17" s="4">
         <v>2050</v>
       </c>
-      <c r="AD17" s="4" t="s">
+      <c r="AE17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AJ17">
+      <c r="AK17">
         <v>9</v>
       </c>
-      <c r="AK17" t="s">
+      <c r="AL17" t="s">
         <v>103</v>
       </c>
-      <c r="AL17" t="s">
+      <c r="AM17" t="s">
         <v>105</v>
       </c>
-      <c r="AM17" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN17" s="10">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>5</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.0.CF6.Y.Y</v>
+        <v>Hi.0.CF6.Y.Y.Y</v>
       </c>
       <c r="C18">
         <f t="shared" si="2"/>
@@ -6718,106 +6764,109 @@
         <v>Hi</v>
       </c>
       <c r="E18">
-        <f t="shared" ref="E18" si="13">E14</f>
+        <f t="shared" ref="E18" si="12">E14</f>
         <v>0</v>
       </c>
       <c r="F18" t="s">
         <v>147</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" ref="G18:G40" si="14">G10</f>
+        <f t="shared" ref="G18:G81" si="13">G10</f>
         <v>Y</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J18" t="s">
+      <c r="I18" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K18" t="s">
         <v>15</v>
       </c>
-      <c r="L18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
-        <v>0</v>
-      </c>
       <c r="M18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="N18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="O18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="P18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="Q18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="R18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$J18)</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="10" t="s">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <v>0</v>
+      </c>
+      <c r="S18" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <v>0</v>
+      </c>
+      <c r="W18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="W18" s="6">
-        <f t="shared" ref="W18:AC20" si="15">L18*W$14</f>
-        <v>0</v>
-      </c>
       <c r="X18" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="X18:AD20" si="14">M18*X$14</f>
         <v>0</v>
       </c>
       <c r="Y18" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" t="s">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="6">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AE18" t="s">
         <v>17</v>
       </c>
-      <c r="AF18" s="2"/>
-      <c r="AJ18">
+      <c r="AG18" s="2"/>
+      <c r="AK18">
         <v>10</v>
       </c>
-      <c r="AK18" t="s">
+      <c r="AL18" t="s">
         <v>106</v>
       </c>
-      <c r="AL18" t="s">
+      <c r="AM18" t="s">
         <v>107</v>
       </c>
-      <c r="AM18" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN18" s="10">
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>5</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.95.CF6.Y.Y</v>
+        <v>Lo.95.CF6.Y.Y.Y</v>
       </c>
       <c r="C19">
         <f t="shared" si="2"/>
@@ -6828,105 +6877,108 @@
         <v>Lo</v>
       </c>
       <c r="E19">
-        <f t="shared" ref="E19" si="16">E15</f>
+        <f t="shared" ref="E19" si="15">E15</f>
         <v>95</v>
       </c>
       <c r="F19" t="s">
         <v>147</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J19" t="s">
+      <c r="I19" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K19" t="s">
         <v>18</v>
       </c>
-      <c r="L19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+      <c r="M19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.4</v>
       </c>
-      <c r="M19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+      <c r="N19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.35</v>
       </c>
-      <c r="N19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+      <c r="O19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.33</v>
       </c>
-      <c r="O19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+      <c r="P19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.32</v>
       </c>
-      <c r="P19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+      <c r="Q19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.31</v>
       </c>
-      <c r="Q19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+      <c r="R19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.31</v>
       </c>
-      <c r="R19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$J19)</f>
+      <c r="S19" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.31</v>
       </c>
-      <c r="V19" s="10" t="s">
+      <c r="W19" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="W19" s="6">
-        <f t="shared" si="15"/>
+      <c r="X19" s="6">
+        <f t="shared" si="14"/>
         <v>91.704000000000008</v>
       </c>
-      <c r="X19" s="6">
-        <f t="shared" si="15"/>
-        <v>88.265100000000004</v>
-      </c>
       <c r="Y19" s="6">
-        <f t="shared" si="15"/>
-        <v>85.680193500000001</v>
+        <f t="shared" si="14"/>
+        <v>96.28919999999998</v>
       </c>
       <c r="Z19" s="6">
-        <f t="shared" si="15"/>
-        <v>85.468127999999993</v>
+        <f t="shared" si="14"/>
+        <v>95.704587000000018</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="15"/>
-        <v>93.457838999999993</v>
+        <f t="shared" si="14"/>
+        <v>97.573055999999994</v>
       </c>
       <c r="AB19" s="6">
-        <f t="shared" si="15"/>
-        <v>106.60589999999999</v>
+        <f t="shared" si="14"/>
+        <v>115.84507799999999</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="15"/>
-        <v>118.04826660000001</v>
-      </c>
-      <c r="AD19" t="s">
+        <f t="shared" si="14"/>
+        <v>142.1412</v>
+      </c>
+      <c r="AD19" s="6">
+        <f t="shared" si="14"/>
+        <v>165.0259332</v>
+      </c>
+      <c r="AE19" t="s">
         <v>17</v>
       </c>
-      <c r="AJ19">
+      <c r="AK19">
         <v>11</v>
       </c>
-      <c r="AK19" t="s">
+      <c r="AL19" t="s">
         <v>84</v>
       </c>
-      <c r="AL19" t="s">
+      <c r="AM19" t="s">
         <v>89</v>
       </c>
-      <c r="AM19" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN19" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>5</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.95.CF6.Y.Y</v>
+        <v>Hi.95.CF6.Y.Y.Y</v>
       </c>
       <c r="C20">
         <f t="shared" si="2"/>
@@ -6937,105 +6989,108 @@
         <v>Hi</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E40" si="17">E16</f>
+        <f t="shared" ref="E20:E83" si="16">E16</f>
         <v>95</v>
       </c>
       <c r="F20" t="s">
         <v>147</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H20" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J20" t="s">
+      <c r="I20" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K20" t="s">
         <v>21</v>
       </c>
-      <c r="L20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+      <c r="M20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.47</v>
       </c>
-      <c r="M20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+      <c r="N20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.52</v>
       </c>
-      <c r="N20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+      <c r="O20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.54</v>
       </c>
-      <c r="O20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+      <c r="P20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.53</v>
       </c>
-      <c r="P20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+      <c r="Q20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.52</v>
       </c>
-      <c r="Q20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+      <c r="R20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.5</v>
       </c>
-      <c r="R20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$J20)</f>
+      <c r="S20" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.48</v>
       </c>
-      <c r="V20" s="10" t="s">
+      <c r="W20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="W20" s="6">
-        <f t="shared" si="15"/>
+      <c r="X20" s="6">
+        <f t="shared" si="14"/>
         <v>107.75219999999999</v>
       </c>
-      <c r="X20" s="6">
-        <f t="shared" si="15"/>
-        <v>131.13672</v>
-      </c>
       <c r="Y20" s="6">
-        <f t="shared" si="15"/>
-        <v>140.20395300000001</v>
+        <f t="shared" si="14"/>
+        <v>143.05823999999998</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" si="15"/>
-        <v>141.55658700000001</v>
+        <f t="shared" si="14"/>
+        <v>156.60750600000003</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="15"/>
-        <v>156.767988</v>
+        <f t="shared" si="14"/>
+        <v>161.60537400000001</v>
       </c>
       <c r="AB20" s="6">
-        <f t="shared" si="15"/>
-        <v>171.94499999999999</v>
+        <f t="shared" si="14"/>
+        <v>194.320776</v>
       </c>
       <c r="AC20" s="6">
-        <f t="shared" si="15"/>
-        <v>182.78441279999998</v>
-      </c>
-      <c r="AD20" t="s">
+        <f t="shared" si="14"/>
+        <v>229.26</v>
+      </c>
+      <c r="AD20" s="6">
+        <f t="shared" si="14"/>
+        <v>255.52402559999999</v>
+      </c>
+      <c r="AE20" t="s">
         <v>17</v>
       </c>
-      <c r="AJ20">
+      <c r="AK20">
         <v>12</v>
       </c>
-      <c r="AK20" t="s">
+      <c r="AL20" t="s">
         <v>85</v>
       </c>
-      <c r="AL20" t="s">
+      <c r="AM20" t="s">
         <v>94</v>
       </c>
-      <c r="AM20" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN20" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>5</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.0.CF6.N.Y</v>
+        <v>Lo.0.CF6.N.Y.Y</v>
       </c>
       <c r="C21">
         <f t="shared" si="2"/>
@@ -7046,99 +7101,102 @@
         <v>Lo</v>
       </c>
       <c r="E21">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F21" t="s">
         <v>147</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J21" t="s">
+      <c r="I21" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+      <c r="M21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
         <v>0.01</v>
       </c>
-      <c r="M21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+      <c r="N21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
         <v>0.01</v>
       </c>
-      <c r="N21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+      <c r="O21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
         <v>0.01</v>
       </c>
-      <c r="O21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+      <c r="P21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
         <v>0.01</v>
       </c>
-      <c r="P21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+      <c r="Q21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
         <v>0.01</v>
       </c>
-      <c r="Q21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+      <c r="R21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
         <v>0.02</v>
       </c>
-      <c r="R21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$J$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$J21)</f>
+      <c r="S21" s="11">
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
         <v>0.02</v>
       </c>
-      <c r="V21" s="10" t="s">
+      <c r="W21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="W21" s="6">
-        <f>L21*W$14</f>
+      <c r="X21" s="6">
+        <f>M21*X$14</f>
         <v>2.2925999999999997</v>
       </c>
-      <c r="X21" s="6">
-        <f t="shared" ref="X21:AC21" si="18">W21</f>
+      <c r="Y21" s="6">
+        <f t="shared" ref="Y21:AD21" si="17">X21</f>
         <v>2.2925999999999997</v>
       </c>
-      <c r="Y21" s="6">
-        <f t="shared" si="18"/>
+      <c r="Z21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="Z21" s="6">
-        <f t="shared" si="18"/>
+      <c r="AA21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="AA21" s="6">
-        <f t="shared" si="18"/>
+      <c r="AB21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="AB21" s="6">
-        <f t="shared" si="18"/>
+      <c r="AC21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="AC21" s="6">
-        <f t="shared" si="18"/>
+      <c r="AD21" s="6">
+        <f t="shared" si="17"/>
         <v>2.2925999999999997</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AE21" t="s">
         <v>17</v>
       </c>
-      <c r="AF21" s="2" t="s">
+      <c r="AG21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AM21" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN21" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>5</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.0.CF6.N.Y</v>
+        <v>Hi.0.CF6.N.Y.Y</v>
       </c>
       <c r="C22">
         <f t="shared" si="2"/>
@@ -7149,65 +7207,68 @@
         <v>Hi</v>
       </c>
       <c r="E22">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F22" t="s">
         <v>147</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H22" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="V22" s="10" t="s">
+      <c r="I22" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W22" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="W22" s="6">
-        <f t="shared" ref="W22:AC22" si="19">W14-SUM(W19:W21)</f>
+      <c r="X22" s="6">
+        <f t="shared" ref="X22:AD22" si="18">X14-SUM(X19:X21)</f>
         <v>27.511200000000002</v>
       </c>
-      <c r="X22" s="6">
-        <f t="shared" si="19"/>
-        <v>30.491580000000027</v>
-      </c>
       <c r="Y22" s="6">
-        <f t="shared" si="19"/>
-        <v>31.460203500000006</v>
+        <f t="shared" si="18"/>
+        <v>33.471960000000024</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="19"/>
-        <v>37.770584999999983</v>
+        <f t="shared" si="18"/>
+        <v>35.409206999999981</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="19"/>
-        <v>48.958473000000026</v>
+        <f t="shared" si="18"/>
+        <v>43.444770000000005</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="19"/>
-        <v>63.046500000000037</v>
+        <f t="shared" si="18"/>
+        <v>61.235345999999993</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="19"/>
-        <v>77.675580600000046</v>
-      </c>
-      <c r="AD22" t="s">
+        <f t="shared" si="18"/>
+        <v>84.826199999999972</v>
+      </c>
+      <c r="AD22" s="6">
+        <f t="shared" si="18"/>
+        <v>109.4991612</v>
+      </c>
+      <c r="AE22" t="s">
         <v>17</v>
       </c>
-      <c r="AM22" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN22" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>5</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.95.CF6.N.Y</v>
+        <v>Lo.95.CF6.N.Y.Y</v>
       </c>
       <c r="C23">
         <f t="shared" si="2"/>
@@ -7218,34 +7279,37 @@
         <v>Lo</v>
       </c>
       <c r="E23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F23" t="s">
         <v>147</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="V23" t="s">
+      <c r="I23" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W23" t="s">
         <v>26</v>
       </c>
-      <c r="AM23" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN23" s="10">
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:40" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>5</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.95.CF6.N.Y</v>
+        <v>Hi.95.CF6.N.Y.Y</v>
       </c>
       <c r="C24">
         <f t="shared" si="2"/>
@@ -7256,91 +7320,94 @@
         <v>Hi</v>
       </c>
       <c r="E24">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F24" t="s">
         <v>147</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="I24" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K24" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="11">
-        <f t="shared" ref="L24:R24" si="20">SUMIF($K$2:$K$6,$E$5,L$2:L$6)</f>
-        <v>0</v>
-      </c>
       <c r="M24" s="11">
-        <f t="shared" si="20"/>
+        <f>SUMIF($L$2:$L$6,$E$5,M$2:M$6)</f>
         <v>0</v>
       </c>
       <c r="N24" s="11">
-        <f t="shared" si="20"/>
+        <f>SUMIF($L$2:$L$6,$E$5,N$2:N$6)</f>
         <v>0</v>
       </c>
       <c r="O24" s="11">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>SUMIF($L$2:$L$6,$E$5,O$2:O$6)</f>
+        <v>3</v>
       </c>
       <c r="P24" s="11">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>SUMIF($L$2:$L$6,$E$5,P$2:P$6)</f>
+        <v>35</v>
       </c>
       <c r="Q24" s="11">
-        <f t="shared" si="20"/>
-        <v>0</v>
+        <f>SUMIF($L$2:$L$6,$E$5,Q$2:Q$6)</f>
+        <v>60</v>
       </c>
       <c r="R24" s="11">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="V24" t="s">
+        <f>SUMIF($L$2:$L$6,$E$5,R$2:R$6)</f>
+        <v>80</v>
+      </c>
+      <c r="S24" s="11">
+        <f>SUMIF($L$2:$L$6,$E$5,S$2:S$6)</f>
+        <v>95</v>
+      </c>
+      <c r="W24" t="s">
         <v>28</v>
       </c>
-      <c r="X24">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="11">
-        <f>N24/1000</f>
+      <c r="Y24">
         <v>0</v>
       </c>
       <c r="Z24" s="11">
         <f>O24/1000</f>
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="AA24" s="11">
         <f>P24/1000</f>
-        <v>0</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="AB24" s="11">
         <f>Q24/1000</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AC24" s="11">
         <f>R24/1000</f>
-        <v>0</v>
-      </c>
-      <c r="AD24" t="s">
+        <v>0.08</v>
+      </c>
+      <c r="AD24" s="11">
+        <f>S24/1000</f>
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="AE24" t="s">
         <v>29</v>
       </c>
-      <c r="AM24" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN24" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:39" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:40" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>5</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.0.CF1.Y.N</v>
+        <v>Lo.0.CF1.Y.N.Y</v>
       </c>
       <c r="C25">
         <f t="shared" si="2"/>
@@ -7351,7 +7418,7 @@
         <v>Lo</v>
       </c>
       <c r="E25">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F25" t="str">
@@ -7359,24 +7426,27 @@
         <v>CF1</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H25" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AM25" s="10">
-        <f t="shared" si="9"/>
+      <c r="I25" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN25" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:40" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A26">
         <v>5</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.0.CF1.Y.N</v>
+        <v>Hi.0.CF1.Y.N.Y</v>
       </c>
       <c r="C26">
         <f t="shared" si="2"/>
@@ -7387,35 +7457,38 @@
         <v>Hi</v>
       </c>
       <c r="E26">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" ref="F26:F40" si="21">F10</f>
+        <f t="shared" ref="F26:F86" si="19">F10</f>
         <v>CF1</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="V26" s="5" t="s">
+      <c r="I26" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W26" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AM26" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN26" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:40" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27">
         <v>5</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.95.CF1.Y.N</v>
+        <v>Lo.95.CF1.Y.N.Y</v>
       </c>
       <c r="C27">
         <f t="shared" si="2"/>
@@ -7426,69 +7499,72 @@
         <v>Lo</v>
       </c>
       <c r="E27">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF1</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="V27" s="4" t="s">
+      <c r="I27" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="W27" s="4">
-        <f t="shared" ref="W27:AC27" si="22">W17</f>
+      <c r="X27" s="4">
+        <f t="shared" ref="X27:AD27" si="20">X17</f>
         <v>2022</v>
       </c>
-      <c r="X27" s="4">
-        <f t="shared" si="22"/>
+      <c r="Y27" s="4">
+        <f t="shared" si="20"/>
         <v>2025</v>
       </c>
-      <c r="Y27" s="4">
-        <f t="shared" si="22"/>
+      <c r="Z27" s="4">
+        <f t="shared" si="20"/>
         <v>2030</v>
       </c>
-      <c r="Z27" s="4">
-        <f t="shared" si="22"/>
+      <c r="AA27" s="4">
+        <f t="shared" si="20"/>
         <v>2035</v>
       </c>
-      <c r="AA27" s="4">
-        <f t="shared" si="22"/>
+      <c r="AB27" s="4">
+        <f t="shared" si="20"/>
         <v>2040</v>
       </c>
-      <c r="AB27" s="4">
-        <f t="shared" si="22"/>
+      <c r="AC27" s="4">
+        <f t="shared" si="20"/>
         <v>2045</v>
       </c>
-      <c r="AC27" s="4">
-        <f t="shared" si="22"/>
+      <c r="AD27" s="4">
+        <f t="shared" si="20"/>
         <v>2050</v>
       </c>
-      <c r="AD27" s="4" t="s">
+      <c r="AE27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AE27" s="4" t="s">
+      <c r="AF27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AM27" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN27" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:40" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A28">
         <v>5</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.95.CF1.Y.N</v>
+        <v>Hi.95.CF1.Y.N.Y</v>
       </c>
       <c r="C28">
         <f t="shared" si="2"/>
@@ -7499,54 +7575,57 @@
         <v>Hi</v>
       </c>
       <c r="E28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF1</v>
       </c>
       <c r="G28" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="T28" s="3">
-        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,Veda!$V$11)</f>
+      <c r="I28" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="U28" s="3">
+        <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,Veda!$W$11)</f>
         <v>10.76</v>
       </c>
-      <c r="V28" t="s">
+      <c r="W28" t="s">
         <v>32</v>
       </c>
-      <c r="W28" s="3">
-        <f>T28</f>
+      <c r="X28" s="3">
+        <f>U28</f>
         <v>10.76</v>
       </c>
-      <c r="Y28" s="6"/>
       <c r="Z28" s="6"/>
       <c r="AA28" s="6"/>
       <c r="AB28" s="6"/>
       <c r="AC28" s="6"/>
-      <c r="AD28" t="s">
+      <c r="AD28" s="6"/>
+      <c r="AE28" t="s">
         <v>33</v>
       </c>
-      <c r="AE28" t="s">
+      <c r="AF28" t="s">
         <v>34</v>
       </c>
-      <c r="AM28" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN28" s="10">
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:40" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29">
         <v>5</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.0.CF1.N.N</v>
+        <v>Lo.0.CF1.N.N.Y</v>
       </c>
       <c r="C29">
         <f t="shared" si="2"/>
@@ -7557,54 +7636,57 @@
         <v>Lo</v>
       </c>
       <c r="E29">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF1</v>
       </c>
       <c r="G29" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="T29" s="3">
-        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,Veda!$V$11)</f>
+      <c r="I29" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="U29" s="3">
+        <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,Veda!$W$11)</f>
         <v>-12.27</v>
       </c>
-      <c r="V29" t="s">
+      <c r="W29" t="s">
         <v>35</v>
       </c>
-      <c r="W29" s="3">
-        <f>-1*T29</f>
+      <c r="X29" s="3">
+        <f>-1*U29</f>
         <v>12.27</v>
       </c>
-      <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
       <c r="AA29" s="6"/>
       <c r="AB29" s="6"/>
       <c r="AC29" s="6"/>
-      <c r="AD29" t="s">
+      <c r="AD29" s="6"/>
+      <c r="AE29" t="s">
         <v>33</v>
       </c>
-      <c r="AE29" t="s">
+      <c r="AF29" t="s">
         <v>34</v>
       </c>
-      <c r="AM29" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN29" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:40" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>5</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.0.CF1.N.N</v>
+        <v>Hi.0.CF1.N.N.Y</v>
       </c>
       <c r="C30">
         <f t="shared" si="2"/>
@@ -7615,32 +7697,35 @@
         <v>Hi</v>
       </c>
       <c r="E30">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF1</v>
       </c>
       <c r="G30" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AM30" s="10">
-        <f t="shared" si="9"/>
+      <c r="I30" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN30" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>5</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.95.CF1.N.N</v>
+        <v>Lo.95.CF1.N.N.Y</v>
       </c>
       <c r="C31">
         <f t="shared" si="2"/>
@@ -7651,32 +7736,35 @@
         <v>Lo</v>
       </c>
       <c r="E31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF1</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H31" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AM31" s="10">
-        <f t="shared" si="9"/>
+      <c r="I31" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN31" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:40" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A32">
         <v>5</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.95.CF1.N.N</v>
+        <v>Hi.95.CF1.N.N.Y</v>
       </c>
       <c r="C32">
         <f t="shared" si="2"/>
@@ -7687,36 +7775,39 @@
         <v>Hi</v>
       </c>
       <c r="E32">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF1</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H32" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="V32" s="5" t="str">
+      <c r="I32" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W32" s="5" t="str">
         <f>IF($G$5="N","~TFM_UPD","DEF correction active")</f>
         <v>DEF correction active</v>
       </c>
-      <c r="AM32" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN32" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:39" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:40" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33">
         <v>5</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.0.CF6.Y.N</v>
+        <v>Lo.0.CF6.Y.N.Y</v>
       </c>
       <c r="C33">
         <f t="shared" si="2"/>
@@ -7727,44 +7818,47 @@
         <v>Lo</v>
       </c>
       <c r="E33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF6</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H33" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="V33" s="4" t="s">
+      <c r="I33" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W33" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="W33" s="4" t="s">
+      <c r="X33" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="X33" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="Y33" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z33" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AM33" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN33" s="10">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>5</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.0.CF6.Y.N</v>
+        <v>Hi.0.CF6.Y.N.Y</v>
       </c>
       <c r="C34">
         <f t="shared" si="2"/>
@@ -7775,44 +7869,47 @@
         <v>Hi</v>
       </c>
       <c r="E34">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF6</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="V34" t="s">
+      <c r="I34" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="W34" t="s">
+        <v>168</v>
+      </c>
+      <c r="X34" t="s">
         <v>169</v>
       </c>
-      <c r="W34" t="s">
-        <v>170</v>
-      </c>
-      <c r="X34" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="AM34" s="10">
-        <f t="shared" si="9"/>
+      <c r="Y34" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>5</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.95.CF6.Y.N</v>
+        <v>Lo.95.CF6.Y.N.Y</v>
       </c>
       <c r="C35">
         <f t="shared" si="2"/>
@@ -7823,32 +7920,35 @@
         <v>Lo</v>
       </c>
       <c r="E35">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF6</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H35" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="AM35" s="10">
-        <f t="shared" si="9"/>
+      <c r="I35" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN35" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>5</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.95.CF6.Y.N</v>
+        <v>Hi.95.CF6.Y.N.Y</v>
       </c>
       <c r="C36">
         <f t="shared" si="2"/>
@@ -7859,35 +7959,38 @@
         <v>Hi</v>
       </c>
       <c r="E36">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF6</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Y</v>
       </c>
       <c r="H36" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="I36" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AM36" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN36" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:40" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A37">
         <v>5</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.0.CF6.N.N</v>
+        <v>Lo.0.CF6.N.N.Y</v>
       </c>
       <c r="C37">
         <f t="shared" si="2"/>
@@ -7898,70 +8001,73 @@
         <v>Lo</v>
       </c>
       <c r="E37">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF6</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H37" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="J37" t="s">
+      <c r="I37" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K37" t="s">
         <v>74</v>
       </c>
-      <c r="L37" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$J$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J37)</f>
-        <v>1</v>
-      </c>
       <c r="M37" s="11">
-        <f>L37</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$K$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K37)</f>
         <v>1</v>
       </c>
       <c r="N37" s="11">
-        <f>M37*(1+$T37)^5</f>
+        <f>M37</f>
+        <v>1</v>
+      </c>
+      <c r="O37" s="11">
+        <f>N37*(1+$U37)^5</f>
         <v>1.0510100500999999</v>
       </c>
-      <c r="O37" s="11">
-        <f t="shared" ref="O37:R37" si="23">N37*(1+$T37)^5</f>
+      <c r="P37" s="11">
+        <f t="shared" ref="P37:S37" si="21">O37*(1+$U37)^5</f>
         <v>1.1046221254112043</v>
       </c>
-      <c r="P37" s="11">
-        <f t="shared" si="23"/>
+      <c r="Q37" s="11">
+        <f t="shared" si="21"/>
         <v>1.1609689553699982</v>
       </c>
-      <c r="Q37" s="11">
-        <f t="shared" si="23"/>
+      <c r="R37" s="11">
+        <f t="shared" si="21"/>
         <v>1.2201900399479664</v>
       </c>
-      <c r="R37" s="11">
-        <f t="shared" si="23"/>
+      <c r="S37" s="11">
+        <f t="shared" si="21"/>
         <v>1.2824319950172332</v>
       </c>
-      <c r="T37">
+      <c r="U37">
         <v>0.01</v>
       </c>
-      <c r="V37" s="5" t="str">
+      <c r="W37" s="5" t="str">
         <f>IF($G$5="N","~TFM_INS: limtype=LO","DEF correction active")</f>
         <v>DEF correction active</v>
       </c>
-      <c r="AM37" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN37" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:39" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:40" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38">
         <v>5</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.0.CF6.N.N</v>
+        <v>Hi.0.CF6.N.N.Y</v>
       </c>
       <c r="C38">
         <f t="shared" si="2"/>
@@ -7972,78 +8078,81 @@
         <v>Hi</v>
       </c>
       <c r="E38">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF6</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H38" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="J38" t="s">
+      <c r="I38" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K38" t="s">
         <v>75</v>
       </c>
-      <c r="L38" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$J$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J38)</f>
-        <v>1</v>
-      </c>
       <c r="M38" s="11">
-        <f t="shared" ref="M38:R38" si="24">L38</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$K$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K38)</f>
         <v>1</v>
       </c>
       <c r="N38" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="N38:S38" si="22">M38</f>
         <v>1</v>
       </c>
       <c r="O38" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="P38" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="Q38" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="R38" s="11">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="V38" s="4" t="s">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="S38" s="11">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
+      <c r="W38" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="W38" s="4" t="s">
+      <c r="X38" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="X38" s="4" t="s">
+      <c r="Y38" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="Y38" s="4" t="s">
+      <c r="Z38" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="Z38" s="4" t="s">
+      <c r="AA38" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="AM38" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN38" s="10">
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>5</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="1"/>
-        <v>Lo.95.CF6.N.N</v>
+        <v>Lo.95.CF6.N.N.Y</v>
       </c>
       <c r="C39">
         <f t="shared" si="2"/>
@@ -8054,78 +8163,81 @@
         <v>Lo</v>
       </c>
       <c r="E39">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF6</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H39" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="J39" t="s">
+      <c r="I39" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K39" t="s">
         <v>76</v>
       </c>
-      <c r="L39" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$J$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J39)</f>
-        <v>1</v>
-      </c>
       <c r="M39" s="11">
-        <f t="shared" ref="M39:R39" si="25">L39</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$K$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K39)</f>
         <v>1</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="N39:S39" si="23">M39</f>
         <v>1</v>
       </c>
       <c r="O39" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P39" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="Q39" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="R39" s="11">
-        <f t="shared" si="25"/>
-        <v>1</v>
-      </c>
-      <c r="V39" t="s">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="S39" s="11">
+        <f t="shared" si="23"/>
+        <v>1</v>
+      </c>
+      <c r="W39" t="s">
         <v>160</v>
       </c>
-      <c r="W39" t="s">
+      <c r="X39" t="s">
         <v>161</v>
       </c>
-      <c r="X39">
-        <v>0</v>
-      </c>
       <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
         <v>-13</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AA39" t="s">
         <v>162</v>
       </c>
-      <c r="AM39" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN39" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>5</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="1"/>
-        <v>Hi.95.CF6.N.N</v>
+        <v>Hi.95.CF6.N.N.Y</v>
       </c>
       <c r="C40">
         <f t="shared" si="2"/>
@@ -8136,542 +8248,1638 @@
         <v>Hi</v>
       </c>
       <c r="E40">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="19"/>
         <v>CF6</v>
       </c>
       <c r="G40" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>N</v>
       </c>
       <c r="H40" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="J40" t="s">
+      <c r="I40" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K40" t="s">
         <v>77</v>
       </c>
-      <c r="L40" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$J$36,ar6_r10!$C$2:$C$999,Veda!L$17,ar6_r10!$M$2:$M$999,Veda!$J40)</f>
-        <v>1</v>
-      </c>
       <c r="M40" s="11">
-        <f t="shared" ref="M40:R40" si="26">L40</f>
+        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,Veda!$K$36,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K40)</f>
         <v>1</v>
       </c>
       <c r="N40" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="N40:S40" si="24">M40</f>
         <v>1</v>
       </c>
       <c r="O40" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="P40" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q40" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R40" s="11">
-        <f t="shared" si="26"/>
-        <v>1</v>
-      </c>
-      <c r="V40" t="s">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="S40" s="11">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
+      <c r="W40" t="s">
         <v>163</v>
       </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
       <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
         <v>-13</v>
       </c>
-      <c r="Z40" t="s">
+      <c r="AA40" t="s">
         <v>164</v>
       </c>
-      <c r="AM40" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN40" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>5</v>
       </c>
-      <c r="AM41" s="10">
-        <f t="shared" si="9"/>
+      <c r="B41" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF1.Y.Y.N</v>
+      </c>
+      <c r="C41">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G41" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H41" s="15" t="str">
+        <f>H9</f>
+        <v>Y</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN41" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>5</v>
       </c>
-      <c r="AM42" s="10">
-        <f t="shared" si="9"/>
+      <c r="B42" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF1.Y.Y.N</v>
+      </c>
+      <c r="C42">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H42" s="15" t="str">
+        <f t="shared" ref="H42:H86" si="25">H10</f>
+        <v>Y</v>
+      </c>
+      <c r="I42" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN42" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>5</v>
       </c>
-      <c r="J43" t="s">
+      <c r="B43" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF1.Y.Y.N</v>
+      </c>
+      <c r="C43">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H43" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="K43" t="s">
         <v>101</v>
       </c>
-      <c r="AM43" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN43" s="10">
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>5</v>
       </c>
-      <c r="J44" t="s">
+      <c r="B44" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF1.Y.Y.N</v>
+      </c>
+      <c r="C44">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G44" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H44" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I44" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="K44" t="s">
         <v>13</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>87</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>2022</v>
       </c>
-      <c r="M44">
-        <f>M17</f>
+      <c r="N44">
+        <f>N17</f>
         <v>2025</v>
       </c>
-      <c r="N44">
-        <f t="shared" ref="N44:R44" si="27">N17</f>
+      <c r="O44">
+        <f t="shared" ref="O44:S44" si="26">O17</f>
         <v>2030</v>
       </c>
-      <c r="O44">
-        <f t="shared" si="27"/>
+      <c r="P44">
+        <f t="shared" si="26"/>
         <v>2035</v>
       </c>
-      <c r="P44">
-        <f t="shared" si="27"/>
+      <c r="Q44">
+        <f t="shared" si="26"/>
         <v>2040</v>
       </c>
-      <c r="Q44">
-        <f t="shared" si="27"/>
+      <c r="R44">
+        <f t="shared" si="26"/>
         <v>2045</v>
       </c>
-      <c r="R44">
-        <f t="shared" si="27"/>
+      <c r="S44">
+        <f t="shared" si="26"/>
         <v>2050</v>
       </c>
-      <c r="U44" t="s">
+      <c r="V44" t="s">
         <v>82</v>
       </c>
-      <c r="V44" t="s">
+      <c r="W44" t="s">
         <v>83</v>
       </c>
-      <c r="AM44" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN44" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>5</v>
       </c>
-      <c r="J45" t="s">
+      <c r="B45" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF1.N.Y.N</v>
+      </c>
+      <c r="C45">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H45" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I45" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="K45" t="s">
         <v>78</v>
       </c>
-      <c r="K45" t="str">
-        <f>J45</f>
+      <c r="L45" t="str">
+        <f>K45</f>
         <v>Gas</v>
       </c>
-      <c r="L45">
-        <f t="shared" ref="L45:R48" si="28">AVERAGE($U45:$V45)*L37</f>
+      <c r="M45">
+        <f t="shared" ref="M45:S48" si="27">AVERAGE($V45:$W45)*M37</f>
         <v>45</v>
       </c>
-      <c r="M45">
-        <f t="shared" si="28"/>
+      <c r="N45">
+        <f t="shared" si="27"/>
         <v>45</v>
       </c>
-      <c r="N45">
-        <f t="shared" si="28"/>
+      <c r="O45">
+        <f t="shared" si="27"/>
         <v>47.295452254499999</v>
       </c>
-      <c r="O45">
-        <f t="shared" si="28"/>
+      <c r="P45">
+        <f t="shared" si="27"/>
         <v>49.707995643504191</v>
       </c>
-      <c r="P45">
-        <f t="shared" si="28"/>
+      <c r="Q45">
+        <f t="shared" si="27"/>
         <v>52.243602991649922</v>
       </c>
-      <c r="Q45">
-        <f t="shared" si="28"/>
+      <c r="R45">
+        <f t="shared" si="27"/>
         <v>54.90855179765849</v>
       </c>
-      <c r="R45">
-        <f t="shared" si="28"/>
+      <c r="S45">
+        <f t="shared" si="27"/>
         <v>57.709439775775493</v>
       </c>
-      <c r="U45">
-        <f>HLOOKUP($J45&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="V45">
+        <f>HLOOKUP($K45&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>45</v>
       </c>
-      <c r="V45">
-        <f>HLOOKUP($J45&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="W45">
+        <f>HLOOKUP($K45&amp;"_"&amp;W$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>45</v>
       </c>
-      <c r="AM45" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN45" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>5</v>
       </c>
-      <c r="J46" t="s">
+      <c r="B46" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF1.N.Y.N</v>
+      </c>
+      <c r="C46">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H46" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I46" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="K46" t="s">
         <v>79</v>
       </c>
-      <c r="K46" t="str">
-        <f t="shared" ref="K46:K48" si="29">J46</f>
+      <c r="L46" t="str">
+        <f t="shared" ref="L46:L48" si="28">K46</f>
         <v>Coal</v>
       </c>
-      <c r="L46">
-        <f t="shared" si="28"/>
+      <c r="M46">
+        <f t="shared" si="27"/>
         <v>4.68</v>
       </c>
-      <c r="M46">
-        <f t="shared" si="28"/>
+      <c r="N46">
+        <f t="shared" si="27"/>
         <v>4.68</v>
       </c>
-      <c r="N46">
-        <f t="shared" si="28"/>
+      <c r="O46">
+        <f t="shared" si="27"/>
         <v>4.68</v>
       </c>
-      <c r="O46">
-        <f t="shared" si="28"/>
+      <c r="P46">
+        <f t="shared" si="27"/>
         <v>4.68</v>
       </c>
-      <c r="P46">
-        <f t="shared" si="28"/>
+      <c r="Q46">
+        <f t="shared" si="27"/>
         <v>4.68</v>
       </c>
-      <c r="Q46">
-        <f t="shared" si="28"/>
+      <c r="R46">
+        <f t="shared" si="27"/>
         <v>4.68</v>
       </c>
-      <c r="R46">
-        <f t="shared" si="28"/>
+      <c r="S46">
+        <f t="shared" si="27"/>
         <v>4.68</v>
       </c>
-      <c r="U46">
-        <f>HLOOKUP($J46&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="V46">
+        <f>HLOOKUP($K46&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>4.32</v>
       </c>
-      <c r="V46">
-        <f>HLOOKUP($J46&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="W46">
+        <f>HLOOKUP($K46&amp;"_"&amp;W$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>5.04</v>
       </c>
-      <c r="AM46" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN46" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>5</v>
       </c>
-      <c r="J47" t="s">
+      <c r="B47" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF1.N.Y.N</v>
+      </c>
+      <c r="C47">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H47" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="K47" t="s">
         <v>80</v>
       </c>
-      <c r="K47" t="str">
-        <f t="shared" si="29"/>
+      <c r="L47" t="str">
+        <f t="shared" si="28"/>
         <v>Oil</v>
       </c>
-      <c r="L47">
-        <f t="shared" si="28"/>
+      <c r="M47">
+        <f t="shared" si="27"/>
         <v>79.2</v>
       </c>
-      <c r="M47">
-        <f t="shared" si="28"/>
+      <c r="N47">
+        <f t="shared" si="27"/>
         <v>79.2</v>
       </c>
-      <c r="N47">
-        <f t="shared" si="28"/>
+      <c r="O47">
+        <f t="shared" si="27"/>
         <v>79.2</v>
       </c>
-      <c r="O47">
-        <f t="shared" si="28"/>
+      <c r="P47">
+        <f t="shared" si="27"/>
         <v>79.2</v>
       </c>
-      <c r="P47">
-        <f t="shared" si="28"/>
+      <c r="Q47">
+        <f t="shared" si="27"/>
         <v>79.2</v>
       </c>
-      <c r="Q47">
-        <f t="shared" si="28"/>
+      <c r="R47">
+        <f t="shared" si="27"/>
         <v>79.2</v>
       </c>
-      <c r="R47">
-        <f t="shared" si="28"/>
+      <c r="S47">
+        <f t="shared" si="27"/>
         <v>79.2</v>
       </c>
-      <c r="U47">
-        <f>HLOOKUP($J47&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="V47">
+        <f>HLOOKUP($K47&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>79.2</v>
       </c>
-      <c r="V47">
-        <f>HLOOKUP($J47&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="W47">
+        <f>HLOOKUP($K47&amp;"_"&amp;W$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>79.2</v>
       </c>
-      <c r="AM47" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN47" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:40" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>5</v>
       </c>
-      <c r="J48" t="s">
+      <c r="B48" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF1.N.Y.N</v>
+      </c>
+      <c r="C48">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H48" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="K48" t="s">
         <v>81</v>
       </c>
-      <c r="K48" t="str">
-        <f t="shared" si="29"/>
+      <c r="L48" t="str">
+        <f t="shared" si="28"/>
         <v>Bioenergy</v>
       </c>
-      <c r="L48">
-        <f t="shared" si="28"/>
+      <c r="M48">
+        <f t="shared" si="27"/>
         <v>22</v>
       </c>
-      <c r="R48" t="e">
-        <f>VLOOKUP($D$5,$AN$9:$AP$15,3,FALSE)*L48</f>
+      <c r="S48" t="e">
+        <f>VLOOKUP($D$5,$AO$9:$AQ$15,3,FALSE)*M48</f>
         <v>#N/A</v>
       </c>
-      <c r="U48">
-        <f>HLOOKUP($J48&amp;"_"&amp;U$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="V48">
+        <f>HLOOKUP($K48&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>18</v>
       </c>
-      <c r="V48">
-        <f>HLOOKUP($J48&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
+      <c r="W48">
+        <f>HLOOKUP($K48&amp;"_"&amp;W$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
         <v>26</v>
       </c>
-      <c r="AM48" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN48" s="10">
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM49" s="10">
-        <f t="shared" si="9"/>
+    <row r="49" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="B49" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF6.Y.Y.N</v>
+      </c>
+      <c r="C49">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H49" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN49" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM50" s="10">
-        <f t="shared" si="9"/>
+    <row r="50" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF6.Y.Y.N</v>
+      </c>
+      <c r="C50">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F50" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H50" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN50" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="22:39" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="V51" s="5" t="str">
+    <row r="51" spans="1:40" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF6.Y.Y.N</v>
+      </c>
+      <c r="C51">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F51" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H51" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I51" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="W51" s="5" t="str">
         <f>IF($H$5="N","~TFM_INS: limtype=LO","GAS available")</f>
         <v>GAS available</v>
       </c>
-      <c r="AM51" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN51" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="22:39" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="V52" s="4" t="s">
+    <row r="52" spans="1:40" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A52">
+        <v>5</v>
+      </c>
+      <c r="B52" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF6.Y.Y.N</v>
+      </c>
+      <c r="C52">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F52" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H52" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I52" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="W52" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="W52" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="X52" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y52" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="Y52" s="4" t="s">
+      <c r="Z52" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="Z52" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="AM52" s="10">
-        <f t="shared" si="9"/>
+      <c r="AA52" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN52" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="V53" t="s">
-        <v>167</v>
-      </c>
-      <c r="W53" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y53">
+    <row r="53" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>5</v>
+      </c>
+      <c r="B53" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF6.N.Y.N</v>
+      </c>
+      <c r="C53">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F53" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H53" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I53" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="W53" t="s">
+        <v>166</v>
+      </c>
+      <c r="X53" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z53">
         <v>2100</v>
       </c>
-      <c r="Z53" t="s">
+      <c r="AA53" t="s">
         <v>165</v>
       </c>
-      <c r="AM53" s="10">
-        <f t="shared" si="9"/>
+      <c r="AN53" s="10">
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM54" s="10">
-        <f t="shared" si="9"/>
+    <row r="54" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>5</v>
+      </c>
+      <c r="B54" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF6.N.Y.N</v>
+      </c>
+      <c r="C54">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H54" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN54" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM55" s="10">
-        <f t="shared" si="9"/>
+    <row r="55" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF6.N.Y.N</v>
+      </c>
+      <c r="C55">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F55" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H55" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I55" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN55" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM56" s="10">
-        <f t="shared" si="9"/>
+    <row r="56" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>5</v>
+      </c>
+      <c r="B56" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF6.N.Y.N</v>
+      </c>
+      <c r="C56">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F56" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H56" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>Y</v>
+      </c>
+      <c r="I56" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN56" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM57" s="10">
-        <f t="shared" si="9"/>
+    <row r="57" spans="1:40" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A57">
+        <v>5</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF1.Y.N.N</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H57" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="W57" s="5" t="str">
+        <f>IF($I$5="N","~TFM_UPD","Transmission costs active")</f>
+        <v>~TFM_UPD</v>
+      </c>
+      <c r="AN57" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM58" s="10">
-        <f t="shared" si="9"/>
+    <row r="58" spans="1:40" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A58">
+        <v>5</v>
+      </c>
+      <c r="B58" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF1.Y.N.N</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H58" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I58" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="W58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="X58" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y58" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z58" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA58" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="AN58" s="10">
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM59" s="10">
-        <f t="shared" si="9"/>
+    <row r="59" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>5</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF1.Y.N.N</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H59" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I59" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="W59" t="s">
+        <v>174</v>
+      </c>
+      <c r="X59" s="20"/>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>175</v>
+      </c>
+      <c r="AN59" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM60" s="10">
-        <f t="shared" si="9"/>
+    <row r="60" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>5</v>
+      </c>
+      <c r="B60" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF1.Y.N.N</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H60" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I60" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN60" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM61" s="10">
-        <f t="shared" si="9"/>
+    <row r="61" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>5</v>
+      </c>
+      <c r="B61" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF1.N.N.N</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H61" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I61" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN61" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM62" s="10">
-        <f t="shared" si="9"/>
+    <row r="62" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF1.N.N.N</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G62" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H62" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN62" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM63" s="10">
-        <f t="shared" si="9"/>
+    <row r="63" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF1.N.N.N</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G63" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H63" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I63" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN63" s="10">
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="22:39" x14ac:dyDescent="0.45">
-      <c r="AM64" s="10">
-        <f t="shared" si="9"/>
+    <row r="64" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF1.N.N.N</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="2"/>
+        <v>56</v>
+      </c>
+      <c r="D64" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="19"/>
+        <v>CF1</v>
+      </c>
+      <c r="G64" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H64" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN64" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM65" s="10">
-        <f t="shared" si="9"/>
+    <row r="65" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF6.Y.N.N</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="2"/>
+        <v>57</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F65" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G65" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H65" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I65" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN65" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM66" s="10">
-        <f t="shared" si="9"/>
+    <row r="66" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF6.Y.N.N</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="2"/>
+        <v>58</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F66" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G66" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H66" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I66" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN66" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM67" s="10">
-        <f t="shared" si="9"/>
+    <row r="67" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF6.Y.N.N</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="2"/>
+        <v>59</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F67" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G67" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H67" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I67" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN67" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM68" s="10">
-        <f t="shared" si="9"/>
+    <row r="68" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF6.Y.N.N</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F68" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G68" t="str">
+        <f t="shared" si="13"/>
+        <v>Y</v>
+      </c>
+      <c r="H68" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN68" s="10">
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM69" s="10">
-        <f t="shared" si="9"/>
+    <row r="69" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.0.CF6.N.N.N</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="2"/>
+        <v>61</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F69" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G69" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H69" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I69" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN69" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM70" s="10">
-        <f t="shared" si="9"/>
+    <row r="70" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.0.CF6.N.N.N</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="2"/>
+        <v>62</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F70" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G70" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H70" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I70" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN70" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM71" s="10">
-        <f t="shared" si="9"/>
+    <row r="71" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71" t="str">
+        <f t="shared" si="1"/>
+        <v>Lo.95.CF6.N.N.N</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="3"/>
+        <v>Lo</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F71" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G71" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H71" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I71" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN71" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM72" s="10">
-        <f t="shared" si="9"/>
+    <row r="72" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi.95.CF6.N.N.N</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="3"/>
+        <v>Hi</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="16"/>
+        <v>95</v>
+      </c>
+      <c r="F72" t="str">
+        <f t="shared" si="19"/>
+        <v>CF6</v>
+      </c>
+      <c r="G72" t="str">
+        <f t="shared" si="13"/>
+        <v>N</v>
+      </c>
+      <c r="H72" s="15" t="str">
+        <f t="shared" si="25"/>
+        <v>N</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN72" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM73" s="10">
-        <f t="shared" si="9"/>
+    <row r="73" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AN73" s="10">
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM74" s="10">
-        <f t="shared" si="9"/>
+    <row r="74" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AN74" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM75" s="10">
-        <f t="shared" si="9"/>
+    <row r="75" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AN75" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM76" s="10">
-        <f t="shared" si="9"/>
+    <row r="76" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AN76" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM77" s="10">
-        <f t="shared" si="9"/>
+    <row r="77" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AN77" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="39:39" x14ac:dyDescent="0.45">
-      <c r="AM78" s="10">
-        <f t="shared" si="9"/>
+    <row r="78" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AN78" s="10">
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
     </row>
@@ -8700,7 +9908,7 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="str">
         <f>Veda!F5</f>
-        <v>CF1</v>
+        <v>CF6</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.45">
@@ -8907,11 +10115,11 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G14" s="11">
         <f>SUMIF($A$7:$A$12,$A$1,G7:G12)</f>
-        <v>1</v>
+        <v>0.57142857142857151</v>
       </c>
       <c r="H14" s="11">
         <f>SUMIF($A$7:$A$12,$A$1,H7:H12)</f>
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
@@ -8933,11 +10141,11 @@
     <row r="18" spans="7:9" x14ac:dyDescent="0.45">
       <c r="G18" t="str">
         <f>"*"&amp;G14</f>
-        <v>*1</v>
+        <v>*0.571428571428572</v>
       </c>
       <c r="H18" t="str">
         <f>"*"&amp;H14</f>
-        <v>*0.5</v>
+        <v>*1.5</v>
       </c>
       <c r="I18" t="s">
         <v>140</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD85998-77EF-4275-ABA1-3DBBC94FE875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EFC434-03FE-4787-A7DA-6FB3EE52BF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -632,7 +632,7 @@
     <t>grid, aggregators</t>
   </si>
   <si>
-    <t>33-64</t>
+    <t>1-64</t>
   </si>
 </sst>
 </file>
@@ -5968,7 +5968,7 @@
     <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
-        <v>~Inputcell: 33-64</v>
+        <v>~Inputcell: 1-64</v>
       </c>
       <c r="L2" t="s">
         <v>151</v>
@@ -6036,27 +6036,27 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="D5" s="21" t="str">
-        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <f t="shared" ref="D5:I5" si="1">VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
         <v>Hi</v>
       </c>
       <c r="E5" s="21">
-        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="F5" s="21" t="str">
-        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>CF6</v>
       </c>
       <c r="G5" s="21" t="str">
-        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>Y</v>
       </c>
       <c r="H5" s="21" t="str">
-        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>Y</v>
       </c>
       <c r="I5" s="21" t="str">
-        <f>VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>N</v>
       </c>
       <c r="L5">
@@ -6207,7 +6207,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" ref="B10:B72" si="1">_xlfn.TEXTJOIN(".",TRUE,D10:I10)</f>
+        <f t="shared" ref="B10:B72" si="2">_xlfn.TEXTJOIN(".",TRUE,D10:I10)</f>
         <v>Hi.0.CF1.Y.Y.Y</v>
       </c>
       <c r="C10">
@@ -6265,11 +6265,11 @@
         <v>5</v>
       </c>
       <c r="B11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF1.Y.Y.Y</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C74" si="2">C10+1</f>
+        <f t="shared" ref="C11:C72" si="3">C10+1</f>
         <v>3</v>
       </c>
       <c r="D11" t="str">
@@ -6325,15 +6325,15 @@
         <v>5</v>
       </c>
       <c r="B12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF1.Y.Y.Y</v>
       </c>
       <c r="C12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="D12" t="str">
-        <f t="shared" ref="D12:D75" si="3">D10</f>
+        <f t="shared" ref="D12:D72" si="4">D10</f>
         <v>Hi</v>
       </c>
       <c r="E12">
@@ -6368,7 +6368,7 @@
         <v>104</v>
       </c>
       <c r="AM12" t="str">
-        <f t="shared" ref="AM12:AM14" si="4">AL12</f>
+        <f t="shared" ref="AM12:AM14" si="5">AL12</f>
         <v>ts_030</v>
       </c>
       <c r="AN12" s="10">
@@ -6389,15 +6389,15 @@
         <v>5</v>
       </c>
       <c r="B13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF1.N.Y.Y</v>
       </c>
       <c r="C13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="D13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E13">
@@ -6426,7 +6426,7 @@
         <v>100</v>
       </c>
       <c r="AM13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>ts_048</v>
       </c>
       <c r="AN13" s="10">
@@ -6447,19 +6447,19 @@
         <v>5</v>
       </c>
       <c r="B14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF1.N.Y.Y</v>
       </c>
       <c r="C14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="D14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14" si="5">E10</f>
+        <f t="shared" ref="E14" si="6">E10</f>
         <v>0</v>
       </c>
       <c r="F14" s="15" t="s">
@@ -6479,27 +6479,27 @@
         <v>229.26</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" ref="Y14:AD14" si="6">$W$12*N15</f>
+        <f t="shared" ref="Y14:AD14" si="7">$W$12*N15</f>
         <v>275.11199999999997</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>290.01390000000004</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>304.91579999999999</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>373.69379999999995</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>458.52</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>532.34172000000001</v>
       </c>
       <c r="AK14">
@@ -6509,7 +6509,7 @@
         <v>108</v>
       </c>
       <c r="AM14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>ts_072</v>
       </c>
       <c r="AN14" s="10">
@@ -6522,19 +6522,19 @@
         <v>5</v>
       </c>
       <c r="B15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF1.N.Y.Y</v>
       </c>
       <c r="C15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="D15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E15">
-        <f t="shared" ref="E15" si="7">E11</f>
+        <f t="shared" ref="E15" si="8">E11</f>
         <v>95</v>
       </c>
       <c r="F15" s="15" t="s">
@@ -6553,31 +6553,31 @@
         <v>11</v>
       </c>
       <c r="M15" s="11">
-        <f>SUMIF($L$2:$L$6,$D$5,M$2:M$6)</f>
+        <f t="shared" ref="M15:S15" si="9">SUMIF($L$2:$L$6,$D$5,M$2:M$6)</f>
         <v>1</v>
       </c>
       <c r="N15" s="11">
-        <f>SUMIF($L$2:$L$6,$D$5,N$2:N$6)</f>
+        <f t="shared" si="9"/>
         <v>1.2</v>
       </c>
       <c r="O15" s="11">
-        <f>SUMIF($L$2:$L$6,$D$5,O$2:O$6)</f>
+        <f t="shared" si="9"/>
         <v>1.2650000000000001</v>
       </c>
       <c r="P15" s="11">
-        <f>SUMIF($L$2:$L$6,$D$5,P$2:P$6)</f>
+        <f t="shared" si="9"/>
         <v>1.33</v>
       </c>
       <c r="Q15" s="11">
-        <f>SUMIF($L$2:$L$6,$D$5,Q$2:Q$6)</f>
+        <f t="shared" si="9"/>
         <v>1.63</v>
       </c>
       <c r="R15" s="11">
-        <f>SUMIF($L$2:$L$6,$D$5,R$2:R$6)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="S15" s="11">
-        <f>SUMIF($L$2:$L$6,$D$5,S$2:S$6)</f>
+        <f t="shared" si="9"/>
         <v>2.3220000000000001</v>
       </c>
       <c r="AK15">
@@ -6590,7 +6590,7 @@
         <v>150</v>
       </c>
       <c r="AN15" s="10">
-        <f t="shared" ref="AN15:AN78" si="8">AN10+1</f>
+        <f t="shared" ref="AN15:AN78" si="10">AN10+1</f>
         <v>2</v>
       </c>
     </row>
@@ -6599,19 +6599,19 @@
         <v>5</v>
       </c>
       <c r="B16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF1.N.Y.Y</v>
       </c>
       <c r="C16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="D16" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16" si="9">E12</f>
+        <f t="shared" ref="E16" si="11">E12</f>
         <v>95</v>
       </c>
       <c r="F16" s="15" t="s">
@@ -6639,7 +6639,7 @@
         <v>148</v>
       </c>
       <c r="AN16" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -6648,19 +6648,19 @@
         <v>5</v>
       </c>
       <c r="B17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF6.Y.Y.Y</v>
       </c>
       <c r="C17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="D17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E17">
-        <f t="shared" ref="E17" si="10">E13</f>
+        <f t="shared" ref="E17" si="12">E13</f>
         <v>0</v>
       </c>
       <c r="F17" t="s">
@@ -6683,27 +6683,27 @@
         <v>2020</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" ref="N17:S17" si="11">Y17</f>
+        <f t="shared" ref="N17:S17" si="13">Y17</f>
         <v>2025</v>
       </c>
       <c r="O17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2030</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2035</v>
       </c>
       <c r="Q17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2040</v>
       </c>
       <c r="R17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2045</v>
       </c>
       <c r="S17" s="7">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2050</v>
       </c>
       <c r="W17" s="4" t="s">
@@ -6743,7 +6743,7 @@
         <v>105</v>
       </c>
       <c r="AN17" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -6752,26 +6752,26 @@
         <v>5</v>
       </c>
       <c r="B18" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF6.Y.Y.Y</v>
       </c>
       <c r="C18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="D18" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E18">
-        <f t="shared" ref="E18" si="12">E14</f>
+        <f t="shared" ref="E18" si="14">E14</f>
         <v>0</v>
       </c>
       <c r="F18" t="s">
         <v>147</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" ref="G18:G81" si="13">G10</f>
+        <f t="shared" ref="G18:G72" si="15">G10</f>
         <v>Y</v>
       </c>
       <c r="H18" s="15" t="s">
@@ -6815,31 +6815,31 @@
         <v>16</v>
       </c>
       <c r="X18" s="6">
-        <f t="shared" ref="X18:AD20" si="14">M18*X$14</f>
+        <f t="shared" ref="X18:AD20" si="16">M18*X$14</f>
         <v>0</v>
       </c>
       <c r="Y18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AD18" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE18" t="s">
@@ -6856,7 +6856,7 @@
         <v>107</v>
       </c>
       <c r="AN18" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>2</v>
       </c>
     </row>
@@ -6865,26 +6865,26 @@
         <v>5</v>
       </c>
       <c r="B19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF6.Y.Y.Y</v>
       </c>
       <c r="C19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E19">
-        <f t="shared" ref="E19" si="15">E15</f>
+        <f t="shared" ref="E19" si="17">E15</f>
         <v>95</v>
       </c>
       <c r="F19" t="s">
         <v>147</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H19" s="15" t="s">
@@ -6928,31 +6928,31 @@
         <v>19</v>
       </c>
       <c r="X19" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>91.704000000000008</v>
       </c>
       <c r="Y19" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>96.28919999999998</v>
       </c>
       <c r="Z19" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>95.704587000000018</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>97.573055999999994</v>
       </c>
       <c r="AB19" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>115.84507799999999</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>142.1412</v>
       </c>
       <c r="AD19" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>165.0259332</v>
       </c>
       <c r="AE19" t="s">
@@ -6968,7 +6968,7 @@
         <v>89</v>
       </c>
       <c r="AN19" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
     </row>
@@ -6977,26 +6977,26 @@
         <v>5</v>
       </c>
       <c r="B20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF6.Y.Y.Y</v>
       </c>
       <c r="C20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="D20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E83" si="16">E16</f>
+        <f t="shared" ref="E20:E72" si="18">E16</f>
         <v>95</v>
       </c>
       <c r="F20" t="s">
         <v>147</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H20" s="15" t="s">
@@ -7040,31 +7040,31 @@
         <v>22</v>
       </c>
       <c r="X20" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>107.75219999999999</v>
       </c>
       <c r="Y20" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>143.05823999999998</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>156.60750600000003</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>161.60537400000001</v>
       </c>
       <c r="AB20" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>194.320776</v>
       </c>
       <c r="AC20" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>229.26</v>
       </c>
       <c r="AD20" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>255.52402559999999</v>
       </c>
       <c r="AE20" t="s">
@@ -7080,7 +7080,7 @@
         <v>94</v>
       </c>
       <c r="AN20" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
     </row>
@@ -7089,26 +7089,26 @@
         <v>5</v>
       </c>
       <c r="B21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF6.N.Y.Y</v>
       </c>
       <c r="C21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="D21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E21">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F21" t="s">
         <v>147</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H21" s="15" t="s">
@@ -7156,27 +7156,27 @@
         <v>2.2925999999999997</v>
       </c>
       <c r="Y21" s="6">
-        <f t="shared" ref="Y21:AD21" si="17">X21</f>
+        <f t="shared" ref="Y21:AD21" si="19">X21</f>
         <v>2.2925999999999997</v>
       </c>
       <c r="Z21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AA21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AB21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AC21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AD21" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AE21" t="s">
@@ -7186,7 +7186,7 @@
         <v>20</v>
       </c>
       <c r="AN21" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
     </row>
@@ -7195,26 +7195,26 @@
         <v>5</v>
       </c>
       <c r="B22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF6.N.Y.Y</v>
       </c>
       <c r="C22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
       <c r="D22" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E22">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F22" t="s">
         <v>147</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H22" s="15" t="s">
@@ -7227,38 +7227,38 @@
         <v>25</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" ref="X22:AD22" si="18">X14-SUM(X19:X21)</f>
+        <f t="shared" ref="X22:AD22" si="20">X14-SUM(X19:X21)</f>
         <v>27.511200000000002</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>33.471960000000024</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>35.409206999999981</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>43.444770000000005</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>61.235345999999993</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>84.826199999999972</v>
       </c>
       <c r="AD22" s="6">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>109.4991612</v>
       </c>
       <c r="AE22" t="s">
         <v>17</v>
       </c>
       <c r="AN22" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
     </row>
@@ -7267,26 +7267,26 @@
         <v>5</v>
       </c>
       <c r="B23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF6.N.Y.Y</v>
       </c>
       <c r="C23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="D23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E23">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F23" t="s">
         <v>147</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H23" s="15" t="s">
@@ -7299,7 +7299,7 @@
         <v>26</v>
       </c>
       <c r="AN23" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>3</v>
       </c>
     </row>
@@ -7308,26 +7308,26 @@
         <v>5</v>
       </c>
       <c r="B24" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF6.N.Y.Y</v>
       </c>
       <c r="C24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D24" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E24">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F24" t="s">
         <v>147</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H24" s="15" t="s">
@@ -7340,31 +7340,31 @@
         <v>27</v>
       </c>
       <c r="M24" s="11">
-        <f>SUMIF($L$2:$L$6,$E$5,M$2:M$6)</f>
+        <f t="shared" ref="M24:S24" si="21">SUMIF($L$2:$L$6,$E$5,M$2:M$6)</f>
         <v>0</v>
       </c>
       <c r="N24" s="11">
-        <f>SUMIF($L$2:$L$6,$E$5,N$2:N$6)</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="O24" s="11">
-        <f>SUMIF($L$2:$L$6,$E$5,O$2:O$6)</f>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="P24" s="11">
-        <f>SUMIF($L$2:$L$6,$E$5,P$2:P$6)</f>
+        <f t="shared" si="21"/>
         <v>35</v>
       </c>
       <c r="Q24" s="11">
-        <f>SUMIF($L$2:$L$6,$E$5,Q$2:Q$6)</f>
+        <f t="shared" si="21"/>
         <v>60</v>
       </c>
       <c r="R24" s="11">
-        <f>SUMIF($L$2:$L$6,$E$5,R$2:R$6)</f>
+        <f t="shared" si="21"/>
         <v>80</v>
       </c>
       <c r="S24" s="11">
-        <f>SUMIF($L$2:$L$6,$E$5,S$2:S$6)</f>
+        <f t="shared" si="21"/>
         <v>95</v>
       </c>
       <c r="W24" t="s">
@@ -7397,7 +7397,7 @@
         <v>29</v>
       </c>
       <c r="AN24" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -7406,19 +7406,19 @@
         <v>5</v>
       </c>
       <c r="B25" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF1.Y.N.Y</v>
       </c>
       <c r="C25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D25" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E25">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F25" t="str">
@@ -7426,7 +7426,7 @@
         <v>CF1</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H25" s="15" t="s">
@@ -7436,7 +7436,7 @@
         <v>155</v>
       </c>
       <c r="AN25" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -7445,27 +7445,27 @@
         <v>5</v>
       </c>
       <c r="B26" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF1.Y.N.Y</v>
       </c>
       <c r="C26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="D26" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E26">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" ref="F26:F86" si="19">F10</f>
+        <f t="shared" ref="F26:F72" si="22">F10</f>
         <v>CF1</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H26" s="15" t="s">
@@ -7478,7 +7478,7 @@
         <v>12</v>
       </c>
       <c r="AN26" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -7487,27 +7487,27 @@
         <v>5</v>
       </c>
       <c r="B27" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF1.Y.N.Y</v>
       </c>
       <c r="C27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
       <c r="D27" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H27" s="15" t="s">
@@ -7520,31 +7520,31 @@
         <v>30</v>
       </c>
       <c r="X27" s="4">
-        <f t="shared" ref="X27:AD27" si="20">X17</f>
+        <f t="shared" ref="X27:AD27" si="23">X17</f>
         <v>2022</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>2025</v>
       </c>
       <c r="Z27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>2030</v>
       </c>
       <c r="AA27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>2035</v>
       </c>
       <c r="AB27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>2040</v>
       </c>
       <c r="AC27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>2045</v>
       </c>
       <c r="AD27" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="23"/>
         <v>2050</v>
       </c>
       <c r="AE27" s="4" t="s">
@@ -7554,7 +7554,7 @@
         <v>31</v>
       </c>
       <c r="AN27" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -7563,27 +7563,27 @@
         <v>5</v>
       </c>
       <c r="B28" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF1.Y.N.Y</v>
       </c>
       <c r="C28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="D28" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E28">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G28" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H28" s="15" t="s">
@@ -7615,7 +7615,7 @@
         <v>34</v>
       </c>
       <c r="AN28" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>4</v>
       </c>
     </row>
@@ -7624,27 +7624,27 @@
         <v>5</v>
       </c>
       <c r="B29" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF1.N.N.Y</v>
       </c>
       <c r="C29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>21</v>
       </c>
       <c r="D29" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E29">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G29" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H29" s="15" t="s">
@@ -7676,7 +7676,7 @@
         <v>34</v>
       </c>
       <c r="AN29" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
     </row>
@@ -7685,27 +7685,27 @@
         <v>5</v>
       </c>
       <c r="B30" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF1.N.N.Y</v>
       </c>
       <c r="C30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="D30" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E30">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H30" s="15" t="s">
@@ -7715,7 +7715,7 @@
         <v>155</v>
       </c>
       <c r="AN30" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
     </row>
@@ -7724,27 +7724,27 @@
         <v>5</v>
       </c>
       <c r="B31" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF1.N.N.Y</v>
       </c>
       <c r="C31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>23</v>
       </c>
       <c r="D31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H31" s="15" t="s">
@@ -7754,7 +7754,7 @@
         <v>155</v>
       </c>
       <c r="AN31" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
     </row>
@@ -7763,27 +7763,27 @@
         <v>5</v>
       </c>
       <c r="B32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF1.N.N.Y</v>
       </c>
       <c r="C32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="D32" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E32">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H32" s="15" t="s">
@@ -7797,7 +7797,7 @@
         <v>DEF correction active</v>
       </c>
       <c r="AN32" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
     </row>
@@ -7806,27 +7806,27 @@
         <v>5</v>
       </c>
       <c r="B33" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF6.Y.N.Y</v>
       </c>
       <c r="C33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="D33" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E33">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H33" s="15" t="s">
@@ -7848,7 +7848,7 @@
         <v>158</v>
       </c>
       <c r="AN33" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
     </row>
@@ -7857,27 +7857,27 @@
         <v>5</v>
       </c>
       <c r="B34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF6.Y.N.Y</v>
       </c>
       <c r="C34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>26</v>
       </c>
       <c r="D34" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E34">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H34" s="15" t="s">
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AN34" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
     </row>
@@ -7908,27 +7908,27 @@
         <v>5</v>
       </c>
       <c r="B35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF6.Y.N.Y</v>
       </c>
       <c r="C35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>27</v>
       </c>
       <c r="D35" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E35">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H35" s="15" t="s">
@@ -7938,7 +7938,7 @@
         <v>155</v>
       </c>
       <c r="AN35" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
     </row>
@@ -7947,27 +7947,27 @@
         <v>5</v>
       </c>
       <c r="B36" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF6.Y.N.Y</v>
       </c>
       <c r="C36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="D36" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H36" s="15" t="s">
@@ -7980,7 +7980,7 @@
         <v>9</v>
       </c>
       <c r="AN36" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
     </row>
@@ -7989,27 +7989,27 @@
         <v>5</v>
       </c>
       <c r="B37" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF6.N.N.Y</v>
       </c>
       <c r="C37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="D37" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E37">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H37" s="15" t="s">
@@ -8034,19 +8034,19 @@
         <v>1.0510100500999999</v>
       </c>
       <c r="P37" s="11">
-        <f t="shared" ref="P37:S37" si="21">O37*(1+$U37)^5</f>
+        <f t="shared" ref="P37:S37" si="24">O37*(1+$U37)^5</f>
         <v>1.1046221254112043</v>
       </c>
       <c r="Q37" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>1.1609689553699982</v>
       </c>
       <c r="R37" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>1.2201900399479664</v>
       </c>
       <c r="S37" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>1.2824319950172332</v>
       </c>
       <c r="U37">
@@ -8057,7 +8057,7 @@
         <v>DEF correction active</v>
       </c>
       <c r="AN37" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
     </row>
@@ -8066,27 +8066,27 @@
         <v>5</v>
       </c>
       <c r="B38" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF6.N.N.Y</v>
       </c>
       <c r="C38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="D38" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E38">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H38" s="15" t="s">
@@ -8103,27 +8103,27 @@
         <v>1</v>
       </c>
       <c r="N38" s="11">
-        <f t="shared" ref="N38:S38" si="22">M38</f>
+        <f t="shared" ref="N38:S38" si="25">M38</f>
         <v>1</v>
       </c>
       <c r="O38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="P38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="Q38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="S38" s="11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="W38" s="4" t="s">
@@ -8142,7 +8142,7 @@
         <v>159</v>
       </c>
       <c r="AN38" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>6</v>
       </c>
     </row>
@@ -8151,27 +8151,27 @@
         <v>5</v>
       </c>
       <c r="B39" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF6.N.N.Y</v>
       </c>
       <c r="C39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="D39" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E39">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H39" s="15" t="s">
@@ -8188,27 +8188,27 @@
         <v>1</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" ref="N39:S39" si="23">M39</f>
+        <f t="shared" ref="N39:S39" si="26">M39</f>
         <v>1</v>
       </c>
       <c r="O39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="P39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="Q39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="R39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="S39" s="11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="W39" t="s">
@@ -8227,7 +8227,7 @@
         <v>162</v>
       </c>
       <c r="AN39" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
     </row>
@@ -8236,27 +8236,27 @@
         <v>5</v>
       </c>
       <c r="B40" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF6.N.N.Y</v>
       </c>
       <c r="C40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="D40" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E40">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G40" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H40" s="15" t="s">
@@ -8273,27 +8273,27 @@
         <v>1</v>
       </c>
       <c r="N40" s="11">
-        <f t="shared" ref="N40:S40" si="24">M40</f>
+        <f t="shared" ref="N40:S40" si="27">M40</f>
         <v>1</v>
       </c>
       <c r="O40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="P40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="Q40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="R40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="S40" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="W40" t="s">
@@ -8309,7 +8309,7 @@
         <v>164</v>
       </c>
       <c r="AN40" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
     </row>
@@ -8318,27 +8318,27 @@
         <v>5</v>
       </c>
       <c r="B41" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF1.Y.Y.N</v>
       </c>
       <c r="C41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>33</v>
       </c>
       <c r="D41" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E41">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H41" s="15" t="str">
@@ -8349,7 +8349,7 @@
         <v>156</v>
       </c>
       <c r="AN41" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
     </row>
@@ -8358,38 +8358,38 @@
         <v>5</v>
       </c>
       <c r="B42" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF1.Y.Y.N</v>
       </c>
       <c r="C42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>34</v>
       </c>
       <c r="D42" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E42">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G42" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H42" s="15" t="str">
-        <f t="shared" ref="H42:H86" si="25">H10</f>
+        <f t="shared" ref="H42:H72" si="28">H10</f>
         <v>Y</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN42" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
     </row>
@@ -8398,31 +8398,31 @@
         <v>5</v>
       </c>
       <c r="B43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF1.Y.Y.N</v>
       </c>
       <c r="C43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>35</v>
       </c>
       <c r="D43" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F43" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G43" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H43" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I43" s="15" t="s">
@@ -8432,7 +8432,7 @@
         <v>101</v>
       </c>
       <c r="AN43" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>7</v>
       </c>
     </row>
@@ -8441,31 +8441,31 @@
         <v>5</v>
       </c>
       <c r="B44" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF1.Y.Y.N</v>
       </c>
       <c r="C44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>36</v>
       </c>
       <c r="D44" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F44" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G44" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H44" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I44" s="15" t="s">
@@ -8485,23 +8485,23 @@
         <v>2025</v>
       </c>
       <c r="O44">
-        <f t="shared" ref="O44:S44" si="26">O17</f>
+        <f t="shared" ref="O44:S44" si="29">O17</f>
         <v>2030</v>
       </c>
       <c r="P44">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2035</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2040</v>
       </c>
       <c r="R44">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2045</v>
       </c>
       <c r="S44">
-        <f t="shared" si="26"/>
+        <f t="shared" si="29"/>
         <v>2050</v>
       </c>
       <c r="V44" t="s">
@@ -8511,7 +8511,7 @@
         <v>83</v>
       </c>
       <c r="AN44" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
     </row>
@@ -8520,31 +8520,31 @@
         <v>5</v>
       </c>
       <c r="B45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF1.N.Y.N</v>
       </c>
       <c r="C45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>37</v>
       </c>
       <c r="D45" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E45">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G45" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H45" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I45" s="15" t="s">
@@ -8558,31 +8558,31 @@
         <v>Gas</v>
       </c>
       <c r="M45">
-        <f t="shared" ref="M45:S48" si="27">AVERAGE($V45:$W45)*M37</f>
+        <f t="shared" ref="M45:S48" si="30">AVERAGE($V45:$W45)*M37</f>
         <v>45</v>
       </c>
       <c r="N45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>45</v>
       </c>
       <c r="O45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>47.295452254499999</v>
       </c>
       <c r="P45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>49.707995643504191</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>52.243602991649922</v>
       </c>
       <c r="R45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>54.90855179765849</v>
       </c>
       <c r="S45">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>57.709439775775493</v>
       </c>
       <c r="V45">
@@ -8594,7 +8594,7 @@
         <v>45</v>
       </c>
       <c r="AN45" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
     </row>
@@ -8603,31 +8603,31 @@
         <v>5</v>
       </c>
       <c r="B46" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF1.N.Y.N</v>
       </c>
       <c r="C46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>38</v>
       </c>
       <c r="D46" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G46" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H46" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I46" s="15" t="s">
@@ -8637,35 +8637,35 @@
         <v>79</v>
       </c>
       <c r="L46" t="str">
-        <f t="shared" ref="L46:L48" si="28">K46</f>
+        <f t="shared" ref="L46:L48" si="31">K46</f>
         <v>Coal</v>
       </c>
       <c r="M46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.68</v>
       </c>
       <c r="N46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.68</v>
       </c>
       <c r="O46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.68</v>
       </c>
       <c r="P46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.68</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.68</v>
       </c>
       <c r="R46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.68</v>
       </c>
       <c r="S46">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>4.68</v>
       </c>
       <c r="V46">
@@ -8677,7 +8677,7 @@
         <v>5.04</v>
       </c>
       <c r="AN46" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
     </row>
@@ -8686,31 +8686,31 @@
         <v>5</v>
       </c>
       <c r="B47" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF1.N.Y.N</v>
       </c>
       <c r="C47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>39</v>
       </c>
       <c r="D47" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F47" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G47" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H47" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I47" s="15" t="s">
@@ -8720,35 +8720,35 @@
         <v>80</v>
       </c>
       <c r="L47" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>Oil</v>
       </c>
       <c r="M47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>79.2</v>
       </c>
       <c r="N47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>79.2</v>
       </c>
       <c r="O47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>79.2</v>
       </c>
       <c r="P47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>79.2</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>79.2</v>
       </c>
       <c r="R47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>79.2</v>
       </c>
       <c r="S47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>79.2</v>
       </c>
       <c r="V47">
@@ -8760,7 +8760,7 @@
         <v>79.2</v>
       </c>
       <c r="AN47" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
     </row>
@@ -8769,31 +8769,31 @@
         <v>5</v>
       </c>
       <c r="B48" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF1.N.Y.N</v>
       </c>
       <c r="C48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="D48" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E48">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F48" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G48" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H48" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I48" s="15" t="s">
@@ -8803,11 +8803,11 @@
         <v>81</v>
       </c>
       <c r="L48" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="31"/>
         <v>Bioenergy</v>
       </c>
       <c r="M48">
-        <f t="shared" si="27"/>
+        <f t="shared" si="30"/>
         <v>22</v>
       </c>
       <c r="S48" t="e">
@@ -8823,7 +8823,7 @@
         <v>26</v>
       </c>
       <c r="AN48" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>8</v>
       </c>
     </row>
@@ -8832,38 +8832,38 @@
         <v>5</v>
       </c>
       <c r="B49" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF6.Y.Y.N</v>
       </c>
       <c r="C49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
       <c r="D49" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E49">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G49" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H49" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN49" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
     </row>
@@ -8872,38 +8872,38 @@
         <v>5</v>
       </c>
       <c r="B50" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF6.Y.Y.N</v>
       </c>
       <c r="C50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
       <c r="D50" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E50">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G50" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H50" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN50" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
     </row>
@@ -8912,31 +8912,31 @@
         <v>5</v>
       </c>
       <c r="B51" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF6.Y.Y.N</v>
       </c>
       <c r="C51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>43</v>
       </c>
       <c r="D51" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E51">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F51" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G51" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H51" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I51" s="15" t="s">
@@ -8947,7 +8947,7 @@
         <v>GAS available</v>
       </c>
       <c r="AN51" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
     </row>
@@ -8956,31 +8956,31 @@
         <v>5</v>
       </c>
       <c r="B52" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF6.Y.Y.N</v>
       </c>
       <c r="C52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>44</v>
       </c>
       <c r="D52" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E52">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F52" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H52" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I52" s="15" t="s">
@@ -9002,7 +9002,7 @@
         <v>167</v>
       </c>
       <c r="AN52" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
     </row>
@@ -9011,31 +9011,31 @@
         <v>5</v>
       </c>
       <c r="B53" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF6.N.Y.N</v>
       </c>
       <c r="C53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="D53" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E53">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G53" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H53" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I53" s="15" t="s">
@@ -9054,7 +9054,7 @@
         <v>165</v>
       </c>
       <c r="AN53" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>9</v>
       </c>
     </row>
@@ -9063,38 +9063,38 @@
         <v>5</v>
       </c>
       <c r="B54" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF6.N.Y.N</v>
       </c>
       <c r="C54">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>46</v>
       </c>
       <c r="D54" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E54">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G54" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H54" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN54" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
     </row>
@@ -9103,38 +9103,38 @@
         <v>5</v>
       </c>
       <c r="B55" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF6.N.Y.N</v>
       </c>
       <c r="C55">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>47</v>
       </c>
       <c r="D55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E55">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G55" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H55" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN55" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
     </row>
@@ -9143,38 +9143,38 @@
         <v>5</v>
       </c>
       <c r="B56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF6.N.Y.N</v>
       </c>
       <c r="C56">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="D56" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E56">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F56" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G56" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H56" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>Y</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN56" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
     </row>
@@ -9183,31 +9183,31 @@
         <v>5</v>
       </c>
       <c r="B57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF1.Y.N.N</v>
       </c>
       <c r="C57">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>49</v>
       </c>
       <c r="D57" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E57">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F57" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G57" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H57" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I57" s="15" t="s">
@@ -9218,7 +9218,7 @@
         <v>~TFM_UPD</v>
       </c>
       <c r="AN57" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
     </row>
@@ -9227,31 +9227,31 @@
         <v>5</v>
       </c>
       <c r="B58" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF1.Y.N.N</v>
       </c>
       <c r="C58">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="D58" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E58">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F58" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H58" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I58" s="15" t="s">
@@ -9273,7 +9273,7 @@
         <v>141</v>
       </c>
       <c r="AN58" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>10</v>
       </c>
     </row>
@@ -9282,31 +9282,31 @@
         <v>5</v>
       </c>
       <c r="B59" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF1.Y.N.N</v>
       </c>
       <c r="C59">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>51</v>
       </c>
       <c r="D59" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E59">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F59" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G59" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H59" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I59" s="15" t="s">
@@ -9323,7 +9323,7 @@
         <v>175</v>
       </c>
       <c r="AN59" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
     </row>
@@ -9332,38 +9332,38 @@
         <v>5</v>
       </c>
       <c r="B60" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF1.Y.N.N</v>
       </c>
       <c r="C60">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="D60" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E60">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F60" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G60" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H60" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN60" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
     </row>
@@ -9372,38 +9372,38 @@
         <v>5</v>
       </c>
       <c r="B61" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF1.N.N.N</v>
       </c>
       <c r="C61">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>53</v>
       </c>
       <c r="D61" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E61">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F61" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G61" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H61" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN61" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
     </row>
@@ -9412,38 +9412,38 @@
         <v>5</v>
       </c>
       <c r="B62" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF1.N.N.N</v>
       </c>
       <c r="C62">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>54</v>
       </c>
       <c r="D62" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E62">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F62" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G62" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H62" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN62" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
     </row>
@@ -9452,38 +9452,38 @@
         <v>5</v>
       </c>
       <c r="B63" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF1.N.N.N</v>
       </c>
       <c r="C63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>55</v>
       </c>
       <c r="D63" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F63" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G63" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H63" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN63" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>11</v>
       </c>
     </row>
@@ -9492,38 +9492,38 @@
         <v>5</v>
       </c>
       <c r="B64" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF1.N.N.N</v>
       </c>
       <c r="C64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>56</v>
       </c>
       <c r="D64" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E64">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F64" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF1</v>
       </c>
       <c r="G64" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H64" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN64" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
     </row>
@@ -9532,38 +9532,38 @@
         <v>5</v>
       </c>
       <c r="B65" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF6.Y.N.N</v>
       </c>
       <c r="C65">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>57</v>
       </c>
       <c r="D65" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E65">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G65" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H65" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN65" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
     </row>
@@ -9572,38 +9572,38 @@
         <v>5</v>
       </c>
       <c r="B66" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF6.Y.N.N</v>
       </c>
       <c r="C66">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>58</v>
       </c>
       <c r="D66" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E66">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F66" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G66" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H66" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN66" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
     </row>
@@ -9612,38 +9612,38 @@
         <v>5</v>
       </c>
       <c r="B67" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF6.Y.N.N</v>
       </c>
       <c r="C67">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>59</v>
       </c>
       <c r="D67" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F67" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G67" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H67" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN67" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
     </row>
@@ -9652,38 +9652,38 @@
         <v>5</v>
       </c>
       <c r="B68" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF6.Y.N.N</v>
       </c>
       <c r="C68">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="D68" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E68">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F68" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G68" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Y</v>
       </c>
       <c r="H68" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN68" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
     </row>
@@ -9692,38 +9692,38 @@
         <v>5</v>
       </c>
       <c r="B69" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.0.CF6.N.N.N</v>
       </c>
       <c r="C69">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>61</v>
       </c>
       <c r="D69" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E69">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F69" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G69" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H69" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN69" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
     </row>
@@ -9732,38 +9732,38 @@
         <v>5</v>
       </c>
       <c r="B70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.0.CF6.N.N.N</v>
       </c>
       <c r="C70">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>62</v>
       </c>
       <c r="D70" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E70">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="F70" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G70" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H70" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN70" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
     </row>
@@ -9772,38 +9772,38 @@
         <v>5</v>
       </c>
       <c r="B71" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Lo.95.CF6.N.N.N</v>
       </c>
       <c r="C71">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>63</v>
       </c>
       <c r="D71" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Lo</v>
       </c>
       <c r="E71">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F71" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G71" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H71" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN71" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
     </row>
@@ -9812,74 +9812,74 @@
         <v>5</v>
       </c>
       <c r="B72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Hi.95.CF6.N.N.N</v>
       </c>
       <c r="C72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>64</v>
       </c>
       <c r="D72" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Hi</v>
       </c>
       <c r="E72">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>95</v>
       </c>
       <c r="F72" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>CF6</v>
       </c>
       <c r="G72" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>N</v>
       </c>
       <c r="H72" s="15" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="28"/>
         <v>N</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>156</v>
       </c>
       <c r="AN72" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN73" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN74" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN75" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN76" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN77" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN78" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
     </row>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EFC434-03FE-4787-A7DA-6FB3EE52BF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A281CA-5C71-47D3-A15E-C2D3ECA3D285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="ar6_r10" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$B$8:$D$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$B$8:$H$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -632,7 +632,7 @@
     <t>grid, aggregators</t>
   </si>
   <si>
-    <t>1-64</t>
+    <t>1-16,33-48</t>
   </si>
 </sst>
 </file>
@@ -5968,7 +5968,7 @@
     <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
-        <v>~Inputcell: 1-64</v>
+        <v>~Inputcell: 1-16,33-48</v>
       </c>
       <c r="L2" t="s">
         <v>151</v>
@@ -8559,39 +8559,39 @@
       </c>
       <c r="M45">
         <f t="shared" ref="M45:S48" si="30">AVERAGE($V45:$W45)*M37</f>
-        <v>45</v>
+        <v>25.2</v>
       </c>
       <c r="N45">
         <f t="shared" si="30"/>
-        <v>45</v>
+        <v>25.2</v>
       </c>
       <c r="O45">
         <f t="shared" si="30"/>
-        <v>47.295452254499999</v>
+        <v>26.485453262519997</v>
       </c>
       <c r="P45">
         <f t="shared" si="30"/>
-        <v>49.707995643504191</v>
+        <v>27.836477560362347</v>
       </c>
       <c r="Q45">
         <f t="shared" si="30"/>
-        <v>52.243602991649922</v>
+        <v>29.256417675323956</v>
       </c>
       <c r="R45">
         <f t="shared" si="30"/>
-        <v>54.90855179765849</v>
+        <v>30.748789006688753</v>
       </c>
       <c r="S45">
         <f t="shared" si="30"/>
-        <v>57.709439775775493</v>
+        <v>32.317286274434274</v>
       </c>
       <c r="V45">
         <f>HLOOKUP($K45&amp;"_"&amp;V$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
-        <v>45</v>
+        <v>25.2</v>
       </c>
       <c r="W45">
         <f>HLOOKUP($K45&amp;"_"&amp;W$44,fuel_prices!$B$10:$I$11,2,FALSE)</f>
-        <v>45</v>
+        <v>25.2</v>
       </c>
       <c r="AN45" s="10">
         <f t="shared" si="10"/>
@@ -10210,12 +10210,12 @@
         <v>110</v>
       </c>
       <c r="B11">
-        <f>12.5*3.6</f>
-        <v>45</v>
+        <f>7*3.6</f>
+        <v>25.2</v>
       </c>
       <c r="C11">
         <f>B11</f>
-        <v>45</v>
+        <v>25.2</v>
       </c>
       <c r="D11">
         <f>1.2*3.6</f>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A281CA-5C71-47D3-A15E-C2D3ECA3D285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4603AF2-F51C-4AC1-A429-2F17CFCCB657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -632,7 +632,7 @@
     <t>grid, aggregators</t>
   </si>
   <si>
-    <t>1-16,33-48</t>
+    <t>1-32</t>
   </si>
 </sst>
 </file>
@@ -1041,22 +1041,22 @@
                   <c:v>229.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>275.11199999999997</c:v>
+                  <c:v>242.36057142857143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>290.01390000000004</c:v>
+                  <c:v>246.61825714285717</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>304.91579999999999</c:v>
+                  <c:v>250.87594285714286</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>373.69379999999995</c:v>
+                  <c:v>270.52679999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>458.52</c:v>
+                  <c:v>294.76285714285711</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>532.34172000000001</c:v>
+                  <c:v>315.85477714285713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1332,19 +1332,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>35</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>80</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>95</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5968,7 +5968,7 @@
     <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
-        <v>~Inputcell: 1-16,33-48</v>
+        <v>~Inputcell: 1-32</v>
       </c>
       <c r="L2" t="s">
         <v>151</v>
@@ -6001,7 +6001,7 @@
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="L3" t="s">
         <v>153</v>
@@ -6010,42 +6010,42 @@
         <v>1</v>
       </c>
       <c r="N3">
-        <f>1+(N2-1)/2</f>
-        <v>1.1000000000000001</v>
+        <f>1+(N2-1)/3.5</f>
+        <v>1.0571428571428572</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:S3" si="0">1+(O2-1)/2</f>
-        <v>1.1325000000000001</v>
+        <f t="shared" ref="O3:S3" si="0">1+(O2-1)/3.5</f>
+        <v>1.0757142857142858</v>
       </c>
       <c r="P3">
         <f t="shared" si="0"/>
-        <v>1.165</v>
+        <v>1.0942857142857143</v>
       </c>
       <c r="Q3">
         <f t="shared" si="0"/>
-        <v>1.3149999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="R3">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>1.2857142857142856</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>1.661</v>
+        <v>1.3777142857142857</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="D5" s="21" t="str">
         <f t="shared" ref="D5:I5" si="1">VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
-        <v>Hi</v>
+        <v>Lo</v>
       </c>
       <c r="E5" s="21">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F5" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>CF6</v>
+        <v>CF1</v>
       </c>
       <c r="G5" s="21" t="str">
         <f t="shared" si="1"/>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="I5" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -6480,27 +6480,27 @@
       </c>
       <c r="Y14" s="8">
         <f t="shared" ref="Y14:AD14" si="7">$W$12*N15</f>
-        <v>275.11199999999997</v>
+        <v>242.36057142857143</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="7"/>
-        <v>290.01390000000004</v>
+        <v>246.61825714285717</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="7"/>
-        <v>304.91579999999999</v>
+        <v>250.87594285714286</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="7"/>
-        <v>373.69379999999995</v>
+        <v>270.52679999999998</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="7"/>
-        <v>458.52</v>
+        <v>294.76285714285711</v>
       </c>
       <c r="AD14" s="8">
         <f t="shared" si="7"/>
-        <v>532.34172000000001</v>
+        <v>315.85477714285713</v>
       </c>
       <c r="AK14">
         <v>6</v>
@@ -6558,27 +6558,27 @@
       </c>
       <c r="N15" s="11">
         <f t="shared" si="9"/>
-        <v>1.2</v>
+        <v>1.0571428571428572</v>
       </c>
       <c r="O15" s="11">
         <f t="shared" si="9"/>
-        <v>1.2650000000000001</v>
+        <v>1.0757142857142858</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="9"/>
-        <v>1.33</v>
+        <v>1.0942857142857143</v>
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="9"/>
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>1.2857142857142856</v>
       </c>
       <c r="S15" s="11">
         <f t="shared" si="9"/>
-        <v>2.3220000000000001</v>
+        <v>1.3777142857142857</v>
       </c>
       <c r="AK15">
         <v>7</v>
@@ -6784,32 +6784,32 @@
         <v>15</v>
       </c>
       <c r="M18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="N18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="O18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="P18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="Q18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="R18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
-        <v>0</v>
+        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <v>0.01</v>
       </c>
       <c r="S18" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
-        <v>0</v>
+        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <v>0.01</v>
       </c>
       <c r="W18" s="10" t="s">
         <v>16</v>
@@ -6836,11 +6836,11 @@
       </c>
       <c r="AC18" s="6">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>2.947628571428571</v>
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3.1585477714285712</v>
       </c>
       <c r="AE18" t="s">
         <v>17</v>
@@ -6933,27 +6933,27 @@
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="16"/>
-        <v>96.28919999999998</v>
+        <v>84.8262</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="16"/>
-        <v>95.704587000000018</v>
+        <v>81.384024857142876</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="16"/>
-        <v>97.573055999999994</v>
+        <v>80.280301714285713</v>
       </c>
       <c r="AB19" s="6">
         <f t="shared" si="16"/>
-        <v>115.84507799999999</v>
+        <v>83.863307999999989</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="16"/>
-        <v>142.1412</v>
+        <v>91.376485714285707</v>
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="16"/>
-        <v>165.0259332</v>
+        <v>97.914980914285707</v>
       </c>
       <c r="AE19" t="s">
         <v>17</v>
@@ -7045,27 +7045,27 @@
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="16"/>
-        <v>143.05823999999998</v>
+        <v>126.02749714285714</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="16"/>
-        <v>156.60750600000003</v>
+        <v>133.17385885714287</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="16"/>
-        <v>161.60537400000001</v>
+        <v>132.96424971428573</v>
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="16"/>
-        <v>194.320776</v>
+        <v>140.673936</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="16"/>
-        <v>229.26</v>
+        <v>147.38142857142856</v>
       </c>
       <c r="AD20" s="6">
         <f t="shared" si="16"/>
-        <v>255.52402559999999</v>
+        <v>151.61029302857142</v>
       </c>
       <c r="AE20" t="s">
         <v>17</v>
@@ -7232,27 +7232,27 @@
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="20"/>
-        <v>33.471960000000024</v>
+        <v>29.214274285714311</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="20"/>
-        <v>35.409206999999981</v>
+        <v>29.767773428571417</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="20"/>
-        <v>43.444770000000005</v>
+        <v>35.338791428571426</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="20"/>
-        <v>61.235345999999993</v>
+        <v>43.696956</v>
       </c>
       <c r="AC22" s="6">
         <f t="shared" si="20"/>
-        <v>84.826199999999972</v>
+        <v>53.712342857142858</v>
       </c>
       <c r="AD22" s="6">
         <f t="shared" si="20"/>
-        <v>109.4991612</v>
+        <v>64.036903200000012</v>
       </c>
       <c r="AE22" t="s">
         <v>17</v>
@@ -7349,23 +7349,23 @@
       </c>
       <c r="O24" s="11">
         <f t="shared" si="21"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P24" s="11">
         <f t="shared" si="21"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="11">
         <f t="shared" si="21"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R24" s="11">
         <f t="shared" si="21"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S24" s="11">
         <f t="shared" si="21"/>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="W24" t="s">
         <v>28</v>
@@ -7375,23 +7375,23 @@
       </c>
       <c r="Z24" s="11">
         <f>O24/1000</f>
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="11">
         <f>P24/1000</f>
-        <v>3.5000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="11">
         <f>Q24/1000</f>
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="11">
         <f>R24/1000</f>
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="11">
         <f>S24/1000</f>
-        <v>9.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="s">
         <v>29</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="W57" s="5" t="str">
         <f>IF($I$5="N","~TFM_UPD","Transmission costs active")</f>
-        <v>~TFM_UPD</v>
+        <v>Transmission costs active</v>
       </c>
       <c r="AN57" s="10">
         <f t="shared" si="10"/>
@@ -9908,7 +9908,7 @@
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="str">
         <f>Veda!F5</f>
-        <v>CF6</v>
+        <v>CF1</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.45">
@@ -10115,11 +10115,11 @@
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G14" s="11">
         <f>SUMIF($A$7:$A$12,$A$1,G7:G12)</f>
-        <v>0.57142857142857151</v>
+        <v>1</v>
       </c>
       <c r="H14" s="11">
         <f>SUMIF($A$7:$A$12,$A$1,H7:H12)</f>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
@@ -10141,11 +10141,11 @@
     <row r="18" spans="7:9" x14ac:dyDescent="0.45">
       <c r="G18" t="str">
         <f>"*"&amp;G14</f>
-        <v>*0.571428571428572</v>
+        <v>*1</v>
       </c>
       <c r="H18" t="str">
         <f>"*"&amp;H14</f>
-        <v>*1.5</v>
+        <v>*0.5</v>
       </c>
       <c r="I18" t="s">
         <v>140</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4603AF2-F51C-4AC1-A429-2F17CFCCB657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2084F0-4428-4B7B-8171-FB553D74A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="159">
   <si>
     <t>C1</t>
   </si>
@@ -356,22 +356,10 @@
     <t>high</t>
   </si>
   <si>
-    <t>s1p1v1_d</t>
-  </si>
-  <si>
-    <t>s5p5v5_d</t>
-  </si>
-  <si>
-    <t>ts_annual</t>
-  </si>
-  <si>
     <t>pset_co</t>
   </si>
   <si>
     <t>e 1.5 deg no OS</t>
-  </si>
-  <si>
-    <t>d9d</t>
   </si>
   <si>
     <t>d 1.5 deg OS</t>
@@ -386,9 +374,6 @@
     <t>a 3 deg</t>
   </si>
   <si>
-    <t>c15d</t>
-  </si>
-  <si>
     <t>~Scenmap</t>
   </si>
   <si>
@@ -401,37 +386,10 @@
     <t>priority</t>
   </si>
   <si>
-    <t>ts_012</t>
-  </si>
-  <si>
-    <t>ts_048</t>
-  </si>
-  <si>
     <t>~TFM_INS-TS: attribute=flo_cost;pset_pn=-IMP*Z</t>
   </si>
   <si>
     <t>bio price multiplier</t>
-  </si>
-  <si>
-    <t>s1v1_d</t>
-  </si>
-  <si>
-    <t>ts_030</t>
-  </si>
-  <si>
-    <t>f2d96</t>
-  </si>
-  <si>
-    <t>ts_096</t>
-  </si>
-  <si>
-    <t>e96</t>
-  </si>
-  <si>
-    <t>ts_072</t>
-  </si>
-  <si>
-    <t>xAnn</t>
   </si>
   <si>
     <t>ZAF</t>
@@ -443,16 +401,7 @@
     <t>Limited gas, abundant cheap coal</t>
   </si>
   <si>
-    <t>ts_60c</t>
-  </si>
-  <si>
-    <t>ts_216c</t>
-  </si>
-  <si>
     <t>co2price</t>
-  </si>
-  <si>
-    <t>c60</t>
   </si>
   <si>
     <t>Mapping to the smoke test</t>
@@ -548,15 +497,6 @@
     <t>CF6</t>
   </si>
   <si>
-    <t>c216</t>
-  </si>
-  <si>
-    <t>ts_108c</t>
-  </si>
-  <si>
-    <t>c108</t>
-  </si>
-  <si>
     <t>Hi</t>
   </si>
   <si>
@@ -632,7 +572,13 @@
     <t>grid, aggregators</t>
   </si>
   <si>
-    <t>1-32</t>
+    <t>NCAP_DRATE</t>
+  </si>
+  <si>
+    <t>1-48</t>
+  </si>
+  <si>
+    <t>NCAP_ELIFE</t>
   </si>
 </sst>
 </file>
@@ -840,7 +786,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -869,6 +815,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1041,22 +993,22 @@
                   <c:v>229.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>242.36057142857143</c:v>
+                  <c:v>275.11199999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>246.61825714285717</c:v>
+                  <c:v>290.01390000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>250.87594285714286</c:v>
+                  <c:v>304.91579999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>270.52679999999998</c:v>
+                  <c:v>373.69379999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>294.76285714285711</c:v>
+                  <c:v>458.52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>315.85477714285713</c:v>
+                  <c:v>532.34172000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5943,7 +5895,8 @@
     <col min="5" max="5" width="7.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.1328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="3.86328125" customWidth="1"/>
+    <col min="8" max="8" width="3.86328125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="1.73046875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.53125" customWidth="1"/>
     <col min="12" max="12" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -5952,6 +5905,8 @@
     <col min="16" max="18" width="5.265625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="6.265625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="5.265625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="2.73046875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="9.265625" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="6.265625" bestFit="1" customWidth="1"/>
@@ -5962,16 +5917,16 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.45">
       <c r="K1" s="16" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
-        <v>~Inputcell: 1-32</v>
+        <v>~Inputcell: 1-48</v>
       </c>
       <c r="L2" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -5996,15 +5951,15 @@
         <v>2.3220000000000001</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L3" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -6037,7 +5992,7 @@
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="D5" s="21" t="str">
         <f t="shared" ref="D5:I5" si="1">VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
-        <v>Lo</v>
+        <v>Hi</v>
       </c>
       <c r="E5" s="21">
         <f t="shared" si="1"/>
@@ -6049,15 +6004,15 @@
       </c>
       <c r="G5" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="H5" s="21" t="str">
         <f t="shared" si="1"/>
         <v>Y</v>
       </c>
-      <c r="I5" s="21" t="str">
+      <c r="I5" s="21">
         <f t="shared" si="1"/>
-        <v>Y</v>
+        <v>0.25</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -6112,40 +6067,40 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:44" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>165</v>
-      </c>
       <c r="I8" s="4" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="J8" s="4"/>
       <c r="AR8" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
@@ -6154,41 +6109,32 @@
       </c>
       <c r="B9" t="str">
         <f>_xlfn.TEXTJOIN(".",TRUE,D9:I9)</f>
-        <v>Lo.0.CF1.Y.Y.Y</v>
+        <v>Lo.0.CF1.Y.Y.1</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="E9" s="15">
         <v>0</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I9" s="22">
+        <v>1</v>
       </c>
       <c r="K9" t="s">
         <v>1</v>
       </c>
-      <c r="AK9">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="s">
-        <v>86</v>
-      </c>
-      <c r="AM9" t="s">
-        <v>109</v>
-      </c>
       <c r="AN9" s="10">
         <v>1</v>
       </c>
@@ -6196,7 +6142,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AQ9" s="12">
         <v>5</v>
@@ -6207,30 +6153,30 @@
         <v>5</v>
       </c>
       <c r="B10" t="str">
-        <f t="shared" ref="B10:B72" si="2">_xlfn.TEXTJOIN(".",TRUE,D10:I10)</f>
-        <v>Hi.0.CF1.Y.Y.Y</v>
+        <f t="shared" ref="B10:B56" si="2">_xlfn.TEXTJOIN(".",TRUE,D10:I10)</f>
+        <v>Hi.0.CF1.Y.Y.1</v>
       </c>
       <c r="C10">
         <f>C9+1</f>
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="E10" s="15">
         <v>0</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I10" s="22">
+        <v>1</v>
       </c>
       <c r="K10" t="s">
         <v>3</v>
@@ -6238,15 +6184,6 @@
       <c r="W10" t="s">
         <v>4</v>
       </c>
-      <c r="AK10">
-        <v>2</v>
-      </c>
-      <c r="AL10" t="s">
-        <v>113</v>
-      </c>
-      <c r="AM10" t="s">
-        <v>116</v>
-      </c>
       <c r="AN10" s="10">
         <v>1</v>
       </c>
@@ -6254,7 +6191,7 @@
         <v>2</v>
       </c>
       <c r="AP10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="AQ10" s="12">
         <v>4</v>
@@ -6266,10 +6203,10 @@
       </c>
       <c r="B11" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.Y.Y.Y</v>
+        <v>Lo.95.CF1.Y.Y.1</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C72" si="3">C10+1</f>
+        <f t="shared" ref="C11:C56" si="3">C10+1</f>
         <v>3</v>
       </c>
       <c r="D11" t="str">
@@ -6280,16 +6217,16 @@
         <v>95</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I11" s="22">
+        <v>1</v>
       </c>
       <c r="K11" t="s">
         <v>6</v>
@@ -6297,16 +6234,6 @@
       <c r="W11" s="1">
         <v>2022</v>
       </c>
-      <c r="AK11">
-        <v>3</v>
-      </c>
-      <c r="AL11" t="s">
-        <v>99</v>
-      </c>
-      <c r="AM11" t="str">
-        <f>AL11</f>
-        <v>ts_012</v>
-      </c>
       <c r="AN11" s="10">
         <v>1</v>
       </c>
@@ -6314,7 +6241,7 @@
         <v>5</v>
       </c>
       <c r="AP11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="AQ11" s="12">
         <v>3</v>
@@ -6326,30 +6253,30 @@
       </c>
       <c r="B12" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.Y.Y.Y</v>
+        <v>Hi.95.CF1.Y.Y.1</v>
       </c>
       <c r="C12">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="D12" t="str">
-        <f t="shared" ref="D12:D72" si="4">D10</f>
+        <f t="shared" ref="D12:D56" si="4">D10</f>
         <v>Hi</v>
       </c>
       <c r="E12">
         <v>95</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I12" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I12" s="22">
+        <v>1</v>
       </c>
       <c r="K12" t="s">
         <v>8</v>
@@ -6361,16 +6288,6 @@
       <c r="X12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AK12">
-        <v>4</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>104</v>
-      </c>
-      <c r="AM12" t="str">
-        <f t="shared" ref="AM12:AM14" si="5">AL12</f>
-        <v>ts_030</v>
-      </c>
       <c r="AN12" s="10">
         <v>1</v>
       </c>
@@ -6378,7 +6295,7 @@
         <v>7</v>
       </c>
       <c r="AP12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AQ12" s="12">
         <v>3</v>
@@ -6390,7 +6307,7 @@
       </c>
       <c r="B13" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.N.Y.Y</v>
+        <v>Lo.0.CF1.N.Y.1</v>
       </c>
       <c r="C13">
         <f t="shared" si="3"/>
@@ -6405,30 +6322,20 @@
         <v>0</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G13" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I13" s="22">
+        <v>1</v>
       </c>
       <c r="K13" t="s">
         <v>10</v>
       </c>
-      <c r="AK13">
-        <v>5</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AM13" t="str">
-        <f t="shared" si="5"/>
-        <v>ts_048</v>
-      </c>
       <c r="AN13" s="10">
         <v>1</v>
       </c>
@@ -6436,7 +6343,7 @@
         <v>9</v>
       </c>
       <c r="AP13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AQ13" s="12">
         <v>1.5</v>
@@ -6448,7 +6355,7 @@
       </c>
       <c r="B14" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.N.Y.Y</v>
+        <v>Hi.0.CF1.N.Y.1</v>
       </c>
       <c r="C14">
         <f t="shared" si="3"/>
@@ -6459,58 +6366,48 @@
         <v>Hi</v>
       </c>
       <c r="E14">
-        <f t="shared" ref="E14" si="6">E10</f>
+        <f t="shared" ref="E14" si="5">E10</f>
         <v>0</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G14" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I14" s="22">
+        <v>1</v>
       </c>
       <c r="X14" s="8">
         <f>W12</f>
         <v>229.26</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" ref="Y14:AD14" si="7">$W$12*N15</f>
-        <v>242.36057142857143</v>
+        <f t="shared" ref="Y14:AD14" si="6">$W$12*N15</f>
+        <v>275.11199999999997</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="7"/>
-        <v>246.61825714285717</v>
+        <f t="shared" si="6"/>
+        <v>290.01390000000004</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" si="7"/>
-        <v>250.87594285714286</v>
+        <f t="shared" si="6"/>
+        <v>304.91579999999999</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="7"/>
-        <v>270.52679999999998</v>
+        <f t="shared" si="6"/>
+        <v>373.69379999999995</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" si="7"/>
-        <v>294.76285714285711</v>
+        <f t="shared" si="6"/>
+        <v>458.52</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="7"/>
-        <v>315.85477714285713</v>
-      </c>
-      <c r="AK14">
-        <v>6</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AM14" t="str">
-        <f t="shared" si="5"/>
-        <v>ts_072</v>
+        <f t="shared" si="6"/>
+        <v>532.34172000000001</v>
       </c>
       <c r="AN14" s="10">
         <f>AN9+1</f>
@@ -6523,7 +6420,7 @@
       </c>
       <c r="B15" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.N.Y.Y</v>
+        <v>Lo.95.CF1.N.Y.1</v>
       </c>
       <c r="C15">
         <f t="shared" si="3"/>
@@ -6534,63 +6431,54 @@
         <v>Lo</v>
       </c>
       <c r="E15">
-        <f t="shared" ref="E15" si="8">E11</f>
+        <f t="shared" ref="E15" si="7">E11</f>
         <v>95</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I15" s="22">
+        <v>1</v>
       </c>
       <c r="K15" t="s">
         <v>11</v>
       </c>
       <c r="M15" s="11">
-        <f t="shared" ref="M15:S15" si="9">SUMIF($L$2:$L$6,$D$5,M$2:M$6)</f>
+        <f t="shared" ref="M15:S15" si="8">SUMIF($L$2:$L$6,$D$5,M$2:M$6)</f>
         <v>1</v>
       </c>
       <c r="N15" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0571428571428572</v>
+        <f t="shared" si="8"/>
+        <v>1.2</v>
       </c>
       <c r="O15" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0757142857142858</v>
+        <f t="shared" si="8"/>
+        <v>1.2650000000000001</v>
       </c>
       <c r="P15" s="11">
-        <f t="shared" si="9"/>
-        <v>1.0942857142857143</v>
+        <f t="shared" si="8"/>
+        <v>1.33</v>
       </c>
       <c r="Q15" s="11">
-        <f t="shared" si="9"/>
-        <v>1.18</v>
+        <f t="shared" si="8"/>
+        <v>1.63</v>
       </c>
       <c r="R15" s="11">
-        <f t="shared" si="9"/>
-        <v>1.2857142857142856</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="S15" s="11">
-        <f t="shared" si="9"/>
-        <v>1.3777142857142857</v>
-      </c>
-      <c r="AK15">
-        <v>7</v>
-      </c>
-      <c r="AL15" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM15" t="s">
-        <v>150</v>
+        <f t="shared" si="8"/>
+        <v>2.3220000000000001</v>
       </c>
       <c r="AN15" s="10">
-        <f t="shared" ref="AN15:AN78" si="10">AN10+1</f>
+        <f t="shared" ref="AN15:AN78" si="9">AN10+1</f>
         <v>2</v>
       </c>
     </row>
@@ -6600,7 +6488,7 @@
       </c>
       <c r="B16" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.N.Y.Y</v>
+        <v>Hi.95.CF1.N.Y.1</v>
       </c>
       <c r="C16">
         <f t="shared" si="3"/>
@@ -6611,35 +6499,26 @@
         <v>Hi</v>
       </c>
       <c r="E16">
-        <f t="shared" ref="E16" si="11">E12</f>
+        <f t="shared" ref="E16" si="10">E12</f>
         <v>95</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I16" s="22">
+        <v>1</v>
       </c>
       <c r="W16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="AK16">
-        <v>8</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>114</v>
-      </c>
-      <c r="AM16" t="s">
-        <v>148</v>
-      </c>
       <c r="AN16" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -6649,7 +6528,7 @@
       </c>
       <c r="B17" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.Y.Y.Y</v>
+        <v>Lo.0.CF6.Y.Y.1</v>
       </c>
       <c r="C17">
         <f t="shared" si="3"/>
@@ -6660,21 +6539,21 @@
         <v>Lo</v>
       </c>
       <c r="E17">
-        <f t="shared" ref="E17" si="12">E13</f>
+        <f t="shared" ref="E17" si="11">E13</f>
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G17" t="str">
         <f>G9</f>
         <v>Y</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I17" s="22">
+        <v>1</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>7</v>
@@ -6683,27 +6562,27 @@
         <v>2020</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" ref="N17:S17" si="13">Y17</f>
+        <f t="shared" ref="N17:S17" si="12">Y17</f>
         <v>2025</v>
       </c>
       <c r="O17" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2030</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2035</v>
       </c>
       <c r="Q17" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2040</v>
       </c>
       <c r="R17" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2045</v>
       </c>
       <c r="S17" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2050</v>
       </c>
       <c r="W17" s="4" t="s">
@@ -6733,17 +6612,8 @@
       <c r="AE17" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="AK17">
-        <v>9</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>103</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>105</v>
-      </c>
       <c r="AN17" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -6753,7 +6623,7 @@
       </c>
       <c r="B18" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.Y.Y.Y</v>
+        <v>Hi.0.CF6.Y.Y.1</v>
       </c>
       <c r="C18">
         <f t="shared" si="3"/>
@@ -6764,21 +6634,21 @@
         <v>Hi</v>
       </c>
       <c r="E18">
-        <f t="shared" ref="E18" si="14">E14</f>
+        <f t="shared" ref="E18" si="13">E14</f>
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" ref="G18:G72" si="15">G10</f>
+        <f t="shared" ref="G18:G56" si="14">G10</f>
         <v>Y</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I18" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I18" s="22">
+        <v>1</v>
       </c>
       <c r="K18" t="s">
         <v>15</v>
@@ -6815,48 +6685,39 @@
         <v>16</v>
       </c>
       <c r="X18" s="6">
-        <f t="shared" ref="X18:AD20" si="16">M18*X$14</f>
+        <f t="shared" ref="X18:AD20" si="15">M18*X$14</f>
         <v>0</v>
       </c>
       <c r="Y18" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Z18" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AA18" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AB18" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AC18" s="6">
-        <f t="shared" si="16"/>
-        <v>2.947628571428571</v>
+        <f t="shared" si="15"/>
+        <v>4.5851999999999995</v>
       </c>
       <c r="AD18" s="6">
-        <f t="shared" si="16"/>
-        <v>3.1585477714285712</v>
+        <f t="shared" si="15"/>
+        <v>5.3234172000000006</v>
       </c>
       <c r="AE18" t="s">
         <v>17</v>
       </c>
       <c r="AG18" s="2"/>
-      <c r="AK18">
-        <v>10</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>106</v>
-      </c>
-      <c r="AM18" t="s">
-        <v>107</v>
-      </c>
       <c r="AN18" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -6866,7 +6727,7 @@
       </c>
       <c r="B19" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.Y.Y.Y</v>
+        <v>Lo.95.CF6.Y.Y.1</v>
       </c>
       <c r="C19">
         <f t="shared" si="3"/>
@@ -6877,21 +6738,21 @@
         <v>Lo</v>
       </c>
       <c r="E19">
-        <f t="shared" ref="E19" si="17">E15</f>
+        <f t="shared" ref="E19" si="16">E15</f>
         <v>95</v>
       </c>
       <c r="F19" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I19" s="22">
+        <v>1</v>
       </c>
       <c r="K19" t="s">
         <v>18</v>
@@ -6928,47 +6789,38 @@
         <v>19</v>
       </c>
       <c r="X19" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>91.704000000000008</v>
       </c>
       <c r="Y19" s="6">
-        <f t="shared" si="16"/>
-        <v>84.8262</v>
+        <f t="shared" si="15"/>
+        <v>96.28919999999998</v>
       </c>
       <c r="Z19" s="6">
-        <f t="shared" si="16"/>
-        <v>81.384024857142876</v>
+        <f t="shared" si="15"/>
+        <v>95.704587000000018</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="16"/>
-        <v>80.280301714285713</v>
+        <f t="shared" si="15"/>
+        <v>97.573055999999994</v>
       </c>
       <c r="AB19" s="6">
-        <f t="shared" si="16"/>
-        <v>83.863307999999989</v>
+        <f t="shared" si="15"/>
+        <v>115.84507799999999</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="16"/>
-        <v>91.376485714285707</v>
+        <f t="shared" si="15"/>
+        <v>142.1412</v>
       </c>
       <c r="AD19" s="6">
-        <f t="shared" si="16"/>
-        <v>97.914980914285707</v>
+        <f t="shared" si="15"/>
+        <v>165.0259332</v>
       </c>
       <c r="AE19" t="s">
         <v>17</v>
       </c>
-      <c r="AK19">
-        <v>11</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>89</v>
-      </c>
       <c r="AN19" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -6978,7 +6830,7 @@
       </c>
       <c r="B20" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.Y.Y.Y</v>
+        <v>Hi.95.CF6.Y.Y.1</v>
       </c>
       <c r="C20">
         <f t="shared" si="3"/>
@@ -6989,21 +6841,21 @@
         <v>Hi</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E72" si="18">E16</f>
+        <f t="shared" ref="E20:E56" si="17">E16</f>
         <v>95</v>
       </c>
       <c r="F20" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I20" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I20" s="22">
+        <v>1</v>
       </c>
       <c r="K20" t="s">
         <v>21</v>
@@ -7040,47 +6892,38 @@
         <v>22</v>
       </c>
       <c r="X20" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>107.75219999999999</v>
       </c>
       <c r="Y20" s="6">
-        <f t="shared" si="16"/>
-        <v>126.02749714285714</v>
+        <f t="shared" si="15"/>
+        <v>143.05823999999998</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" si="16"/>
-        <v>133.17385885714287</v>
+        <f t="shared" si="15"/>
+        <v>156.60750600000003</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" si="16"/>
-        <v>132.96424971428573</v>
+        <f t="shared" si="15"/>
+        <v>161.60537400000001</v>
       </c>
       <c r="AB20" s="6">
-        <f t="shared" si="16"/>
-        <v>140.673936</v>
+        <f t="shared" si="15"/>
+        <v>194.320776</v>
       </c>
       <c r="AC20" s="6">
-        <f t="shared" si="16"/>
-        <v>147.38142857142856</v>
+        <f t="shared" si="15"/>
+        <v>229.26</v>
       </c>
       <c r="AD20" s="6">
-        <f t="shared" si="16"/>
-        <v>151.61029302857142</v>
+        <f t="shared" si="15"/>
+        <v>255.52402559999999</v>
       </c>
       <c r="AE20" t="s">
         <v>17</v>
       </c>
-      <c r="AK20">
-        <v>12</v>
-      </c>
-      <c r="AL20" t="s">
-        <v>85</v>
-      </c>
-      <c r="AM20" t="s">
-        <v>94</v>
-      </c>
       <c r="AN20" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -7090,7 +6933,7 @@
       </c>
       <c r="B21" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.N.Y.Y</v>
+        <v>Lo.0.CF6.N.Y.1</v>
       </c>
       <c r="C21">
         <f t="shared" si="3"/>
@@ -7101,21 +6944,21 @@
         <v>Lo</v>
       </c>
       <c r="E21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I21" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I21" s="22">
+        <v>1</v>
       </c>
       <c r="K21" t="s">
         <v>23</v>
@@ -7156,27 +6999,27 @@
         <v>2.2925999999999997</v>
       </c>
       <c r="Y21" s="6">
-        <f t="shared" ref="Y21:AD21" si="19">X21</f>
+        <f t="shared" ref="Y21:AD21" si="18">X21</f>
         <v>2.2925999999999997</v>
       </c>
       <c r="Z21" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AA21" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AB21" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AC21" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AD21" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.2925999999999997</v>
       </c>
       <c r="AE21" t="s">
@@ -7186,7 +7029,7 @@
         <v>20</v>
       </c>
       <c r="AN21" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -7196,7 +7039,7 @@
       </c>
       <c r="B22" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.N.Y.Y</v>
+        <v>Hi.0.CF6.N.Y.1</v>
       </c>
       <c r="C22">
         <f t="shared" si="3"/>
@@ -7207,58 +7050,58 @@
         <v>Hi</v>
       </c>
       <c r="E22">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I22" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I22" s="22">
+        <v>1</v>
       </c>
       <c r="W22" s="10" t="s">
         <v>25</v>
       </c>
       <c r="X22" s="6">
-        <f t="shared" ref="X22:AD22" si="20">X14-SUM(X19:X21)</f>
+        <f t="shared" ref="X22:AD22" si="19">X14-SUM(X19:X21)</f>
         <v>27.511200000000002</v>
       </c>
       <c r="Y22" s="6">
-        <f t="shared" si="20"/>
-        <v>29.214274285714311</v>
+        <f t="shared" si="19"/>
+        <v>33.471960000000024</v>
       </c>
       <c r="Z22" s="6">
-        <f t="shared" si="20"/>
-        <v>29.767773428571417</v>
+        <f t="shared" si="19"/>
+        <v>35.409206999999981</v>
       </c>
       <c r="AA22" s="6">
-        <f t="shared" si="20"/>
-        <v>35.338791428571426</v>
+        <f t="shared" si="19"/>
+        <v>43.444770000000005</v>
       </c>
       <c r="AB22" s="6">
-        <f t="shared" si="20"/>
-        <v>43.696956</v>
+        <f t="shared" si="19"/>
+        <v>61.235345999999993</v>
       </c>
       <c r="AC22" s="6">
-        <f t="shared" si="20"/>
-        <v>53.712342857142858</v>
+        <f t="shared" si="19"/>
+        <v>84.826199999999972</v>
       </c>
       <c r="AD22" s="6">
-        <f t="shared" si="20"/>
-        <v>64.036903200000012</v>
+        <f t="shared" si="19"/>
+        <v>109.4991612</v>
       </c>
       <c r="AE22" t="s">
         <v>17</v>
       </c>
       <c r="AN22" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -7268,7 +7111,7 @@
       </c>
       <c r="B23" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.N.Y.Y</v>
+        <v>Lo.95.CF6.N.Y.1</v>
       </c>
       <c r="C23">
         <f t="shared" si="3"/>
@@ -7279,27 +7122,27 @@
         <v>Lo</v>
       </c>
       <c r="E23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I23" s="22">
+        <v>1</v>
       </c>
       <c r="W23" t="s">
         <v>26</v>
       </c>
       <c r="AN23" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -7309,7 +7152,7 @@
       </c>
       <c r="B24" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.N.Y.Y</v>
+        <v>Hi.95.CF6.N.Y.1</v>
       </c>
       <c r="C24">
         <f t="shared" si="3"/>
@@ -7320,51 +7163,51 @@
         <v>Hi</v>
       </c>
       <c r="E24">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F24" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I24" s="22">
+        <v>1</v>
       </c>
       <c r="K24" s="10" t="s">
         <v>27</v>
       </c>
       <c r="M24" s="11">
-        <f t="shared" ref="M24:S24" si="21">SUMIF($L$2:$L$6,$E$5,M$2:M$6)</f>
+        <f t="shared" ref="M24:S24" si="20">SUMIF($L$2:$L$6,$E$5,M$2:M$6)</f>
         <v>0</v>
       </c>
       <c r="N24" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="O24" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="P24" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q24" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="R24" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="S24" s="11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="W24" t="s">
@@ -7397,7 +7240,7 @@
         <v>29</v>
       </c>
       <c r="AN24" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7407,7 +7250,7 @@
       </c>
       <c r="B25" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.Y.N.Y</v>
+        <v>Lo.0.CF1.Y.Y.0.25</v>
       </c>
       <c r="C25">
         <f t="shared" si="3"/>
@@ -7418,7 +7261,7 @@
         <v>Lo</v>
       </c>
       <c r="E25">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F25" t="str">
@@ -7426,17 +7269,17 @@
         <v>CF1</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I25" s="23">
+        <v>0.25</v>
       </c>
       <c r="AN25" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7446,7 +7289,7 @@
       </c>
       <c r="B26" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.Y.N.Y</v>
+        <v>Hi.0.CF1.Y.Y.0.25</v>
       </c>
       <c r="C26">
         <f t="shared" si="3"/>
@@ -7457,28 +7300,28 @@
         <v>Hi</v>
       </c>
       <c r="E26">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" ref="F26:F72" si="22">F10</f>
+        <f t="shared" ref="F26:F56" si="21">F10</f>
         <v>CF1</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I26" s="23">
+        <v>0.25</v>
       </c>
       <c r="W26" s="5" t="s">
         <v>12</v>
       </c>
       <c r="AN26" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7488,7 +7331,7 @@
       </c>
       <c r="B27" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.Y.N.Y</v>
+        <v>Lo.95.CF1.Y.Y.0.25</v>
       </c>
       <c r="C27">
         <f t="shared" si="3"/>
@@ -7499,52 +7342,52 @@
         <v>Lo</v>
       </c>
       <c r="E27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I27" s="23">
+        <v>0.25</v>
       </c>
       <c r="W27" s="4" t="s">
         <v>30</v>
       </c>
       <c r="X27" s="4">
-        <f t="shared" ref="X27:AD27" si="23">X17</f>
+        <f t="shared" ref="X27:AD27" si="22">X17</f>
         <v>2022</v>
       </c>
       <c r="Y27" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2025</v>
       </c>
       <c r="Z27" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2030</v>
       </c>
       <c r="AA27" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2035</v>
       </c>
       <c r="AB27" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2040</v>
       </c>
       <c r="AC27" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2045</v>
       </c>
       <c r="AD27" s="4">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>2050</v>
       </c>
       <c r="AE27" s="4" t="s">
@@ -7554,7 +7397,7 @@
         <v>31</v>
       </c>
       <c r="AN27" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7564,7 +7407,7 @@
       </c>
       <c r="B28" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.Y.N.Y</v>
+        <v>Hi.95.CF1.Y.Y.0.25</v>
       </c>
       <c r="C28">
         <f t="shared" si="3"/>
@@ -7575,22 +7418,22 @@
         <v>Hi</v>
       </c>
       <c r="E28">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G28" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I28" s="23">
+        <v>0.25</v>
       </c>
       <c r="U28" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,Veda!$W$11)</f>
@@ -7615,7 +7458,7 @@
         <v>34</v>
       </c>
       <c r="AN28" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -7625,7 +7468,7 @@
       </c>
       <c r="B29" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.N.N.Y</v>
+        <v>Lo.0.CF1.N.Y.0.25</v>
       </c>
       <c r="C29">
         <f t="shared" si="3"/>
@@ -7636,22 +7479,22 @@
         <v>Lo</v>
       </c>
       <c r="E29">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I29" s="23">
+        <v>0.25</v>
       </c>
       <c r="U29" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,Veda!$W$11)</f>
@@ -7676,7 +7519,7 @@
         <v>34</v>
       </c>
       <c r="AN29" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -7686,7 +7529,7 @@
       </c>
       <c r="B30" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.N.N.Y</v>
+        <v>Hi.0.CF1.N.Y.0.25</v>
       </c>
       <c r="C30">
         <f t="shared" si="3"/>
@@ -7697,25 +7540,25 @@
         <v>Hi</v>
       </c>
       <c r="E30">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G30" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I30" s="23">
+        <v>0.25</v>
       </c>
       <c r="AN30" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -7725,7 +7568,7 @@
       </c>
       <c r="B31" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.N.N.Y</v>
+        <v>Lo.95.CF1.N.Y.0.25</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
@@ -7736,25 +7579,25 @@
         <v>Lo</v>
       </c>
       <c r="E31">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I31" s="23">
+        <v>0.25</v>
       </c>
       <c r="AN31" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -7764,7 +7607,7 @@
       </c>
       <c r="B32" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.N.N.Y</v>
+        <v>Hi.95.CF1.N.Y.0.25</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
@@ -7775,29 +7618,29 @@
         <v>Hi</v>
       </c>
       <c r="E32">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I32" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I32" s="23">
+        <v>0.25</v>
       </c>
       <c r="W32" s="5" t="str">
         <f>IF($G$5="N","~TFM_UPD","DEF correction active")</f>
-        <v>DEF correction active</v>
+        <v>~TFM_UPD</v>
       </c>
       <c r="AN32" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -7807,7 +7650,7 @@
       </c>
       <c r="B33" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.Y.N.Y</v>
+        <v>Lo.0.CF6.Y.Y.0.25</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
@@ -7818,22 +7661,22 @@
         <v>Lo</v>
       </c>
       <c r="E33">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I33" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I33" s="23">
+        <v>0.25</v>
       </c>
       <c r="W33" s="4" t="s">
         <v>14</v>
@@ -7842,13 +7685,13 @@
         <v>13</v>
       </c>
       <c r="Y33" s="4" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="Z33" s="4" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="AN33" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -7858,7 +7701,7 @@
       </c>
       <c r="B34" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.Y.N.Y</v>
+        <v>Hi.0.CF6.Y.Y.0.25</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
@@ -7869,37 +7712,37 @@
         <v>Hi</v>
       </c>
       <c r="E34">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I34" s="23">
+        <v>0.25</v>
       </c>
       <c r="W34" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="X34" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="Y34" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="Z34">
         <v>0</v>
       </c>
       <c r="AN34" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
@@ -7909,7 +7752,7 @@
       </c>
       <c r="B35" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.Y.N.Y</v>
+        <v>Lo.95.CF6.Y.Y.0.25</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
@@ -7920,25 +7763,25 @@
         <v>Lo</v>
       </c>
       <c r="E35">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I35" s="23">
+        <v>0.25</v>
       </c>
       <c r="AN35" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
@@ -7948,7 +7791,7 @@
       </c>
       <c r="B36" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.Y.N.Y</v>
+        <v>Hi.95.CF6.Y.Y.0.25</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
@@ -7959,28 +7802,28 @@
         <v>Hi</v>
       </c>
       <c r="E36">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I36" s="23">
+        <v>0.25</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="AN36" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
@@ -7990,7 +7833,7 @@
       </c>
       <c r="B37" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.N.N.Y</v>
+        <v>Lo.0.CF6.N.Y.0.25</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
@@ -8001,22 +7844,22 @@
         <v>Lo</v>
       </c>
       <c r="E37">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I37" s="23">
+        <v>0.25</v>
       </c>
       <c r="K37" t="s">
         <v>74</v>
@@ -8034,19 +7877,19 @@
         <v>1.0510100500999999</v>
       </c>
       <c r="P37" s="11">
-        <f t="shared" ref="P37:S37" si="24">O37*(1+$U37)^5</f>
+        <f t="shared" ref="P37:S37" si="23">O37*(1+$U37)^5</f>
         <v>1.1046221254112043</v>
       </c>
       <c r="Q37" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1.1609689553699982</v>
       </c>
       <c r="R37" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1.2201900399479664</v>
       </c>
       <c r="S37" s="11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>1.2824319950172332</v>
       </c>
       <c r="U37">
@@ -8054,10 +7897,10 @@
       </c>
       <c r="W37" s="5" t="str">
         <f>IF($G$5="N","~TFM_INS: limtype=LO","DEF correction active")</f>
-        <v>DEF correction active</v>
+        <v>~TFM_INS: limtype=LO</v>
       </c>
       <c r="AN37" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
@@ -8067,7 +7910,7 @@
       </c>
       <c r="B38" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.N.N.Y</v>
+        <v>Hi.0.CF6.N.Y.0.25</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
@@ -8078,22 +7921,22 @@
         <v>Hi</v>
       </c>
       <c r="E38">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F38" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I38" s="23">
+        <v>0.25</v>
       </c>
       <c r="K38" t="s">
         <v>75</v>
@@ -8103,46 +7946,46 @@
         <v>1</v>
       </c>
       <c r="N38" s="11">
-        <f t="shared" ref="N38:S38" si="25">M38</f>
+        <f t="shared" ref="N38:S38" si="24">M38</f>
         <v>1</v>
       </c>
       <c r="O38" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="P38" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q38" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="R38" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="S38" s="11">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="W38" s="4" t="s">
         <v>14</v>
       </c>
       <c r="X38" s="4" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="Y38" s="4" t="s">
         <v>37</v>
       </c>
       <c r="Z38" s="4" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="AA38" s="4" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="AN38" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
     </row>
@@ -8152,7 +7995,7 @@
       </c>
       <c r="B39" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.N.N.Y</v>
+        <v>Lo.95.CF6.N.Y.0.25</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -8163,22 +8006,22 @@
         <v>Lo</v>
       </c>
       <c r="E39">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I39" s="23">
+        <v>0.25</v>
       </c>
       <c r="K39" t="s">
         <v>76</v>
@@ -8188,34 +8031,34 @@
         <v>1</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" ref="N39:S39" si="26">M39</f>
+        <f t="shared" ref="N39:S39" si="25">M39</f>
         <v>1</v>
       </c>
       <c r="O39" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="P39" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="Q39" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R39" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="S39" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="W39" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="X39" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="Y39">
         <v>0</v>
@@ -8224,10 +8067,10 @@
         <v>-13</v>
       </c>
       <c r="AA39" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="AN39" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8237,7 +8080,7 @@
       </c>
       <c r="B40" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.N.N.Y</v>
+        <v>Hi.95.CF6.N.Y.0.25</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
@@ -8248,22 +8091,22 @@
         <v>Hi</v>
       </c>
       <c r="E40">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G40" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>155</v>
+        <v>135</v>
+      </c>
+      <c r="I40" s="23">
+        <v>0.25</v>
       </c>
       <c r="K40" t="s">
         <v>77</v>
@@ -8273,31 +8116,31 @@
         <v>1</v>
       </c>
       <c r="N40" s="11">
-        <f t="shared" ref="N40:S40" si="27">M40</f>
+        <f t="shared" ref="N40:S40" si="26">M40</f>
         <v>1</v>
       </c>
       <c r="O40" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="P40" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="Q40" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="R40" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="S40" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>1</v>
       </c>
       <c r="W40" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="Y40">
         <v>0</v>
@@ -8306,10 +8149,10 @@
         <v>-13</v>
       </c>
       <c r="AA40" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="AN40" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8319,7 +8162,7 @@
       </c>
       <c r="B41" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.Y.Y.N</v>
+        <v>Lo.0.CF1.Y.Y.2</v>
       </c>
       <c r="C41">
         <f t="shared" si="3"/>
@@ -8330,26 +8173,25 @@
         <v>Lo</v>
       </c>
       <c r="E41">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F41" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G41" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
-      <c r="H41" s="15" t="str">
-        <f>H9</f>
-        <v>Y</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>156</v>
+      <c r="H41" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I41" s="23">
+        <v>2</v>
       </c>
       <c r="AN41" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8359,7 +8201,7 @@
       </c>
       <c r="B42" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.Y.Y.N</v>
+        <v>Hi.0.CF1.Y.Y.2</v>
       </c>
       <c r="C42">
         <f t="shared" si="3"/>
@@ -8370,26 +8212,25 @@
         <v>Hi</v>
       </c>
       <c r="E42">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F42" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G42" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
-      <c r="H42" s="15" t="str">
-        <f t="shared" ref="H42:H72" si="28">H10</f>
-        <v>Y</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>156</v>
+      <c r="H42" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I42" s="23">
+        <v>2</v>
       </c>
       <c r="AN42" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8399,7 +8240,7 @@
       </c>
       <c r="B43" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.Y.Y.N</v>
+        <v>Lo.95.CF1.Y.Y.2</v>
       </c>
       <c r="C43">
         <f t="shared" si="3"/>
@@ -8410,29 +8251,28 @@
         <v>Lo</v>
       </c>
       <c r="E43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F43" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G43" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
-      <c r="H43" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>156</v>
+      <c r="H43" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I43" s="23">
+        <v>2</v>
       </c>
       <c r="K43" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="AN43" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
     </row>
@@ -8442,7 +8282,7 @@
       </c>
       <c r="B44" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.Y.Y.N</v>
+        <v>Hi.95.CF1.Y.Y.2</v>
       </c>
       <c r="C44">
         <f t="shared" si="3"/>
@@ -8453,29 +8293,28 @@
         <v>Hi</v>
       </c>
       <c r="E44">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F44" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G44" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
-      <c r="H44" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>156</v>
+      <c r="H44" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I44" s="23">
+        <v>2</v>
       </c>
       <c r="K44" t="s">
         <v>13</v>
       </c>
       <c r="L44" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M44">
         <v>2022</v>
@@ -8485,23 +8324,23 @@
         <v>2025</v>
       </c>
       <c r="O44">
-        <f t="shared" ref="O44:S44" si="29">O17</f>
+        <f t="shared" ref="O44:S44" si="27">O17</f>
         <v>2030</v>
       </c>
       <c r="P44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>2035</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>2040</v>
       </c>
       <c r="R44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>2045</v>
       </c>
       <c r="S44">
-        <f t="shared" si="29"/>
+        <f t="shared" si="27"/>
         <v>2050</v>
       </c>
       <c r="V44" t="s">
@@ -8511,7 +8350,7 @@
         <v>83</v>
       </c>
       <c r="AN44" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8521,7 +8360,7 @@
       </c>
       <c r="B45" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.N.Y.N</v>
+        <v>Lo.0.CF1.N.Y.2</v>
       </c>
       <c r="C45">
         <f t="shared" si="3"/>
@@ -8532,23 +8371,22 @@
         <v>Lo</v>
       </c>
       <c r="E45">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F45" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G45" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
-      <c r="H45" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>156</v>
+      <c r="H45" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I45" s="23">
+        <v>2</v>
       </c>
       <c r="K45" t="s">
         <v>78</v>
@@ -8558,31 +8396,31 @@
         <v>Gas</v>
       </c>
       <c r="M45">
-        <f t="shared" ref="M45:S48" si="30">AVERAGE($V45:$W45)*M37</f>
+        <f t="shared" ref="M45:S48" si="28">AVERAGE($V45:$W45)*M37</f>
         <v>25.2</v>
       </c>
       <c r="N45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>25.2</v>
       </c>
       <c r="O45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>26.485453262519997</v>
       </c>
       <c r="P45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>27.836477560362347</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>29.256417675323956</v>
       </c>
       <c r="R45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>30.748789006688753</v>
       </c>
       <c r="S45">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>32.317286274434274</v>
       </c>
       <c r="V45">
@@ -8594,7 +8432,7 @@
         <v>25.2</v>
       </c>
       <c r="AN45" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8604,7 +8442,7 @@
       </c>
       <c r="B46" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.N.Y.N</v>
+        <v>Hi.0.CF1.N.Y.2</v>
       </c>
       <c r="C46">
         <f t="shared" si="3"/>
@@ -8615,57 +8453,56 @@
         <v>Hi</v>
       </c>
       <c r="E46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F46" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G46" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
-      <c r="H46" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>156</v>
+      <c r="H46" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I46" s="23">
+        <v>2</v>
       </c>
       <c r="K46" t="s">
         <v>79</v>
       </c>
       <c r="L46" t="str">
-        <f t="shared" ref="L46:L48" si="31">K46</f>
+        <f t="shared" ref="L46:L48" si="29">K46</f>
         <v>Coal</v>
       </c>
       <c r="M46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="N46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="O46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="P46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="R46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="S46">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>4.68</v>
       </c>
       <c r="V46">
@@ -8677,7 +8514,7 @@
         <v>5.04</v>
       </c>
       <c r="AN46" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8687,7 +8524,7 @@
       </c>
       <c r="B47" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.N.Y.N</v>
+        <v>Lo.95.CF1.N.Y.2</v>
       </c>
       <c r="C47">
         <f t="shared" si="3"/>
@@ -8698,57 +8535,56 @@
         <v>Lo</v>
       </c>
       <c r="E47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F47" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G47" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
-      <c r="H47" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>156</v>
+      <c r="H47" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I47" s="23">
+        <v>2</v>
       </c>
       <c r="K47" t="s">
         <v>80</v>
       </c>
       <c r="L47" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>Oil</v>
       </c>
       <c r="M47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="N47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="O47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="P47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="R47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="S47">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>79.2</v>
       </c>
       <c r="V47">
@@ -8760,7 +8596,7 @@
         <v>79.2</v>
       </c>
       <c r="AN47" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8770,7 +8606,7 @@
       </c>
       <c r="B48" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.N.Y.N</v>
+        <v>Hi.95.CF1.N.Y.2</v>
       </c>
       <c r="C48">
         <f t="shared" si="3"/>
@@ -8781,33 +8617,32 @@
         <v>Hi</v>
       </c>
       <c r="E48">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F48" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF1</v>
       </c>
       <c r="G48" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
-      <c r="H48" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>156</v>
+      <c r="H48" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I48" s="23">
+        <v>2</v>
       </c>
       <c r="K48" t="s">
         <v>81</v>
       </c>
       <c r="L48" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>Bioenergy</v>
       </c>
       <c r="M48">
-        <f t="shared" si="30"/>
+        <f t="shared" si="28"/>
         <v>22</v>
       </c>
       <c r="S48" t="e">
@@ -8823,7 +8658,7 @@
         <v>26</v>
       </c>
       <c r="AN48" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -8833,7 +8668,7 @@
       </c>
       <c r="B49" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.Y.Y.N</v>
+        <v>Lo.0.CF6.Y.Y.2</v>
       </c>
       <c r="C49">
         <f t="shared" si="3"/>
@@ -8844,26 +8679,25 @@
         <v>Lo</v>
       </c>
       <c r="E49">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F49" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G49" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
-      <c r="H49" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>156</v>
+      <c r="H49" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I49" s="23">
+        <v>2</v>
       </c>
       <c r="AN49" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -8873,7 +8707,7 @@
       </c>
       <c r="B50" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.Y.Y.N</v>
+        <v>Hi.0.CF6.Y.Y.2</v>
       </c>
       <c r="C50">
         <f t="shared" si="3"/>
@@ -8884,26 +8718,25 @@
         <v>Hi</v>
       </c>
       <c r="E50">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F50" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G50" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
-      <c r="H50" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>156</v>
+      <c r="H50" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I50" s="23">
+        <v>2</v>
       </c>
       <c r="AN50" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -8913,7 +8746,7 @@
       </c>
       <c r="B51" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.Y.Y.N</v>
+        <v>Lo.95.CF6.Y.Y.2</v>
       </c>
       <c r="C51">
         <f t="shared" si="3"/>
@@ -8924,30 +8757,29 @@
         <v>Lo</v>
       </c>
       <c r="E51">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F51" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G51" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
-      <c r="H51" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>156</v>
+      <c r="H51" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I51" s="23">
+        <v>2</v>
       </c>
       <c r="W51" s="5" t="str">
         <f>IF($H$5="N","~TFM_INS: limtype=LO","GAS available")</f>
         <v>GAS available</v>
       </c>
       <c r="AN51" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -8957,7 +8789,7 @@
       </c>
       <c r="B52" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.Y.Y.N</v>
+        <v>Hi.95.CF6.Y.Y.2</v>
       </c>
       <c r="C52">
         <f t="shared" si="3"/>
@@ -8968,41 +8800,40 @@
         <v>Hi</v>
       </c>
       <c r="E52">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F52" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>Y</v>
       </c>
-      <c r="H52" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>156</v>
+      <c r="H52" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I52" s="23">
+        <v>2</v>
       </c>
       <c r="W52" s="4" t="s">
         <v>14</v>
       </c>
       <c r="X52" s="4" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="Y52" s="4" t="s">
         <v>37</v>
       </c>
       <c r="Z52" s="4" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="AA52" s="4" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="AN52" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -9012,7 +8843,7 @@
       </c>
       <c r="B53" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.N.Y.N</v>
+        <v>Lo.0.CF6.N.Y.2</v>
       </c>
       <c r="C53">
         <f t="shared" si="3"/>
@@ -9023,38 +8854,37 @@
         <v>Lo</v>
       </c>
       <c r="E53">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G53" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
-      <c r="H53" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>156</v>
+      <c r="H53" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I53" s="23">
+        <v>2</v>
       </c>
       <c r="W53" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="X53" s="20" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="Z53">
         <v>2100</v>
       </c>
       <c r="AA53" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="AN53" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -9064,7 +8894,7 @@
       </c>
       <c r="B54" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.N.Y.N</v>
+        <v>Hi.0.CF6.N.Y.2</v>
       </c>
       <c r="C54">
         <f t="shared" si="3"/>
@@ -9075,26 +8905,25 @@
         <v>Hi</v>
       </c>
       <c r="E54">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="F54" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G54" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
-      <c r="H54" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I54" s="15" t="s">
-        <v>156</v>
+      <c r="H54" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I54" s="23">
+        <v>2</v>
       </c>
       <c r="AN54" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
@@ -9104,7 +8933,7 @@
       </c>
       <c r="B55" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.N.Y.N</v>
+        <v>Lo.95.CF6.N.Y.2</v>
       </c>
       <c r="C55">
         <f t="shared" si="3"/>
@@ -9115,26 +8944,25 @@
         <v>Lo</v>
       </c>
       <c r="E55">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F55" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G55" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
-      <c r="H55" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I55" s="15" t="s">
-        <v>156</v>
+      <c r="H55" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I55" s="23">
+        <v>2</v>
       </c>
       <c r="AN55" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
@@ -9144,7 +8972,7 @@
       </c>
       <c r="B56" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.N.Y.N</v>
+        <v>Hi.95.CF6.N.Y.2</v>
       </c>
       <c r="C56">
         <f t="shared" si="3"/>
@@ -9155,731 +8983,228 @@
         <v>Hi</v>
       </c>
       <c r="E56">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="F56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>CF6</v>
       </c>
       <c r="G56" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>N</v>
       </c>
-      <c r="H56" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>Y</v>
-      </c>
-      <c r="I56" s="15" t="s">
-        <v>156</v>
+      <c r="H56" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I56" s="23">
+        <v>2</v>
       </c>
       <c r="AN56" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:40" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A57">
-        <v>5</v>
-      </c>
-      <c r="B57" t="str">
-        <f t="shared" si="2"/>
-        <v>Lo.0.CF1.Y.N.N</v>
-      </c>
-      <c r="C57">
-        <f t="shared" si="3"/>
-        <v>49</v>
-      </c>
-      <c r="D57" t="str">
-        <f t="shared" si="4"/>
-        <v>Lo</v>
-      </c>
-      <c r="E57">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F57" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="G57" t="str">
-        <f t="shared" si="15"/>
-        <v>Y</v>
-      </c>
-      <c r="H57" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I57" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="W57" s="5" t="str">
-        <f>IF($I$5="N","~TFM_UPD","Transmission costs active")</f>
-        <v>Transmission costs active</v>
+        <f>IF($I$5&lt;&gt;1,"~TFM_UPD","Transmission costs default")</f>
+        <v>~TFM_UPD</v>
+      </c>
+      <c r="AC57" s="5" t="str">
+        <f>IF($I$5&lt;1,"~TFM_INS","No hurdle rate")</f>
+        <v>~TFM_INS</v>
+      </c>
+      <c r="AG57" s="5" t="str">
+        <f>IF($I$5&gt;1,"~TFM_INS","No ELife")</f>
+        <v>No ELife</v>
       </c>
       <c r="AN57" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:40" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A58">
-        <v>5</v>
-      </c>
-      <c r="B58" t="str">
-        <f t="shared" si="2"/>
-        <v>Hi.0.CF1.Y.N.N</v>
-      </c>
-      <c r="C58">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-      <c r="D58" t="str">
-        <f t="shared" si="4"/>
-        <v>Hi</v>
-      </c>
-      <c r="E58">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F58" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="G58" t="str">
-        <f t="shared" si="15"/>
-        <v>Y</v>
-      </c>
-      <c r="H58" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="W58" s="4" t="s">
         <v>14</v>
       </c>
       <c r="X58" s="4" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="Y58" s="4" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
       <c r="Z58" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD58" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AE58" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH58" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI58" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN58" s="10">
+        <f t="shared" si="9"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="W59" t="s">
+        <v>154</v>
+      </c>
+      <c r="X59" s="20"/>
+      <c r="Y59" t="str">
+        <f>"*"&amp;$I$5</f>
+        <v>*0.25</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>155</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD59">
+        <v>0.02</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG59" t="s">
         <v>158</v>
       </c>
-      <c r="AA58" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AN58" s="10">
-        <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A59">
-        <v>5</v>
-      </c>
-      <c r="B59" t="str">
-        <f t="shared" si="2"/>
-        <v>Lo.95.CF1.Y.N.N</v>
-      </c>
-      <c r="C59">
-        <f t="shared" si="3"/>
-        <v>51</v>
-      </c>
-      <c r="D59" t="str">
-        <f t="shared" si="4"/>
-        <v>Lo</v>
-      </c>
-      <c r="E59">
-        <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="F59" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="G59" t="str">
-        <f t="shared" si="15"/>
-        <v>Y</v>
-      </c>
-      <c r="H59" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I59" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="W59" t="s">
-        <v>174</v>
-      </c>
-      <c r="X59" s="20"/>
-      <c r="Z59">
-        <v>0</v>
-      </c>
-      <c r="AA59" t="s">
-        <v>175</v>
+      <c r="AH59">
+        <v>30</v>
+      </c>
+      <c r="AI59" t="s">
+        <v>155</v>
       </c>
       <c r="AN59" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A60">
-        <v>5</v>
-      </c>
-      <c r="B60" t="str">
-        <f t="shared" si="2"/>
-        <v>Hi.95.CF1.Y.N.N</v>
-      </c>
-      <c r="C60">
-        <f t="shared" si="3"/>
-        <v>52</v>
-      </c>
-      <c r="D60" t="str">
-        <f t="shared" si="4"/>
-        <v>Hi</v>
-      </c>
-      <c r="E60">
-        <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="F60" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="G60" t="str">
-        <f t="shared" si="15"/>
-        <v>Y</v>
-      </c>
-      <c r="H60" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I60" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="AN60" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A61">
-        <v>5</v>
-      </c>
-      <c r="B61" t="str">
-        <f t="shared" si="2"/>
-        <v>Lo.0.CF1.N.N.N</v>
-      </c>
-      <c r="C61">
-        <f t="shared" si="3"/>
-        <v>53</v>
-      </c>
-      <c r="D61" t="str">
-        <f t="shared" si="4"/>
-        <v>Lo</v>
-      </c>
-      <c r="E61">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F61" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="G61" t="str">
-        <f t="shared" si="15"/>
-        <v>N</v>
-      </c>
-      <c r="H61" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I61" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="AN61" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A62">
-        <v>5</v>
-      </c>
-      <c r="B62" t="str">
-        <f t="shared" si="2"/>
-        <v>Hi.0.CF1.N.N.N</v>
-      </c>
-      <c r="C62">
-        <f t="shared" si="3"/>
-        <v>54</v>
-      </c>
-      <c r="D62" t="str">
-        <f t="shared" si="4"/>
-        <v>Hi</v>
-      </c>
-      <c r="E62">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F62" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="G62" t="str">
-        <f t="shared" si="15"/>
-        <v>N</v>
-      </c>
-      <c r="H62" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I62" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="AN62" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A63">
-        <v>5</v>
-      </c>
-      <c r="B63" t="str">
-        <f t="shared" si="2"/>
-        <v>Lo.95.CF1.N.N.N</v>
-      </c>
-      <c r="C63">
-        <f t="shared" si="3"/>
-        <v>55</v>
-      </c>
-      <c r="D63" t="str">
-        <f t="shared" si="4"/>
-        <v>Lo</v>
-      </c>
-      <c r="E63">
-        <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="F63" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="G63" t="str">
-        <f t="shared" si="15"/>
-        <v>N</v>
-      </c>
-      <c r="H63" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I63" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="AN63" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A64">
-        <v>5</v>
-      </c>
-      <c r="B64" t="str">
-        <f t="shared" si="2"/>
-        <v>Hi.95.CF1.N.N.N</v>
-      </c>
-      <c r="C64">
-        <f t="shared" si="3"/>
-        <v>56</v>
-      </c>
-      <c r="D64" t="str">
-        <f t="shared" si="4"/>
-        <v>Hi</v>
-      </c>
-      <c r="E64">
-        <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="F64" t="str">
-        <f t="shared" si="22"/>
-        <v>CF1</v>
-      </c>
-      <c r="G64" t="str">
-        <f t="shared" si="15"/>
-        <v>N</v>
-      </c>
-      <c r="H64" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I64" s="15" t="s">
-        <v>156</v>
-      </c>
       <c r="AN64" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A65">
-        <v>5</v>
-      </c>
-      <c r="B65" t="str">
-        <f t="shared" si="2"/>
-        <v>Lo.0.CF6.Y.N.N</v>
-      </c>
-      <c r="C65">
-        <f t="shared" si="3"/>
-        <v>57</v>
-      </c>
-      <c r="D65" t="str">
-        <f t="shared" si="4"/>
-        <v>Lo</v>
-      </c>
-      <c r="E65">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F65" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="G65" t="str">
-        <f t="shared" si="15"/>
-        <v>Y</v>
-      </c>
-      <c r="H65" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I65" s="15" t="s">
-        <v>156</v>
-      </c>
+    <row r="65" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN65" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A66">
-        <v>5</v>
-      </c>
-      <c r="B66" t="str">
-        <f t="shared" si="2"/>
-        <v>Hi.0.CF6.Y.N.N</v>
-      </c>
-      <c r="C66">
-        <f t="shared" si="3"/>
-        <v>58</v>
-      </c>
-      <c r="D66" t="str">
-        <f t="shared" si="4"/>
-        <v>Hi</v>
-      </c>
-      <c r="E66">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F66" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="G66" t="str">
-        <f t="shared" si="15"/>
-        <v>Y</v>
-      </c>
-      <c r="H66" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I66" s="15" t="s">
-        <v>156</v>
-      </c>
+    <row r="66" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN66" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A67">
-        <v>5</v>
-      </c>
-      <c r="B67" t="str">
-        <f t="shared" si="2"/>
-        <v>Lo.95.CF6.Y.N.N</v>
-      </c>
-      <c r="C67">
-        <f t="shared" si="3"/>
-        <v>59</v>
-      </c>
-      <c r="D67" t="str">
-        <f t="shared" si="4"/>
-        <v>Lo</v>
-      </c>
-      <c r="E67">
-        <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="F67" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="G67" t="str">
-        <f t="shared" si="15"/>
-        <v>Y</v>
-      </c>
-      <c r="H67" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I67" s="15" t="s">
-        <v>156</v>
-      </c>
+    <row r="67" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN67" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A68">
-        <v>5</v>
-      </c>
-      <c r="B68" t="str">
-        <f t="shared" si="2"/>
-        <v>Hi.95.CF6.Y.N.N</v>
-      </c>
-      <c r="C68">
-        <f t="shared" si="3"/>
-        <v>60</v>
-      </c>
-      <c r="D68" t="str">
-        <f t="shared" si="4"/>
-        <v>Hi</v>
-      </c>
-      <c r="E68">
-        <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="F68" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="G68" t="str">
-        <f t="shared" si="15"/>
-        <v>Y</v>
-      </c>
-      <c r="H68" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I68" s="15" t="s">
-        <v>156</v>
-      </c>
+    <row r="68" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN68" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A69">
-        <v>5</v>
-      </c>
-      <c r="B69" t="str">
-        <f t="shared" si="2"/>
-        <v>Lo.0.CF6.N.N.N</v>
-      </c>
-      <c r="C69">
-        <f t="shared" si="3"/>
-        <v>61</v>
-      </c>
-      <c r="D69" t="str">
-        <f t="shared" si="4"/>
-        <v>Lo</v>
-      </c>
-      <c r="E69">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F69" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="G69" t="str">
-        <f t="shared" si="15"/>
-        <v>N</v>
-      </c>
-      <c r="H69" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I69" s="15" t="s">
-        <v>156</v>
-      </c>
+    <row r="69" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN69" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A70">
-        <v>5</v>
-      </c>
-      <c r="B70" t="str">
-        <f t="shared" si="2"/>
-        <v>Hi.0.CF6.N.N.N</v>
-      </c>
-      <c r="C70">
-        <f t="shared" si="3"/>
-        <v>62</v>
-      </c>
-      <c r="D70" t="str">
-        <f t="shared" si="4"/>
-        <v>Hi</v>
-      </c>
-      <c r="E70">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="F70" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="G70" t="str">
-        <f t="shared" si="15"/>
-        <v>N</v>
-      </c>
-      <c r="H70" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I70" s="15" t="s">
-        <v>156</v>
-      </c>
+    <row r="70" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN70" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A71">
-        <v>5</v>
-      </c>
-      <c r="B71" t="str">
-        <f t="shared" si="2"/>
-        <v>Lo.95.CF6.N.N.N</v>
-      </c>
-      <c r="C71">
-        <f t="shared" si="3"/>
-        <v>63</v>
-      </c>
-      <c r="D71" t="str">
-        <f t="shared" si="4"/>
-        <v>Lo</v>
-      </c>
-      <c r="E71">
-        <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="F71" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="G71" t="str">
-        <f t="shared" si="15"/>
-        <v>N</v>
-      </c>
-      <c r="H71" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I71" s="15" t="s">
-        <v>156</v>
-      </c>
+    <row r="71" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN71" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:40" x14ac:dyDescent="0.45">
-      <c r="A72">
-        <v>5</v>
-      </c>
-      <c r="B72" t="str">
-        <f t="shared" si="2"/>
-        <v>Hi.95.CF6.N.N.N</v>
-      </c>
-      <c r="C72">
-        <f t="shared" si="3"/>
-        <v>64</v>
-      </c>
-      <c r="D72" t="str">
-        <f t="shared" si="4"/>
-        <v>Hi</v>
-      </c>
-      <c r="E72">
-        <f t="shared" si="18"/>
-        <v>95</v>
-      </c>
-      <c r="F72" t="str">
-        <f t="shared" si="22"/>
-        <v>CF6</v>
-      </c>
-      <c r="G72" t="str">
-        <f t="shared" si="15"/>
-        <v>N</v>
-      </c>
-      <c r="H72" s="15" t="str">
-        <f t="shared" si="28"/>
-        <v>N</v>
-      </c>
-      <c r="I72" s="15" t="s">
-        <v>156</v>
-      </c>
+    <row r="72" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN72" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="73" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN73" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="74" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN74" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="75" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN75" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="76" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN76" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="77" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN77" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="78" spans="40:40" x14ac:dyDescent="0.45">
       <c r="AN78" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
@@ -9913,35 +9238,35 @@
     </row>
     <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.45">
       <c r="B2" s="18" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="B6" s="19" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E6" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>122</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
@@ -9950,16 +9275,16 @@
         <v>CF1</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D7" s="17">
         <v>0.7</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F7" s="17">
         <v>0</v>
@@ -9978,16 +9303,16 @@
         <v>CF2</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D8" s="17">
         <v>0.5</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="F8" s="17">
         <v>0</v>
@@ -10006,16 +9331,16 @@
         <v>CF3</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D9" s="17">
         <v>0.7</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="F9" s="17">
         <v>1</v>
@@ -10034,16 +9359,16 @@
         <v>CF4</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="D10" s="17">
         <v>0.5</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="F10" s="17">
         <v>1</v>
@@ -10062,16 +9387,16 @@
         <v>CF5</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D11" s="17">
         <v>0.7</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="F11" s="17">
         <v>6</v>
@@ -10090,16 +9415,16 @@
         <v>CF6</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D12" s="17">
         <v>0.4</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F12" s="17">
         <v>12</v>
@@ -10124,18 +9449,18 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="G16" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="7:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="G17" s="13" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="7:9" x14ac:dyDescent="0.45">
@@ -10148,7 +9473,7 @@
         <v>*0.5</v>
       </c>
       <c r="I18" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -10207,7 +9532,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B11">
         <f>7*3.6</f>
@@ -10240,7 +9565,7 @@
         <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -10301,7 +9626,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B11">
         <v>2000</v>
@@ -10330,7 +9655,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B12">
         <v>2001</v>
@@ -10359,7 +9684,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B13">
         <v>2002</v>
@@ -10388,7 +9713,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B14">
         <v>2003</v>
@@ -10417,7 +9742,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B15">
         <v>2004</v>
@@ -10446,7 +9771,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B16">
         <v>2005</v>
@@ -10475,7 +9800,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B17">
         <v>2006</v>
@@ -10504,7 +9829,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B18">
         <v>2007</v>
@@ -10533,7 +9858,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B19">
         <v>2008</v>
@@ -10562,7 +9887,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B20">
         <v>2009</v>
@@ -10591,7 +9916,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B21">
         <v>2010</v>
@@ -10620,7 +9945,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B22">
         <v>2011</v>
@@ -10649,7 +9974,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B23">
         <v>2012</v>
@@ -10678,7 +10003,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B24">
         <v>2013</v>
@@ -10707,7 +10032,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B25">
         <v>2014</v>
@@ -10736,7 +10061,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B26">
         <v>2015</v>
@@ -10765,7 +10090,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B27">
         <v>2016</v>
@@ -10794,7 +10119,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B28">
         <v>2017</v>
@@ -10823,7 +10148,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B29">
         <v>2018</v>
@@ -10852,7 +10177,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B30">
         <v>2019</v>
@@ -10881,7 +10206,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B31">
         <v>2020</v>
@@ -10910,7 +10235,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B32">
         <v>2021</v>
@@ -10939,7 +10264,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B33">
         <v>2022</v>
@@ -11039,7 +10364,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C11">
         <v>2020</v>
@@ -11080,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C12">
         <v>2025</v>
@@ -11121,7 +10446,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C13">
         <v>2030</v>
@@ -11162,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C14">
         <v>2035</v>
@@ -11203,7 +10528,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C15">
         <v>2040</v>
@@ -11244,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C16">
         <v>2045</v>
@@ -11285,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C17">
         <v>2050</v>
@@ -11326,7 +10651,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C18">
         <v>2020</v>
@@ -11367,7 +10692,7 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C19">
         <v>2025</v>
@@ -11408,7 +10733,7 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C20">
         <v>2030</v>
@@ -11449,7 +10774,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C21">
         <v>2035</v>
@@ -11490,7 +10815,7 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C22">
         <v>2040</v>
@@ -11531,7 +10856,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C23">
         <v>2045</v>
@@ -11572,7 +10897,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C24">
         <v>2050</v>
@@ -11613,7 +10938,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C25">
         <v>2020</v>
@@ -11654,7 +10979,7 @@
         <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C26">
         <v>2025</v>
@@ -11695,7 +11020,7 @@
         <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C27">
         <v>2030</v>
@@ -11736,7 +11061,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C28">
         <v>2035</v>
@@ -11777,7 +11102,7 @@
         <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C29">
         <v>2040</v>
@@ -11818,7 +11143,7 @@
         <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C30">
         <v>2045</v>
@@ -11859,7 +11184,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C31">
         <v>2050</v>
@@ -11900,7 +11225,7 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>2020</v>
@@ -11941,7 +11266,7 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C33">
         <v>2025</v>
@@ -11982,7 +11307,7 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C34">
         <v>2030</v>
@@ -12023,7 +11348,7 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C35">
         <v>2035</v>
@@ -12064,7 +11389,7 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C36">
         <v>2040</v>
@@ -12105,7 +11430,7 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C37">
         <v>2045</v>
@@ -12146,7 +11471,7 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C38">
         <v>2050</v>
@@ -12187,7 +11512,7 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C39">
         <v>2020</v>
@@ -12228,7 +11553,7 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C40">
         <v>2025</v>
@@ -12269,7 +11594,7 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C41">
         <v>2030</v>
@@ -12310,7 +11635,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C42">
         <v>2035</v>
@@ -12351,7 +11676,7 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C43">
         <v>2040</v>
@@ -12392,7 +11717,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C44">
         <v>2045</v>
@@ -12433,7 +11758,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C45">
         <v>2050</v>
@@ -12474,7 +11799,7 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C46">
         <v>2020</v>
@@ -12515,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C47">
         <v>2025</v>
@@ -12556,7 +11881,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C48">
         <v>2030</v>
@@ -12597,7 +11922,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C49">
         <v>2035</v>
@@ -12638,7 +11963,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C50">
         <v>2040</v>
@@ -12679,7 +12004,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C51">
         <v>2045</v>
@@ -12720,7 +12045,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C52">
         <v>2050</v>
@@ -12761,7 +12086,7 @@
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C53">
         <v>2020</v>
@@ -12802,7 +12127,7 @@
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C54">
         <v>2025</v>
@@ -12843,7 +12168,7 @@
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C55">
         <v>2030</v>
@@ -12884,7 +12209,7 @@
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C56">
         <v>2035</v>
@@ -12925,7 +12250,7 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C57">
         <v>2040</v>
@@ -12966,7 +12291,7 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C58">
         <v>2045</v>
@@ -13007,7 +12332,7 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C59">
         <v>2050</v>
@@ -13048,7 +12373,7 @@
         <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C60">
         <v>2020</v>
@@ -13089,7 +12414,7 @@
         <v>5</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C61">
         <v>2025</v>
@@ -13130,7 +12455,7 @@
         <v>5</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C62">
         <v>2030</v>
@@ -13171,7 +12496,7 @@
         <v>5</v>
       </c>
       <c r="B63" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C63">
         <v>2035</v>
@@ -13212,7 +12537,7 @@
         <v>5</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C64">
         <v>2040</v>
@@ -13253,7 +12578,7 @@
         <v>5</v>
       </c>
       <c r="B65" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C65">
         <v>2045</v>
@@ -13294,7 +12619,7 @@
         <v>5</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C66">
         <v>2050</v>
@@ -13335,7 +12660,7 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C67">
         <v>2020</v>
@@ -13376,7 +12701,7 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C68">
         <v>2025</v>
@@ -13417,7 +12742,7 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C69">
         <v>2030</v>
@@ -13458,7 +12783,7 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C70">
         <v>2035</v>
@@ -13499,7 +12824,7 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>2040</v>
@@ -13540,7 +12865,7 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C72">
         <v>2045</v>
@@ -13581,7 +12906,7 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C73">
         <v>2050</v>
@@ -13622,7 +12947,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>2020</v>
@@ -13663,7 +12988,7 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>2025</v>
@@ -13704,7 +13029,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C76">
         <v>2030</v>
@@ -13745,7 +13070,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C77">
         <v>2035</v>
@@ -13786,7 +13111,7 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C78">
         <v>2040</v>
@@ -13827,7 +13152,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C79">
         <v>2045</v>
@@ -13868,7 +13193,7 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C80">
         <v>2050</v>
@@ -13909,7 +13234,7 @@
         <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C81">
         <v>2020</v>
@@ -13950,7 +13275,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C82">
         <v>2025</v>
@@ -13991,7 +13316,7 @@
         <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C83">
         <v>2030</v>
@@ -14032,7 +13357,7 @@
         <v>0</v>
       </c>
       <c r="B84" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C84">
         <v>2035</v>
@@ -14073,7 +13398,7 @@
         <v>0</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C85">
         <v>2040</v>
@@ -14114,7 +13439,7 @@
         <v>0</v>
       </c>
       <c r="B86" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C86">
         <v>2045</v>
@@ -14155,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C87">
         <v>2050</v>
@@ -14196,7 +13521,7 @@
         <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C88">
         <v>2020</v>
@@ -14237,7 +13562,7 @@
         <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C89">
         <v>2025</v>
@@ -14278,7 +13603,7 @@
         <v>2</v>
       </c>
       <c r="B90" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C90">
         <v>2030</v>
@@ -14319,7 +13644,7 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C91">
         <v>2035</v>
@@ -14360,7 +13685,7 @@
         <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C92">
         <v>2040</v>
@@ -14401,7 +13726,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C93">
         <v>2045</v>
@@ -14442,7 +13767,7 @@
         <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C94">
         <v>2050</v>
@@ -14483,7 +13808,7 @@
         <v>5</v>
       </c>
       <c r="B95" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C95">
         <v>2020</v>
@@ -14524,7 +13849,7 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C96">
         <v>2025</v>
@@ -14565,7 +13890,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C97">
         <v>2030</v>
@@ -14606,7 +13931,7 @@
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C98">
         <v>2035</v>
@@ -14647,7 +13972,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C99">
         <v>2040</v>
@@ -14688,7 +14013,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C100">
         <v>2045</v>
@@ -14729,7 +14054,7 @@
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C101">
         <v>2050</v>
@@ -14770,7 +14095,7 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C102">
         <v>2020</v>
@@ -14811,7 +14136,7 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C103">
         <v>2025</v>
@@ -14852,7 +14177,7 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C104">
         <v>2030</v>
@@ -14893,7 +14218,7 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C105">
         <v>2035</v>
@@ -14934,7 +14259,7 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C106">
         <v>2040</v>
@@ -14975,7 +14300,7 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C107">
         <v>2045</v>
@@ -15016,7 +14341,7 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C108">
         <v>2050</v>
@@ -15057,7 +14382,7 @@
         <v>9</v>
       </c>
       <c r="B109" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C109">
         <v>2020</v>
@@ -15098,7 +14423,7 @@
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C110">
         <v>2025</v>
@@ -15139,7 +14464,7 @@
         <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C111">
         <v>2030</v>
@@ -15180,7 +14505,7 @@
         <v>9</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C112">
         <v>2035</v>
@@ -15221,7 +14546,7 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C113">
         <v>2040</v>
@@ -15262,7 +14587,7 @@
         <v>9</v>
       </c>
       <c r="B114" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C114">
         <v>2045</v>
@@ -15303,7 +14628,7 @@
         <v>9</v>
       </c>
       <c r="B115" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C115">
         <v>2050</v>
@@ -15344,7 +14669,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C116">
         <v>2020</v>
@@ -15385,7 +14710,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C117">
         <v>2025</v>
@@ -15426,7 +14751,7 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C118">
         <v>2030</v>
@@ -15467,7 +14792,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C119">
         <v>2035</v>
@@ -15508,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C120">
         <v>2040</v>
@@ -15549,7 +14874,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C121">
         <v>2045</v>
@@ -15590,7 +14915,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C122">
         <v>2050</v>
@@ -15631,7 +14956,7 @@
         <v>2</v>
       </c>
       <c r="B123" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C123">
         <v>2020</v>
@@ -15672,7 +14997,7 @@
         <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C124">
         <v>2025</v>
@@ -15713,7 +15038,7 @@
         <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C125">
         <v>2030</v>
@@ -15754,7 +15079,7 @@
         <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C126">
         <v>2035</v>
@@ -15795,7 +15120,7 @@
         <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C127">
         <v>2040</v>
@@ -15836,7 +15161,7 @@
         <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C128">
         <v>2045</v>
@@ -15877,7 +15202,7 @@
         <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C129">
         <v>2050</v>
@@ -15918,7 +15243,7 @@
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C130">
         <v>2020</v>
@@ -15959,7 +15284,7 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C131">
         <v>2025</v>
@@ -16000,7 +15325,7 @@
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C132">
         <v>2030</v>
@@ -16041,7 +15366,7 @@
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C133">
         <v>2035</v>
@@ -16082,7 +15407,7 @@
         <v>5</v>
       </c>
       <c r="B134" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C134">
         <v>2040</v>
@@ -16123,7 +15448,7 @@
         <v>5</v>
       </c>
       <c r="B135" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C135">
         <v>2045</v>
@@ -16164,7 +15489,7 @@
         <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C136">
         <v>2050</v>
@@ -16205,7 +15530,7 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C137">
         <v>2020</v>
@@ -16246,7 +15571,7 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C138">
         <v>2025</v>
@@ -16287,7 +15612,7 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C139">
         <v>2030</v>
@@ -16328,7 +15653,7 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C140">
         <v>2035</v>
@@ -16369,7 +15694,7 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C141">
         <v>2040</v>
@@ -16410,7 +15735,7 @@
         <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C142">
         <v>2045</v>
@@ -16451,7 +15776,7 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C143">
         <v>2050</v>
@@ -16492,7 +15817,7 @@
         <v>9</v>
       </c>
       <c r="B144" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C144">
         <v>2020</v>
@@ -16533,7 +15858,7 @@
         <v>9</v>
       </c>
       <c r="B145" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C145">
         <v>2025</v>
@@ -16574,7 +15899,7 @@
         <v>9</v>
       </c>
       <c r="B146" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C146">
         <v>2030</v>
@@ -16615,7 +15940,7 @@
         <v>9</v>
       </c>
       <c r="B147" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C147">
         <v>2035</v>
@@ -16656,7 +15981,7 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C148">
         <v>2040</v>
@@ -16697,7 +16022,7 @@
         <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C149">
         <v>2045</v>
@@ -16738,7 +16063,7 @@
         <v>9</v>
       </c>
       <c r="B150" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C150">
         <v>2050</v>
@@ -16779,7 +16104,7 @@
         <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C151">
         <v>2020</v>
@@ -16820,7 +16145,7 @@
         <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C152">
         <v>2025</v>
@@ -16861,7 +16186,7 @@
         <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C153">
         <v>2030</v>
@@ -16902,7 +16227,7 @@
         <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C154">
         <v>2035</v>
@@ -16943,7 +16268,7 @@
         <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C155">
         <v>2040</v>
@@ -16984,7 +16309,7 @@
         <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C156">
         <v>2045</v>
@@ -17025,7 +16350,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C157">
         <v>2050</v>
@@ -17066,7 +16391,7 @@
         <v>2</v>
       </c>
       <c r="B158" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C158">
         <v>2020</v>
@@ -17107,7 +16432,7 @@
         <v>2</v>
       </c>
       <c r="B159" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C159">
         <v>2025</v>
@@ -17148,7 +16473,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C160">
         <v>2030</v>
@@ -17189,7 +16514,7 @@
         <v>2</v>
       </c>
       <c r="B161" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C161">
         <v>2035</v>
@@ -17230,7 +16555,7 @@
         <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C162">
         <v>2040</v>
@@ -17271,7 +16596,7 @@
         <v>2</v>
       </c>
       <c r="B163" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C163">
         <v>2045</v>
@@ -17312,7 +16637,7 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C164">
         <v>2050</v>
@@ -17353,7 +16678,7 @@
         <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C165">
         <v>2020</v>
@@ -17394,7 +16719,7 @@
         <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C166">
         <v>2025</v>
@@ -17435,7 +16760,7 @@
         <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C167">
         <v>2030</v>
@@ -17476,7 +16801,7 @@
         <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C168">
         <v>2035</v>
@@ -17517,7 +16842,7 @@
         <v>5</v>
       </c>
       <c r="B169" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C169">
         <v>2040</v>
@@ -17558,7 +16883,7 @@
         <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C170">
         <v>2045</v>
@@ -17599,7 +16924,7 @@
         <v>5</v>
       </c>
       <c r="B171" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C171">
         <v>2050</v>
@@ -17640,7 +16965,7 @@
         <v>7</v>
       </c>
       <c r="B172" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C172">
         <v>2020</v>
@@ -17681,7 +17006,7 @@
         <v>7</v>
       </c>
       <c r="B173" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C173">
         <v>2025</v>
@@ -17722,7 +17047,7 @@
         <v>7</v>
       </c>
       <c r="B174" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C174">
         <v>2030</v>
@@ -17763,7 +17088,7 @@
         <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C175">
         <v>2035</v>
@@ -17804,7 +17129,7 @@
         <v>7</v>
       </c>
       <c r="B176" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C176">
         <v>2040</v>
@@ -17845,7 +17170,7 @@
         <v>7</v>
       </c>
       <c r="B177" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C177">
         <v>2045</v>
@@ -17886,7 +17211,7 @@
         <v>7</v>
       </c>
       <c r="B178" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C178">
         <v>2050</v>
@@ -17927,7 +17252,7 @@
         <v>9</v>
       </c>
       <c r="B179" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C179">
         <v>2020</v>
@@ -17968,7 +17293,7 @@
         <v>9</v>
       </c>
       <c r="B180" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C180">
         <v>2025</v>
@@ -18009,7 +17334,7 @@
         <v>9</v>
       </c>
       <c r="B181" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C181">
         <v>2030</v>
@@ -18050,7 +17375,7 @@
         <v>9</v>
       </c>
       <c r="B182" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C182">
         <v>2035</v>
@@ -18091,7 +17416,7 @@
         <v>9</v>
       </c>
       <c r="B183" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C183">
         <v>2040</v>
@@ -18132,7 +17457,7 @@
         <v>9</v>
       </c>
       <c r="B184" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C184">
         <v>2045</v>
@@ -18173,7 +17498,7 @@
         <v>9</v>
       </c>
       <c r="B185" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C185">
         <v>2050</v>
@@ -18214,7 +17539,7 @@
         <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C186">
         <v>2020</v>
@@ -18255,7 +17580,7 @@
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C187">
         <v>2025</v>
@@ -18296,7 +17621,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C188">
         <v>2030</v>
@@ -18337,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C189">
         <v>2035</v>
@@ -18378,7 +17703,7 @@
         <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C190">
         <v>2040</v>
@@ -18419,7 +17744,7 @@
         <v>0</v>
       </c>
       <c r="B191" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C191">
         <v>2045</v>
@@ -18460,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="B192" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C192">
         <v>2050</v>
@@ -18501,7 +17826,7 @@
         <v>2</v>
       </c>
       <c r="B193" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C193">
         <v>2020</v>
@@ -18542,7 +17867,7 @@
         <v>2</v>
       </c>
       <c r="B194" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C194">
         <v>2025</v>
@@ -18583,7 +17908,7 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C195">
         <v>2030</v>
@@ -18624,7 +17949,7 @@
         <v>2</v>
       </c>
       <c r="B196" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C196">
         <v>2035</v>
@@ -18665,7 +17990,7 @@
         <v>2</v>
       </c>
       <c r="B197" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C197">
         <v>2040</v>
@@ -18706,7 +18031,7 @@
         <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C198">
         <v>2045</v>
@@ -18747,7 +18072,7 @@
         <v>2</v>
       </c>
       <c r="B199" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C199">
         <v>2050</v>
@@ -18788,7 +18113,7 @@
         <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C200">
         <v>2020</v>
@@ -18829,7 +18154,7 @@
         <v>5</v>
       </c>
       <c r="B201" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C201">
         <v>2025</v>
@@ -18870,7 +18195,7 @@
         <v>5</v>
       </c>
       <c r="B202" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C202">
         <v>2030</v>
@@ -18911,7 +18236,7 @@
         <v>5</v>
       </c>
       <c r="B203" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C203">
         <v>2035</v>
@@ -18952,7 +18277,7 @@
         <v>5</v>
       </c>
       <c r="B204" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C204">
         <v>2040</v>
@@ -18993,7 +18318,7 @@
         <v>5</v>
       </c>
       <c r="B205" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C205">
         <v>2045</v>
@@ -19034,7 +18359,7 @@
         <v>5</v>
       </c>
       <c r="B206" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C206">
         <v>2050</v>
@@ -19075,7 +18400,7 @@
         <v>7</v>
       </c>
       <c r="B207" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C207">
         <v>2020</v>
@@ -19116,7 +18441,7 @@
         <v>7</v>
       </c>
       <c r="B208" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C208">
         <v>2025</v>
@@ -19157,7 +18482,7 @@
         <v>7</v>
       </c>
       <c r="B209" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C209">
         <v>2030</v>
@@ -19198,7 +18523,7 @@
         <v>7</v>
       </c>
       <c r="B210" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C210">
         <v>2035</v>
@@ -19239,7 +18564,7 @@
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C211">
         <v>2040</v>
@@ -19280,7 +18605,7 @@
         <v>7</v>
       </c>
       <c r="B212" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C212">
         <v>2045</v>
@@ -19321,7 +18646,7 @@
         <v>7</v>
       </c>
       <c r="B213" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C213">
         <v>2050</v>
@@ -19362,7 +18687,7 @@
         <v>9</v>
       </c>
       <c r="B214" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C214">
         <v>2020</v>
@@ -19403,7 +18728,7 @@
         <v>9</v>
       </c>
       <c r="B215" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C215">
         <v>2025</v>
@@ -19444,7 +18769,7 @@
         <v>9</v>
       </c>
       <c r="B216" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C216">
         <v>2030</v>
@@ -19485,7 +18810,7 @@
         <v>9</v>
       </c>
       <c r="B217" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C217">
         <v>2035</v>
@@ -19526,7 +18851,7 @@
         <v>9</v>
       </c>
       <c r="B218" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C218">
         <v>2040</v>
@@ -19567,7 +18892,7 @@
         <v>9</v>
       </c>
       <c r="B219" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C219">
         <v>2045</v>
@@ -19608,7 +18933,7 @@
         <v>9</v>
       </c>
       <c r="B220" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C220">
         <v>2050</v>
@@ -19649,7 +18974,7 @@
         <v>0</v>
       </c>
       <c r="B221" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C221">
         <v>2020</v>
@@ -19690,7 +19015,7 @@
         <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C222">
         <v>2025</v>
@@ -19731,7 +19056,7 @@
         <v>0</v>
       </c>
       <c r="B223" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C223">
         <v>2030</v>
@@ -19772,7 +19097,7 @@
         <v>0</v>
       </c>
       <c r="B224" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C224">
         <v>2035</v>
@@ -19813,7 +19138,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C225">
         <v>2040</v>
@@ -19854,7 +19179,7 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C226">
         <v>2045</v>
@@ -19895,7 +19220,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C227">
         <v>2050</v>
@@ -19936,7 +19261,7 @@
         <v>2</v>
       </c>
       <c r="B228" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C228">
         <v>2020</v>
@@ -19977,7 +19302,7 @@
         <v>2</v>
       </c>
       <c r="B229" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C229">
         <v>2025</v>
@@ -20018,7 +19343,7 @@
         <v>2</v>
       </c>
       <c r="B230" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C230">
         <v>2030</v>
@@ -20059,7 +19384,7 @@
         <v>2</v>
       </c>
       <c r="B231" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C231">
         <v>2035</v>
@@ -20100,7 +19425,7 @@
         <v>2</v>
       </c>
       <c r="B232" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C232">
         <v>2040</v>
@@ -20141,7 +19466,7 @@
         <v>2</v>
       </c>
       <c r="B233" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C233">
         <v>2045</v>
@@ -20182,7 +19507,7 @@
         <v>2</v>
       </c>
       <c r="B234" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C234">
         <v>2050</v>
@@ -20223,7 +19548,7 @@
         <v>5</v>
       </c>
       <c r="B235" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C235">
         <v>2020</v>
@@ -20264,7 +19589,7 @@
         <v>5</v>
       </c>
       <c r="B236" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C236">
         <v>2025</v>
@@ -20305,7 +19630,7 @@
         <v>5</v>
       </c>
       <c r="B237" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C237">
         <v>2030</v>
@@ -20346,7 +19671,7 @@
         <v>5</v>
       </c>
       <c r="B238" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C238">
         <v>2035</v>
@@ -20387,7 +19712,7 @@
         <v>5</v>
       </c>
       <c r="B239" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C239">
         <v>2040</v>
@@ -20428,7 +19753,7 @@
         <v>5</v>
       </c>
       <c r="B240" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C240">
         <v>2045</v>
@@ -20469,7 +19794,7 @@
         <v>5</v>
       </c>
       <c r="B241" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C241">
         <v>2050</v>
@@ -20510,7 +19835,7 @@
         <v>7</v>
       </c>
       <c r="B242" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C242">
         <v>2020</v>
@@ -20551,7 +19876,7 @@
         <v>7</v>
       </c>
       <c r="B243" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C243">
         <v>2025</v>
@@ -20592,7 +19917,7 @@
         <v>7</v>
       </c>
       <c r="B244" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C244">
         <v>2030</v>
@@ -20633,7 +19958,7 @@
         <v>7</v>
       </c>
       <c r="B245" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C245">
         <v>2035</v>
@@ -20674,7 +19999,7 @@
         <v>7</v>
       </c>
       <c r="B246" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C246">
         <v>2040</v>
@@ -20715,7 +20040,7 @@
         <v>7</v>
       </c>
       <c r="B247" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C247">
         <v>2045</v>
@@ -20756,7 +20081,7 @@
         <v>7</v>
       </c>
       <c r="B248" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C248">
         <v>2050</v>
@@ -20797,7 +20122,7 @@
         <v>9</v>
       </c>
       <c r="B249" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C249">
         <v>2020</v>
@@ -20838,7 +20163,7 @@
         <v>9</v>
       </c>
       <c r="B250" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C250">
         <v>2025</v>
@@ -20879,7 +20204,7 @@
         <v>9</v>
       </c>
       <c r="B251" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C251">
         <v>2030</v>
@@ -20920,7 +20245,7 @@
         <v>9</v>
       </c>
       <c r="B252" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C252">
         <v>2035</v>
@@ -20961,7 +20286,7 @@
         <v>9</v>
       </c>
       <c r="B253" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C253">
         <v>2040</v>
@@ -21002,7 +20327,7 @@
         <v>9</v>
       </c>
       <c r="B254" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C254">
         <v>2045</v>
@@ -21043,7 +20368,7 @@
         <v>9</v>
       </c>
       <c r="B255" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C255">
         <v>2050</v>
@@ -21084,7 +20409,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C256">
         <v>2020</v>
@@ -21125,7 +20450,7 @@
         <v>0</v>
       </c>
       <c r="B257" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C257">
         <v>2025</v>
@@ -21166,7 +20491,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C258">
         <v>2030</v>
@@ -21207,7 +20532,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C259">
         <v>2035</v>
@@ -21248,7 +20573,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C260">
         <v>2040</v>
@@ -21289,7 +20614,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C261">
         <v>2045</v>
@@ -21330,7 +20655,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C262">
         <v>2050</v>
@@ -21371,7 +20696,7 @@
         <v>2</v>
       </c>
       <c r="B263" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C263">
         <v>2020</v>
@@ -21412,7 +20737,7 @@
         <v>2</v>
       </c>
       <c r="B264" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C264">
         <v>2025</v>
@@ -21453,7 +20778,7 @@
         <v>2</v>
       </c>
       <c r="B265" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C265">
         <v>2030</v>
@@ -21494,7 +20819,7 @@
         <v>2</v>
       </c>
       <c r="B266" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C266">
         <v>2035</v>
@@ -21535,7 +20860,7 @@
         <v>2</v>
       </c>
       <c r="B267" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C267">
         <v>2040</v>
@@ -21576,7 +20901,7 @@
         <v>2</v>
       </c>
       <c r="B268" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C268">
         <v>2045</v>
@@ -21617,7 +20942,7 @@
         <v>2</v>
       </c>
       <c r="B269" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C269">
         <v>2050</v>
@@ -21658,7 +20983,7 @@
         <v>5</v>
       </c>
       <c r="B270" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C270">
         <v>2020</v>
@@ -21699,7 +21024,7 @@
         <v>5</v>
       </c>
       <c r="B271" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C271">
         <v>2025</v>
@@ -21740,7 +21065,7 @@
         <v>5</v>
       </c>
       <c r="B272" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C272">
         <v>2030</v>
@@ -21781,7 +21106,7 @@
         <v>5</v>
       </c>
       <c r="B273" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C273">
         <v>2035</v>
@@ -21822,7 +21147,7 @@
         <v>5</v>
       </c>
       <c r="B274" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C274">
         <v>2040</v>
@@ -21863,7 +21188,7 @@
         <v>5</v>
       </c>
       <c r="B275" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C275">
         <v>2045</v>
@@ -21904,7 +21229,7 @@
         <v>5</v>
       </c>
       <c r="B276" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C276">
         <v>2050</v>
@@ -21945,7 +21270,7 @@
         <v>7</v>
       </c>
       <c r="B277" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C277">
         <v>2020</v>
@@ -21986,7 +21311,7 @@
         <v>7</v>
       </c>
       <c r="B278" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C278">
         <v>2025</v>
@@ -22027,7 +21352,7 @@
         <v>7</v>
       </c>
       <c r="B279" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C279">
         <v>2030</v>
@@ -22068,7 +21393,7 @@
         <v>7</v>
       </c>
       <c r="B280" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C280">
         <v>2035</v>
@@ -22109,7 +21434,7 @@
         <v>7</v>
       </c>
       <c r="B281" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C281">
         <v>2040</v>
@@ -22150,7 +21475,7 @@
         <v>7</v>
       </c>
       <c r="B282" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C282">
         <v>2045</v>
@@ -22191,7 +21516,7 @@
         <v>7</v>
       </c>
       <c r="B283" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C283">
         <v>2050</v>
@@ -22232,7 +21557,7 @@
         <v>9</v>
       </c>
       <c r="B284" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C284">
         <v>2020</v>
@@ -22273,7 +21598,7 @@
         <v>9</v>
       </c>
       <c r="B285" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C285">
         <v>2025</v>
@@ -22314,7 +21639,7 @@
         <v>9</v>
       </c>
       <c r="B286" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C286">
         <v>2030</v>
@@ -22355,7 +21680,7 @@
         <v>9</v>
       </c>
       <c r="B287" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C287">
         <v>2035</v>
@@ -22396,7 +21721,7 @@
         <v>9</v>
       </c>
       <c r="B288" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C288">
         <v>2040</v>
@@ -22437,7 +21762,7 @@
         <v>9</v>
       </c>
       <c r="B289" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C289">
         <v>2045</v>
@@ -22478,7 +21803,7 @@
         <v>9</v>
       </c>
       <c r="B290" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C290">
         <v>2050</v>
@@ -22519,7 +21844,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C291">
         <v>2020</v>
@@ -22560,7 +21885,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C292">
         <v>2025</v>
@@ -22601,7 +21926,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C293">
         <v>2030</v>
@@ -22642,7 +21967,7 @@
         <v>0</v>
       </c>
       <c r="B294" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C294">
         <v>2035</v>
@@ -22683,7 +22008,7 @@
         <v>0</v>
       </c>
       <c r="B295" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C295">
         <v>2040</v>
@@ -22724,7 +22049,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C296">
         <v>2045</v>
@@ -22765,7 +22090,7 @@
         <v>0</v>
       </c>
       <c r="B297" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C297">
         <v>2050</v>
@@ -22806,7 +22131,7 @@
         <v>2</v>
       </c>
       <c r="B298" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C298">
         <v>2020</v>
@@ -22847,7 +22172,7 @@
         <v>2</v>
       </c>
       <c r="B299" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C299">
         <v>2025</v>
@@ -22888,7 +22213,7 @@
         <v>2</v>
       </c>
       <c r="B300" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C300">
         <v>2030</v>
@@ -22929,7 +22254,7 @@
         <v>2</v>
       </c>
       <c r="B301" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C301">
         <v>2035</v>
@@ -22970,7 +22295,7 @@
         <v>2</v>
       </c>
       <c r="B302" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C302">
         <v>2040</v>
@@ -23011,7 +22336,7 @@
         <v>2</v>
       </c>
       <c r="B303" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C303">
         <v>2045</v>
@@ -23052,7 +22377,7 @@
         <v>2</v>
       </c>
       <c r="B304" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C304">
         <v>2050</v>
@@ -23093,7 +22418,7 @@
         <v>5</v>
       </c>
       <c r="B305" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C305">
         <v>2020</v>
@@ -23134,7 +22459,7 @@
         <v>5</v>
       </c>
       <c r="B306" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C306">
         <v>2025</v>
@@ -23175,7 +22500,7 @@
         <v>5</v>
       </c>
       <c r="B307" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C307">
         <v>2030</v>
@@ -23216,7 +22541,7 @@
         <v>5</v>
       </c>
       <c r="B308" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C308">
         <v>2035</v>
@@ -23257,7 +22582,7 @@
         <v>5</v>
       </c>
       <c r="B309" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C309">
         <v>2040</v>
@@ -23298,7 +22623,7 @@
         <v>5</v>
       </c>
       <c r="B310" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C310">
         <v>2045</v>
@@ -23339,7 +22664,7 @@
         <v>5</v>
       </c>
       <c r="B311" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C311">
         <v>2050</v>
@@ -23380,7 +22705,7 @@
         <v>7</v>
       </c>
       <c r="B312" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C312">
         <v>2020</v>
@@ -23421,7 +22746,7 @@
         <v>7</v>
       </c>
       <c r="B313" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C313">
         <v>2025</v>
@@ -23462,7 +22787,7 @@
         <v>7</v>
       </c>
       <c r="B314" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C314">
         <v>2030</v>
@@ -23503,7 +22828,7 @@
         <v>7</v>
       </c>
       <c r="B315" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C315">
         <v>2035</v>
@@ -23544,7 +22869,7 @@
         <v>7</v>
       </c>
       <c r="B316" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C316">
         <v>2040</v>
@@ -23585,7 +22910,7 @@
         <v>7</v>
       </c>
       <c r="B317" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C317">
         <v>2045</v>
@@ -23626,7 +22951,7 @@
         <v>7</v>
       </c>
       <c r="B318" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C318">
         <v>2050</v>
@@ -23667,7 +22992,7 @@
         <v>9</v>
       </c>
       <c r="B319" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C319">
         <v>2020</v>
@@ -23708,7 +23033,7 @@
         <v>9</v>
       </c>
       <c r="B320" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C320">
         <v>2025</v>
@@ -23749,7 +23074,7 @@
         <v>9</v>
       </c>
       <c r="B321" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C321">
         <v>2030</v>
@@ -23790,7 +23115,7 @@
         <v>9</v>
       </c>
       <c r="B322" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C322">
         <v>2035</v>
@@ -23831,7 +23156,7 @@
         <v>9</v>
       </c>
       <c r="B323" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C323">
         <v>2040</v>
@@ -23872,7 +23197,7 @@
         <v>9</v>
       </c>
       <c r="B324" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C324">
         <v>2045</v>
@@ -23913,7 +23238,7 @@
         <v>9</v>
       </c>
       <c r="B325" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C325">
         <v>2050</v>
@@ -23954,7 +23279,7 @@
         <v>0</v>
       </c>
       <c r="B326" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C326">
         <v>2020</v>
@@ -23995,7 +23320,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C327">
         <v>2025</v>
@@ -24036,7 +23361,7 @@
         <v>0</v>
       </c>
       <c r="B328" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C328">
         <v>2030</v>
@@ -24077,7 +23402,7 @@
         <v>0</v>
       </c>
       <c r="B329" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C329">
         <v>2035</v>
@@ -24118,7 +23443,7 @@
         <v>0</v>
       </c>
       <c r="B330" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C330">
         <v>2040</v>
@@ -24159,7 +23484,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C331">
         <v>2045</v>
@@ -24200,7 +23525,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C332">
         <v>2050</v>
@@ -24241,7 +23566,7 @@
         <v>2</v>
       </c>
       <c r="B333" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C333">
         <v>2020</v>
@@ -24282,7 +23607,7 @@
         <v>2</v>
       </c>
       <c r="B334" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C334">
         <v>2025</v>
@@ -24323,7 +23648,7 @@
         <v>2</v>
       </c>
       <c r="B335" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C335">
         <v>2030</v>
@@ -24364,7 +23689,7 @@
         <v>2</v>
       </c>
       <c r="B336" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C336">
         <v>2035</v>
@@ -24405,7 +23730,7 @@
         <v>2</v>
       </c>
       <c r="B337" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C337">
         <v>2040</v>
@@ -24446,7 +23771,7 @@
         <v>2</v>
       </c>
       <c r="B338" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C338">
         <v>2045</v>
@@ -24487,7 +23812,7 @@
         <v>2</v>
       </c>
       <c r="B339" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C339">
         <v>2050</v>
@@ -24528,7 +23853,7 @@
         <v>5</v>
       </c>
       <c r="B340" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C340">
         <v>2020</v>
@@ -24569,7 +23894,7 @@
         <v>5</v>
       </c>
       <c r="B341" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C341">
         <v>2025</v>
@@ -24610,7 +23935,7 @@
         <v>5</v>
       </c>
       <c r="B342" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C342">
         <v>2030</v>
@@ -24651,7 +23976,7 @@
         <v>5</v>
       </c>
       <c r="B343" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C343">
         <v>2035</v>
@@ -24692,7 +24017,7 @@
         <v>5</v>
       </c>
       <c r="B344" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C344">
         <v>2040</v>
@@ -24733,7 +24058,7 @@
         <v>5</v>
       </c>
       <c r="B345" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C345">
         <v>2045</v>
@@ -24774,7 +24099,7 @@
         <v>5</v>
       </c>
       <c r="B346" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C346">
         <v>2050</v>
@@ -24815,7 +24140,7 @@
         <v>7</v>
       </c>
       <c r="B347" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C347">
         <v>2020</v>
@@ -24856,7 +24181,7 @@
         <v>7</v>
       </c>
       <c r="B348" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C348">
         <v>2025</v>
@@ -24897,7 +24222,7 @@
         <v>7</v>
       </c>
       <c r="B349" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C349">
         <v>2030</v>
@@ -24938,7 +24263,7 @@
         <v>7</v>
       </c>
       <c r="B350" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C350">
         <v>2035</v>
@@ -24979,7 +24304,7 @@
         <v>7</v>
       </c>
       <c r="B351" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C351">
         <v>2040</v>
@@ -25020,7 +24345,7 @@
         <v>7</v>
       </c>
       <c r="B352" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C352">
         <v>2045</v>
@@ -25061,7 +24386,7 @@
         <v>7</v>
       </c>
       <c r="B353" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C353">
         <v>2050</v>
@@ -25102,7 +24427,7 @@
         <v>9</v>
       </c>
       <c r="B354" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C354">
         <v>2020</v>
@@ -25143,7 +24468,7 @@
         <v>9</v>
       </c>
       <c r="B355" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C355">
         <v>2025</v>
@@ -25184,7 +24509,7 @@
         <v>9</v>
       </c>
       <c r="B356" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C356">
         <v>2030</v>
@@ -25225,7 +24550,7 @@
         <v>9</v>
       </c>
       <c r="B357" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C357">
         <v>2035</v>
@@ -25266,7 +24591,7 @@
         <v>9</v>
       </c>
       <c r="B358" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C358">
         <v>2040</v>
@@ -25307,7 +24632,7 @@
         <v>9</v>
       </c>
       <c r="B359" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C359">
         <v>2045</v>
@@ -25348,7 +24673,7 @@
         <v>9</v>
       </c>
       <c r="B360" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C360">
         <v>2050</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2084F0-4428-4B7B-8171-FB553D74A031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F4F0F2-7A1F-4E71-B2DF-B41E9C175D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="159">
   <si>
     <t>C1</t>
   </si>
@@ -575,10 +575,10 @@
     <t>NCAP_DRATE</t>
   </si>
   <si>
-    <t>1-48</t>
+    <t>NCAP_ELIFE</t>
   </si>
   <si>
-    <t>NCAP_ELIFE</t>
+    <t>49-64</t>
   </si>
 </sst>
 </file>
@@ -993,22 +993,22 @@
                   <c:v>229.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>275.11199999999997</c:v>
+                  <c:v>242.36057142857143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>290.01390000000004</c:v>
+                  <c:v>246.61825714285717</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>304.91579999999999</c:v>
+                  <c:v>250.87594285714286</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>373.69379999999995</c:v>
+                  <c:v>270.52679999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>458.52</c:v>
+                  <c:v>294.76285714285711</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>532.34172000000001</c:v>
+                  <c:v>315.85477714285713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1284,19 +1284,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5917,13 +5917,13 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.45">
       <c r="K1" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
-        <v>~Inputcell: 1-48</v>
+        <v>~Inputcell: 49-64</v>
       </c>
       <c r="L2" t="s">
         <v>131</v>
@@ -5956,7 +5956,7 @@
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s">
         <v>133</v>
@@ -5992,11 +5992,11 @@
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="D5" s="21" t="str">
         <f t="shared" ref="D5:I5" si="1">VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
-        <v>Hi</v>
+        <v>Lo</v>
       </c>
       <c r="E5" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F5" s="21" t="str">
         <f t="shared" si="1"/>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="I5" s="21">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -6206,7 +6206,7 @@
         <v>Lo.95.CF1.Y.Y.1</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C56" si="3">C10+1</f>
+        <f t="shared" ref="C11:C72" si="3">C10+1</f>
         <v>3</v>
       </c>
       <c r="D11" t="str">
@@ -6260,7 +6260,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="str">
-        <f t="shared" ref="D12:D56" si="4">D10</f>
+        <f t="shared" ref="D12:D72" si="4">D10</f>
         <v>Hi</v>
       </c>
       <c r="E12">
@@ -6387,27 +6387,27 @@
       </c>
       <c r="Y14" s="8">
         <f t="shared" ref="Y14:AD14" si="6">$W$12*N15</f>
-        <v>275.11199999999997</v>
+        <v>242.36057142857143</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="6"/>
-        <v>290.01390000000004</v>
+        <v>246.61825714285717</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="6"/>
-        <v>304.91579999999999</v>
+        <v>250.87594285714286</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="6"/>
-        <v>373.69379999999995</v>
+        <v>270.52679999999998</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="6"/>
-        <v>458.52</v>
+        <v>294.76285714285711</v>
       </c>
       <c r="AD14" s="8">
         <f t="shared" si="6"/>
-        <v>532.34172000000001</v>
+        <v>315.85477714285713</v>
       </c>
       <c r="AN14" s="10">
         <f>AN9+1</f>
@@ -6455,27 +6455,27 @@
       </c>
       <c r="N15" s="11">
         <f t="shared" si="8"/>
-        <v>1.2</v>
+        <v>1.0571428571428572</v>
       </c>
       <c r="O15" s="11">
         <f t="shared" si="8"/>
-        <v>1.2650000000000001</v>
+        <v>1.0757142857142858</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="8"/>
-        <v>1.33</v>
+        <v>1.0942857142857143</v>
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="8"/>
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>1.2857142857142856</v>
       </c>
       <c r="S15" s="11">
         <f t="shared" si="8"/>
-        <v>2.3220000000000001</v>
+        <v>1.3777142857142857</v>
       </c>
       <c r="AN15" s="10">
         <f t="shared" ref="AN15:AN78" si="9">AN10+1</f>
@@ -6641,7 +6641,7 @@
         <v>130</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" ref="G18:G56" si="14">G10</f>
+        <f t="shared" ref="G18:G72" si="14">G10</f>
         <v>Y</v>
       </c>
       <c r="H18" s="15" t="s">
@@ -6706,11 +6706,11 @@
       </c>
       <c r="AC18" s="6">
         <f t="shared" si="15"/>
-        <v>4.5851999999999995</v>
+        <v>2.947628571428571</v>
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="15"/>
-        <v>5.3234172000000006</v>
+        <v>3.1585477714285712</v>
       </c>
       <c r="AE18" t="s">
         <v>17</v>
@@ -6794,27 +6794,27 @@
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="15"/>
-        <v>96.28919999999998</v>
+        <v>84.8262</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="15"/>
-        <v>95.704587000000018</v>
+        <v>81.384024857142876</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="15"/>
-        <v>97.573055999999994</v>
+        <v>80.280301714285713</v>
       </c>
       <c r="AB19" s="6">
         <f t="shared" si="15"/>
-        <v>115.84507799999999</v>
+        <v>83.863307999999989</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="15"/>
-        <v>142.1412</v>
+        <v>91.376485714285707</v>
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="15"/>
-        <v>165.0259332</v>
+        <v>97.914980914285707</v>
       </c>
       <c r="AE19" t="s">
         <v>17</v>
@@ -6841,7 +6841,7 @@
         <v>Hi</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E56" si="17">E16</f>
+        <f t="shared" ref="E20:E72" si="17">E16</f>
         <v>95</v>
       </c>
       <c r="F20" t="s">
@@ -6897,27 +6897,27 @@
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="15"/>
-        <v>143.05823999999998</v>
+        <v>126.02749714285714</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="15"/>
-        <v>156.60750600000003</v>
+        <v>133.17385885714287</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="15"/>
-        <v>161.60537400000001</v>
+        <v>132.96424971428573</v>
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="15"/>
-        <v>194.320776</v>
+        <v>140.673936</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="15"/>
-        <v>229.26</v>
+        <v>147.38142857142856</v>
       </c>
       <c r="AD20" s="6">
         <f t="shared" si="15"/>
-        <v>255.52402559999999</v>
+        <v>151.61029302857142</v>
       </c>
       <c r="AE20" t="s">
         <v>17</v>
@@ -7075,27 +7075,27 @@
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="19"/>
-        <v>33.471960000000024</v>
+        <v>29.214274285714311</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="19"/>
-        <v>35.409206999999981</v>
+        <v>29.767773428571417</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="19"/>
-        <v>43.444770000000005</v>
+        <v>35.338791428571426</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="19"/>
-        <v>61.235345999999993</v>
+        <v>43.696956</v>
       </c>
       <c r="AC22" s="6">
         <f t="shared" si="19"/>
-        <v>84.826199999999972</v>
+        <v>53.712342857142858</v>
       </c>
       <c r="AD22" s="6">
         <f t="shared" si="19"/>
-        <v>109.4991612</v>
+        <v>64.036903200000012</v>
       </c>
       <c r="AE22" t="s">
         <v>17</v>
@@ -7192,23 +7192,23 @@
       </c>
       <c r="O24" s="11">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P24" s="11">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q24" s="11">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R24" s="11">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S24" s="11">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="W24" t="s">
         <v>28</v>
@@ -7218,23 +7218,23 @@
       </c>
       <c r="Z24" s="11">
         <f>O24/1000</f>
-        <v>0</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="AA24" s="11">
         <f>P24/1000</f>
-        <v>0</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="AB24" s="11">
         <f>Q24/1000</f>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AC24" s="11">
         <f>R24/1000</f>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AD24" s="11">
         <f>S24/1000</f>
-        <v>0</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AE24" t="s">
         <v>29</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" ref="F26:F56" si="21">F10</f>
+        <f t="shared" ref="F26:F72" si="21">F10</f>
         <v>CF1</v>
       </c>
       <c r="G26" t="str">
@@ -9006,6 +9006,39 @@
       </c>
     </row>
     <row r="57" spans="1:40" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A57">
+        <v>5</v>
+      </c>
+      <c r="B57" t="str">
+        <f t="shared" ref="B57:B72" si="30">_xlfn.TEXTJOIN(".",TRUE,D57:I57)</f>
+        <v>Lo.0.CF1.Y.Y.0.1</v>
+      </c>
+      <c r="C57">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F57" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H57" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I57" s="23">
+        <v>0.1</v>
+      </c>
       <c r="W57" s="5" t="str">
         <f>IF($I$5&lt;&gt;1,"~TFM_UPD","Transmission costs default")</f>
         <v>~TFM_UPD</v>
@@ -9024,6 +9057,39 @@
       </c>
     </row>
     <row r="58" spans="1:40" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A58">
+        <v>5</v>
+      </c>
+      <c r="B58" t="str">
+        <f t="shared" si="30"/>
+        <v>Hi.0.CF1.Y.Y.0.1</v>
+      </c>
+      <c r="C58">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F58" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I58" s="23">
+        <v>0.1</v>
+      </c>
       <c r="W58" s="4" t="s">
         <v>14</v>
       </c>
@@ -9060,13 +9126,46 @@
       </c>
     </row>
     <row r="59" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>5</v>
+      </c>
+      <c r="B59" t="str">
+        <f t="shared" si="30"/>
+        <v>Lo.95.CF1.Y.Y.0.1</v>
+      </c>
+      <c r="C59">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I59" s="23">
+        <v>0.1</v>
+      </c>
       <c r="W59" t="s">
         <v>154</v>
       </c>
       <c r="X59" s="20"/>
       <c r="Y59" t="str">
         <f>"*"&amp;$I$5</f>
-        <v>*0.25</v>
+        <v>*0.1</v>
       </c>
       <c r="Z59" t="s">
         <v>155</v>
@@ -9081,7 +9180,7 @@
         <v>155</v>
       </c>
       <c r="AG59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AH59">
         <v>30</v>
@@ -9095,114 +9194,543 @@
       </c>
     </row>
     <row r="60" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>5</v>
+      </c>
+      <c r="B60" t="str">
+        <f t="shared" si="30"/>
+        <v>Hi.95.CF1.Y.Y.0.1</v>
+      </c>
+      <c r="C60">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H60" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I60" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN60" s="10">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>5</v>
+      </c>
+      <c r="B61" t="str">
+        <f t="shared" si="30"/>
+        <v>Lo.0.CF1.N.Y.0.1</v>
+      </c>
+      <c r="C61">
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H61" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I61" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN61" s="10">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>5</v>
+      </c>
+      <c r="B62" t="str">
+        <f t="shared" si="30"/>
+        <v>Hi.0.CF1.N.Y.0.1</v>
+      </c>
+      <c r="C62">
+        <f t="shared" si="3"/>
+        <v>54</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G62" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I62" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN62" s="10">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="B63" t="str">
+        <f t="shared" si="30"/>
+        <v>Lo.95.CF1.N.Y.0.1</v>
+      </c>
+      <c r="C63">
+        <f t="shared" si="3"/>
+        <v>55</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G63" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H63" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I63" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN63" s="10">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>5</v>
+      </c>
+      <c r="B64" t="str">
+        <f t="shared" si="30"/>
+        <v>Hi.95.CF1.N.Y.0.1</v>
+      </c>
+      <c r="C64">
+        <f t="shared" si="3"/>
+        <v>56</v>
+      </c>
+      <c r="D64" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G64" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I64" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN64" s="10">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>5</v>
+      </c>
+      <c r="B65" t="str">
+        <f t="shared" si="30"/>
+        <v>Lo.0.CF6.Y.Y.0.1</v>
+      </c>
+      <c r="C65">
+        <f t="shared" si="3"/>
+        <v>57</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F65" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G65" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I65" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN65" s="10">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>5</v>
+      </c>
+      <c r="B66" t="str">
+        <f t="shared" si="30"/>
+        <v>Hi.0.CF6.Y.Y.0.1</v>
+      </c>
+      <c r="C66">
+        <f t="shared" si="3"/>
+        <v>58</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F66" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G66" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I66" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN66" s="10">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>5</v>
+      </c>
+      <c r="B67" t="str">
+        <f t="shared" si="30"/>
+        <v>Lo.95.CF6.Y.Y.0.1</v>
+      </c>
+      <c r="C67">
+        <f t="shared" si="3"/>
+        <v>59</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F67" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G67" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I67" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN67" s="10">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68" t="str">
+        <f t="shared" si="30"/>
+        <v>Hi.95.CF6.Y.Y.0.1</v>
+      </c>
+      <c r="C68">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F68" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G68" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I68" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN68" s="10">
         <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69" t="str">
+        <f t="shared" si="30"/>
+        <v>Lo.0.CF6.N.Y.0.1</v>
+      </c>
+      <c r="C69">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F69" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G69" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I69" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN69" s="10">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>5</v>
+      </c>
+      <c r="B70" t="str">
+        <f t="shared" si="30"/>
+        <v>Hi.0.CF6.N.Y.0.1</v>
+      </c>
+      <c r="C70">
+        <f t="shared" si="3"/>
+        <v>62</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F70" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G70" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I70" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN70" s="10">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>5</v>
+      </c>
+      <c r="B71" t="str">
+        <f t="shared" si="30"/>
+        <v>Lo.95.CF6.N.Y.0.1</v>
+      </c>
+      <c r="C71">
+        <f t="shared" si="3"/>
+        <v>63</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F71" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G71" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I71" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN71" s="10">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>5</v>
+      </c>
+      <c r="B72" t="str">
+        <f t="shared" si="30"/>
+        <v>Hi.95.CF6.N.Y.0.1</v>
+      </c>
+      <c r="C72">
+        <f t="shared" si="3"/>
+        <v>64</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F72" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G72" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="I72" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN72" s="10">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN73" s="10">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN74" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN75" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN76" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN77" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="40:40" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:40" x14ac:dyDescent="0.45">
       <c r="AN78" s="10">
         <f t="shared" si="9"/>
         <v>14</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F4F0F2-7A1F-4E71-B2DF-B41E9C175D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A34ED71-C666-437A-B69B-5D2835A13E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,7 +578,7 @@
     <t>NCAP_ELIFE</t>
   </si>
   <si>
-    <t>49-64</t>
+    <t>1-64</t>
   </si>
 </sst>
 </file>
@@ -5923,7 +5923,7 @@
     <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
-        <v>~Inputcell: 49-64</v>
+        <v>~Inputcell: 1-64</v>
       </c>
       <c r="L2" t="s">
         <v>131</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A34ED71-C666-437A-B69B-5D2835A13E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF40DA37-5777-4189-9114-1F5B94DA040C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="ar6_r10" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$B$8:$H$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$C$8:$H$136</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="165">
   <si>
     <t>C1</t>
   </si>
@@ -578,7 +578,25 @@
     <t>NCAP_ELIFE</t>
   </si>
   <si>
-    <t>1-64</t>
+    <t>CoaRet</t>
+  </si>
+  <si>
+    <t>Pln</t>
+  </si>
+  <si>
+    <t>Eco</t>
+  </si>
+  <si>
+    <t>NCAP_TLIFE</t>
+  </si>
+  <si>
+    <t>+25</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>ep_coal_sub*,-*rf</t>
   </si>
 </sst>
 </file>
@@ -786,7 +804,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -823,6 +841,9 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -993,22 +1014,22 @@
                   <c:v>229.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>242.36057142857143</c:v>
+                  <c:v>275.11199999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>246.61825714285717</c:v>
+                  <c:v>290.01390000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>250.87594285714286</c:v>
+                  <c:v>304.91579999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>270.52679999999998</c:v>
+                  <c:v>373.69379999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>294.76285714285711</c:v>
+                  <c:v>458.52</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>315.85477714285713</c:v>
+                  <c:v>532.34172000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1284,19 +1305,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>35</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>60</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>80</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>95</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5885,7 +5906,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR78"/>
+  <dimension ref="A1:AR136"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.46484375" bestFit="1" customWidth="1"/>
@@ -5895,7 +5916,7 @@
     <col min="5" max="5" width="7.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.1328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.86328125" customWidth="1"/>
+    <col min="8" max="8" width="6.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="1.73046875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24.53125" customWidth="1"/>
@@ -5916,14 +5937,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="K1" s="16" t="s">
-        <v>158</v>
+      <c r="K1" s="16">
+        <v>65</v>
+      </c>
+      <c r="L1">
+        <v>66</v>
+      </c>
+      <c r="M1">
+        <v>67</v>
+      </c>
+      <c r="N1">
+        <v>68</v>
+      </c>
+      <c r="O1">
+        <v>73</v>
+      </c>
+      <c r="P1">
+        <v>74</v>
+      </c>
+      <c r="Q1">
+        <v>75</v>
+      </c>
+      <c r="R1">
+        <v>76</v>
+      </c>
+      <c r="S1">
+        <v>81</v>
+      </c>
+      <c r="T1">
+        <v>82</v>
+      </c>
+      <c r="U1">
+        <v>83</v>
+      </c>
+      <c r="V1">
+        <v>84</v>
+      </c>
+      <c r="W1">
+        <v>89</v>
+      </c>
+      <c r="X1">
+        <v>90</v>
+      </c>
+      <c r="Y1">
+        <v>91</v>
+      </c>
+      <c r="Z1">
+        <v>92</v>
+      </c>
+      <c r="AA1">
+        <v>97</v>
+      </c>
+      <c r="AB1">
+        <v>98</v>
+      </c>
+      <c r="AC1">
+        <v>99</v>
+      </c>
+      <c r="AD1">
+        <v>100</v>
+      </c>
+      <c r="AE1">
+        <v>105</v>
+      </c>
+      <c r="AF1">
+        <v>106</v>
+      </c>
+      <c r="AG1">
+        <v>107</v>
+      </c>
+      <c r="AH1">
+        <v>108</v>
+      </c>
+      <c r="AI1">
+        <v>113</v>
+      </c>
+      <c r="AJ1">
+        <v>114</v>
+      </c>
+      <c r="AK1">
+        <v>115</v>
+      </c>
+      <c r="AL1">
+        <v>116</v>
+      </c>
+      <c r="AM1">
+        <v>121</v>
+      </c>
+      <c r="AN1">
+        <v>122</v>
+      </c>
+      <c r="AO1">
+        <v>123</v>
+      </c>
+      <c r="AP1">
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
-        <v>~Inputcell: 1-64</v>
+        <v>~Inputcell: 65,66,67,68,73,74,75,76,81,82,83,84,89,90,91,92,97,98,99,100,105,106,107,108,113,114,115,116,121,122,123,124</v>
       </c>
       <c r="L2" t="s">
         <v>131</v>
@@ -5956,7 +6070,7 @@
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="L3" t="s">
         <v>133</v>
@@ -5992,11 +6106,11 @@
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="D5" s="21" t="str">
         <f t="shared" ref="D5:I5" si="1">VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
-        <v>Lo</v>
+        <v>Hi</v>
       </c>
       <c r="E5" s="21">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F5" s="21" t="str">
         <f t="shared" si="1"/>
@@ -6004,11 +6118,11 @@
       </c>
       <c r="G5" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="H5" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>Y</v>
+        <v>Eco</v>
       </c>
       <c r="I5" s="21">
         <f t="shared" si="1"/>
@@ -6093,7 +6207,7 @@
         <v>134</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>152</v>
@@ -6109,7 +6223,7 @@
       </c>
       <c r="B9" t="str">
         <f>_xlfn.TEXTJOIN(".",TRUE,D9:I9)</f>
-        <v>Lo.0.CF1.Y.Y.1</v>
+        <v>Lo.0.CF1.Y.Pln.1</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6127,7 +6241,7 @@
         <v>135</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I9" s="22">
         <v>1</v>
@@ -6154,7 +6268,7 @@
       </c>
       <c r="B10" t="str">
         <f t="shared" ref="B10:B56" si="2">_xlfn.TEXTJOIN(".",TRUE,D10:I10)</f>
-        <v>Hi.0.CF1.Y.Y.1</v>
+        <v>Hi.0.CF1.Y.Pln.1</v>
       </c>
       <c r="C10">
         <f>C9+1</f>
@@ -6173,7 +6287,7 @@
         <v>135</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I10" s="22">
         <v>1</v>
@@ -6203,10 +6317,10 @@
       </c>
       <c r="B11" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.Y.Y.1</v>
+        <v>Lo.95.CF1.Y.Pln.1</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:C72" si="3">C10+1</f>
+        <f t="shared" ref="C11:C74" si="3">C10+1</f>
         <v>3</v>
       </c>
       <c r="D11" t="str">
@@ -6223,7 +6337,7 @@
         <v>135</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I11" s="22">
         <v>1</v>
@@ -6253,14 +6367,14 @@
       </c>
       <c r="B12" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.Y.Y.1</v>
+        <v>Hi.95.CF1.Y.Pln.1</v>
       </c>
       <c r="C12">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="D12" t="str">
-        <f t="shared" ref="D12:D72" si="4">D10</f>
+        <f t="shared" ref="D12:D75" si="4">D10</f>
         <v>Hi</v>
       </c>
       <c r="E12">
@@ -6273,7 +6387,7 @@
         <v>135</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I12" s="22">
         <v>1</v>
@@ -6307,7 +6421,7 @@
       </c>
       <c r="B13" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.N.Y.1</v>
+        <v>Lo.0.CF1.N.Pln.1</v>
       </c>
       <c r="C13">
         <f t="shared" si="3"/>
@@ -6328,7 +6442,7 @@
         <v>136</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I13" s="22">
         <v>1</v>
@@ -6355,7 +6469,7 @@
       </c>
       <c r="B14" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.N.Y.1</v>
+        <v>Hi.0.CF1.N.Pln.1</v>
       </c>
       <c r="C14">
         <f t="shared" si="3"/>
@@ -6376,7 +6490,7 @@
         <v>136</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I14" s="22">
         <v>1</v>
@@ -6387,27 +6501,27 @@
       </c>
       <c r="Y14" s="8">
         <f t="shared" ref="Y14:AD14" si="6">$W$12*N15</f>
-        <v>242.36057142857143</v>
+        <v>275.11199999999997</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="6"/>
-        <v>246.61825714285717</v>
+        <v>290.01390000000004</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="6"/>
-        <v>250.87594285714286</v>
+        <v>304.91579999999999</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="6"/>
-        <v>270.52679999999998</v>
+        <v>373.69379999999995</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="6"/>
-        <v>294.76285714285711</v>
+        <v>458.52</v>
       </c>
       <c r="AD14" s="8">
         <f t="shared" si="6"/>
-        <v>315.85477714285713</v>
+        <v>532.34172000000001</v>
       </c>
       <c r="AN14" s="10">
         <f>AN9+1</f>
@@ -6420,7 +6534,7 @@
       </c>
       <c r="B15" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.N.Y.1</v>
+        <v>Lo.95.CF1.N.Pln.1</v>
       </c>
       <c r="C15">
         <f t="shared" si="3"/>
@@ -6441,7 +6555,7 @@
         <v>136</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I15" s="22">
         <v>1</v>
@@ -6455,27 +6569,27 @@
       </c>
       <c r="N15" s="11">
         <f t="shared" si="8"/>
-        <v>1.0571428571428572</v>
+        <v>1.2</v>
       </c>
       <c r="O15" s="11">
         <f t="shared" si="8"/>
-        <v>1.0757142857142858</v>
+        <v>1.2650000000000001</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="8"/>
-        <v>1.0942857142857143</v>
+        <v>1.33</v>
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="8"/>
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="8"/>
-        <v>1.2857142857142856</v>
+        <v>2</v>
       </c>
       <c r="S15" s="11">
         <f t="shared" si="8"/>
-        <v>1.3777142857142857</v>
+        <v>2.3220000000000001</v>
       </c>
       <c r="AN15" s="10">
         <f t="shared" ref="AN15:AN78" si="9">AN10+1</f>
@@ -6488,7 +6602,7 @@
       </c>
       <c r="B16" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.N.Y.1</v>
+        <v>Hi.95.CF1.N.Pln.1</v>
       </c>
       <c r="C16">
         <f t="shared" si="3"/>
@@ -6509,7 +6623,7 @@
         <v>136</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I16" s="22">
         <v>1</v>
@@ -6528,7 +6642,7 @@
       </c>
       <c r="B17" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.Y.Y.1</v>
+        <v>Lo.0.CF6.Y.Pln.1</v>
       </c>
       <c r="C17">
         <f t="shared" si="3"/>
@@ -6550,7 +6664,7 @@
         <v>Y</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I17" s="22">
         <v>1</v>
@@ -6623,7 +6737,7 @@
       </c>
       <c r="B18" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.Y.Y.1</v>
+        <v>Hi.0.CF6.Y.Pln.1</v>
       </c>
       <c r="C18">
         <f t="shared" si="3"/>
@@ -6641,11 +6755,11 @@
         <v>130</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" ref="G18:G72" si="14">G10</f>
+        <f t="shared" ref="G18:G81" si="14">G10</f>
         <v>Y</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I18" s="22">
         <v>1</v>
@@ -6706,11 +6820,11 @@
       </c>
       <c r="AC18" s="6">
         <f t="shared" si="15"/>
-        <v>2.947628571428571</v>
+        <v>4.5851999999999995</v>
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="15"/>
-        <v>3.1585477714285712</v>
+        <v>5.3234172000000006</v>
       </c>
       <c r="AE18" t="s">
         <v>17</v>
@@ -6727,7 +6841,7 @@
       </c>
       <c r="B19" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.Y.Y.1</v>
+        <v>Lo.95.CF6.Y.Pln.1</v>
       </c>
       <c r="C19">
         <f t="shared" si="3"/>
@@ -6749,7 +6863,7 @@
         <v>Y</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I19" s="22">
         <v>1</v>
@@ -6794,27 +6908,27 @@
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="15"/>
-        <v>84.8262</v>
+        <v>96.28919999999998</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="15"/>
-        <v>81.384024857142876</v>
+        <v>95.704587000000018</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="15"/>
-        <v>80.280301714285713</v>
+        <v>97.573055999999994</v>
       </c>
       <c r="AB19" s="6">
         <f t="shared" si="15"/>
-        <v>83.863307999999989</v>
+        <v>115.84507799999999</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="15"/>
-        <v>91.376485714285707</v>
+        <v>142.1412</v>
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="15"/>
-        <v>97.914980914285707</v>
+        <v>165.0259332</v>
       </c>
       <c r="AE19" t="s">
         <v>17</v>
@@ -6830,7 +6944,7 @@
       </c>
       <c r="B20" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.Y.Y.1</v>
+        <v>Hi.95.CF6.Y.Pln.1</v>
       </c>
       <c r="C20">
         <f t="shared" si="3"/>
@@ -6841,7 +6955,7 @@
         <v>Hi</v>
       </c>
       <c r="E20">
-        <f t="shared" ref="E20:E72" si="17">E16</f>
+        <f t="shared" ref="E20:E83" si="17">E16</f>
         <v>95</v>
       </c>
       <c r="F20" t="s">
@@ -6852,7 +6966,7 @@
         <v>Y</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I20" s="22">
         <v>1</v>
@@ -6897,27 +7011,27 @@
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="15"/>
-        <v>126.02749714285714</v>
+        <v>143.05823999999998</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="15"/>
-        <v>133.17385885714287</v>
+        <v>156.60750600000003</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="15"/>
-        <v>132.96424971428573</v>
+        <v>161.60537400000001</v>
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="15"/>
-        <v>140.673936</v>
+        <v>194.320776</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="15"/>
-        <v>147.38142857142856</v>
+        <v>229.26</v>
       </c>
       <c r="AD20" s="6">
         <f t="shared" si="15"/>
-        <v>151.61029302857142</v>
+        <v>255.52402559999999</v>
       </c>
       <c r="AE20" t="s">
         <v>17</v>
@@ -6933,7 +7047,7 @@
       </c>
       <c r="B21" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.N.Y.1</v>
+        <v>Lo.0.CF6.N.Pln.1</v>
       </c>
       <c r="C21">
         <f t="shared" si="3"/>
@@ -6955,7 +7069,7 @@
         <v>N</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I21" s="22">
         <v>1</v>
@@ -7039,7 +7153,7 @@
       </c>
       <c r="B22" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.N.Y.1</v>
+        <v>Hi.0.CF6.N.Pln.1</v>
       </c>
       <c r="C22">
         <f t="shared" si="3"/>
@@ -7061,7 +7175,7 @@
         <v>N</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I22" s="22">
         <v>1</v>
@@ -7075,27 +7189,27 @@
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="19"/>
-        <v>29.214274285714311</v>
+        <v>33.471960000000024</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="19"/>
-        <v>29.767773428571417</v>
+        <v>35.409206999999981</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="19"/>
-        <v>35.338791428571426</v>
+        <v>43.444770000000005</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="19"/>
-        <v>43.696956</v>
+        <v>61.235345999999993</v>
       </c>
       <c r="AC22" s="6">
         <f t="shared" si="19"/>
-        <v>53.712342857142858</v>
+        <v>84.826199999999972</v>
       </c>
       <c r="AD22" s="6">
         <f t="shared" si="19"/>
-        <v>64.036903200000012</v>
+        <v>109.4991612</v>
       </c>
       <c r="AE22" t="s">
         <v>17</v>
@@ -7111,7 +7225,7 @@
       </c>
       <c r="B23" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.N.Y.1</v>
+        <v>Lo.95.CF6.N.Pln.1</v>
       </c>
       <c r="C23">
         <f t="shared" si="3"/>
@@ -7133,7 +7247,7 @@
         <v>N</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I23" s="22">
         <v>1</v>
@@ -7152,7 +7266,7 @@
       </c>
       <c r="B24" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.N.Y.1</v>
+        <v>Hi.95.CF6.N.Pln.1</v>
       </c>
       <c r="C24">
         <f t="shared" si="3"/>
@@ -7174,7 +7288,7 @@
         <v>N</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I24" s="22">
         <v>1</v>
@@ -7192,23 +7306,23 @@
       </c>
       <c r="O24" s="11">
         <f t="shared" si="20"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P24" s="11">
         <f t="shared" si="20"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="11">
         <f t="shared" si="20"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="R24" s="11">
         <f t="shared" si="20"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S24" s="11">
         <f t="shared" si="20"/>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="W24" t="s">
         <v>28</v>
@@ -7218,23 +7332,23 @@
       </c>
       <c r="Z24" s="11">
         <f>O24/1000</f>
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="11">
         <f>P24/1000</f>
-        <v>3.5000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="11">
         <f>Q24/1000</f>
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="11">
         <f>R24/1000</f>
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="11">
         <f>S24/1000</f>
-        <v>9.5000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="s">
         <v>29</v>
@@ -7250,7 +7364,7 @@
       </c>
       <c r="B25" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.Y.Y.0.25</v>
+        <v>Lo.0.CF1.Y.Pln.0.25</v>
       </c>
       <c r="C25">
         <f t="shared" si="3"/>
@@ -7273,7 +7387,7 @@
         <v>Y</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I25" s="23">
         <v>0.25</v>
@@ -7289,7 +7403,7 @@
       </c>
       <c r="B26" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.Y.Y.0.25</v>
+        <v>Hi.0.CF1.Y.Pln.0.25</v>
       </c>
       <c r="C26">
         <f t="shared" si="3"/>
@@ -7304,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" ref="F26:F72" si="21">F10</f>
+        <f t="shared" ref="F26:F89" si="21">F10</f>
         <v>CF1</v>
       </c>
       <c r="G26" t="str">
@@ -7312,7 +7426,7 @@
         <v>Y</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I26" s="23">
         <v>0.25</v>
@@ -7331,7 +7445,7 @@
       </c>
       <c r="B27" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.Y.Y.0.25</v>
+        <v>Lo.95.CF1.Y.Pln.0.25</v>
       </c>
       <c r="C27">
         <f t="shared" si="3"/>
@@ -7354,7 +7468,7 @@
         <v>Y</v>
       </c>
       <c r="H27" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I27" s="23">
         <v>0.25</v>
@@ -7407,7 +7521,7 @@
       </c>
       <c r="B28" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.Y.Y.0.25</v>
+        <v>Hi.95.CF1.Y.Pln.0.25</v>
       </c>
       <c r="C28">
         <f t="shared" si="3"/>
@@ -7430,7 +7544,7 @@
         <v>Y</v>
       </c>
       <c r="H28" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I28" s="23">
         <v>0.25</v>
@@ -7468,7 +7582,7 @@
       </c>
       <c r="B29" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.N.Y.0.25</v>
+        <v>Lo.0.CF1.N.Pln.0.25</v>
       </c>
       <c r="C29">
         <f t="shared" si="3"/>
@@ -7491,7 +7605,7 @@
         <v>N</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I29" s="23">
         <v>0.25</v>
@@ -7529,7 +7643,7 @@
       </c>
       <c r="B30" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.N.Y.0.25</v>
+        <v>Hi.0.CF1.N.Pln.0.25</v>
       </c>
       <c r="C30">
         <f t="shared" si="3"/>
@@ -7552,7 +7666,7 @@
         <v>N</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I30" s="23">
         <v>0.25</v>
@@ -7568,7 +7682,7 @@
       </c>
       <c r="B31" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.N.Y.0.25</v>
+        <v>Lo.95.CF1.N.Pln.0.25</v>
       </c>
       <c r="C31">
         <f t="shared" si="3"/>
@@ -7591,7 +7705,7 @@
         <v>N</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I31" s="23">
         <v>0.25</v>
@@ -7607,7 +7721,7 @@
       </c>
       <c r="B32" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.N.Y.0.25</v>
+        <v>Hi.95.CF1.N.Pln.0.25</v>
       </c>
       <c r="C32">
         <f t="shared" si="3"/>
@@ -7630,14 +7744,14 @@
         <v>N</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I32" s="23">
         <v>0.25</v>
       </c>
       <c r="W32" s="5" t="str">
         <f>IF($G$5="N","~TFM_UPD","DEF correction active")</f>
-        <v>~TFM_UPD</v>
+        <v>DEF correction active</v>
       </c>
       <c r="AN32" s="10">
         <f t="shared" si="9"/>
@@ -7650,7 +7764,7 @@
       </c>
       <c r="B33" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.Y.Y.0.25</v>
+        <v>Lo.0.CF6.Y.Pln.0.25</v>
       </c>
       <c r="C33">
         <f t="shared" si="3"/>
@@ -7673,7 +7787,7 @@
         <v>Y</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I33" s="23">
         <v>0.25</v>
@@ -7701,7 +7815,7 @@
       </c>
       <c r="B34" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.Y.Y.0.25</v>
+        <v>Hi.0.CF6.Y.Pln.0.25</v>
       </c>
       <c r="C34">
         <f t="shared" si="3"/>
@@ -7724,7 +7838,7 @@
         <v>Y</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I34" s="23">
         <v>0.25</v>
@@ -7752,7 +7866,7 @@
       </c>
       <c r="B35" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.Y.Y.0.25</v>
+        <v>Lo.95.CF6.Y.Pln.0.25</v>
       </c>
       <c r="C35">
         <f t="shared" si="3"/>
@@ -7775,7 +7889,7 @@
         <v>Y</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I35" s="23">
         <v>0.25</v>
@@ -7791,7 +7905,7 @@
       </c>
       <c r="B36" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.Y.Y.0.25</v>
+        <v>Hi.95.CF6.Y.Pln.0.25</v>
       </c>
       <c r="C36">
         <f t="shared" si="3"/>
@@ -7814,7 +7928,7 @@
         <v>Y</v>
       </c>
       <c r="H36" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I36" s="23">
         <v>0.25</v>
@@ -7833,7 +7947,7 @@
       </c>
       <c r="B37" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.N.Y.0.25</v>
+        <v>Lo.0.CF6.N.Pln.0.25</v>
       </c>
       <c r="C37">
         <f t="shared" si="3"/>
@@ -7856,7 +7970,7 @@
         <v>N</v>
       </c>
       <c r="H37" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I37" s="23">
         <v>0.25</v>
@@ -7897,7 +8011,7 @@
       </c>
       <c r="W37" s="5" t="str">
         <f>IF($G$5="N","~TFM_INS: limtype=LO","DEF correction active")</f>
-        <v>~TFM_INS: limtype=LO</v>
+        <v>DEF correction active</v>
       </c>
       <c r="AN37" s="10">
         <f t="shared" si="9"/>
@@ -7910,7 +8024,7 @@
       </c>
       <c r="B38" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.N.Y.0.25</v>
+        <v>Hi.0.CF6.N.Pln.0.25</v>
       </c>
       <c r="C38">
         <f t="shared" si="3"/>
@@ -7933,7 +8047,7 @@
         <v>N</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I38" s="23">
         <v>0.25</v>
@@ -7995,7 +8109,7 @@
       </c>
       <c r="B39" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.N.Y.0.25</v>
+        <v>Lo.95.CF6.N.Pln.0.25</v>
       </c>
       <c r="C39">
         <f t="shared" si="3"/>
@@ -8018,7 +8132,7 @@
         <v>N</v>
       </c>
       <c r="H39" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I39" s="23">
         <v>0.25</v>
@@ -8080,7 +8194,7 @@
       </c>
       <c r="B40" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.N.Y.0.25</v>
+        <v>Hi.95.CF6.N.Pln.0.25</v>
       </c>
       <c r="C40">
         <f t="shared" si="3"/>
@@ -8103,7 +8217,7 @@
         <v>N</v>
       </c>
       <c r="H40" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I40" s="23">
         <v>0.25</v>
@@ -8162,7 +8276,7 @@
       </c>
       <c r="B41" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.Y.Y.2</v>
+        <v>Lo.0.CF1.Y.Pln.2</v>
       </c>
       <c r="C41">
         <f t="shared" si="3"/>
@@ -8185,7 +8299,7 @@
         <v>Y</v>
       </c>
       <c r="H41" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I41" s="23">
         <v>2</v>
@@ -8201,7 +8315,7 @@
       </c>
       <c r="B42" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.Y.Y.2</v>
+        <v>Hi.0.CF1.Y.Pln.2</v>
       </c>
       <c r="C42">
         <f t="shared" si="3"/>
@@ -8224,7 +8338,7 @@
         <v>Y</v>
       </c>
       <c r="H42" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I42" s="23">
         <v>2</v>
@@ -8240,7 +8354,7 @@
       </c>
       <c r="B43" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.Y.Y.2</v>
+        <v>Lo.95.CF1.Y.Pln.2</v>
       </c>
       <c r="C43">
         <f t="shared" si="3"/>
@@ -8263,7 +8377,7 @@
         <v>Y</v>
       </c>
       <c r="H43" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I43" s="23">
         <v>2</v>
@@ -8282,7 +8396,7 @@
       </c>
       <c r="B44" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.Y.Y.2</v>
+        <v>Hi.95.CF1.Y.Pln.2</v>
       </c>
       <c r="C44">
         <f t="shared" si="3"/>
@@ -8305,7 +8419,7 @@
         <v>Y</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I44" s="23">
         <v>2</v>
@@ -8360,7 +8474,7 @@
       </c>
       <c r="B45" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF1.N.Y.2</v>
+        <v>Lo.0.CF1.N.Pln.2</v>
       </c>
       <c r="C45">
         <f t="shared" si="3"/>
@@ -8383,7 +8497,7 @@
         <v>N</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I45" s="23">
         <v>2</v>
@@ -8442,7 +8556,7 @@
       </c>
       <c r="B46" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF1.N.Y.2</v>
+        <v>Hi.0.CF1.N.Pln.2</v>
       </c>
       <c r="C46">
         <f t="shared" si="3"/>
@@ -8465,7 +8579,7 @@
         <v>N</v>
       </c>
       <c r="H46" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I46" s="23">
         <v>2</v>
@@ -8524,7 +8638,7 @@
       </c>
       <c r="B47" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF1.N.Y.2</v>
+        <v>Lo.95.CF1.N.Pln.2</v>
       </c>
       <c r="C47">
         <f t="shared" si="3"/>
@@ -8547,7 +8661,7 @@
         <v>N</v>
       </c>
       <c r="H47" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I47" s="23">
         <v>2</v>
@@ -8606,7 +8720,7 @@
       </c>
       <c r="B48" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF1.N.Y.2</v>
+        <v>Hi.95.CF1.N.Pln.2</v>
       </c>
       <c r="C48">
         <f t="shared" si="3"/>
@@ -8629,7 +8743,7 @@
         <v>N</v>
       </c>
       <c r="H48" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I48" s="23">
         <v>2</v>
@@ -8668,7 +8782,7 @@
       </c>
       <c r="B49" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.Y.Y.2</v>
+        <v>Lo.0.CF6.Y.Pln.2</v>
       </c>
       <c r="C49">
         <f t="shared" si="3"/>
@@ -8691,7 +8805,7 @@
         <v>Y</v>
       </c>
       <c r="H49" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I49" s="23">
         <v>2</v>
@@ -8707,7 +8821,7 @@
       </c>
       <c r="B50" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.Y.Y.2</v>
+        <v>Hi.0.CF6.Y.Pln.2</v>
       </c>
       <c r="C50">
         <f t="shared" si="3"/>
@@ -8730,7 +8844,7 @@
         <v>Y</v>
       </c>
       <c r="H50" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I50" s="23">
         <v>2</v>
@@ -8746,7 +8860,7 @@
       </c>
       <c r="B51" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.Y.Y.2</v>
+        <v>Lo.95.CF6.Y.Pln.2</v>
       </c>
       <c r="C51">
         <f t="shared" si="3"/>
@@ -8769,13 +8883,16 @@
         <v>Y</v>
       </c>
       <c r="H51" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I51" s="23">
         <v>2</v>
       </c>
+      <c r="U51" t="s">
+        <v>135</v>
+      </c>
       <c r="W51" s="5" t="str">
-        <f>IF($H$5="N","~TFM_INS: limtype=LO","GAS available")</f>
+        <f>IF($U$51="N","~TFM_INS: limtype=LO","GAS available")</f>
         <v>GAS available</v>
       </c>
       <c r="AN51" s="10">
@@ -8789,7 +8906,7 @@
       </c>
       <c r="B52" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.Y.Y.2</v>
+        <v>Hi.95.CF6.Y.Pln.2</v>
       </c>
       <c r="C52">
         <f t="shared" si="3"/>
@@ -8812,7 +8929,7 @@
         <v>Y</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I52" s="23">
         <v>2</v>
@@ -8843,7 +8960,7 @@
       </c>
       <c r="B53" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.0.CF6.N.Y.2</v>
+        <v>Lo.0.CF6.N.Pln.2</v>
       </c>
       <c r="C53">
         <f t="shared" si="3"/>
@@ -8866,7 +8983,7 @@
         <v>N</v>
       </c>
       <c r="H53" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I53" s="23">
         <v>2</v>
@@ -8894,7 +9011,7 @@
       </c>
       <c r="B54" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.0.CF6.N.Y.2</v>
+        <v>Hi.0.CF6.N.Pln.2</v>
       </c>
       <c r="C54">
         <f t="shared" si="3"/>
@@ -8917,7 +9034,7 @@
         <v>N</v>
       </c>
       <c r="H54" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I54" s="23">
         <v>2</v>
@@ -8933,7 +9050,7 @@
       </c>
       <c r="B55" t="str">
         <f t="shared" si="2"/>
-        <v>Lo.95.CF6.N.Y.2</v>
+        <v>Lo.95.CF6.N.Pln.2</v>
       </c>
       <c r="C55">
         <f t="shared" si="3"/>
@@ -8956,7 +9073,7 @@
         <v>N</v>
       </c>
       <c r="H55" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I55" s="23">
         <v>2</v>
@@ -8972,7 +9089,7 @@
       </c>
       <c r="B56" t="str">
         <f t="shared" si="2"/>
-        <v>Hi.95.CF6.N.Y.2</v>
+        <v>Hi.95.CF6.N.Pln.2</v>
       </c>
       <c r="C56">
         <f t="shared" si="3"/>
@@ -8995,7 +9112,7 @@
         <v>N</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I56" s="23">
         <v>2</v>
@@ -9011,7 +9128,7 @@
       </c>
       <c r="B57" t="str">
         <f t="shared" ref="B57:B72" si="30">_xlfn.TEXTJOIN(".",TRUE,D57:I57)</f>
-        <v>Lo.0.CF1.Y.Y.0.1</v>
+        <v>Lo.0.CF1.Y.Pln.0.1</v>
       </c>
       <c r="C57">
         <f t="shared" si="3"/>
@@ -9034,7 +9151,7 @@
         <v>Y</v>
       </c>
       <c r="H57" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I57" s="23">
         <v>0.1</v>
@@ -9062,7 +9179,7 @@
       </c>
       <c r="B58" t="str">
         <f t="shared" si="30"/>
-        <v>Hi.0.CF1.Y.Y.0.1</v>
+        <v>Hi.0.CF1.Y.Pln.0.1</v>
       </c>
       <c r="C58">
         <f t="shared" si="3"/>
@@ -9085,7 +9202,7 @@
         <v>Y</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I58" s="23">
         <v>0.1</v>
@@ -9131,7 +9248,7 @@
       </c>
       <c r="B59" t="str">
         <f t="shared" si="30"/>
-        <v>Lo.95.CF1.Y.Y.0.1</v>
+        <v>Lo.95.CF1.Y.Pln.0.1</v>
       </c>
       <c r="C59">
         <f t="shared" si="3"/>
@@ -9154,7 +9271,7 @@
         <v>Y</v>
       </c>
       <c r="H59" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I59" s="23">
         <v>0.1</v>
@@ -9199,7 +9316,7 @@
       </c>
       <c r="B60" t="str">
         <f t="shared" si="30"/>
-        <v>Hi.95.CF1.Y.Y.0.1</v>
+        <v>Hi.95.CF1.Y.Pln.0.1</v>
       </c>
       <c r="C60">
         <f t="shared" si="3"/>
@@ -9222,7 +9339,7 @@
         <v>Y</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I60" s="23">
         <v>0.1</v>
@@ -9238,7 +9355,7 @@
       </c>
       <c r="B61" t="str">
         <f t="shared" si="30"/>
-        <v>Lo.0.CF1.N.Y.0.1</v>
+        <v>Lo.0.CF1.N.Pln.0.1</v>
       </c>
       <c r="C61">
         <f t="shared" si="3"/>
@@ -9261,7 +9378,7 @@
         <v>N</v>
       </c>
       <c r="H61" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I61" s="23">
         <v>0.1</v>
@@ -9271,13 +9388,13 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:40" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A62">
         <v>5</v>
       </c>
       <c r="B62" t="str">
         <f t="shared" si="30"/>
-        <v>Hi.0.CF1.N.Y.0.1</v>
+        <v>Hi.0.CF1.N.Pln.0.1</v>
       </c>
       <c r="C62">
         <f t="shared" si="3"/>
@@ -9300,23 +9417,27 @@
         <v>N</v>
       </c>
       <c r="H62" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I62" s="23">
         <v>0.1</v>
+      </c>
+      <c r="W62" s="5" t="str">
+        <f>IF($H$5&lt;&gt;"Pln","~TFM_UPD","Coal plants retire as per plan")</f>
+        <v>~TFM_UPD</v>
       </c>
       <c r="AN62" s="10">
         <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:40" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>5</v>
       </c>
       <c r="B63" t="str">
         <f t="shared" si="30"/>
-        <v>Lo.95.CF1.N.Y.0.1</v>
+        <v>Lo.95.CF1.N.Pln.0.1</v>
       </c>
       <c r="C63">
         <f t="shared" si="3"/>
@@ -9339,10 +9460,22 @@
         <v>N</v>
       </c>
       <c r="H63" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I63" s="23">
         <v>0.1</v>
+      </c>
+      <c r="W63" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="X63" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y63" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="Z63" s="24" t="s">
+        <v>163</v>
       </c>
       <c r="AN63" s="10">
         <f t="shared" si="9"/>
@@ -9355,7 +9488,7 @@
       </c>
       <c r="B64" t="str">
         <f t="shared" si="30"/>
-        <v>Hi.95.CF1.N.Y.0.1</v>
+        <v>Hi.95.CF1.N.Pln.0.1</v>
       </c>
       <c r="C64">
         <f t="shared" si="3"/>
@@ -9378,10 +9511,20 @@
         <v>N</v>
       </c>
       <c r="H64" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I64" s="23">
         <v>0.1</v>
+      </c>
+      <c r="W64" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="X64" s="26"/>
+      <c r="Y64" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z64" s="25" t="s">
+        <v>164</v>
       </c>
       <c r="AN64" s="10">
         <f t="shared" si="9"/>
@@ -9394,7 +9537,7 @@
       </c>
       <c r="B65" t="str">
         <f t="shared" si="30"/>
-        <v>Lo.0.CF6.Y.Y.0.1</v>
+        <v>Lo.0.CF6.Y.Pln.0.1</v>
       </c>
       <c r="C65">
         <f t="shared" si="3"/>
@@ -9417,7 +9560,7 @@
         <v>Y</v>
       </c>
       <c r="H65" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I65" s="23">
         <v>0.1</v>
@@ -9433,7 +9576,7 @@
       </c>
       <c r="B66" t="str">
         <f t="shared" si="30"/>
-        <v>Hi.0.CF6.Y.Y.0.1</v>
+        <v>Hi.0.CF6.Y.Pln.0.1</v>
       </c>
       <c r="C66">
         <f t="shared" si="3"/>
@@ -9456,7 +9599,7 @@
         <v>Y</v>
       </c>
       <c r="H66" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I66" s="23">
         <v>0.1</v>
@@ -9472,7 +9615,7 @@
       </c>
       <c r="B67" t="str">
         <f t="shared" si="30"/>
-        <v>Lo.95.CF6.Y.Y.0.1</v>
+        <v>Lo.95.CF6.Y.Pln.0.1</v>
       </c>
       <c r="C67">
         <f t="shared" si="3"/>
@@ -9495,7 +9638,7 @@
         <v>Y</v>
       </c>
       <c r="H67" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I67" s="23">
         <v>0.1</v>
@@ -9511,7 +9654,7 @@
       </c>
       <c r="B68" t="str">
         <f t="shared" si="30"/>
-        <v>Hi.95.CF6.Y.Y.0.1</v>
+        <v>Hi.95.CF6.Y.Pln.0.1</v>
       </c>
       <c r="C68">
         <f t="shared" si="3"/>
@@ -9534,7 +9677,7 @@
         <v>Y</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I68" s="23">
         <v>0.1</v>
@@ -9550,7 +9693,7 @@
       </c>
       <c r="B69" t="str">
         <f t="shared" si="30"/>
-        <v>Lo.0.CF6.N.Y.0.1</v>
+        <v>Lo.0.CF6.N.Pln.0.1</v>
       </c>
       <c r="C69">
         <f t="shared" si="3"/>
@@ -9573,7 +9716,7 @@
         <v>N</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I69" s="23">
         <v>0.1</v>
@@ -9589,7 +9732,7 @@
       </c>
       <c r="B70" t="str">
         <f t="shared" si="30"/>
-        <v>Hi.0.CF6.N.Y.0.1</v>
+        <v>Hi.0.CF6.N.Pln.0.1</v>
       </c>
       <c r="C70">
         <f t="shared" si="3"/>
@@ -9612,7 +9755,7 @@
         <v>N</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I70" s="23">
         <v>0.1</v>
@@ -9628,7 +9771,7 @@
       </c>
       <c r="B71" t="str">
         <f t="shared" si="30"/>
-        <v>Lo.95.CF6.N.Y.0.1</v>
+        <v>Lo.95.CF6.N.Pln.0.1</v>
       </c>
       <c r="C71">
         <f t="shared" si="3"/>
@@ -9651,7 +9794,7 @@
         <v>N</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I71" s="23">
         <v>0.1</v>
@@ -9667,7 +9810,7 @@
       </c>
       <c r="B72" t="str">
         <f t="shared" si="30"/>
-        <v>Hi.95.CF6.N.Y.0.1</v>
+        <v>Hi.95.CF6.N.Pln.0.1</v>
       </c>
       <c r="C72">
         <f t="shared" si="3"/>
@@ -9690,7 +9833,7 @@
         <v>N</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="I72" s="23">
         <v>0.1</v>
@@ -9701,39 +9844,2267 @@
       </c>
     </row>
     <row r="73" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>5</v>
+      </c>
+      <c r="B73" t="str">
+        <f t="shared" ref="B73:B136" si="31">_xlfn.TEXTJOIN(".",TRUE,D73:I73)</f>
+        <v>Lo.0.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C73">
+        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F73" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G73" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I73" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN73" s="10">
         <f t="shared" si="9"/>
         <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>5</v>
+      </c>
+      <c r="B74" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C74">
+        <f t="shared" si="3"/>
+        <v>66</v>
+      </c>
+      <c r="D74" t="str">
+        <f t="shared" si="4"/>
+        <v>Hi</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F74" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G74" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H74" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I74" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN74" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <v>5</v>
+      </c>
+      <c r="B75" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C75">
+        <f t="shared" ref="C75:C138" si="32">C74+1</f>
+        <v>67</v>
+      </c>
+      <c r="D75" t="str">
+        <f t="shared" si="4"/>
+        <v>Lo</v>
+      </c>
+      <c r="E75">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F75" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G75" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H75" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I75" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN75" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <v>5</v>
+      </c>
+      <c r="B76" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C76">
+        <f t="shared" si="32"/>
+        <v>68</v>
+      </c>
+      <c r="D76" t="str">
+        <f t="shared" ref="D76:D139" si="33">D74</f>
+        <v>Hi</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F76" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G76" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I76" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN76" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A77">
+        <v>5</v>
+      </c>
+      <c r="B77" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C77">
+        <f t="shared" si="32"/>
+        <v>69</v>
+      </c>
+      <c r="D77" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F77" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G77" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I77" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN77" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A78">
+        <v>5</v>
+      </c>
+      <c r="B78" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C78">
+        <f t="shared" si="32"/>
+        <v>70</v>
+      </c>
+      <c r="D78" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F78" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G78" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H78" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I78" s="23">
+        <v>0.1</v>
+      </c>
       <c r="AN78" s="10">
         <f t="shared" si="9"/>
         <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A79">
+        <v>5</v>
+      </c>
+      <c r="B79" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C79">
+        <f t="shared" si="32"/>
+        <v>71</v>
+      </c>
+      <c r="D79" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F79" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G79" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H79" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I79" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="A80">
+        <v>5</v>
+      </c>
+      <c r="B80" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C80">
+        <f t="shared" si="32"/>
+        <v>72</v>
+      </c>
+      <c r="D80" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F80" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G80" t="str">
+        <f t="shared" si="14"/>
+        <v>N</v>
+      </c>
+      <c r="H80" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I80" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <v>5</v>
+      </c>
+      <c r="B81" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C81">
+        <f t="shared" si="32"/>
+        <v>73</v>
+      </c>
+      <c r="D81" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F81" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G81" t="str">
+        <f t="shared" si="14"/>
+        <v>Y</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I81" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <v>5</v>
+      </c>
+      <c r="B82" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C82">
+        <f t="shared" si="32"/>
+        <v>74</v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="F82" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G82" t="str">
+        <f t="shared" ref="G82:G145" si="34">G74</f>
+        <v>Y</v>
+      </c>
+      <c r="H82" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I82" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <v>5</v>
+      </c>
+      <c r="B83" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C83">
+        <f t="shared" si="32"/>
+        <v>75</v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="17"/>
+        <v>95</v>
+      </c>
+      <c r="F83" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G83" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H83" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I83" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <v>5</v>
+      </c>
+      <c r="B84" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C84">
+        <f t="shared" si="32"/>
+        <v>76</v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E84">
+        <f t="shared" ref="E84:E147" si="35">E80</f>
+        <v>95</v>
+      </c>
+      <c r="F84" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G84" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H84" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I84" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>5</v>
+      </c>
+      <c r="B85" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C85">
+        <f t="shared" si="32"/>
+        <v>77</v>
+      </c>
+      <c r="D85" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F85" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G85" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H85" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I85" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>5</v>
+      </c>
+      <c r="B86" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C86">
+        <f t="shared" si="32"/>
+        <v>78</v>
+      </c>
+      <c r="D86" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F86" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G86" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H86" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I86" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <v>5</v>
+      </c>
+      <c r="B87" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C87">
+        <f t="shared" si="32"/>
+        <v>79</v>
+      </c>
+      <c r="D87" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F87" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G87" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H87" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I87" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <v>5</v>
+      </c>
+      <c r="B88" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C88">
+        <f t="shared" si="32"/>
+        <v>80</v>
+      </c>
+      <c r="D88" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F88" t="str">
+        <f t="shared" si="21"/>
+        <v>CF6</v>
+      </c>
+      <c r="G88" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H88" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I88" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <v>5</v>
+      </c>
+      <c r="B89" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C89">
+        <f t="shared" si="32"/>
+        <v>81</v>
+      </c>
+      <c r="D89" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F89" t="str">
+        <f t="shared" si="21"/>
+        <v>CF1</v>
+      </c>
+      <c r="G89" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H89" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I89" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A90">
+        <v>5</v>
+      </c>
+      <c r="B90" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C90">
+        <f t="shared" si="32"/>
+        <v>82</v>
+      </c>
+      <c r="D90" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F90" t="str">
+        <f t="shared" ref="F90:F153" si="36">F74</f>
+        <v>CF1</v>
+      </c>
+      <c r="G90" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H90" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I90" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A91">
+        <v>5</v>
+      </c>
+      <c r="B91" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C91">
+        <f t="shared" si="32"/>
+        <v>83</v>
+      </c>
+      <c r="D91" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F91" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G91" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H91" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I91" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <v>5</v>
+      </c>
+      <c r="B92" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C92">
+        <f t="shared" si="32"/>
+        <v>84</v>
+      </c>
+      <c r="D92" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F92" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G92" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H92" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I92" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <v>5</v>
+      </c>
+      <c r="B93" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C93">
+        <f t="shared" si="32"/>
+        <v>85</v>
+      </c>
+      <c r="D93" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F93" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G93" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H93" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I93" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <v>5</v>
+      </c>
+      <c r="B94" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C94">
+        <f t="shared" si="32"/>
+        <v>86</v>
+      </c>
+      <c r="D94" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F94" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G94" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H94" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I94" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <v>5</v>
+      </c>
+      <c r="B95" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C95">
+        <f t="shared" si="32"/>
+        <v>87</v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F95" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G95" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H95" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I95" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <v>5</v>
+      </c>
+      <c r="B96" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C96">
+        <f t="shared" si="32"/>
+        <v>88</v>
+      </c>
+      <c r="D96" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F96" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G96" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H96" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I96" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A97">
+        <v>5</v>
+      </c>
+      <c r="B97" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C97">
+        <f t="shared" si="32"/>
+        <v>89</v>
+      </c>
+      <c r="D97" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F97" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G97" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H97" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I97" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A98">
+        <v>5</v>
+      </c>
+      <c r="B98" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C98">
+        <f t="shared" si="32"/>
+        <v>90</v>
+      </c>
+      <c r="D98" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F98" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G98" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H98" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I98" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <v>5</v>
+      </c>
+      <c r="B99" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C99">
+        <f t="shared" si="32"/>
+        <v>91</v>
+      </c>
+      <c r="D99" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F99" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G99" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H99" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I99" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <v>5</v>
+      </c>
+      <c r="B100" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C100">
+        <f t="shared" si="32"/>
+        <v>92</v>
+      </c>
+      <c r="D100" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F100" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G100" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H100" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I100" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <v>5</v>
+      </c>
+      <c r="B101" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C101">
+        <f t="shared" si="32"/>
+        <v>93</v>
+      </c>
+      <c r="D101" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E101">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F101" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G101" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H101" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I101" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A102">
+        <v>5</v>
+      </c>
+      <c r="B102" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="32"/>
+        <v>94</v>
+      </c>
+      <c r="D102" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E102">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F102" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G102" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H102" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I102" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A103">
+        <v>5</v>
+      </c>
+      <c r="B103" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C103">
+        <f t="shared" si="32"/>
+        <v>95</v>
+      </c>
+      <c r="D103" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E103">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F103" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G103" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H103" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I103" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A104">
+        <v>5</v>
+      </c>
+      <c r="B104" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C104">
+        <f t="shared" si="32"/>
+        <v>96</v>
+      </c>
+      <c r="D104" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F104" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G104" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H104" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I104" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A105">
+        <v>5</v>
+      </c>
+      <c r="B105" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C105">
+        <f t="shared" si="32"/>
+        <v>97</v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F105" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G105" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H105" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I105" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A106">
+        <v>5</v>
+      </c>
+      <c r="B106" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C106">
+        <f t="shared" si="32"/>
+        <v>98</v>
+      </c>
+      <c r="D106" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F106" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G106" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H106" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I106" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A107">
+        <v>5</v>
+      </c>
+      <c r="B107" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C107">
+        <f t="shared" si="32"/>
+        <v>99</v>
+      </c>
+      <c r="D107" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E107">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F107" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G107" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H107" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I107" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A108">
+        <v>5</v>
+      </c>
+      <c r="B108" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C108">
+        <f t="shared" si="32"/>
+        <v>100</v>
+      </c>
+      <c r="D108" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E108">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F108" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G108" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H108" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I108" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A109">
+        <v>5</v>
+      </c>
+      <c r="B109" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C109">
+        <f t="shared" si="32"/>
+        <v>101</v>
+      </c>
+      <c r="D109" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E109">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F109" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G109" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H109" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I109" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A110">
+        <v>5</v>
+      </c>
+      <c r="B110" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C110">
+        <f t="shared" si="32"/>
+        <v>102</v>
+      </c>
+      <c r="D110" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E110">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F110" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G110" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H110" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I110" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A111">
+        <v>5</v>
+      </c>
+      <c r="B111" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C111">
+        <f t="shared" si="32"/>
+        <v>103</v>
+      </c>
+      <c r="D111" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E111">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F111" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G111" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H111" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I111" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A112">
+        <v>5</v>
+      </c>
+      <c r="B112" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C112">
+        <f t="shared" si="32"/>
+        <v>104</v>
+      </c>
+      <c r="D112" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E112">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F112" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G112" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H112" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I112" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A113">
+        <v>5</v>
+      </c>
+      <c r="B113" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C113">
+        <f t="shared" si="32"/>
+        <v>105</v>
+      </c>
+      <c r="D113" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E113">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F113" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G113" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H113" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I113" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A114">
+        <v>5</v>
+      </c>
+      <c r="B114" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C114">
+        <f t="shared" si="32"/>
+        <v>106</v>
+      </c>
+      <c r="D114" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E114">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F114" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G114" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H114" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I114" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A115">
+        <v>5</v>
+      </c>
+      <c r="B115" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C115">
+        <f t="shared" si="32"/>
+        <v>107</v>
+      </c>
+      <c r="D115" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E115">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F115" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G115" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H115" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I115" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A116">
+        <v>5</v>
+      </c>
+      <c r="B116" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C116">
+        <f t="shared" si="32"/>
+        <v>108</v>
+      </c>
+      <c r="D116" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E116">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F116" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G116" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H116" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I116" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <v>5</v>
+      </c>
+      <c r="B117" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C117">
+        <f t="shared" si="32"/>
+        <v>109</v>
+      </c>
+      <c r="D117" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E117">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F117" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G117" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H117" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I117" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A118">
+        <v>5</v>
+      </c>
+      <c r="B118" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C118">
+        <f t="shared" si="32"/>
+        <v>110</v>
+      </c>
+      <c r="D118" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E118">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F118" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G118" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H118" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I118" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A119">
+        <v>5</v>
+      </c>
+      <c r="B119" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C119">
+        <f t="shared" si="32"/>
+        <v>111</v>
+      </c>
+      <c r="D119" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E119">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F119" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G119" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H119" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I119" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A120">
+        <v>5</v>
+      </c>
+      <c r="B120" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C120">
+        <f t="shared" si="32"/>
+        <v>112</v>
+      </c>
+      <c r="D120" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E120">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F120" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G120" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H120" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I120" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A121">
+        <v>5</v>
+      </c>
+      <c r="B121" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C121">
+        <f t="shared" si="32"/>
+        <v>113</v>
+      </c>
+      <c r="D121" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E121">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F121" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G121" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H121" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I121" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A122">
+        <v>5</v>
+      </c>
+      <c r="B122" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C122">
+        <f t="shared" si="32"/>
+        <v>114</v>
+      </c>
+      <c r="D122" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E122">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F122" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G122" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H122" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I122" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A123">
+        <v>5</v>
+      </c>
+      <c r="B123" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C123">
+        <f t="shared" si="32"/>
+        <v>115</v>
+      </c>
+      <c r="D123" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E123">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F123" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G123" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H123" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I123" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A124">
+        <v>5</v>
+      </c>
+      <c r="B124" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF1.Y.Eco.0.1</v>
+      </c>
+      <c r="C124">
+        <f t="shared" si="32"/>
+        <v>116</v>
+      </c>
+      <c r="D124" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E124">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F124" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G124" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H124" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I124" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A125">
+        <v>5</v>
+      </c>
+      <c r="B125" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C125">
+        <f t="shared" si="32"/>
+        <v>117</v>
+      </c>
+      <c r="D125" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E125">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F125" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G125" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H125" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I125" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A126">
+        <v>5</v>
+      </c>
+      <c r="B126" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C126">
+        <f t="shared" si="32"/>
+        <v>118</v>
+      </c>
+      <c r="D126" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E126">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F126" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G126" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H126" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I126" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A127">
+        <v>5</v>
+      </c>
+      <c r="B127" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C127">
+        <f t="shared" si="32"/>
+        <v>119</v>
+      </c>
+      <c r="D127" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E127">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F127" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G127" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H127" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I127" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A128">
+        <v>5</v>
+      </c>
+      <c r="B128" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF1.N.Eco.0.1</v>
+      </c>
+      <c r="C128">
+        <f t="shared" si="32"/>
+        <v>120</v>
+      </c>
+      <c r="D128" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E128">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F128" t="str">
+        <f t="shared" si="36"/>
+        <v>CF1</v>
+      </c>
+      <c r="G128" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H128" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I128" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A129">
+        <v>5</v>
+      </c>
+      <c r="B129" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C129">
+        <f t="shared" si="32"/>
+        <v>121</v>
+      </c>
+      <c r="D129" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E129">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F129" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G129" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H129" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I129" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A130">
+        <v>5</v>
+      </c>
+      <c r="B130" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C130">
+        <f t="shared" si="32"/>
+        <v>122</v>
+      </c>
+      <c r="D130" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E130">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F130" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G130" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H130" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I130" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A131">
+        <v>5</v>
+      </c>
+      <c r="B131" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C131">
+        <f t="shared" si="32"/>
+        <v>123</v>
+      </c>
+      <c r="D131" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E131">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F131" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G131" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H131" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I131" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A132">
+        <v>5</v>
+      </c>
+      <c r="B132" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF6.Y.Eco.0.1</v>
+      </c>
+      <c r="C132">
+        <f t="shared" si="32"/>
+        <v>124</v>
+      </c>
+      <c r="D132" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E132">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F132" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G132" t="str">
+        <f t="shared" si="34"/>
+        <v>Y</v>
+      </c>
+      <c r="H132" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I132" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A133">
+        <v>5</v>
+      </c>
+      <c r="B133" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.0.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C133">
+        <f t="shared" si="32"/>
+        <v>125</v>
+      </c>
+      <c r="D133" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E133">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F133" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G133" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H133" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I133" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A134">
+        <v>5</v>
+      </c>
+      <c r="B134" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.0.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C134">
+        <f t="shared" si="32"/>
+        <v>126</v>
+      </c>
+      <c r="D134" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E134">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="F134" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G134" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H134" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I134" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A135">
+        <v>5</v>
+      </c>
+      <c r="B135" t="str">
+        <f t="shared" si="31"/>
+        <v>Lo.95.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C135">
+        <f t="shared" si="32"/>
+        <v>127</v>
+      </c>
+      <c r="D135" t="str">
+        <f t="shared" si="33"/>
+        <v>Lo</v>
+      </c>
+      <c r="E135">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F135" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G135" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H135" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I135" s="23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A136">
+        <v>5</v>
+      </c>
+      <c r="B136" t="str">
+        <f t="shared" si="31"/>
+        <v>Hi.95.CF6.N.Eco.0.1</v>
+      </c>
+      <c r="C136">
+        <f t="shared" si="32"/>
+        <v>128</v>
+      </c>
+      <c r="D136" t="str">
+        <f t="shared" si="33"/>
+        <v>Hi</v>
+      </c>
+      <c r="E136">
+        <f t="shared" si="35"/>
+        <v>95</v>
+      </c>
+      <c r="F136" t="str">
+        <f t="shared" si="36"/>
+        <v>CF6</v>
+      </c>
+      <c r="G136" t="str">
+        <f t="shared" si="34"/>
+        <v>N</v>
+      </c>
+      <c r="H136" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="I136" s="23">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF40DA37-5777-4189-9114-1F5B94DA040C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5167D59-B8FF-49F1-9219-A4A330DC069B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -804,7 +804,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -842,8 +842,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -6126,7 +6124,7 @@
       </c>
       <c r="I5" s="21">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -9158,11 +9156,11 @@
       </c>
       <c r="W57" s="5" t="str">
         <f>IF($I$5&lt;&gt;1,"~TFM_UPD","Transmission costs default")</f>
-        <v>~TFM_UPD</v>
+        <v>Transmission costs default</v>
       </c>
       <c r="AC57" s="5" t="str">
         <f>IF($I$5&lt;1,"~TFM_INS","No hurdle rate")</f>
-        <v>~TFM_INS</v>
+        <v>No hurdle rate</v>
       </c>
       <c r="AG57" s="5" t="str">
         <f>IF($I$5&gt;1,"~TFM_INS","No ELife")</f>
@@ -9282,7 +9280,7 @@
       <c r="X59" s="20"/>
       <c r="Y59" t="str">
         <f>"*"&amp;$I$5</f>
-        <v>*0.1</v>
+        <v>*1</v>
       </c>
       <c r="Z59" t="s">
         <v>155</v>
@@ -9516,14 +9514,14 @@
       <c r="I64" s="23">
         <v>0.1</v>
       </c>
-      <c r="W64" s="25" t="s">
+      <c r="W64" t="s">
         <v>161</v>
       </c>
-      <c r="X64" s="26"/>
-      <c r="Y64" s="26" t="s">
+      <c r="X64" s="20"/>
+      <c r="Y64" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="Z64" s="25" t="s">
+      <c r="Z64" t="s">
         <v>164</v>
       </c>
       <c r="AN64" s="10">
@@ -9849,7 +9847,7 @@
       </c>
       <c r="B73" t="str">
         <f t="shared" ref="B73:B136" si="31">_xlfn.TEXTJOIN(".",TRUE,D73:I73)</f>
-        <v>Lo.0.CF1.Y.Eco.0.1</v>
+        <v>Lo.0.CF1.Y.Eco.1</v>
       </c>
       <c r="C73">
         <f t="shared" si="3"/>
@@ -9875,7 +9873,8 @@
         <v>160</v>
       </c>
       <c r="I73" s="23">
-        <v>0.1</v>
+        <f>I9</f>
+        <v>1</v>
       </c>
       <c r="AN73" s="10">
         <f t="shared" si="9"/>
@@ -9888,7 +9887,7 @@
       </c>
       <c r="B74" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF1.Y.Eco.0.1</v>
+        <v>Hi.0.CF1.Y.Eco.1</v>
       </c>
       <c r="C74">
         <f t="shared" si="3"/>
@@ -9914,7 +9913,8 @@
         <v>160</v>
       </c>
       <c r="I74" s="23">
-        <v>0.1</v>
+        <f t="shared" ref="I74:I136" si="32">I10</f>
+        <v>1</v>
       </c>
       <c r="AN74" s="10">
         <f t="shared" si="9"/>
@@ -9927,10 +9927,10 @@
       </c>
       <c r="B75" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF1.Y.Eco.0.1</v>
+        <v>Lo.95.CF1.Y.Eco.1</v>
       </c>
       <c r="C75">
-        <f t="shared" ref="C75:C138" si="32">C74+1</f>
+        <f t="shared" ref="C75:C136" si="33">C74+1</f>
         <v>67</v>
       </c>
       <c r="D75" t="str">
@@ -9953,7 +9953,8 @@
         <v>160</v>
       </c>
       <c r="I75" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
       <c r="AN75" s="10">
         <f t="shared" si="9"/>
@@ -9966,14 +9967,14 @@
       </c>
       <c r="B76" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF1.Y.Eco.0.1</v>
+        <v>Hi.95.CF1.Y.Eco.1</v>
       </c>
       <c r="C76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>68</v>
       </c>
       <c r="D76" t="str">
-        <f t="shared" ref="D76:D139" si="33">D74</f>
+        <f t="shared" ref="D76:D136" si="34">D74</f>
         <v>Hi</v>
       </c>
       <c r="E76">
@@ -9992,7 +9993,8 @@
         <v>160</v>
       </c>
       <c r="I76" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
       <c r="AN76" s="10">
         <f t="shared" si="9"/>
@@ -10005,14 +10007,14 @@
       </c>
       <c r="B77" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF1.N.Eco.0.1</v>
+        <v>Lo.0.CF1.N.Eco.1</v>
       </c>
       <c r="C77">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>69</v>
       </c>
       <c r="D77" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E77">
@@ -10031,7 +10033,8 @@
         <v>160</v>
       </c>
       <c r="I77" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
       <c r="AN77" s="10">
         <f t="shared" si="9"/>
@@ -10044,14 +10047,14 @@
       </c>
       <c r="B78" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF1.N.Eco.0.1</v>
+        <v>Hi.0.CF1.N.Eco.1</v>
       </c>
       <c r="C78">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>70</v>
       </c>
       <c r="D78" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E78">
@@ -10070,7 +10073,8 @@
         <v>160</v>
       </c>
       <c r="I78" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
       <c r="AN78" s="10">
         <f t="shared" si="9"/>
@@ -10083,14 +10087,14 @@
       </c>
       <c r="B79" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF1.N.Eco.0.1</v>
+        <v>Lo.95.CF1.N.Eco.1</v>
       </c>
       <c r="C79">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>71</v>
       </c>
       <c r="D79" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E79">
@@ -10109,7 +10113,8 @@
         <v>160</v>
       </c>
       <c r="I79" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:40" x14ac:dyDescent="0.45">
@@ -10118,14 +10123,14 @@
       </c>
       <c r="B80" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF1.N.Eco.0.1</v>
+        <v>Hi.95.CF1.N.Eco.1</v>
       </c>
       <c r="C80">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>72</v>
       </c>
       <c r="D80" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E80">
@@ -10144,7 +10149,8 @@
         <v>160</v>
       </c>
       <c r="I80" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.45">
@@ -10153,14 +10159,14 @@
       </c>
       <c r="B81" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF6.Y.Eco.0.1</v>
+        <v>Lo.0.CF6.Y.Eco.1</v>
       </c>
       <c r="C81">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>73</v>
       </c>
       <c r="D81" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E81">
@@ -10179,7 +10185,8 @@
         <v>160</v>
       </c>
       <c r="I81" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.45">
@@ -10188,14 +10195,14 @@
       </c>
       <c r="B82" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF6.Y.Eco.0.1</v>
+        <v>Hi.0.CF6.Y.Eco.1</v>
       </c>
       <c r="C82">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>74</v>
       </c>
       <c r="D82" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E82">
@@ -10207,14 +10214,15 @@
         <v>CF6</v>
       </c>
       <c r="G82" t="str">
-        <f t="shared" ref="G82:G145" si="34">G74</f>
+        <f t="shared" ref="G82:G136" si="35">G74</f>
         <v>Y</v>
       </c>
       <c r="H82" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I82" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.45">
@@ -10223,14 +10231,14 @@
       </c>
       <c r="B83" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF6.Y.Eco.0.1</v>
+        <v>Lo.95.CF6.Y.Eco.1</v>
       </c>
       <c r="C83">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>75</v>
       </c>
       <c r="D83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E83">
@@ -10242,14 +10250,15 @@
         <v>CF6</v>
       </c>
       <c r="G83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>Y</v>
       </c>
       <c r="H83" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I83" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.45">
@@ -10258,18 +10267,18 @@
       </c>
       <c r="B84" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF6.Y.Eco.0.1</v>
+        <v>Hi.95.CF6.Y.Eco.1</v>
       </c>
       <c r="C84">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>76</v>
       </c>
       <c r="D84" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E84">
-        <f t="shared" ref="E84:E147" si="35">E80</f>
+        <f t="shared" ref="E84:E136" si="36">E80</f>
         <v>95</v>
       </c>
       <c r="F84" t="str">
@@ -10277,14 +10286,15 @@
         <v>CF6</v>
       </c>
       <c r="G84" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>Y</v>
       </c>
       <c r="H84" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I84" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.45">
@@ -10293,18 +10303,18 @@
       </c>
       <c r="B85" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF6.N.Eco.0.1</v>
+        <v>Lo.0.CF6.N.Eco.1</v>
       </c>
       <c r="C85">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>77</v>
       </c>
       <c r="D85" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E85">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="F85" t="str">
@@ -10312,14 +10322,15 @@
         <v>CF6</v>
       </c>
       <c r="G85" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>N</v>
       </c>
       <c r="H85" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I85" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.45">
@@ -10328,18 +10339,18 @@
       </c>
       <c r="B86" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF6.N.Eco.0.1</v>
+        <v>Hi.0.CF6.N.Eco.1</v>
       </c>
       <c r="C86">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>78</v>
       </c>
       <c r="D86" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E86">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="F86" t="str">
@@ -10347,14 +10358,15 @@
         <v>CF6</v>
       </c>
       <c r="G86" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>N</v>
       </c>
       <c r="H86" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I86" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.45">
@@ -10363,18 +10375,18 @@
       </c>
       <c r="B87" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF6.N.Eco.0.1</v>
+        <v>Lo.95.CF6.N.Eco.1</v>
       </c>
       <c r="C87">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>79</v>
       </c>
       <c r="D87" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E87">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>95</v>
       </c>
       <c r="F87" t="str">
@@ -10382,14 +10394,15 @@
         <v>CF6</v>
       </c>
       <c r="G87" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>N</v>
       </c>
       <c r="H87" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I87" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.45">
@@ -10398,18 +10411,18 @@
       </c>
       <c r="B88" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF6.N.Eco.0.1</v>
+        <v>Hi.95.CF6.N.Eco.1</v>
       </c>
       <c r="C88">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>80</v>
       </c>
       <c r="D88" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E88">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>95</v>
       </c>
       <c r="F88" t="str">
@@ -10417,14 +10430,15 @@
         <v>CF6</v>
       </c>
       <c r="G88" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>N</v>
       </c>
       <c r="H88" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I88" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.45">
@@ -10433,18 +10447,18 @@
       </c>
       <c r="B89" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF1.Y.Eco.0.1</v>
+        <v>Lo.0.CF1.Y.Eco.0.25</v>
       </c>
       <c r="C89">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>81</v>
       </c>
       <c r="D89" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E89">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="F89" t="str">
@@ -10452,14 +10466,15 @@
         <v>CF1</v>
       </c>
       <c r="G89" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>Y</v>
       </c>
       <c r="H89" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I89" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.45">
@@ -10468,33 +10483,34 @@
       </c>
       <c r="B90" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF1.Y.Eco.0.1</v>
+        <v>Hi.0.CF1.Y.Eco.0.25</v>
       </c>
       <c r="C90">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>82</v>
       </c>
       <c r="D90" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E90">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F90" t="str">
+        <f t="shared" ref="F90:F136" si="37">F74</f>
+        <v>CF1</v>
+      </c>
+      <c r="G90" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F90" t="str">
-        <f t="shared" ref="F90:F153" si="36">F74</f>
-        <v>CF1</v>
-      </c>
-      <c r="G90" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H90" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I90" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.45">
@@ -10503,33 +10519,34 @@
       </c>
       <c r="B91" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF1.Y.Eco.0.1</v>
+        <v>Lo.95.CF1.Y.Eco.0.25</v>
       </c>
       <c r="C91">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>83</v>
       </c>
       <c r="D91" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E91">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F91" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G91" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F91" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G91" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H91" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I91" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.45">
@@ -10538,33 +10555,34 @@
       </c>
       <c r="B92" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF1.Y.Eco.0.1</v>
+        <v>Hi.95.CF1.Y.Eco.0.25</v>
       </c>
       <c r="C92">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>84</v>
       </c>
       <c r="D92" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E92">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F92" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G92" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F92" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G92" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H92" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I92" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.45">
@@ -10573,33 +10591,34 @@
       </c>
       <c r="B93" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF1.N.Eco.0.1</v>
+        <v>Lo.0.CF1.N.Eco.0.25</v>
       </c>
       <c r="C93">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>85</v>
       </c>
       <c r="D93" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E93">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F93" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G93" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F93" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G93" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H93" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I93" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.45">
@@ -10608,33 +10627,34 @@
       </c>
       <c r="B94" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF1.N.Eco.0.1</v>
+        <v>Hi.0.CF1.N.Eco.0.25</v>
       </c>
       <c r="C94">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>86</v>
       </c>
       <c r="D94" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E94">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F94" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G94" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F94" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G94" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H94" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I94" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.45">
@@ -10643,33 +10663,34 @@
       </c>
       <c r="B95" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF1.N.Eco.0.1</v>
+        <v>Lo.95.CF1.N.Eco.0.25</v>
       </c>
       <c r="C95">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>87</v>
       </c>
       <c r="D95" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E95">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F95" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G95" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F95" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G95" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H95" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I95" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.45">
@@ -10678,33 +10699,34 @@
       </c>
       <c r="B96" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF1.N.Eco.0.1</v>
+        <v>Hi.95.CF1.N.Eco.0.25</v>
       </c>
       <c r="C96">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>88</v>
       </c>
       <c r="D96" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E96">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F96" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G96" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F96" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G96" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H96" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I96" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.45">
@@ -10713,33 +10735,34 @@
       </c>
       <c r="B97" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF6.Y.Eco.0.1</v>
+        <v>Lo.0.CF6.Y.Eco.0.25</v>
       </c>
       <c r="C97">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>89</v>
       </c>
       <c r="D97" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E97">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F97" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G97" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F97" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G97" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H97" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I97" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.45">
@@ -10748,33 +10771,34 @@
       </c>
       <c r="B98" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF6.Y.Eco.0.1</v>
+        <v>Hi.0.CF6.Y.Eco.0.25</v>
       </c>
       <c r="C98">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>90</v>
       </c>
       <c r="D98" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E98">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F98" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G98" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F98" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G98" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H98" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I98" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.45">
@@ -10783,33 +10807,34 @@
       </c>
       <c r="B99" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF6.Y.Eco.0.1</v>
+        <v>Lo.95.CF6.Y.Eco.0.25</v>
       </c>
       <c r="C99">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>91</v>
       </c>
       <c r="D99" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E99">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F99" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G99" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F99" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G99" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H99" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I99" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.45">
@@ -10818,33 +10843,34 @@
       </c>
       <c r="B100" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF6.Y.Eco.0.1</v>
+        <v>Hi.95.CF6.Y.Eco.0.25</v>
       </c>
       <c r="C100">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>92</v>
       </c>
       <c r="D100" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E100">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F100" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G100" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F100" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G100" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H100" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I100" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.45">
@@ -10853,33 +10879,34 @@
       </c>
       <c r="B101" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF6.N.Eco.0.1</v>
+        <v>Lo.0.CF6.N.Eco.0.25</v>
       </c>
       <c r="C101">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>93</v>
       </c>
       <c r="D101" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E101">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F101" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G101" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F101" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G101" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H101" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I101" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.45">
@@ -10888,33 +10915,34 @@
       </c>
       <c r="B102" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF6.N.Eco.0.1</v>
+        <v>Hi.0.CF6.N.Eco.0.25</v>
       </c>
       <c r="C102">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>94</v>
       </c>
       <c r="D102" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E102">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F102" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G102" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F102" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G102" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H102" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I102" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.45">
@@ -10923,33 +10951,34 @@
       </c>
       <c r="B103" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF6.N.Eco.0.1</v>
+        <v>Lo.95.CF6.N.Eco.0.25</v>
       </c>
       <c r="C103">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>95</v>
       </c>
       <c r="D103" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E103">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F103" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G103" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F103" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G103" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H103" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I103" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.45">
@@ -10958,33 +10987,34 @@
       </c>
       <c r="B104" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF6.N.Eco.0.1</v>
+        <v>Hi.95.CF6.N.Eco.0.25</v>
       </c>
       <c r="C104">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>96</v>
       </c>
       <c r="D104" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E104">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F104" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G104" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F104" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G104" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H104" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I104" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>0.25</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.45">
@@ -10993,33 +11023,34 @@
       </c>
       <c r="B105" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF1.Y.Eco.0.1</v>
+        <v>Lo.0.CF1.Y.Eco.2</v>
       </c>
       <c r="C105">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>97</v>
       </c>
       <c r="D105" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E105">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F105" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G105" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F105" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G105" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H105" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I105" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.45">
@@ -11028,33 +11059,34 @@
       </c>
       <c r="B106" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF1.Y.Eco.0.1</v>
+        <v>Hi.0.CF1.Y.Eco.2</v>
       </c>
       <c r="C106">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>98</v>
       </c>
       <c r="D106" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E106">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F106" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G106" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F106" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G106" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H106" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I106" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.45">
@@ -11063,33 +11095,34 @@
       </c>
       <c r="B107" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF1.Y.Eco.0.1</v>
+        <v>Lo.95.CF1.Y.Eco.2</v>
       </c>
       <c r="C107">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>99</v>
       </c>
       <c r="D107" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E107">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F107" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G107" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F107" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G107" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H107" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I107" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.45">
@@ -11098,33 +11131,34 @@
       </c>
       <c r="B108" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF1.Y.Eco.0.1</v>
+        <v>Hi.95.CF1.Y.Eco.2</v>
       </c>
       <c r="C108">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>100</v>
       </c>
       <c r="D108" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E108">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F108" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G108" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F108" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G108" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H108" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I108" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.45">
@@ -11133,33 +11167,34 @@
       </c>
       <c r="B109" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF1.N.Eco.0.1</v>
+        <v>Lo.0.CF1.N.Eco.2</v>
       </c>
       <c r="C109">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>101</v>
       </c>
       <c r="D109" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E109">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F109" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G109" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F109" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G109" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H109" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I109" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.45">
@@ -11168,33 +11203,34 @@
       </c>
       <c r="B110" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF1.N.Eco.0.1</v>
+        <v>Hi.0.CF1.N.Eco.2</v>
       </c>
       <c r="C110">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>102</v>
       </c>
       <c r="D110" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E110">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F110" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G110" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F110" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G110" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H110" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I110" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.45">
@@ -11203,33 +11239,34 @@
       </c>
       <c r="B111" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF1.N.Eco.0.1</v>
+        <v>Lo.95.CF1.N.Eco.2</v>
       </c>
       <c r="C111">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>103</v>
       </c>
       <c r="D111" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E111">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F111" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G111" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F111" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G111" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H111" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I111" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.45">
@@ -11238,33 +11275,34 @@
       </c>
       <c r="B112" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF1.N.Eco.0.1</v>
+        <v>Hi.95.CF1.N.Eco.2</v>
       </c>
       <c r="C112">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>104</v>
       </c>
       <c r="D112" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E112">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F112" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G112" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F112" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G112" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H112" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I112" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.45">
@@ -11273,33 +11311,34 @@
       </c>
       <c r="B113" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF6.Y.Eco.0.1</v>
+        <v>Lo.0.CF6.Y.Eco.2</v>
       </c>
       <c r="C113">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>105</v>
       </c>
       <c r="D113" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E113">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F113" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G113" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F113" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G113" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H113" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I113" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.45">
@@ -11308,33 +11347,34 @@
       </c>
       <c r="B114" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF6.Y.Eco.0.1</v>
+        <v>Hi.0.CF6.Y.Eco.2</v>
       </c>
       <c r="C114">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>106</v>
       </c>
       <c r="D114" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E114">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F114" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G114" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F114" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G114" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H114" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I114" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.45">
@@ -11343,33 +11383,34 @@
       </c>
       <c r="B115" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF6.Y.Eco.0.1</v>
+        <v>Lo.95.CF6.Y.Eco.2</v>
       </c>
       <c r="C115">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>107</v>
       </c>
       <c r="D115" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E115">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F115" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G115" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F115" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G115" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H115" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I115" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.45">
@@ -11378,33 +11419,34 @@
       </c>
       <c r="B116" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF6.Y.Eco.0.1</v>
+        <v>Hi.95.CF6.Y.Eco.2</v>
       </c>
       <c r="C116">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>108</v>
       </c>
       <c r="D116" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E116">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F116" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G116" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F116" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G116" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H116" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I116" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.45">
@@ -11413,33 +11455,34 @@
       </c>
       <c r="B117" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.0.CF6.N.Eco.0.1</v>
+        <v>Lo.0.CF6.N.Eco.2</v>
       </c>
       <c r="C117">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>109</v>
       </c>
       <c r="D117" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E117">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F117" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G117" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F117" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G117" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H117" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I117" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.45">
@@ -11448,33 +11491,34 @@
       </c>
       <c r="B118" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.0.CF6.N.Eco.0.1</v>
+        <v>Hi.0.CF6.N.Eco.2</v>
       </c>
       <c r="C118">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>110</v>
       </c>
       <c r="D118" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E118">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F118" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G118" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F118" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G118" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H118" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I118" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.45">
@@ -11483,33 +11527,34 @@
       </c>
       <c r="B119" t="str">
         <f t="shared" si="31"/>
-        <v>Lo.95.CF6.N.Eco.0.1</v>
+        <v>Lo.95.CF6.N.Eco.2</v>
       </c>
       <c r="C119">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>111</v>
       </c>
       <c r="D119" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E119">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F119" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G119" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F119" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G119" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H119" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I119" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.45">
@@ -11518,33 +11563,34 @@
       </c>
       <c r="B120" t="str">
         <f t="shared" si="31"/>
-        <v>Hi.95.CF6.N.Eco.0.1</v>
+        <v>Hi.95.CF6.N.Eco.2</v>
       </c>
       <c r="C120">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>112</v>
       </c>
       <c r="D120" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E120">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F120" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G120" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F120" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G120" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H120" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I120" s="23">
-        <v>0.1</v>
+        <f t="shared" si="32"/>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.45">
@@ -11556,29 +11602,30 @@
         <v>Lo.0.CF1.Y.Eco.0.1</v>
       </c>
       <c r="C121">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>113</v>
       </c>
       <c r="D121" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E121">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F121" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G121" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F121" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G121" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H121" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I121" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11591,29 +11638,30 @@
         <v>Hi.0.CF1.Y.Eco.0.1</v>
       </c>
       <c r="C122">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>114</v>
       </c>
       <c r="D122" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E122">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F122" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G122" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F122" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G122" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H122" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I122" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11626,29 +11674,30 @@
         <v>Lo.95.CF1.Y.Eco.0.1</v>
       </c>
       <c r="C123">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>115</v>
       </c>
       <c r="D123" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E123">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F123" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G123" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F123" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G123" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H123" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I123" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11661,29 +11710,30 @@
         <v>Hi.95.CF1.Y.Eco.0.1</v>
       </c>
       <c r="C124">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>116</v>
       </c>
       <c r="D124" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E124">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F124" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G124" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F124" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G124" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H124" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I124" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11696,29 +11746,30 @@
         <v>Lo.0.CF1.N.Eco.0.1</v>
       </c>
       <c r="C125">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>117</v>
       </c>
       <c r="D125" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E125">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F125" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G125" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F125" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G125" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H125" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I125" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11731,29 +11782,30 @@
         <v>Hi.0.CF1.N.Eco.0.1</v>
       </c>
       <c r="C126">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>118</v>
       </c>
       <c r="D126" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E126">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F126" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G126" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F126" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G126" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H126" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I126" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11766,29 +11818,30 @@
         <v>Lo.95.CF1.N.Eco.0.1</v>
       </c>
       <c r="C127">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>119</v>
       </c>
       <c r="D127" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E127">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F127" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G127" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F127" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G127" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H127" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I127" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11801,29 +11854,30 @@
         <v>Hi.95.CF1.N.Eco.0.1</v>
       </c>
       <c r="C128">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>120</v>
       </c>
       <c r="D128" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E128">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F128" t="str">
+        <f t="shared" si="37"/>
+        <v>CF1</v>
+      </c>
+      <c r="G128" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F128" t="str">
-        <f t="shared" si="36"/>
-        <v>CF1</v>
-      </c>
-      <c r="G128" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H128" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I128" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11836,29 +11890,30 @@
         <v>Lo.0.CF6.Y.Eco.0.1</v>
       </c>
       <c r="C129">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>121</v>
       </c>
       <c r="D129" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E129">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F129" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G129" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F129" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G129" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H129" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I129" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11871,29 +11926,30 @@
         <v>Hi.0.CF6.Y.Eco.0.1</v>
       </c>
       <c r="C130">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>122</v>
       </c>
       <c r="D130" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E130">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F130" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G130" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F130" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G130" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H130" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I130" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11906,29 +11962,30 @@
         <v>Lo.95.CF6.Y.Eco.0.1</v>
       </c>
       <c r="C131">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>123</v>
       </c>
       <c r="D131" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E131">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F131" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G131" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F131" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G131" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H131" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I131" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11941,29 +11998,30 @@
         <v>Hi.95.CF6.Y.Eco.0.1</v>
       </c>
       <c r="C132">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>124</v>
       </c>
       <c r="D132" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E132">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F132" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G132" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F132" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G132" t="str">
-        <f t="shared" si="34"/>
         <v>Y</v>
       </c>
       <c r="H132" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I132" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -11976,29 +12034,30 @@
         <v>Lo.0.CF6.N.Eco.0.1</v>
       </c>
       <c r="C133">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>125</v>
       </c>
       <c r="D133" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E133">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F133" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G133" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F133" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G133" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H133" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I133" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -12011,29 +12070,30 @@
         <v>Hi.0.CF6.N.Eco.0.1</v>
       </c>
       <c r="C134">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>126</v>
       </c>
       <c r="D134" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E134">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="F134" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G134" t="str">
         <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="F134" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G134" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H134" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I134" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -12046,29 +12106,30 @@
         <v>Lo.95.CF6.N.Eco.0.1</v>
       </c>
       <c r="C135">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>127</v>
       </c>
       <c r="D135" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Lo</v>
       </c>
       <c r="E135">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F135" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G135" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F135" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G135" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H135" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I135" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>
@@ -12081,29 +12142,30 @@
         <v>Hi.95.CF6.N.Eco.0.1</v>
       </c>
       <c r="C136">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>128</v>
       </c>
       <c r="D136" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Hi</v>
       </c>
       <c r="E136">
+        <f t="shared" si="36"/>
+        <v>95</v>
+      </c>
+      <c r="F136" t="str">
+        <f t="shared" si="37"/>
+        <v>CF6</v>
+      </c>
+      <c r="G136" t="str">
         <f t="shared" si="35"/>
-        <v>95</v>
-      </c>
-      <c r="F136" t="str">
-        <f t="shared" si="36"/>
-        <v>CF6</v>
-      </c>
-      <c r="G136" t="str">
-        <f t="shared" si="34"/>
         <v>N</v>
       </c>
       <c r="H136" s="15" t="s">
         <v>160</v>
       </c>
       <c r="I136" s="23">
+        <f t="shared" si="32"/>
         <v>0.1</v>
       </c>
     </row>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5167D59-B8FF-49F1-9219-A4A330DC069B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFAAB13-8DB7-47AC-BC0E-E5E65BB8D390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="ar6_r10" sheetId="3" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$C$8:$H$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Veda!$A$8:$I$136</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5904,7 +5904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR136"/>
+  <dimension ref="A1:BV136"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6.46484375" bestFit="1" customWidth="1"/>
@@ -5934,108 +5934,204 @@
     <col min="42" max="42" width="12.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:74" x14ac:dyDescent="0.45">
       <c r="K1" s="16">
+        <v>1</v>
+      </c>
+      <c r="L1">
+        <v>2</v>
+      </c>
+      <c r="M1">
+        <v>3</v>
+      </c>
+      <c r="N1">
+        <v>4</v>
+      </c>
+      <c r="O1">
+        <v>9</v>
+      </c>
+      <c r="P1">
+        <v>10</v>
+      </c>
+      <c r="Q1">
+        <v>11</v>
+      </c>
+      <c r="R1">
+        <v>12</v>
+      </c>
+      <c r="S1">
+        <v>17</v>
+      </c>
+      <c r="T1">
+        <v>18</v>
+      </c>
+      <c r="U1">
+        <v>19</v>
+      </c>
+      <c r="V1">
+        <v>20</v>
+      </c>
+      <c r="W1">
+        <v>25</v>
+      </c>
+      <c r="X1">
+        <v>26</v>
+      </c>
+      <c r="Y1">
+        <v>27</v>
+      </c>
+      <c r="Z1">
+        <v>28</v>
+      </c>
+      <c r="AA1">
+        <v>33</v>
+      </c>
+      <c r="AB1">
+        <v>34</v>
+      </c>
+      <c r="AC1">
+        <v>35</v>
+      </c>
+      <c r="AD1">
+        <v>36</v>
+      </c>
+      <c r="AE1">
+        <v>41</v>
+      </c>
+      <c r="AF1">
+        <v>42</v>
+      </c>
+      <c r="AG1">
+        <v>43</v>
+      </c>
+      <c r="AH1">
+        <v>44</v>
+      </c>
+      <c r="AI1">
+        <v>49</v>
+      </c>
+      <c r="AJ1">
+        <v>50</v>
+      </c>
+      <c r="AK1">
+        <v>51</v>
+      </c>
+      <c r="AL1">
+        <v>52</v>
+      </c>
+      <c r="AM1">
+        <v>57</v>
+      </c>
+      <c r="AN1">
+        <v>58</v>
+      </c>
+      <c r="AO1">
+        <v>59</v>
+      </c>
+      <c r="AP1">
+        <v>60</v>
+      </c>
+      <c r="AQ1">
         <v>65</v>
       </c>
-      <c r="L1">
+      <c r="AR1">
         <v>66</v>
       </c>
-      <c r="M1">
+      <c r="AS1">
         <v>67</v>
       </c>
-      <c r="N1">
+      <c r="AT1">
         <v>68</v>
       </c>
-      <c r="O1">
+      <c r="AU1">
         <v>73</v>
       </c>
-      <c r="P1">
+      <c r="AV1">
         <v>74</v>
       </c>
-      <c r="Q1">
+      <c r="AW1">
         <v>75</v>
       </c>
-      <c r="R1">
+      <c r="AX1">
         <v>76</v>
       </c>
-      <c r="S1">
+      <c r="AY1">
         <v>81</v>
       </c>
-      <c r="T1">
+      <c r="AZ1">
         <v>82</v>
       </c>
-      <c r="U1">
+      <c r="BA1">
         <v>83</v>
       </c>
-      <c r="V1">
+      <c r="BB1">
         <v>84</v>
       </c>
-      <c r="W1">
+      <c r="BC1">
         <v>89</v>
       </c>
-      <c r="X1">
+      <c r="BD1">
         <v>90</v>
       </c>
-      <c r="Y1">
+      <c r="BE1">
         <v>91</v>
       </c>
-      <c r="Z1">
+      <c r="BF1">
         <v>92</v>
       </c>
-      <c r="AA1">
-        <v>97</v>
-      </c>
-      <c r="AB1">
+      <c r="BG1">
+        <v>97</v>
+      </c>
+      <c r="BH1">
         <v>98</v>
       </c>
-      <c r="AC1">
+      <c r="BI1">
         <v>99</v>
       </c>
-      <c r="AD1">
+      <c r="BJ1">
         <v>100</v>
       </c>
-      <c r="AE1">
+      <c r="BK1">
         <v>105</v>
       </c>
-      <c r="AF1">
+      <c r="BL1">
         <v>106</v>
       </c>
-      <c r="AG1">
+      <c r="BM1">
         <v>107</v>
       </c>
-      <c r="AH1">
+      <c r="BN1">
         <v>108</v>
       </c>
-      <c r="AI1">
+      <c r="BO1">
         <v>113</v>
       </c>
-      <c r="AJ1">
+      <c r="BP1">
         <v>114</v>
       </c>
-      <c r="AK1">
+      <c r="BQ1">
         <v>115</v>
       </c>
-      <c r="AL1">
+      <c r="BR1">
         <v>116</v>
       </c>
-      <c r="AM1">
+      <c r="BS1">
         <v>121</v>
       </c>
-      <c r="AN1">
+      <c r="BT1">
         <v>122</v>
       </c>
-      <c r="AO1">
+      <c r="BU1">
         <v>123</v>
       </c>
-      <c r="AP1">
+      <c r="BV1">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:74" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,K1:EI1)</f>
-        <v>~Inputcell: 65,66,67,68,73,74,75,76,81,82,83,84,89,90,91,92,97,98,99,100,105,106,107,108,113,114,115,116,121,122,123,124</v>
+        <v>~Inputcell: 1,2,3,4,9,10,11,12,17,18,19,20,25,26,27,28,33,34,35,36,41,42,43,44,49,50,51,52,57,58,59,60,65,66,67,68,73,74,75,76,81,82,83,84,89,90,91,92,97,98,99,100,105,106,107,108,113,114,115,116,121,122,123,124</v>
       </c>
       <c r="L2" t="s">
         <v>131</v>
@@ -6066,7 +6162,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:74" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
         <v>66</v>
       </c>
@@ -6101,7 +6197,7 @@
         <v>1.3777142857142857</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:74" x14ac:dyDescent="0.45">
       <c r="D5" s="21" t="str">
         <f t="shared" ref="D5:I5" si="1">VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
         <v>Hi</v>
@@ -6151,7 +6247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:74" x14ac:dyDescent="0.45">
       <c r="L6">
         <v>95</v>
       </c>
@@ -6177,12 +6273,12 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:74" x14ac:dyDescent="0.45">
       <c r="B7" s="14" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:74" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="4" t="s">
         <v>93</v>
       </c>
@@ -6215,7 +6311,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:74" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>5</v>
       </c>
@@ -6260,7 +6356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:74" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>5</v>
       </c>
@@ -6309,7 +6405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:74" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>5</v>
       </c>
@@ -6359,7 +6455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:74" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12">
         <v>5</v>
       </c>
@@ -6413,7 +6509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:74" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>5</v>
       </c>
@@ -6461,7 +6557,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:74" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>5</v>
       </c>
@@ -6526,7 +6622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:74" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>5</v>
       </c>
@@ -6594,7 +6690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:74" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>5</v>
       </c>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFAAB13-8DB7-47AC-BC0E-E5E65BB8D390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3019B4-E821-4529-93CB-55EFA89A2748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1012,22 +1012,22 @@
                   <c:v>229.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>275.11199999999997</c:v>
+                  <c:v>242.36057142857143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>290.01390000000004</c:v>
+                  <c:v>246.61825714285717</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>304.91579999999999</c:v>
+                  <c:v>250.87594285714286</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>373.69379999999995</c:v>
+                  <c:v>270.52679999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>458.52</c:v>
+                  <c:v>294.76285714285711</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>532.34172000000001</c:v>
+                  <c:v>315.85477714285713</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6164,7 +6164,7 @@
     </row>
     <row r="3" spans="1:74" x14ac:dyDescent="0.45">
       <c r="B3" s="9">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="L3" t="s">
         <v>133</v>
@@ -6200,7 +6200,7 @@
     <row r="5" spans="1:74" x14ac:dyDescent="0.45">
       <c r="D5" s="21" t="str">
         <f t="shared" ref="D5:I5" si="1">VLOOKUP($B$3,$C$9:$K$999,COLUMN()-2,FALSE)</f>
-        <v>Hi</v>
+        <v>Lo</v>
       </c>
       <c r="E5" s="21">
         <f t="shared" si="1"/>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="H5" s="21" t="str">
         <f t="shared" si="1"/>
-        <v>Eco</v>
+        <v>Pln</v>
       </c>
       <c r="I5" s="21">
         <f t="shared" si="1"/>
@@ -6595,27 +6595,27 @@
       </c>
       <c r="Y14" s="8">
         <f t="shared" ref="Y14:AD14" si="6">$W$12*N15</f>
-        <v>275.11199999999997</v>
+        <v>242.36057142857143</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="6"/>
-        <v>290.01390000000004</v>
+        <v>246.61825714285717</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="6"/>
-        <v>304.91579999999999</v>
+        <v>250.87594285714286</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="6"/>
-        <v>373.69379999999995</v>
+        <v>270.52679999999998</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="6"/>
-        <v>458.52</v>
+        <v>294.76285714285711</v>
       </c>
       <c r="AD14" s="8">
         <f t="shared" si="6"/>
-        <v>532.34172000000001</v>
+        <v>315.85477714285713</v>
       </c>
       <c r="AN14" s="10">
         <f>AN9+1</f>
@@ -6663,27 +6663,27 @@
       </c>
       <c r="N15" s="11">
         <f t="shared" si="8"/>
-        <v>1.2</v>
+        <v>1.0571428571428572</v>
       </c>
       <c r="O15" s="11">
         <f t="shared" si="8"/>
-        <v>1.2650000000000001</v>
+        <v>1.0757142857142858</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="8"/>
-        <v>1.33</v>
+        <v>1.0942857142857143</v>
       </c>
       <c r="Q15" s="11">
         <f t="shared" si="8"/>
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="R15" s="11">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>1.2857142857142856</v>
       </c>
       <c r="S15" s="11">
         <f t="shared" si="8"/>
-        <v>2.3220000000000001</v>
+        <v>1.3777142857142857</v>
       </c>
       <c r="AN15" s="10">
         <f t="shared" ref="AN15:AN78" si="9">AN10+1</f>
@@ -6862,31 +6862,31 @@
         <v>15</v>
       </c>
       <c r="M18" s="11">
-        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="N18" s="11">
-        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="O18" s="11">
-        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="P18" s="11">
-        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="Q18" s="11">
-        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0</v>
       </c>
       <c r="R18" s="11">
-        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
-        <v>0.01</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <v>0</v>
       </c>
       <c r="S18" s="11">
-        <f>SUMIFS(ar6_r10!$K$2:$K$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K18)</f>
         <v>0.01</v>
       </c>
       <c r="W18" s="10" t="s">
@@ -6914,11 +6914,11 @@
       </c>
       <c r="AC18" s="6">
         <f t="shared" si="15"/>
-        <v>4.5851999999999995</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="15"/>
-        <v>5.3234172000000006</v>
+        <v>3.1585477714285712</v>
       </c>
       <c r="AE18" t="s">
         <v>17</v>
@@ -6966,63 +6966,63 @@
         <v>18</v>
       </c>
       <c r="M19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
-        <v>0.4</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
+        <v>0.45</v>
       </c>
       <c r="N19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
+        <v>0.44</v>
+      </c>
+      <c r="O19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
+        <v>0.34</v>
+      </c>
+      <c r="P19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.35</v>
       </c>
-      <c r="O19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
+      <c r="Q19" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
         <v>0.33</v>
       </c>
-      <c r="P19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
-        <v>0.32</v>
-      </c>
-      <c r="Q19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
-        <v>0.31</v>
-      </c>
       <c r="R19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
-        <v>0.31</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
+        <v>0.38</v>
       </c>
       <c r="S19" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
-        <v>0.31</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K19)</f>
+        <v>0.36</v>
       </c>
       <c r="W19" s="10" t="s">
         <v>19</v>
       </c>
       <c r="X19" s="6">
         <f t="shared" si="15"/>
-        <v>91.704000000000008</v>
+        <v>103.167</v>
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="15"/>
-        <v>96.28919999999998</v>
+        <v>106.63865142857144</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="15"/>
-        <v>95.704587000000018</v>
+        <v>83.850207428571451</v>
       </c>
       <c r="AA19" s="6">
         <f t="shared" si="15"/>
-        <v>97.573055999999994</v>
+        <v>87.806579999999997</v>
       </c>
       <c r="AB19" s="6">
         <f t="shared" si="15"/>
-        <v>115.84507799999999</v>
+        <v>89.273843999999997</v>
       </c>
       <c r="AC19" s="6">
         <f t="shared" si="15"/>
-        <v>142.1412</v>
+        <v>112.0098857142857</v>
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="15"/>
-        <v>165.0259332</v>
+        <v>113.70771977142856</v>
       </c>
       <c r="AE19" t="s">
         <v>17</v>
@@ -7069,63 +7069,63 @@
         <v>21</v>
       </c>
       <c r="M20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
-        <v>0.47</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
+        <v>0.54</v>
       </c>
       <c r="N20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
-        <v>0.52</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
+        <v>0.54</v>
       </c>
       <c r="O20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="P20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
+        <v>0.61</v>
+      </c>
+      <c r="Q20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
+        <v>0.61</v>
+      </c>
+      <c r="R20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.54</v>
       </c>
-      <c r="P20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
+      <c r="S20" s="11">
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
         <v>0.53</v>
-      </c>
-      <c r="Q20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
-        <v>0.52</v>
-      </c>
-      <c r="R20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
-        <v>0.5</v>
-      </c>
-      <c r="S20" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K20)</f>
-        <v>0.48</v>
       </c>
       <c r="W20" s="10" t="s">
         <v>22</v>
       </c>
       <c r="X20" s="6">
         <f t="shared" si="15"/>
-        <v>107.75219999999999</v>
+        <v>123.8004</v>
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="15"/>
-        <v>143.05823999999998</v>
+        <v>130.87470857142858</v>
       </c>
       <c r="Z20" s="6">
         <f t="shared" si="15"/>
-        <v>156.60750600000003</v>
+        <v>140.57240657142859</v>
       </c>
       <c r="AA20" s="6">
         <f t="shared" si="15"/>
-        <v>161.60537400000001</v>
+        <v>153.03432514285714</v>
       </c>
       <c r="AB20" s="6">
         <f t="shared" si="15"/>
-        <v>194.320776</v>
+        <v>165.02134799999999</v>
       </c>
       <c r="AC20" s="6">
         <f t="shared" si="15"/>
-        <v>229.26</v>
+        <v>159.17194285714285</v>
       </c>
       <c r="AD20" s="6">
         <f t="shared" si="15"/>
-        <v>255.52402559999999</v>
+        <v>167.40303188571428</v>
       </c>
       <c r="AE20" t="s">
         <v>17</v>
@@ -7172,32 +7172,32 @@
         <v>23</v>
       </c>
       <c r="M21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!M$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
         <v>0.01</v>
       </c>
       <c r="N21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
-        <v>0.01</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!N$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
+        <v>0.02</v>
       </c>
       <c r="O21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
-        <v>0.01</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!O$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
+        <v>0.02</v>
       </c>
       <c r="P21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
-        <v>0.01</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!P$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
+        <v>0.03</v>
       </c>
       <c r="Q21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
-        <v>0.01</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!Q$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
+        <v>0.04</v>
       </c>
       <c r="R21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
-        <v>0.02</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!R$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
+        <v>0.06</v>
       </c>
       <c r="S21" s="11">
-        <f>SUMIFS(ar6_r10!$J$2:$J$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
-        <v>0.02</v>
+        <f>SUMIFS(ar6_r10!$F$2:$F$999,ar6_r10!$A$2:$A$999,$K$17,ar6_r10!$C$2:$C$999,Veda!S$17,ar6_r10!$M$2:$M$999,Veda!$K21)</f>
+        <v>0.06</v>
       </c>
       <c r="W21" s="10" t="s">
         <v>24</v>
@@ -7279,31 +7279,31 @@
       </c>
       <c r="X22" s="6">
         <f t="shared" ref="X22:AD22" si="19">X14-SUM(X19:X21)</f>
-        <v>27.511200000000002</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="19"/>
-        <v>33.471960000000024</v>
+        <v>2.5546114285714054</v>
       </c>
       <c r="Z22" s="6">
         <f t="shared" si="19"/>
-        <v>35.409206999999981</v>
+        <v>19.903043142857143</v>
       </c>
       <c r="AA22" s="6">
         <f t="shared" si="19"/>
-        <v>43.444770000000005</v>
+        <v>7.7424377142857281</v>
       </c>
       <c r="AB22" s="6">
         <f t="shared" si="19"/>
-        <v>61.235345999999993</v>
+        <v>13.939008000000001</v>
       </c>
       <c r="AC22" s="6">
         <f t="shared" si="19"/>
-        <v>84.826199999999972</v>
+        <v>21.28842857142854</v>
       </c>
       <c r="AD22" s="6">
         <f t="shared" si="19"/>
-        <v>109.4991612</v>
+        <v>32.45142548571431</v>
       </c>
       <c r="AE22" t="s">
         <v>17</v>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="W62" s="5" t="str">
         <f>IF($H$5&lt;&gt;"Pln","~TFM_UPD","Coal plants retire as per plan")</f>
-        <v>~TFM_UPD</v>
+        <v>Coal plants retire as per plan</v>
       </c>
       <c r="AN62" s="10">
         <f t="shared" si="9"/>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_Par-ETSAP_CT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3019B4-E821-4529-93CB-55EFA89A2748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5654E48B-04FB-4ADA-9994-4ACBE710CD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Veda" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="166">
   <si>
     <t>C1</t>
   </si>
@@ -597,6 +597,9 @@
   </si>
   <si>
     <t>ep_coal_sub*,-*rf</t>
+  </si>
+  <si>
+    <t>ACT_CSTUP</t>
   </si>
 </sst>
 </file>
@@ -12275,7 +12278,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20724745-3322-4C1F-9C31-A0A8C865A4ED}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="26.796875" customWidth="1"/>
@@ -12285,25 +12288,26 @@
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.9296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="str">
         <f>Veda!F5</f>
         <v>CF1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="23.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="23.25" x14ac:dyDescent="0.45">
       <c r="B2" s="18" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="B6" s="19" t="s">
         <v>102</v>
       </c>
@@ -12326,7 +12330,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
         <f>LEFT(B7,3)</f>
         <v>CF1</v>
@@ -12353,8 +12357,11 @@
       <c r="H7">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I7" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
         <f t="shared" ref="A8:A12" si="0">LEFT(B8,3)</f>
         <v>CF2</v>
@@ -12381,8 +12388,11 @@
       <c r="H8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I8" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>CF3</v>
@@ -12409,8 +12419,11 @@
       <c r="H9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I9" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>CF4</v>
@@ -12437,8 +12450,11 @@
       <c r="H10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I10" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>CF5</v>
@@ -12465,8 +12481,11 @@
       <c r="H11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I11" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>CF6</v>
@@ -12493,8 +12512,11 @@
       <c r="H12">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I12" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="G14" s="11">
         <f>SUMIF($A$7:$A$12,$A$1,G7:G12)</f>
         <v>1</v>
@@ -12503,13 +12525,17 @@
         <f>SUMIF($A$7:$A$12,$A$1,H7:H12)</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I14" s="11">
+        <f>SUMIF($A$7:$A$12,$A$1,I7:I12)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="G16" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="7:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="7:10" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="G17" s="13" t="s">
         <v>125</v>
       </c>
@@ -12517,10 +12543,13 @@
         <v>126</v>
       </c>
       <c r="I17" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="J17" s="13" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="7:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G18" t="str">
         <f>"*"&amp;G14</f>
         <v>*1</v>
@@ -12529,7 +12558,11 @@
         <f>"*"&amp;H14</f>
         <v>*0.5</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" t="str">
+        <f>"*"&amp;I14</f>
+        <v>*10</v>
+      </c>
+      <c r="J18" t="s">
         <v>123</v>
       </c>
     </row>
